--- a/IPL_Fantasy_Points.xlsx
+++ b/IPL_Fantasy_Points.xlsx
@@ -1335,19 +1335,19 @@
         </is>
       </c>
       <c r="G21" t="n">
-        <v>357</v>
+        <v>400</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>357</v>
+        <v>400</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>357</v>
+        <v>400</v>
       </c>
     </row>
     <row r="22">
@@ -2367,19 +2367,19 @@
         </is>
       </c>
       <c r="G45" t="n">
-        <v>48</v>
+        <v>110</v>
       </c>
       <c r="H45" t="n">
         <v>0</v>
       </c>
       <c r="I45" t="n">
-        <v>48</v>
+        <v>110</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
       </c>
       <c r="K45" t="n">
-        <v>48</v>
+        <v>110</v>
       </c>
     </row>
     <row r="46">
@@ -2441,15 +2441,15 @@
           <t>BOWL</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr"/>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>lokesh rahul</t>
-        </is>
-      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>lockie ferguson</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr">
         <is>
-          <t>no_stats_yet</t>
+          <t>exact/alias</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -2883,19 +2883,19 @@
         </is>
       </c>
       <c r="G57" t="n">
-        <v>232</v>
+        <v>248</v>
       </c>
       <c r="H57" t="n">
         <v>0</v>
       </c>
       <c r="I57" t="n">
-        <v>232</v>
+        <v>248</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
       </c>
       <c r="K57" t="n">
-        <v>232</v>
+        <v>248</v>
       </c>
     </row>
     <row r="58">
@@ -3614,19 +3614,19 @@
         </is>
       </c>
       <c r="G74" t="n">
-        <v>287</v>
+        <v>346</v>
       </c>
       <c r="H74" t="n">
         <v>0</v>
       </c>
       <c r="I74" t="n">
-        <v>287</v>
+        <v>346</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
       </c>
       <c r="K74" t="n">
-        <v>287</v>
+        <v>346</v>
       </c>
     </row>
     <row r="75">
@@ -3657,19 +3657,19 @@
         </is>
       </c>
       <c r="G75" t="n">
-        <v>254</v>
+        <v>283</v>
       </c>
       <c r="H75" t="n">
         <v>0</v>
       </c>
       <c r="I75" t="n">
-        <v>254</v>
+        <v>283</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
       </c>
       <c r="K75" t="n">
-        <v>254</v>
+        <v>283</v>
       </c>
     </row>
     <row r="76">
@@ -4001,19 +4001,19 @@
         </is>
       </c>
       <c r="G83" t="n">
-        <v>240</v>
+        <v>270</v>
       </c>
       <c r="H83" t="n">
         <v>0</v>
       </c>
       <c r="I83" t="n">
-        <v>240</v>
+        <v>270</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
       </c>
       <c r="K83" t="n">
-        <v>240</v>
+        <v>270</v>
       </c>
     </row>
     <row r="84">
@@ -4047,16 +4047,16 @@
         <v>0</v>
       </c>
       <c r="H84" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I84" t="n">
         <v>0</v>
       </c>
       <c r="J84" t="n">
-        <v>140</v>
+        <v>160</v>
       </c>
       <c r="K84" t="n">
-        <v>140</v>
+        <v>160</v>
       </c>
     </row>
     <row r="85">
@@ -4302,19 +4302,19 @@
         </is>
       </c>
       <c r="G90" t="n">
-        <v>255</v>
+        <v>306</v>
       </c>
       <c r="H90" t="n">
         <v>0</v>
       </c>
       <c r="I90" t="n">
-        <v>255</v>
+        <v>306</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
       </c>
       <c r="K90" t="n">
-        <v>255</v>
+        <v>306</v>
       </c>
     </row>
     <row r="91">
@@ -4388,19 +4388,19 @@
         </is>
       </c>
       <c r="G92" t="n">
-        <v>279</v>
+        <v>309</v>
       </c>
       <c r="H92" t="n">
         <v>0</v>
       </c>
       <c r="I92" t="n">
-        <v>279</v>
+        <v>309</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
       </c>
       <c r="K92" t="n">
-        <v>279</v>
+        <v>309</v>
       </c>
     </row>
     <row r="93">
@@ -4732,19 +4732,19 @@
         </is>
       </c>
       <c r="G100" t="n">
-        <v>88</v>
+        <v>117</v>
       </c>
       <c r="H100" t="n">
         <v>2</v>
       </c>
       <c r="I100" t="n">
-        <v>88</v>
+        <v>117</v>
       </c>
       <c r="J100" t="n">
         <v>40</v>
       </c>
       <c r="K100" t="n">
-        <v>128</v>
+        <v>157</v>
       </c>
     </row>
     <row r="101">
@@ -5036,16 +5036,16 @@
         <v>3</v>
       </c>
       <c r="H107" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I107" t="n">
         <v>0</v>
       </c>
       <c r="J107" t="n">
-        <v>160</v>
+        <v>180</v>
       </c>
       <c r="K107" t="n">
-        <v>160</v>
+        <v>180</v>
       </c>
     </row>
     <row r="108">
@@ -5420,19 +5420,19 @@
         </is>
       </c>
       <c r="G116" t="n">
-        <v>130</v>
+        <v>182</v>
       </c>
       <c r="H116" t="n">
         <v>1</v>
       </c>
       <c r="I116" t="n">
-        <v>130</v>
+        <v>182</v>
       </c>
       <c r="J116" t="n">
         <v>20</v>
       </c>
       <c r="K116" t="n">
-        <v>150</v>
+        <v>202</v>
       </c>
     </row>
     <row r="117">
@@ -6916,7 +6916,7 @@
       <c r="D151" t="inlineStr"/>
       <c r="E151" t="inlineStr">
         <is>
-          <t>suyash sharma</t>
+          <t>suryansh shedge</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
@@ -7057,16 +7057,16 @@
         <v>13</v>
       </c>
       <c r="H154" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I154" t="n">
         <v>13</v>
       </c>
       <c r="J154" t="n">
-        <v>260</v>
+        <v>280</v>
       </c>
       <c r="K154" t="n">
-        <v>273</v>
+        <v>293</v>
       </c>
     </row>
     <row r="155">
@@ -7143,16 +7143,16 @@
         <v>0</v>
       </c>
       <c r="H156" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I156" t="n">
         <v>0</v>
       </c>
       <c r="J156" t="n">
-        <v>80</v>
+        <v>140</v>
       </c>
       <c r="K156" t="n">
-        <v>80</v>
+        <v>140</v>
       </c>
     </row>
     <row r="157">
@@ -7902,15 +7902,15 @@
           <t>BOWL</t>
         </is>
       </c>
-      <c r="D174" t="inlineStr"/>
-      <c r="E174" t="inlineStr">
-        <is>
-          <t>jasprit bumrah</t>
-        </is>
-      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>harpreet brar</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr"/>
       <c r="F174" t="inlineStr">
         <is>
-          <t>no_stats_yet</t>
+          <t>exact/alias</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -8185,7 +8185,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2664</v>
+        <v>2802</v>
       </c>
     </row>
     <row r="3">
@@ -8198,7 +8198,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2312</v>
+        <v>2355</v>
       </c>
     </row>
     <row r="4">
@@ -8207,11 +8207,11 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>AMEY11</t>
+          <t>NAKUL11</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2017</v>
+        <v>2104</v>
       </c>
     </row>
     <row r="5">
@@ -8220,11 +8220,11 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>BABA11</t>
+          <t>AMEY11</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1985</v>
+        <v>2097</v>
       </c>
     </row>
     <row r="6">
@@ -8233,11 +8233,11 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>NAKUL11</t>
+          <t>SKY11</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1974</v>
+        <v>2005</v>
       </c>
     </row>
     <row r="7">
@@ -8246,11 +8246,11 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>SKY11</t>
+          <t>BABA11</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1953</v>
+        <v>2001</v>
       </c>
     </row>
     <row r="8">
@@ -8272,11 +8272,11 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>HARSH11</t>
+          <t>VATSAL11</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1748</v>
+        <v>1755</v>
       </c>
     </row>
     <row r="10">
@@ -8285,11 +8285,11 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>VATSAL11</t>
+          <t>HARSH11</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1693</v>
+        <v>1748</v>
       </c>
     </row>
     <row r="11">
@@ -8316,7 +8316,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C170"/>
+  <dimension ref="A1:C174"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8528,7 +8528,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
@@ -8707,7 +8707,7 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>240</v>
+        <v>270</v>
       </c>
       <c r="C30" t="n">
         <v>0</v>
@@ -8742,11 +8742,11 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>david miller</t>
+          <t>dasun shanaka</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>123</v>
+        <v>0</v>
       </c>
       <c r="C33" t="n">
         <v>0</v>
@@ -8755,50 +8755,50 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>david payne</t>
+          <t>david miller</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>6</v>
+        <v>123</v>
       </c>
       <c r="C34" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>deepak chahar</t>
+          <t>david payne</t>
         </is>
       </c>
       <c r="B35" t="n">
         <v>6</v>
       </c>
       <c r="C35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>devdutt padikkal</t>
+          <t>deepak chahar</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>242</v>
+        <v>6</v>
       </c>
       <c r="C36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>dewald brevis</t>
+          <t>devdutt padikkal</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>64</v>
+        <v>242</v>
       </c>
       <c r="C37" t="n">
         <v>0</v>
@@ -8807,11 +8807,11 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>dhruv chand jurel</t>
+          <t>dewald brevis</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>232</v>
+        <v>64</v>
       </c>
       <c r="C38" t="n">
         <v>0</v>
@@ -8820,37 +8820,37 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>digvesh rathi</t>
+          <t>dhruv chand jurel</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>2</v>
+        <v>248</v>
       </c>
       <c r="C39" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>dilshan madushanka</t>
+          <t>digvesh rathi</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C40" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>donavon ferreira</t>
+          <t>dilshan madushanka</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>130</v>
+        <v>0</v>
       </c>
       <c r="C41" t="n">
         <v>1</v>
@@ -8859,89 +8859,89 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>dushmantha chameera</t>
+          <t>donavon ferreira</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0</v>
+        <v>182</v>
       </c>
       <c r="C42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>eshan malinga</t>
+          <t>dushmantha chameera</t>
         </is>
       </c>
       <c r="B43" t="n">
         <v>0</v>
       </c>
       <c r="C43" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>finn allen</t>
+          <t>eshan malinga</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>81</v>
+        <v>0</v>
       </c>
       <c r="C44" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>george linde</t>
+          <t>finn allen</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>31</v>
+        <v>81</v>
       </c>
       <c r="C45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>glenn phillips</t>
+          <t>george linde</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>67</v>
+        <v>31</v>
       </c>
       <c r="C46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>gurjapneet singh</t>
+          <t>glenn phillips</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="C47" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>hardik pandya</t>
+          <t>gurjapneet singh</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>97</v>
+        <v>0</v>
       </c>
       <c r="C48" t="n">
         <v>3</v>
@@ -8950,24 +8950,24 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>harsh dubey</t>
+          <t>hardik pandya</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>13</v>
+        <v>97</v>
       </c>
       <c r="C49" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>harshal patel</t>
+          <t>harpreet brar</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C50" t="n">
         <v>0</v>
@@ -8976,24 +8976,24 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>heinrich klaasen</t>
+          <t>harsh dubey</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>349</v>
+        <v>13</v>
       </c>
       <c r="C51" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>himmat singh</t>
+          <t>harshal patel</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>35</v>
+        <v>4</v>
       </c>
       <c r="C52" t="n">
         <v>0</v>
@@ -9002,11 +9002,11 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>ishan kishan</t>
+          <t>heinrich klaasen</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>312</v>
+        <v>349</v>
       </c>
       <c r="C53" t="n">
         <v>0</v>
@@ -9015,11 +9015,11 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>jacob bethell</t>
+          <t>himmat singh</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C54" t="n">
         <v>0</v>
@@ -9028,102 +9028,102 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>jacob duffy</t>
+          <t>ishan kishan</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0</v>
+        <v>312</v>
       </c>
       <c r="C55" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>jamie overton</t>
+          <t>jacob bethell</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>136</v>
+        <v>34</v>
       </c>
       <c r="C56" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>jason holder</t>
+          <t>jacob duffy</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="C57" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>jasprit bumrah</t>
+          <t>jamie overton</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>7</v>
+        <v>136</v>
       </c>
       <c r="C58" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>jaydev unadkat</t>
+          <t>jason holder</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="C59" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>jitesh sharma</t>
+          <t>jasprit bumrah</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>62</v>
+        <v>7</v>
       </c>
       <c r="C60" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>jofra archer</t>
+          <t>jaydev unadkat</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="C61" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>jos buttler</t>
+          <t>jitesh sharma</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>270</v>
+        <v>62</v>
       </c>
       <c r="C62" t="n">
         <v>0</v>
@@ -9132,63 +9132,63 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>josh hazlewood</t>
+          <t>jofra archer</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="C63" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>kagiso rabada</t>
+          <t>jos buttler</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>35</v>
+        <v>270</v>
       </c>
       <c r="C64" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>kartik sharma</t>
+          <t>josh hazlewood</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="C65" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>kartik tyagi</t>
+          <t>kagiso rabada</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="C66" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>karun nair</t>
+          <t>kartik sharma</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>5</v>
+        <v>58</v>
       </c>
       <c r="C67" t="n">
         <v>0</v>
@@ -9197,24 +9197,24 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>khaleel ahmed</t>
+          <t>kartik tyagi</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="C68" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>krish bhagat</t>
+          <t>karun nair</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C69" t="n">
         <v>0</v>
@@ -9223,63 +9223,63 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>krunal pandya</t>
+          <t>khaleel ahmed</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="C70" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>kuldeep yadav</t>
+          <t>krish bhagat</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C71" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>kumar kushagra</t>
+          <t>krunal pandya</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="C72" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>kyle jamieson</t>
+          <t>kuldeep yadav</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C73" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>lhuan dre pretorius</t>
+          <t>kumar kushagra</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="C74" t="n">
         <v>0</v>
@@ -9288,24 +9288,24 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>liam livingstone</t>
+          <t>kyle jamieson</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>lokesh rahul</t>
+          <t>lhuan dre pretorius</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>358</v>
+        <v>0</v>
       </c>
       <c r="C76" t="n">
         <v>0</v>
@@ -9314,102 +9314,102 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>lungi ngidi</t>
+          <t>liam livingstone</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="C77" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>manav suthar</t>
+          <t>lockie ferguson</t>
         </is>
       </c>
       <c r="B78" t="n">
         <v>0</v>
       </c>
       <c r="C78" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>manimaran siddharth</t>
+          <t>lokesh rahul</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0</v>
+        <v>358</v>
       </c>
       <c r="C79" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>marco jansen</t>
+          <t>lungi ngidi</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C80" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>marcus stoinis</t>
+          <t>manav suthar</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="C81" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>matt henry</t>
+          <t>manimaran siddharth</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C82" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>matt short</t>
+          <t>marco jansen</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="C83" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>mayank markande</t>
+          <t>marcus stoinis</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="C84" t="n">
         <v>0</v>
@@ -9418,24 +9418,24 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>mayank rawat</t>
+          <t>matt henry</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C85" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>mayank yadav</t>
+          <t>matt short</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>5</v>
+        <v>36</v>
       </c>
       <c r="C86" t="n">
         <v>0</v>
@@ -9444,11 +9444,11 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>mitchell marsh</t>
+          <t>mayank markande</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>212</v>
+        <v>0</v>
       </c>
       <c r="C87" t="n">
         <v>0</v>
@@ -9457,128 +9457,128 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>mitchell santner</t>
+          <t>mayank rawat</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="C88" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>mohammed shami</t>
+          <t>mayank yadav</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>31</v>
+        <v>5</v>
       </c>
       <c r="C89" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>mohammed siraj</t>
+          <t>mitchell marsh</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0</v>
+        <v>212</v>
       </c>
       <c r="C90" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>mohsin khan</t>
+          <t>mitchell santner</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="C91" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>mukesh choudhary</t>
+          <t>mohammed shami</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="C92" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>mukesh kumar</t>
+          <t>mohammed siraj</t>
         </is>
       </c>
       <c r="B93" t="n">
         <v>0</v>
       </c>
       <c r="C93" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>mukul choudhary</t>
+          <t>mohsin khan</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>156</v>
+        <v>0</v>
       </c>
       <c r="C94" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>naman dhir</t>
+          <t>mukesh choudhary</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>154</v>
+        <v>0</v>
       </c>
       <c r="C95" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>nandre burger</t>
+          <t>mukesh kumar</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C96" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>navdeep saini</t>
+          <t>mukul choudhary</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>0</v>
+        <v>156</v>
       </c>
       <c r="C97" t="n">
         <v>0</v>
@@ -9587,11 +9587,11 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>nehal wadhera</t>
+          <t>naman dhir</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>65</v>
+        <v>154</v>
       </c>
       <c r="C98" t="n">
         <v>0</v>
@@ -9600,37 +9600,37 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>nicholas pooran</t>
+          <t>nandre burger</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>82</v>
+        <v>3</v>
       </c>
       <c r="C99" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>nitish kumar reddy</t>
+          <t>navdeep saini</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>172</v>
+        <v>0</v>
       </c>
       <c r="C100" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>nitish rana</t>
+          <t>nehal wadhera</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>169</v>
+        <v>65</v>
       </c>
       <c r="C101" t="n">
         <v>0</v>
@@ -9639,37 +9639,37 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>noor ahmad</t>
+          <t>nicholas pooran</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>10</v>
+        <v>82</v>
       </c>
       <c r="C102" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>pat cummins</t>
+          <t>nitish kumar reddy</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>0</v>
+        <v>172</v>
       </c>
       <c r="C103" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>pathum nissanka</t>
+          <t>nitish rana</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>147</v>
+        <v>169</v>
       </c>
       <c r="C104" t="n">
         <v>0</v>
@@ -9678,50 +9678,50 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>philip salt</t>
+          <t>noor ahmad</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>202</v>
+        <v>10</v>
       </c>
       <c r="C105" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>prabhsimran singh</t>
+          <t>pat cummins</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>287</v>
+        <v>0</v>
       </c>
       <c r="C106" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>praful hinge</t>
+          <t>pathum nissanka</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>0</v>
+        <v>147</v>
       </c>
       <c r="C107" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>prashant veer</t>
+          <t>philip salt</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>49</v>
+        <v>202</v>
       </c>
       <c r="C108" t="n">
         <v>0</v>
@@ -9730,37 +9730,37 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>prasidh krishna</t>
+          <t>prabhsimran singh</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>0</v>
+        <v>346</v>
       </c>
       <c r="C109" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>prince yadav</t>
+          <t>praful hinge</t>
         </is>
       </c>
       <c r="B110" t="n">
         <v>0</v>
       </c>
       <c r="C110" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>priyansh arya</t>
+          <t>prashant veer</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>254</v>
+        <v>49</v>
       </c>
       <c r="C111" t="n">
         <v>0</v>
@@ -9769,37 +9769,37 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>quinton de kock</t>
+          <t>prasidh krishna</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>132</v>
+        <v>0</v>
       </c>
       <c r="C112" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>rahul chahar</t>
+          <t>prince yadav</t>
         </is>
       </c>
       <c r="B113" t="n">
         <v>0</v>
       </c>
       <c r="C113" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>rahul tewatia</t>
+          <t>priyansh arya</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>49</v>
+        <v>283</v>
       </c>
       <c r="C114" t="n">
         <v>0</v>
@@ -9808,11 +9808,11 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>rajat patidar</t>
+          <t>quinton de kock</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>238</v>
+        <v>132</v>
       </c>
       <c r="C115" t="n">
         <v>0</v>
@@ -9821,115 +9821,115 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>ramandeep singh</t>
+          <t>rahul chahar</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="C116" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>rashid khan</t>
+          <t>rahul tewatia</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>28</v>
+        <v>49</v>
       </c>
       <c r="C117" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>rasikh salam</t>
+          <t>rajat patidar</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>0</v>
+        <v>238</v>
       </c>
       <c r="C118" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>ravi bishnoi</t>
+          <t>ramandeep singh</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="C119" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>ravindra jadeja</t>
+          <t>rashid khan</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>132</v>
+        <v>28</v>
       </c>
       <c r="C120" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>rinku singh</t>
+          <t>rasikh salam</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="C121" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>rishabh pant</t>
+          <t>ravi bishnoi</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>189</v>
+        <v>0</v>
       </c>
       <c r="C122" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>riyan parag</t>
+          <t>ravindra jadeja</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>88</v>
+        <v>132</v>
       </c>
       <c r="C123" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>rohit sharma</t>
+          <t>rinku singh</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>137</v>
+        <v>215</v>
       </c>
       <c r="C124" t="n">
         <v>0</v>
@@ -9938,37 +9938,37 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>romario shepherd</t>
+          <t>rishabh pant</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>39</v>
+        <v>189</v>
       </c>
       <c r="C125" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>rovman powell</t>
+          <t>riyan parag</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="C126" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>ruturaj gaikwad</t>
+          <t>rohit sharma</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>178</v>
+        <v>137</v>
       </c>
       <c r="C127" t="n">
         <v>0</v>
@@ -9977,24 +9977,24 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>ryan rickelton</t>
+          <t>romario shepherd</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>137</v>
+        <v>39</v>
       </c>
       <c r="C128" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>sahil parakh</t>
+          <t>rovman powell</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>0</v>
+        <v>121</v>
       </c>
       <c r="C129" t="n">
         <v>0</v>
@@ -10003,24 +10003,24 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>sakib hussain</t>
+          <t>ruturaj gaikwad</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>0</v>
+        <v>178</v>
       </c>
       <c r="C130" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>salil arora</t>
+          <t>ryan rickelton</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>63</v>
+        <v>137</v>
       </c>
       <c r="C131" t="n">
         <v>0</v>
@@ -10029,11 +10029,11 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>sameer rizvi</t>
+          <t>sahil parakh</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>209</v>
+        <v>0</v>
       </c>
       <c r="C132" t="n">
         <v>0</v>
@@ -10042,24 +10042,24 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>sandeep sharma</t>
+          <t>sakib hussain</t>
         </is>
       </c>
       <c r="B133" t="n">
         <v>0</v>
       </c>
       <c r="C133" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>sanju samson</t>
+          <t>salil arora</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>304</v>
+        <v>63</v>
       </c>
       <c r="C134" t="n">
         <v>0</v>
@@ -10068,11 +10068,11 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>sarfaraz khan</t>
+          <t>sameer rizvi</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>161</v>
+        <v>209</v>
       </c>
       <c r="C135" t="n">
         <v>0</v>
@@ -10081,24 +10081,24 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>shahbaz ahmed</t>
+          <t>sandeep sharma</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="C136" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>shahrukh khan</t>
+          <t>sanju samson</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>35</v>
+        <v>304</v>
       </c>
       <c r="C137" t="n">
         <v>0</v>
@@ -10107,37 +10107,37 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>shardul thakur</t>
+          <t>sarfaraz khan</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>14</v>
+        <v>161</v>
       </c>
       <c r="C138" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>shashank singh</t>
+          <t>shahbaz ahmed</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>70</v>
+        <v>15</v>
       </c>
       <c r="C139" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>sherfane rutherford</t>
+          <t>shahrukh khan</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>103</v>
+        <v>35</v>
       </c>
       <c r="C140" t="n">
         <v>0</v>
@@ -10146,50 +10146,50 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>shimron hetmyer</t>
+          <t>shardul thakur</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>72</v>
+        <v>14</v>
       </c>
       <c r="C141" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>shivam dube</t>
+          <t>shashank singh</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>150</v>
+        <v>70</v>
       </c>
       <c r="C142" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>shivang kumar</t>
+          <t>sherfane rutherford</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>21</v>
+        <v>103</v>
       </c>
       <c r="C143" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>shreyas iyer</t>
+          <t>shimron hetmyer</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>279</v>
+        <v>72</v>
       </c>
       <c r="C144" t="n">
         <v>0</v>
@@ -10198,50 +10198,50 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>shubham badriprasad dubey</t>
+          <t>shivam dube</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>19</v>
+        <v>150</v>
       </c>
       <c r="C145" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>shubman gill</t>
+          <t>shivang kumar</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>330</v>
+        <v>21</v>
       </c>
       <c r="C146" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>sunil narine</t>
+          <t>shreyas iyer</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>40</v>
+        <v>309</v>
       </c>
       <c r="C147" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>suryakumar yadav</t>
+          <t>shubham badriprasad dubey</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>157</v>
+        <v>50</v>
       </c>
       <c r="C148" t="n">
         <v>0</v>
@@ -10250,37 +10250,37 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>suyash sharma</t>
+          <t>shubman gill</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>0</v>
+        <v>330</v>
       </c>
       <c r="C149" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>t natarajan</t>
+          <t>sunil narine</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>1</v>
+        <v>40</v>
       </c>
       <c r="C150" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>tilak varma</t>
+          <t>suryakumar yadav</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>181</v>
+        <v>157</v>
       </c>
       <c r="C151" t="n">
         <v>0</v>
@@ -10289,11 +10289,11 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>tim david</t>
+          <t>suryansh shedge</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>183</v>
+        <v>3</v>
       </c>
       <c r="C152" t="n">
         <v>0</v>
@@ -10302,50 +10302,50 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>tim seifert</t>
+          <t>suyash sharma</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="C153" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>travis head</t>
+          <t>t natarajan</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>186</v>
+        <v>1</v>
       </c>
       <c r="C154" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>trent boult</t>
+          <t>tilak varma</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>1</v>
+        <v>181</v>
       </c>
       <c r="C155" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>tristan stubbs</t>
+          <t>tim david</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>201</v>
+        <v>183</v>
       </c>
       <c r="C156" t="n">
         <v>0</v>
@@ -10354,24 +10354,24 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>tushar deshpande</t>
+          <t>tim seifert</t>
         </is>
       </c>
       <c r="B157" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="C157" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>urvil patel</t>
+          <t>travis head</t>
         </is>
       </c>
       <c r="B158" t="n">
-        <v>4</v>
+        <v>186</v>
       </c>
       <c r="C158" t="n">
         <v>0</v>
@@ -10380,24 +10380,24 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>vaibhav arora</t>
+          <t>trent boult</t>
         </is>
       </c>
       <c r="B159" t="n">
         <v>1</v>
       </c>
       <c r="C159" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>vaibhav suryavanshi</t>
+          <t>tristan stubbs</t>
         </is>
       </c>
       <c r="B160" t="n">
-        <v>357</v>
+        <v>201</v>
       </c>
       <c r="C160" t="n">
         <v>0</v>
@@ -10406,24 +10406,24 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>varun chakravarthy</t>
+          <t>tushar deshpande</t>
         </is>
       </c>
       <c r="B161" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="C161" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>venkatesh iyer</t>
+          <t>urvil patel</t>
         </is>
       </c>
       <c r="B162" t="n">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="C162" t="n">
         <v>0</v>
@@ -10432,89 +10432,89 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>vijaykumar vyshak</t>
+          <t>vaibhav arora</t>
         </is>
       </c>
       <c r="B163" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C163" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>vipraj nigam</t>
+          <t>vaibhav suryavanshi</t>
         </is>
       </c>
       <c r="B164" t="n">
-        <v>12</v>
+        <v>400</v>
       </c>
       <c r="C164" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>virat kohli</t>
+          <t>varun chakravarthy</t>
         </is>
       </c>
       <c r="B165" t="n">
-        <v>351</v>
+        <v>0</v>
       </c>
       <c r="C165" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>washington sundar</t>
+          <t>venkatesh iyer</t>
         </is>
       </c>
       <c r="B166" t="n">
-        <v>157</v>
+        <v>29</v>
       </c>
       <c r="C166" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>xavier bartlett</t>
+          <t>vijaykumar vyshak</t>
         </is>
       </c>
       <c r="B167" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="C167" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>yash raj punja</t>
+          <t>vipraj nigam</t>
         </is>
       </c>
       <c r="B168" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="C168" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>yashasvi jaiswal</t>
+          <t>virat kohli</t>
         </is>
       </c>
       <c r="B169" t="n">
-        <v>255</v>
+        <v>351</v>
       </c>
       <c r="C169" t="n">
         <v>0</v>
@@ -10523,14 +10523,66 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
+          <t>washington sundar</t>
+        </is>
+      </c>
+      <c r="B170" t="n">
+        <v>157</v>
+      </c>
+      <c r="C170" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>xavier bartlett</t>
+        </is>
+      </c>
+      <c r="B171" t="n">
+        <v>11</v>
+      </c>
+      <c r="C171" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>yash raj punja</t>
+        </is>
+      </c>
+      <c r="B172" t="n">
+        <v>0</v>
+      </c>
+      <c r="C172" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>yashasvi jaiswal</t>
+        </is>
+      </c>
+      <c r="B173" t="n">
+        <v>306</v>
+      </c>
+      <c r="C173" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
           <t>yuzvendra chahal</t>
         </is>
       </c>
-      <c r="B170" t="n">
-        <v>0</v>
-      </c>
-      <c r="C170" t="n">
-        <v>4</v>
+      <c r="B174" t="n">
+        <v>0</v>
+      </c>
+      <c r="C174" t="n">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -10544,7 +10596,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K43"/>
+  <dimension ref="A1:K41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10951,7 +11003,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Lockie Ferguson</t>
+          <t>Adam Milne</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -10967,7 +11019,7 @@
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>lokesh rahul</t>
+          <t>david miller</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -10994,23 +11046,23 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Adam Milne</t>
+          <t>Jos Inglis</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>VATSAL11</t>
+          <t>BABA11</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>david miller</t>
+          <t>marcus stoinis</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -11037,7 +11089,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Jos Inglis</t>
+          <t>Prithvi Shaw</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -11053,7 +11105,7 @@
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>marcus stoinis</t>
+          <t>prasidh krishna</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -11080,7 +11132,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Prithvi Shaw</t>
+          <t>liam livingston</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -11090,13 +11142,13 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>prasidh krishna</t>
+          <t>liam livingstone</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -11123,7 +11175,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>liam livingston</t>
+          <t>rachin ravindra</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -11139,7 +11191,7 @@
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>liam livingstone</t>
+          <t>rashid khan</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -11166,7 +11218,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>rachin ravindra</t>
+          <t>Zeeshan Ansari</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -11176,13 +11228,13 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>rashid khan</t>
+          <t>eshan malinga</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -11209,7 +11261,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Zeeshan Ansari</t>
+          <t>Mitchell Starc</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -11225,7 +11277,7 @@
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>eshan malinga</t>
+          <t>mitchell santner</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -11252,17 +11304,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Mitchell Starc</t>
+          <t>Mitchel Owen</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>BABA11</t>
+          <t>DIPESH11</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -11295,7 +11347,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Mitchel Owen</t>
+          <t>Auqib Dar</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -11305,13 +11357,13 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>mitchell santner</t>
+          <t>auqib nabi</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -11338,23 +11390,23 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Auqib Dar</t>
+          <t>Arshin Kulkarni</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>DIPESH11</t>
+          <t>NAKUL11</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>auqib nabi</t>
+          <t>ashwani kumar</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -11381,7 +11433,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Arshin Kulkarni</t>
+          <t>Nishant Sindhu</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -11391,13 +11443,13 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>ashwani kumar</t>
+          <t>shashank singh</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -11424,7 +11476,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Nishant Sindhu</t>
+          <t>Jayant Yadav</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -11440,7 +11492,7 @@
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>shashank singh</t>
+          <t>mayank yadav</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -11467,7 +11519,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Jayant Yadav</t>
+          <t>Ajay Mandal</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -11483,7 +11535,7 @@
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>mayank yadav</t>
+          <t>rajat patidar</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -11510,7 +11562,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Ajay Mandal</t>
+          <t>Will Jacks</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -11526,7 +11578,7 @@
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>rajat patidar</t>
+          <t>mitchell marsh</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -11553,7 +11605,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Will Jacks</t>
+          <t>Matheesha Pathirana</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -11563,13 +11615,13 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>mitchell marsh</t>
+          <t>eshan malinga</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -11596,7 +11648,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Matheesha Pathirana</t>
+          <t>Ben Dwarshuis</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -11612,7 +11664,7 @@
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>eshan malinga</t>
+          <t>b sai sudharshan</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -11639,23 +11691,23 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Ben Dwarshuis</t>
+          <t>Manish Pandey</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>NAKUL11</t>
+          <t>SKY11</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>b sai sudharshan</t>
+          <t>hardik pandya</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -11682,7 +11734,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Manish Pandey</t>
+          <t>Arjun Tendulkar</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -11692,13 +11744,13 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>hardik pandya</t>
+          <t>karun nair</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -11725,7 +11777,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Arjun Tendulkar</t>
+          <t>Kwena Maphaka</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -11741,7 +11793,7 @@
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>karun nair</t>
+          <t>aiden markram</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -11768,23 +11820,23 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Kwena Maphaka</t>
+          <t>Ramkrishna Ghosh</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>SKY11</t>
+          <t>HARSH11</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
-          <t>aiden markram</t>
+          <t>angkrish raghuvanshi</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -11811,7 +11863,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Ramkrishna Ghosh</t>
+          <t>Azmatullah Omarzai</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -11821,13 +11873,13 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
-          <t>angkrish raghuvanshi</t>
+          <t>mitchell marsh</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -11854,23 +11906,23 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Azmatullah Omarzai</t>
+          <t>akshat raghuwanshi</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>HARSH11</t>
+          <t>AMEY11</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
-          <t>mitchell marsh</t>
+          <t>angkrish raghuvanshi</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -11897,7 +11949,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>akshat raghuwanshi</t>
+          <t>Suryansh Shegde</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -11913,7 +11965,7 @@
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
-          <t>angkrish raghuvanshi</t>
+          <t>suryansh shedge</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -11940,7 +11992,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Suryansh Shegde</t>
+          <t>Tejasvi Singh</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -11956,7 +12008,7 @@
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>suyash sharma</t>
+          <t>prabhsimran singh</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -11983,7 +12035,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Tejasvi Singh</t>
+          <t>Sai Kishor</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -11993,13 +12045,13 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
-          <t>prabhsimran singh</t>
+          <t>ishan kishan</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -12026,7 +12078,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Sai Kishor</t>
+          <t>Akash Deep</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -12042,7 +12094,7 @@
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
-          <t>ishan kishan</t>
+          <t>arshdeep singh</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -12069,23 +12121,23 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Akash Deep</t>
+          <t>Ben Duckett</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>AMEY11</t>
+          <t>PRATIK11</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
-          <t>arshdeep singh</t>
+          <t>ryan rickelton</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -12112,7 +12164,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Ben Duckett</t>
+          <t>Rahul Tripathi</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -12128,7 +12180,7 @@
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
-          <t>ryan rickelton</t>
+          <t>rahul tewatia</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -12155,7 +12207,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Rahul Tripathi</t>
+          <t>Dre Pretorius</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -12171,7 +12223,7 @@
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
-          <t>rahul tewatia</t>
+          <t>lhuan dre pretorius</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -12198,7 +12250,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Dre Pretorius</t>
+          <t>Matthew Breetzke</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -12214,7 +12266,7 @@
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr">
         <is>
-          <t>lhuan dre pretorius</t>
+          <t>matt henry</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -12241,7 +12293,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Matthew Breetzke</t>
+          <t>Anuj Rawat</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -12257,7 +12309,7 @@
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
-          <t>matt henry</t>
+          <t>mayank rawat</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -12284,7 +12336,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Anuj Rawat</t>
+          <t>Wanindu Hasaranga</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -12294,13 +12346,13 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
-          <t>mayank rawat</t>
+          <t>sandeep sharma</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -12321,92 +12373,6 @@
         <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>Wanindu Hasaranga</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>PRATIK11</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>AR</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr"/>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>sandeep sharma</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>no_stats_yet</t>
-        </is>
-      </c>
-      <c r="G42" t="n">
-        <v>0</v>
-      </c>
-      <c r="H42" t="n">
-        <v>0</v>
-      </c>
-      <c r="I42" t="n">
-        <v>0</v>
-      </c>
-      <c r="J42" t="n">
-        <v>0</v>
-      </c>
-      <c r="K42" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>Harpreet Brar</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>PRATIK11</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>BOWL</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr"/>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>jasprit bumrah</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>no_stats_yet</t>
-        </is>
-      </c>
-      <c r="G43" t="n">
-        <v>0</v>
-      </c>
-      <c r="H43" t="n">
-        <v>0</v>
-      </c>
-      <c r="I43" t="n">
-        <v>0</v>
-      </c>
-      <c r="J43" t="n">
-        <v>0</v>
-      </c>
-      <c r="K43" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12580,19 +12546,19 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>130</v>
+        <v>182</v>
       </c>
       <c r="H2" t="n">
         <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>130</v>
+        <v>182</v>
       </c>
       <c r="J2" t="n">
         <v>20</v>
       </c>
       <c r="K2" t="n">
-        <v>150</v>
+        <v>202</v>
       </c>
     </row>
     <row r="3">

--- a/IPL_Fantasy_Points.xlsx
+++ b/IPL_Fantasy_Points.xlsx
@@ -604,19 +604,19 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>186</v>
+        <v>262</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>186</v>
+        <v>262</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>186</v>
+        <v>262</v>
       </c>
     </row>
     <row r="5">
@@ -819,19 +819,19 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>154</v>
+        <v>176</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>154</v>
+        <v>176</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>154</v>
+        <v>176</v>
       </c>
     </row>
     <row r="10">
@@ -1811,16 +1811,16 @@
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I32" t="n">
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>160</v>
+        <v>200</v>
       </c>
       <c r="K32" t="n">
-        <v>160</v>
+        <v>200</v>
       </c>
     </row>
     <row r="33">
@@ -2023,19 +2023,19 @@
         </is>
       </c>
       <c r="G37" t="n">
-        <v>349</v>
+        <v>414</v>
       </c>
       <c r="H37" t="n">
         <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>349</v>
+        <v>414</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>349</v>
+        <v>414</v>
       </c>
     </row>
     <row r="38">
@@ -2109,19 +2109,19 @@
         </is>
       </c>
       <c r="G39" t="n">
-        <v>172</v>
+        <v>193</v>
       </c>
       <c r="H39" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I39" t="n">
-        <v>172</v>
+        <v>193</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>172</v>
+        <v>193</v>
       </c>
     </row>
     <row r="40">
@@ -3012,19 +3012,19 @@
         </is>
       </c>
       <c r="G60" t="n">
-        <v>137</v>
+        <v>260</v>
       </c>
       <c r="H60" t="n">
         <v>0</v>
       </c>
       <c r="I60" t="n">
-        <v>137</v>
+        <v>260</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
       </c>
       <c r="K60" t="n">
-        <v>137</v>
+        <v>260</v>
       </c>
     </row>
     <row r="61">
@@ -4677,31 +4677,31 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="D99" t="inlineStr"/>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>mitchell marsh</t>
-        </is>
-      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>will jacks</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr"/>
       <c r="F99" t="inlineStr">
         <is>
-          <t>no_stats_yet</t>
+          <t>exact/alias</t>
         </is>
       </c>
       <c r="G99" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="H99" t="n">
         <v>0</v>
       </c>
       <c r="I99" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
       </c>
       <c r="K99" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
     </row>
     <row r="100">
@@ -5334,19 +5334,19 @@
         </is>
       </c>
       <c r="G114" t="n">
-        <v>97</v>
+        <v>128</v>
       </c>
       <c r="H114" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I114" t="n">
-        <v>97</v>
+        <v>128</v>
       </c>
       <c r="J114" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="K114" t="n">
-        <v>157</v>
+        <v>208</v>
       </c>
     </row>
     <row r="115">
@@ -6065,19 +6065,19 @@
         </is>
       </c>
       <c r="G131" t="n">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="H131" t="n">
         <v>0</v>
       </c>
       <c r="I131" t="n">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
       </c>
       <c r="K131" t="n">
-        <v>181</v>
+        <v>188</v>
       </c>
     </row>
     <row r="132">
@@ -6409,19 +6409,19 @@
         </is>
       </c>
       <c r="G139" t="n">
-        <v>63</v>
+        <v>93</v>
       </c>
       <c r="H139" t="n">
         <v>0</v>
       </c>
       <c r="I139" t="n">
-        <v>63</v>
+        <v>93</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
       </c>
       <c r="K139" t="n">
-        <v>63</v>
+        <v>93</v>
       </c>
     </row>
     <row r="140">
@@ -6584,16 +6584,16 @@
         <v>1</v>
       </c>
       <c r="H143" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I143" t="n">
         <v>0</v>
       </c>
       <c r="J143" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="K143" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
     </row>
     <row r="144">
@@ -6667,19 +6667,19 @@
         </is>
       </c>
       <c r="G145" t="n">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="H145" t="n">
         <v>0</v>
       </c>
       <c r="I145" t="n">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
       </c>
       <c r="K145" t="n">
-        <v>157</v>
+        <v>162</v>
       </c>
     </row>
     <row r="146">
@@ -7398,19 +7398,19 @@
         </is>
       </c>
       <c r="G162" t="n">
-        <v>380</v>
+        <v>425</v>
       </c>
       <c r="H162" t="n">
         <v>0</v>
       </c>
       <c r="I162" t="n">
-        <v>380</v>
+        <v>425</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
       </c>
       <c r="K162" t="n">
-        <v>380</v>
+        <v>425</v>
       </c>
     </row>
     <row r="163">
@@ -8198,7 +8198,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2355</v>
+        <v>2395</v>
       </c>
     </row>
     <row r="4">
@@ -8211,7 +8211,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2104</v>
+        <v>2150</v>
       </c>
     </row>
     <row r="5">
@@ -8220,11 +8220,11 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>AMEY11</t>
+          <t>BABA11</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2097</v>
+        <v>2124</v>
       </c>
     </row>
     <row r="6">
@@ -8233,11 +8233,11 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SKY11</t>
+          <t>AMEY11</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2005</v>
+        <v>2102</v>
       </c>
     </row>
     <row r="7">
@@ -8246,11 +8246,11 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>BABA11</t>
+          <t>SKY11</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2001</v>
+        <v>2056</v>
       </c>
     </row>
     <row r="8">
@@ -8263,7 +8263,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1788</v>
+        <v>1886</v>
       </c>
     </row>
     <row r="9">
@@ -8276,7 +8276,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1755</v>
+        <v>1841</v>
       </c>
     </row>
     <row r="10">
@@ -8289,7 +8289,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1748</v>
+        <v>1805</v>
       </c>
     </row>
     <row r="11">
@@ -8302,7 +8302,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1442</v>
+        <v>1487</v>
       </c>
     </row>
   </sheetData>
@@ -8316,7 +8316,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C174"/>
+  <dimension ref="A1:C176"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8369,7 +8369,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>380</v>
+        <v>425</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
@@ -8437,7 +8437,7 @@
         <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10">
@@ -8892,7 +8892,7 @@
         <v>0</v>
       </c>
       <c r="C44" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="45">
@@ -8954,10 +8954,10 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>97</v>
+        <v>128</v>
       </c>
       <c r="C49" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="50">
@@ -9006,7 +9006,7 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>349</v>
+        <v>414</v>
       </c>
       <c r="C53" t="n">
         <v>0</v>
@@ -9591,7 +9591,7 @@
         </is>
       </c>
       <c r="B98" t="n">
-        <v>154</v>
+        <v>176</v>
       </c>
       <c r="C98" t="n">
         <v>0</v>
@@ -9656,10 +9656,10 @@
         </is>
       </c>
       <c r="B103" t="n">
-        <v>172</v>
+        <v>193</v>
       </c>
       <c r="C103" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="104">
@@ -9750,7 +9750,7 @@
         <v>0</v>
       </c>
       <c r="C110" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="111">
@@ -9964,11 +9964,11 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>rohit sharma</t>
+          <t>robin minz</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>137</v>
+        <v>1</v>
       </c>
       <c r="C127" t="n">
         <v>0</v>
@@ -9977,37 +9977,37 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>romario shepherd</t>
+          <t>rohit sharma</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>39</v>
+        <v>137</v>
       </c>
       <c r="C128" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>rovman powell</t>
+          <t>romario shepherd</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>121</v>
+        <v>39</v>
       </c>
       <c r="C129" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>ruturaj gaikwad</t>
+          <t>rovman powell</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>178</v>
+        <v>121</v>
       </c>
       <c r="C130" t="n">
         <v>0</v>
@@ -10016,11 +10016,11 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>ryan rickelton</t>
+          <t>ruturaj gaikwad</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>137</v>
+        <v>178</v>
       </c>
       <c r="C131" t="n">
         <v>0</v>
@@ -10029,11 +10029,11 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>sahil parakh</t>
+          <t>ryan rickelton</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>0</v>
+        <v>260</v>
       </c>
       <c r="C132" t="n">
         <v>0</v>
@@ -10042,37 +10042,37 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>sakib hussain</t>
+          <t>sahil parakh</t>
         </is>
       </c>
       <c r="B133" t="n">
         <v>0</v>
       </c>
       <c r="C133" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>salil arora</t>
+          <t>sakib hussain</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="C134" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>sameer rizvi</t>
+          <t>salil arora</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>209</v>
+        <v>93</v>
       </c>
       <c r="C135" t="n">
         <v>0</v>
@@ -10081,37 +10081,37 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>sandeep sharma</t>
+          <t>sameer rizvi</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>0</v>
+        <v>209</v>
       </c>
       <c r="C136" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>sanju samson</t>
+          <t>sandeep sharma</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>304</v>
+        <v>0</v>
       </c>
       <c r="C137" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>sarfaraz khan</t>
+          <t>sanju samson</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>161</v>
+        <v>304</v>
       </c>
       <c r="C138" t="n">
         <v>0</v>
@@ -10120,11 +10120,11 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>shahbaz ahmed</t>
+          <t>sarfaraz khan</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>15</v>
+        <v>161</v>
       </c>
       <c r="C139" t="n">
         <v>0</v>
@@ -10133,11 +10133,11 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>shahrukh khan</t>
+          <t>shahbaz ahmed</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="C140" t="n">
         <v>0</v>
@@ -10146,50 +10146,50 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>shardul thakur</t>
+          <t>shahrukh khan</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>14</v>
+        <v>35</v>
       </c>
       <c r="C141" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>shashank singh</t>
+          <t>shardul thakur</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>70</v>
+        <v>14</v>
       </c>
       <c r="C142" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>sherfane rutherford</t>
+          <t>shashank singh</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>103</v>
+        <v>70</v>
       </c>
       <c r="C143" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>shimron hetmyer</t>
+          <t>sherfane rutherford</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>72</v>
+        <v>103</v>
       </c>
       <c r="C144" t="n">
         <v>0</v>
@@ -10198,50 +10198,50 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>shivam dube</t>
+          <t>shimron hetmyer</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>150</v>
+        <v>72</v>
       </c>
       <c r="C145" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>shivang kumar</t>
+          <t>shivam dube</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>21</v>
+        <v>150</v>
       </c>
       <c r="C146" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>shreyas iyer</t>
+          <t>shivang kumar</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>309</v>
+        <v>21</v>
       </c>
       <c r="C147" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>shubham badriprasad dubey</t>
+          <t>shreyas iyer</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>50</v>
+        <v>309</v>
       </c>
       <c r="C148" t="n">
         <v>0</v>
@@ -10250,11 +10250,11 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>shubman gill</t>
+          <t>shubham badriprasad dubey</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>330</v>
+        <v>50</v>
       </c>
       <c r="C149" t="n">
         <v>0</v>
@@ -10263,37 +10263,37 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>sunil narine</t>
+          <t>shubman gill</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>40</v>
+        <v>330</v>
       </c>
       <c r="C150" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>suryakumar yadav</t>
+          <t>sunil narine</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>157</v>
+        <v>40</v>
       </c>
       <c r="C151" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>suryansh shedge</t>
+          <t>suryakumar yadav</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>3</v>
+        <v>162</v>
       </c>
       <c r="C152" t="n">
         <v>0</v>
@@ -10302,50 +10302,50 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>suyash sharma</t>
+          <t>suryansh shedge</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C153" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>t natarajan</t>
+          <t>suyash sharma</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C154" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>tilak varma</t>
+          <t>t natarajan</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>181</v>
+        <v>1</v>
       </c>
       <c r="C155" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>tim david</t>
+          <t>tilak varma</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="C156" t="n">
         <v>0</v>
@@ -10354,11 +10354,11 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>tim seifert</t>
+          <t>tim david</t>
         </is>
       </c>
       <c r="B157" t="n">
-        <v>19</v>
+        <v>183</v>
       </c>
       <c r="C157" t="n">
         <v>0</v>
@@ -10367,11 +10367,11 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>travis head</t>
+          <t>tim seifert</t>
         </is>
       </c>
       <c r="B158" t="n">
-        <v>186</v>
+        <v>19</v>
       </c>
       <c r="C158" t="n">
         <v>0</v>
@@ -10380,208 +10380,234 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>trent boult</t>
+          <t>travis head</t>
         </is>
       </c>
       <c r="B159" t="n">
-        <v>1</v>
+        <v>262</v>
       </c>
       <c r="C159" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>tristan stubbs</t>
+          <t>trent boult</t>
         </is>
       </c>
       <c r="B160" t="n">
-        <v>201</v>
+        <v>1</v>
       </c>
       <c r="C160" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>tushar deshpande</t>
+          <t>tristan stubbs</t>
         </is>
       </c>
       <c r="B161" t="n">
-        <v>25</v>
+        <v>201</v>
       </c>
       <c r="C161" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>urvil patel</t>
+          <t>tushar deshpande</t>
         </is>
       </c>
       <c r="B162" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="C162" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>vaibhav arora</t>
+          <t>urvil patel</t>
         </is>
       </c>
       <c r="B163" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C163" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>vaibhav suryavanshi</t>
+          <t>vaibhav arora</t>
         </is>
       </c>
       <c r="B164" t="n">
-        <v>400</v>
+        <v>1</v>
       </c>
       <c r="C164" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>varun chakravarthy</t>
+          <t>vaibhav suryavanshi</t>
         </is>
       </c>
       <c r="B165" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="C165" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>venkatesh iyer</t>
+          <t>varun chakravarthy</t>
         </is>
       </c>
       <c r="B166" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="C166" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>vijaykumar vyshak</t>
+          <t>venkatesh iyer</t>
         </is>
       </c>
       <c r="B167" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="C167" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>vipraj nigam</t>
+          <t>vijaykumar vyshak</t>
         </is>
       </c>
       <c r="B168" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="C168" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>virat kohli</t>
+          <t>vipraj nigam</t>
         </is>
       </c>
       <c r="B169" t="n">
-        <v>351</v>
+        <v>12</v>
       </c>
       <c r="C169" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>washington sundar</t>
+          <t>virat kohli</t>
         </is>
       </c>
       <c r="B170" t="n">
-        <v>157</v>
+        <v>351</v>
       </c>
       <c r="C170" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>xavier bartlett</t>
+          <t>washington sundar</t>
         </is>
       </c>
       <c r="B171" t="n">
-        <v>11</v>
+        <v>157</v>
       </c>
       <c r="C171" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>yash raj punja</t>
+          <t>will jacks</t>
         </is>
       </c>
       <c r="B172" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="C172" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>yashasvi jaiswal</t>
+          <t>xavier bartlett</t>
         </is>
       </c>
       <c r="B173" t="n">
-        <v>306</v>
+        <v>11</v>
       </c>
       <c r="C173" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
+          <t>yash raj punja</t>
+        </is>
+      </c>
+      <c r="B174" t="n">
+        <v>0</v>
+      </c>
+      <c r="C174" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>yashasvi jaiswal</t>
+        </is>
+      </c>
+      <c r="B175" t="n">
+        <v>306</v>
+      </c>
+      <c r="C175" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
           <t>yuzvendra chahal</t>
         </is>
       </c>
-      <c r="B174" t="n">
-        <v>0</v>
-      </c>
-      <c r="C174" t="n">
+      <c r="B176" t="n">
+        <v>0</v>
+      </c>
+      <c r="C176" t="n">
         <v>7</v>
       </c>
     </row>
@@ -10596,7 +10622,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K41"/>
+  <dimension ref="A1:K40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11562,7 +11588,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Will Jacks</t>
+          <t>Matheesha Pathirana</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -11572,13 +11598,13 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>mitchell marsh</t>
+          <t>eshan malinga</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -11605,7 +11631,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Matheesha Pathirana</t>
+          <t>Ben Dwarshuis</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -11621,7 +11647,7 @@
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>eshan malinga</t>
+          <t>b sai sudharshan</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -11648,23 +11674,23 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Ben Dwarshuis</t>
+          <t>Manish Pandey</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>NAKUL11</t>
+          <t>SKY11</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>b sai sudharshan</t>
+          <t>hardik pandya</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -11691,7 +11717,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Manish Pandey</t>
+          <t>Arjun Tendulkar</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -11701,13 +11727,13 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>hardik pandya</t>
+          <t>karun nair</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -11734,7 +11760,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Arjun Tendulkar</t>
+          <t>Kwena Maphaka</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -11750,7 +11776,7 @@
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>karun nair</t>
+          <t>aiden markram</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -11777,23 +11803,23 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Kwena Maphaka</t>
+          <t>Ramkrishna Ghosh</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>SKY11</t>
+          <t>HARSH11</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>aiden markram</t>
+          <t>angkrish raghuvanshi</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -11820,7 +11846,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Ramkrishna Ghosh</t>
+          <t>Azmatullah Omarzai</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -11830,13 +11856,13 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
-          <t>angkrish raghuvanshi</t>
+          <t>mitchell marsh</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -11863,23 +11889,23 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Azmatullah Omarzai</t>
+          <t>akshat raghuwanshi</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>HARSH11</t>
+          <t>AMEY11</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
-          <t>mitchell marsh</t>
+          <t>angkrish raghuvanshi</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -11906,7 +11932,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>akshat raghuwanshi</t>
+          <t>Suryansh Shegde</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -11922,7 +11948,7 @@
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
-          <t>angkrish raghuvanshi</t>
+          <t>suryansh shedge</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -11949,7 +11975,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Suryansh Shegde</t>
+          <t>Tejasvi Singh</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -11965,7 +11991,7 @@
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
-          <t>suryansh shedge</t>
+          <t>prabhsimran singh</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -11992,7 +12018,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Tejasvi Singh</t>
+          <t>Sai Kishor</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -12002,13 +12028,13 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>prabhsimran singh</t>
+          <t>ishan kishan</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -12035,7 +12061,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Sai Kishor</t>
+          <t>Akash Deep</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -12051,7 +12077,7 @@
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
-          <t>ishan kishan</t>
+          <t>arshdeep singh</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -12078,23 +12104,23 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Akash Deep</t>
+          <t>Ben Duckett</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>AMEY11</t>
+          <t>PRATIK11</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
-          <t>arshdeep singh</t>
+          <t>ryan rickelton</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -12121,7 +12147,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Ben Duckett</t>
+          <t>Rahul Tripathi</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -12137,7 +12163,7 @@
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
-          <t>ryan rickelton</t>
+          <t>rahul tewatia</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -12164,7 +12190,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Rahul Tripathi</t>
+          <t>Dre Pretorius</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -12180,7 +12206,7 @@
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
-          <t>rahul tewatia</t>
+          <t>lhuan dre pretorius</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -12207,7 +12233,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Dre Pretorius</t>
+          <t>Matthew Breetzke</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -12223,7 +12249,7 @@
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
-          <t>lhuan dre pretorius</t>
+          <t>matt henry</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -12250,7 +12276,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Matthew Breetzke</t>
+          <t>Anuj Rawat</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -12266,7 +12292,7 @@
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr">
         <is>
-          <t>matt henry</t>
+          <t>mayank rawat</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -12293,7 +12319,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Anuj Rawat</t>
+          <t>Wanindu Hasaranga</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -12303,13 +12329,13 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
-          <t>mayank rawat</t>
+          <t>sandeep sharma</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -12330,49 +12356,6 @@
         <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>Wanindu Hasaranga</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>PRATIK11</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>AR</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr"/>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>sandeep sharma</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>no_stats_yet</t>
-        </is>
-      </c>
-      <c r="G41" t="n">
-        <v>0</v>
-      </c>
-      <c r="H41" t="n">
-        <v>0</v>
-      </c>
-      <c r="I41" t="n">
-        <v>0</v>
-      </c>
-      <c r="J41" t="n">
-        <v>0</v>
-      </c>
-      <c r="K41" t="n">
         <v>0</v>
       </c>
     </row>

--- a/IPL_Fantasy_Points.xlsx
+++ b/IPL_Fantasy_Points.xlsx
@@ -647,19 +647,19 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="6">
@@ -690,19 +690,19 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>238</v>
+        <v>257</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>238</v>
+        <v>257</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>238</v>
+        <v>257</v>
       </c>
     </row>
     <row r="7">
@@ -994,16 +994,16 @@
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>160</v>
+        <v>180</v>
       </c>
       <c r="K13" t="n">
-        <v>160</v>
+        <v>180</v>
       </c>
     </row>
     <row r="14">
@@ -1249,19 +1249,19 @@
         </is>
       </c>
       <c r="G19" t="n">
-        <v>330</v>
+        <v>373</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>330</v>
+        <v>373</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>330</v>
+        <v>373</v>
       </c>
     </row>
     <row r="20">
@@ -1550,19 +1550,19 @@
         </is>
       </c>
       <c r="G26" t="n">
-        <v>49</v>
+        <v>76</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>49</v>
+        <v>76</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>49</v>
+        <v>76</v>
       </c>
     </row>
     <row r="27">
@@ -1593,19 +1593,19 @@
         </is>
       </c>
       <c r="G27" t="n">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="H27" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I27" t="n">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="J27" t="n">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="K27" t="n">
-        <v>43</v>
+        <v>95</v>
       </c>
     </row>
     <row r="28">
@@ -2238,19 +2238,19 @@
         </is>
       </c>
       <c r="G42" t="n">
-        <v>39</v>
+        <v>56</v>
       </c>
       <c r="H42" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I42" t="n">
-        <v>39</v>
+        <v>56</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>39</v>
+        <v>56</v>
       </c>
     </row>
     <row r="43">
@@ -3184,19 +3184,19 @@
         </is>
       </c>
       <c r="G64" t="n">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="H64" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I64" t="n">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="J64" t="n">
-        <v>160</v>
+        <v>200</v>
       </c>
       <c r="K64" t="n">
-        <v>188</v>
+        <v>235</v>
       </c>
     </row>
     <row r="65">
@@ -3571,19 +3571,19 @@
         </is>
       </c>
       <c r="G73" t="n">
-        <v>322</v>
+        <v>328</v>
       </c>
       <c r="H73" t="n">
         <v>0</v>
       </c>
       <c r="I73" t="n">
-        <v>322</v>
+        <v>328</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
       </c>
       <c r="K73" t="n">
-        <v>322</v>
+        <v>328</v>
       </c>
     </row>
     <row r="74">
@@ -3958,19 +3958,19 @@
         </is>
       </c>
       <c r="G82" t="n">
-        <v>183</v>
+        <v>192</v>
       </c>
       <c r="H82" t="n">
         <v>0</v>
       </c>
       <c r="I82" t="n">
-        <v>183</v>
+        <v>192</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
       </c>
       <c r="K82" t="n">
-        <v>183</v>
+        <v>192</v>
       </c>
     </row>
     <row r="83">
@@ -4431,19 +4431,19 @@
         </is>
       </c>
       <c r="G93" t="n">
-        <v>270</v>
+        <v>309</v>
       </c>
       <c r="H93" t="n">
         <v>0</v>
       </c>
       <c r="I93" t="n">
-        <v>270</v>
+        <v>309</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
       </c>
       <c r="K93" t="n">
-        <v>270</v>
+        <v>309</v>
       </c>
     </row>
     <row r="94">
@@ -4778,16 +4778,16 @@
         <v>35</v>
       </c>
       <c r="H101" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I101" t="n">
         <v>0</v>
       </c>
       <c r="J101" t="n">
-        <v>260</v>
+        <v>280</v>
       </c>
       <c r="K101" t="n">
-        <v>260</v>
+        <v>280</v>
       </c>
     </row>
     <row r="102">
@@ -5850,19 +5850,19 @@
         </is>
       </c>
       <c r="G126" t="n">
-        <v>242</v>
+        <v>282</v>
       </c>
       <c r="H126" t="n">
         <v>0</v>
       </c>
       <c r="I126" t="n">
-        <v>242</v>
+        <v>282</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
       </c>
       <c r="K126" t="n">
-        <v>242</v>
+        <v>282</v>
       </c>
     </row>
     <row r="127">
@@ -5936,19 +5936,19 @@
         </is>
       </c>
       <c r="G128" t="n">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="H128" t="n">
         <v>0</v>
       </c>
       <c r="I128" t="n">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
       </c>
       <c r="K128" t="n">
-        <v>29</v>
+        <v>41</v>
       </c>
     </row>
     <row r="129">
@@ -5979,19 +5979,19 @@
         </is>
       </c>
       <c r="G129" t="n">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="H129" t="n">
         <v>0</v>
       </c>
       <c r="I129" t="n">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
       </c>
       <c r="K129" t="n">
-        <v>35</v>
+        <v>43</v>
       </c>
     </row>
     <row r="130">
@@ -6280,19 +6280,19 @@
         </is>
       </c>
       <c r="G136" t="n">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="H136" t="n">
         <v>1</v>
       </c>
       <c r="I136" t="n">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="J136" t="n">
         <v>20</v>
       </c>
       <c r="K136" t="n">
-        <v>177</v>
+        <v>189</v>
       </c>
     </row>
     <row r="137">
@@ -6624,19 +6624,19 @@
         </is>
       </c>
       <c r="G144" t="n">
-        <v>351</v>
+        <v>379</v>
       </c>
       <c r="H144" t="n">
         <v>0</v>
       </c>
       <c r="I144" t="n">
-        <v>351</v>
+        <v>379</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
       </c>
       <c r="K144" t="n">
-        <v>351</v>
+        <v>379</v>
       </c>
     </row>
     <row r="145">
@@ -7011,19 +7011,19 @@
         </is>
       </c>
       <c r="G153" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="H153" t="n">
         <v>9</v>
       </c>
       <c r="I153" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="J153" t="n">
         <v>180</v>
       </c>
       <c r="K153" t="n">
-        <v>216</v>
+        <v>220</v>
       </c>
     </row>
     <row r="154">
@@ -7183,19 +7183,19 @@
         </is>
       </c>
       <c r="G157" t="n">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="H157" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I157" t="n">
         <v>0</v>
       </c>
       <c r="J157" t="n">
-        <v>280</v>
+        <v>340</v>
       </c>
       <c r="K157" t="n">
-        <v>280</v>
+        <v>340</v>
       </c>
     </row>
     <row r="158">
@@ -8003,16 +8003,16 @@
         <v>0</v>
       </c>
       <c r="H176" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I176" t="n">
         <v>0</v>
       </c>
       <c r="J176" t="n">
-        <v>120</v>
+        <v>140</v>
       </c>
       <c r="K176" t="n">
-        <v>120</v>
+        <v>140</v>
       </c>
     </row>
     <row r="177">
@@ -8185,7 +8185,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2802</v>
+        <v>2817</v>
       </c>
     </row>
     <row r="3">
@@ -8198,7 +8198,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2395</v>
+        <v>2517</v>
       </c>
     </row>
     <row r="4">
@@ -8211,7 +8211,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2150</v>
+        <v>2209</v>
       </c>
     </row>
     <row r="5">
@@ -8220,11 +8220,11 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>BABA11</t>
+          <t>AMEY11</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2124</v>
+        <v>2194</v>
       </c>
     </row>
     <row r="6">
@@ -8233,11 +8233,11 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>AMEY11</t>
+          <t>BABA11</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2102</v>
+        <v>2171</v>
       </c>
     </row>
     <row r="7">
@@ -8263,7 +8263,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1886</v>
+        <v>1926</v>
       </c>
     </row>
     <row r="9">
@@ -8272,11 +8272,11 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>VATSAL11</t>
+          <t>HARSH11</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1841</v>
+        <v>1877</v>
       </c>
     </row>
     <row r="10">
@@ -8285,11 +8285,11 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>HARSH11</t>
+          <t>VATSAL11</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1805</v>
+        <v>1858</v>
       </c>
     </row>
     <row r="11">
@@ -8302,7 +8302,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1487</v>
+        <v>1507</v>
       </c>
     </row>
   </sheetData>
@@ -8515,7 +8515,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16">
@@ -8642,7 +8642,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>322</v>
+        <v>328</v>
       </c>
       <c r="C25" t="n">
         <v>0</v>
@@ -8655,10 +8655,10 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="C26" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="27">
@@ -8798,7 +8798,7 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>242</v>
+        <v>282</v>
       </c>
       <c r="C37" t="n">
         <v>0</v>
@@ -9045,7 +9045,7 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="C56" t="n">
         <v>0</v>
@@ -9084,10 +9084,10 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="C59" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="60">
@@ -9123,7 +9123,7 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C62" t="n">
         <v>0</v>
@@ -9149,7 +9149,7 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>270</v>
+        <v>309</v>
       </c>
       <c r="C64" t="n">
         <v>0</v>
@@ -9178,7 +9178,7 @@
         <v>35</v>
       </c>
       <c r="C66" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="67">
@@ -9253,7 +9253,7 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="C72" t="n">
         <v>9</v>
@@ -9529,7 +9529,7 @@
         <v>0</v>
       </c>
       <c r="C93" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="94">
@@ -9838,7 +9838,7 @@
         </is>
       </c>
       <c r="B117" t="n">
-        <v>49</v>
+        <v>76</v>
       </c>
       <c r="C117" t="n">
         <v>0</v>
@@ -9851,7 +9851,7 @@
         </is>
       </c>
       <c r="B118" t="n">
-        <v>238</v>
+        <v>257</v>
       </c>
       <c r="C118" t="n">
         <v>0</v>
@@ -9877,10 +9877,10 @@
         </is>
       </c>
       <c r="B120" t="n">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="C120" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="121">
@@ -9994,10 +9994,10 @@
         </is>
       </c>
       <c r="B129" t="n">
-        <v>39</v>
+        <v>56</v>
       </c>
       <c r="C129" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="130">
@@ -10150,7 +10150,7 @@
         </is>
       </c>
       <c r="B141" t="n">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="C141" t="n">
         <v>0</v>
@@ -10267,7 +10267,7 @@
         </is>
       </c>
       <c r="B150" t="n">
-        <v>330</v>
+        <v>373</v>
       </c>
       <c r="C150" t="n">
         <v>0</v>
@@ -10322,7 +10322,7 @@
         <v>0</v>
       </c>
       <c r="C154" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="155">
@@ -10358,7 +10358,7 @@
         </is>
       </c>
       <c r="B157" t="n">
-        <v>183</v>
+        <v>192</v>
       </c>
       <c r="C157" t="n">
         <v>0</v>
@@ -10488,7 +10488,7 @@
         </is>
       </c>
       <c r="B167" t="n">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="C167" t="n">
         <v>0</v>
@@ -10527,7 +10527,7 @@
         </is>
       </c>
       <c r="B170" t="n">
-        <v>351</v>
+        <v>379</v>
       </c>
       <c r="C170" t="n">
         <v>0</v>
@@ -10540,7 +10540,7 @@
         </is>
       </c>
       <c r="B171" t="n">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="C171" t="n">
         <v>1</v>

--- a/IPL_Fantasy_Points.xlsx
+++ b/IPL_Fantasy_Points.xlsx
@@ -1335,19 +1335,19 @@
         </is>
       </c>
       <c r="G21" t="n">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>400</v>
+        <v>404</v>
       </c>
     </row>
     <row r="22">
@@ -1682,16 +1682,16 @@
         <v>25</v>
       </c>
       <c r="H29" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="K29" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
     </row>
     <row r="30">
@@ -2281,19 +2281,19 @@
         </is>
       </c>
       <c r="G43" t="n">
-        <v>132</v>
+        <v>152</v>
       </c>
       <c r="H43" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I43" t="n">
-        <v>132</v>
+        <v>152</v>
       </c>
       <c r="J43" t="n">
-        <v>120</v>
+        <v>140</v>
       </c>
       <c r="K43" t="n">
-        <v>252</v>
+        <v>292</v>
       </c>
     </row>
     <row r="44">
@@ -2883,19 +2883,19 @@
         </is>
       </c>
       <c r="G57" t="n">
-        <v>248</v>
+        <v>290</v>
       </c>
       <c r="H57" t="n">
         <v>0</v>
       </c>
       <c r="I57" t="n">
-        <v>248</v>
+        <v>290</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
       </c>
       <c r="K57" t="n">
-        <v>248</v>
+        <v>290</v>
       </c>
     </row>
     <row r="58">
@@ -3430,31 +3430,31 @@
           <t>BOWL</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr"/>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>mitchell santner</t>
-        </is>
-      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>mitchell starc</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr"/>
       <c r="F70" t="inlineStr">
         <is>
-          <t>no_stats_yet</t>
+          <t>exact/alias</t>
         </is>
       </c>
       <c r="G70" t="n">
         <v>0</v>
       </c>
       <c r="H70" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I70" t="n">
         <v>0</v>
       </c>
       <c r="J70" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="K70" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="71">
@@ -3786,19 +3786,19 @@
         </is>
       </c>
       <c r="G78" t="n">
-        <v>201</v>
+        <v>219</v>
       </c>
       <c r="H78" t="n">
         <v>0</v>
       </c>
       <c r="I78" t="n">
-        <v>201</v>
+        <v>219</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
       </c>
       <c r="K78" t="n">
-        <v>201</v>
+        <v>219</v>
       </c>
     </row>
     <row r="79">
@@ -4302,19 +4302,19 @@
         </is>
       </c>
       <c r="G90" t="n">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="H90" t="n">
         <v>0</v>
       </c>
       <c r="I90" t="n">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
       </c>
       <c r="K90" t="n">
-        <v>306</v>
+        <v>312</v>
       </c>
     </row>
     <row r="91">
@@ -4345,19 +4345,19 @@
         </is>
       </c>
       <c r="G91" t="n">
-        <v>358</v>
+        <v>433</v>
       </c>
       <c r="H91" t="n">
         <v>0</v>
       </c>
       <c r="I91" t="n">
-        <v>358</v>
+        <v>433</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
       </c>
       <c r="K91" t="n">
-        <v>358</v>
+        <v>433</v>
       </c>
     </row>
     <row r="92">
@@ -4732,19 +4732,19 @@
         </is>
       </c>
       <c r="G100" t="n">
-        <v>117</v>
+        <v>207</v>
       </c>
       <c r="H100" t="n">
         <v>2</v>
       </c>
       <c r="I100" t="n">
-        <v>117</v>
+        <v>207</v>
       </c>
       <c r="J100" t="n">
         <v>40</v>
       </c>
       <c r="K100" t="n">
-        <v>157</v>
+        <v>247</v>
       </c>
     </row>
     <row r="101">
@@ -4864,16 +4864,16 @@
         <v>12</v>
       </c>
       <c r="H103" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I103" t="n">
         <v>0</v>
       </c>
       <c r="J103" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="K103" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
     </row>
     <row r="104">
@@ -5291,19 +5291,19 @@
         </is>
       </c>
       <c r="G113" t="n">
-        <v>147</v>
+        <v>209</v>
       </c>
       <c r="H113" t="n">
         <v>0</v>
       </c>
       <c r="I113" t="n">
-        <v>147</v>
+        <v>209</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
       </c>
       <c r="K113" t="n">
-        <v>147</v>
+        <v>209</v>
       </c>
     </row>
     <row r="114">
@@ -5420,19 +5420,19 @@
         </is>
       </c>
       <c r="G116" t="n">
-        <v>182</v>
+        <v>229</v>
       </c>
       <c r="H116" t="n">
         <v>1</v>
       </c>
       <c r="I116" t="n">
-        <v>182</v>
+        <v>229</v>
       </c>
       <c r="J116" t="n">
         <v>20</v>
       </c>
       <c r="K116" t="n">
-        <v>202</v>
+        <v>249</v>
       </c>
     </row>
     <row r="117">
@@ -6022,19 +6022,19 @@
         </is>
       </c>
       <c r="G130" t="n">
-        <v>33</v>
+        <v>58</v>
       </c>
       <c r="H130" t="n">
         <v>0</v>
       </c>
       <c r="I130" t="n">
-        <v>33</v>
+        <v>58</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
       </c>
       <c r="K130" t="n">
-        <v>33</v>
+        <v>58</v>
       </c>
     </row>
     <row r="131">
@@ -6326,16 +6326,16 @@
         <v>31</v>
       </c>
       <c r="H137" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I137" t="n">
         <v>31</v>
       </c>
       <c r="J137" t="n">
-        <v>140</v>
+        <v>160</v>
       </c>
       <c r="K137" t="n">
-        <v>171</v>
+        <v>191</v>
       </c>
     </row>
     <row r="138">
@@ -6753,19 +6753,19 @@
         </is>
       </c>
       <c r="G147" t="n">
-        <v>169</v>
+        <v>202</v>
       </c>
       <c r="H147" t="n">
         <v>0</v>
       </c>
       <c r="I147" t="n">
-        <v>169</v>
+        <v>202</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
       </c>
       <c r="K147" t="n">
-        <v>169</v>
+        <v>202</v>
       </c>
     </row>
     <row r="148">
@@ -7054,19 +7054,19 @@
         </is>
       </c>
       <c r="G154" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H154" t="n">
+        <v>15</v>
+      </c>
+      <c r="I154" t="n">
         <v>14</v>
       </c>
-      <c r="I154" t="n">
-        <v>13</v>
-      </c>
       <c r="J154" t="n">
-        <v>280</v>
+        <v>300</v>
       </c>
       <c r="K154" t="n">
-        <v>293</v>
+        <v>314</v>
       </c>
     </row>
     <row r="155">
@@ -7100,16 +7100,16 @@
         <v>1</v>
       </c>
       <c r="H155" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I155" t="n">
         <v>1</v>
       </c>
       <c r="J155" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="K155" t="n">
-        <v>81</v>
+        <v>101</v>
       </c>
     </row>
     <row r="156">
@@ -8185,7 +8185,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2817</v>
+        <v>2835</v>
       </c>
     </row>
     <row r="3">
@@ -8198,7 +8198,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2517</v>
+        <v>2541</v>
       </c>
     </row>
     <row r="4">
@@ -8211,7 +8211,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2209</v>
+        <v>2400</v>
       </c>
     </row>
     <row r="5">
@@ -8220,11 +8220,11 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>AMEY11</t>
+          <t>BABA11</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2194</v>
+        <v>2273</v>
       </c>
     </row>
     <row r="6">
@@ -8233,11 +8233,11 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>BABA11</t>
+          <t>AMEY11</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2171</v>
+        <v>2268</v>
       </c>
     </row>
     <row r="7">
@@ -8250,7 +8250,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2056</v>
+        <v>2165</v>
       </c>
     </row>
     <row r="8">
@@ -8276,7 +8276,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1877</v>
+        <v>1922</v>
       </c>
     </row>
     <row r="10">
@@ -8289,7 +8289,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1858</v>
+        <v>1898</v>
       </c>
     </row>
     <row r="11">
@@ -8316,7 +8316,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C176"/>
+  <dimension ref="A1:C177"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8551,7 +8551,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>33</v>
+        <v>58</v>
       </c>
       <c r="C18" t="n">
         <v>0</v>
@@ -8606,7 +8606,7 @@
         <v>31</v>
       </c>
       <c r="C22" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="23">
@@ -8824,7 +8824,7 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>248</v>
+        <v>290</v>
       </c>
       <c r="C39" t="n">
         <v>0</v>
@@ -8863,7 +8863,7 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>182</v>
+        <v>229</v>
       </c>
       <c r="C42" t="n">
         <v>1</v>
@@ -9136,10 +9136,10 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C63" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="64">
@@ -9295,7 +9295,7 @@
         <v>12</v>
       </c>
       <c r="C75" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="76">
@@ -9344,7 +9344,7 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>358</v>
+        <v>433</v>
       </c>
       <c r="C79" t="n">
         <v>0</v>
@@ -9509,33 +9509,33 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>mohammed shami</t>
+          <t>mitchell starc</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="C92" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>mohammed siraj</t>
+          <t>mohammed shami</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="C93" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>mohsin khan</t>
+          <t>mohammed siraj</t>
         </is>
       </c>
       <c r="B94" t="n">
@@ -9548,50 +9548,50 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>mukesh choudhary</t>
+          <t>mohsin khan</t>
         </is>
       </c>
       <c r="B95" t="n">
         <v>0</v>
       </c>
       <c r="C95" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>mukesh kumar</t>
+          <t>mukesh choudhary</t>
         </is>
       </c>
       <c r="B96" t="n">
         <v>0</v>
       </c>
       <c r="C96" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>mukul choudhary</t>
+          <t>mukesh kumar</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>156</v>
+        <v>0</v>
       </c>
       <c r="C97" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>naman dhir</t>
+          <t>mukul choudhary</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>176</v>
+        <v>156</v>
       </c>
       <c r="C98" t="n">
         <v>0</v>
@@ -9600,37 +9600,37 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>nandre burger</t>
+          <t>naman dhir</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>3</v>
+        <v>176</v>
       </c>
       <c r="C99" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>navdeep saini</t>
+          <t>nandre burger</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C100" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>nehal wadhera</t>
+          <t>navdeep saini</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="C101" t="n">
         <v>0</v>
@@ -9639,11 +9639,11 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>nicholas pooran</t>
+          <t>nehal wadhera</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>82</v>
+        <v>65</v>
       </c>
       <c r="C102" t="n">
         <v>0</v>
@@ -9652,76 +9652,76 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>nitish kumar reddy</t>
+          <t>nicholas pooran</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>193</v>
+        <v>82</v>
       </c>
       <c r="C103" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>nitish rana</t>
+          <t>nitish kumar reddy</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>169</v>
+        <v>193</v>
       </c>
       <c r="C104" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>noor ahmad</t>
+          <t>nitish rana</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>10</v>
+        <v>202</v>
       </c>
       <c r="C105" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>pat cummins</t>
+          <t>noor ahmad</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="C106" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>pathum nissanka</t>
+          <t>pat cummins</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>147</v>
+        <v>0</v>
       </c>
       <c r="C107" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>philip salt</t>
+          <t>pathum nissanka</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>202</v>
+        <v>209</v>
       </c>
       <c r="C108" t="n">
         <v>0</v>
@@ -9730,11 +9730,11 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>prabhsimran singh</t>
+          <t>philip salt</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>346</v>
+        <v>202</v>
       </c>
       <c r="C109" t="n">
         <v>0</v>
@@ -9743,76 +9743,76 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>praful hinge</t>
+          <t>prabhsimran singh</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>0</v>
+        <v>346</v>
       </c>
       <c r="C110" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>prashant veer</t>
+          <t>praful hinge</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="C111" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>prasidh krishna</t>
+          <t>prashant veer</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="C112" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>prince yadav</t>
+          <t>prasidh krishna</t>
         </is>
       </c>
       <c r="B113" t="n">
         <v>0</v>
       </c>
       <c r="C113" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>priyansh arya</t>
+          <t>prince yadav</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>283</v>
+        <v>0</v>
       </c>
       <c r="C114" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>quinton de kock</t>
+          <t>priyansh arya</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>132</v>
+        <v>283</v>
       </c>
       <c r="C115" t="n">
         <v>0</v>
@@ -9821,11 +9821,11 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>rahul chahar</t>
+          <t>quinton de kock</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>0</v>
+        <v>132</v>
       </c>
       <c r="C116" t="n">
         <v>0</v>
@@ -9834,11 +9834,11 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>rahul tewatia</t>
+          <t>rahul chahar</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>76</v>
+        <v>0</v>
       </c>
       <c r="C117" t="n">
         <v>0</v>
@@ -9847,11 +9847,11 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>rajat patidar</t>
+          <t>rahul tewatia</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>257</v>
+        <v>76</v>
       </c>
       <c r="C118" t="n">
         <v>0</v>
@@ -9860,89 +9860,89 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>ramandeep singh</t>
+          <t>rajat patidar</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>82</v>
+        <v>257</v>
       </c>
       <c r="C119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>rashid khan</t>
+          <t>ramandeep singh</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>35</v>
+        <v>82</v>
       </c>
       <c r="C120" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>rasikh salam</t>
+          <t>rashid khan</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="C121" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>ravi bishnoi</t>
+          <t>rasikh salam</t>
         </is>
       </c>
       <c r="B122" t="n">
         <v>0</v>
       </c>
       <c r="C122" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>ravindra jadeja</t>
+          <t>ravi bishnoi</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>132</v>
+        <v>0</v>
       </c>
       <c r="C123" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>rinku singh</t>
+          <t>ravindra jadeja</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>215</v>
+        <v>152</v>
       </c>
       <c r="C124" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>rishabh pant</t>
+          <t>rinku singh</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>189</v>
+        <v>215</v>
       </c>
       <c r="C125" t="n">
         <v>0</v>
@@ -9951,37 +9951,37 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>riyan parag</t>
+          <t>rishabh pant</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>117</v>
+        <v>189</v>
       </c>
       <c r="C126" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>robin minz</t>
+          <t>riyan parag</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>1</v>
+        <v>207</v>
       </c>
       <c r="C127" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>rohit sharma</t>
+          <t>robin minz</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>137</v>
+        <v>1</v>
       </c>
       <c r="C128" t="n">
         <v>0</v>
@@ -9990,37 +9990,37 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>romario shepherd</t>
+          <t>rohit sharma</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>56</v>
+        <v>137</v>
       </c>
       <c r="C129" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>rovman powell</t>
+          <t>romario shepherd</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>121</v>
+        <v>56</v>
       </c>
       <c r="C130" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>ruturaj gaikwad</t>
+          <t>rovman powell</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>178</v>
+        <v>121</v>
       </c>
       <c r="C131" t="n">
         <v>0</v>
@@ -10029,11 +10029,11 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>ryan rickelton</t>
+          <t>ruturaj gaikwad</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>260</v>
+        <v>178</v>
       </c>
       <c r="C132" t="n">
         <v>0</v>
@@ -10042,11 +10042,11 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>sahil parakh</t>
+          <t>ryan rickelton</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>0</v>
+        <v>260</v>
       </c>
       <c r="C133" t="n">
         <v>0</v>
@@ -10055,37 +10055,37 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>sakib hussain</t>
+          <t>sahil parakh</t>
         </is>
       </c>
       <c r="B134" t="n">
         <v>0</v>
       </c>
       <c r="C134" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>salil arora</t>
+          <t>sakib hussain</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>93</v>
+        <v>0</v>
       </c>
       <c r="C135" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>sameer rizvi</t>
+          <t>salil arora</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>209</v>
+        <v>93</v>
       </c>
       <c r="C136" t="n">
         <v>0</v>
@@ -10094,37 +10094,37 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>sandeep sharma</t>
+          <t>sameer rizvi</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>0</v>
+        <v>209</v>
       </c>
       <c r="C137" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>sanju samson</t>
+          <t>sandeep sharma</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>304</v>
+        <v>0</v>
       </c>
       <c r="C138" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>sarfaraz khan</t>
+          <t>sanju samson</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>161</v>
+        <v>304</v>
       </c>
       <c r="C139" t="n">
         <v>0</v>
@@ -10133,11 +10133,11 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>shahbaz ahmed</t>
+          <t>sarfaraz khan</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>15</v>
+        <v>161</v>
       </c>
       <c r="C140" t="n">
         <v>0</v>
@@ -10146,11 +10146,11 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>shahrukh khan</t>
+          <t>shahbaz ahmed</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>43</v>
+        <v>15</v>
       </c>
       <c r="C141" t="n">
         <v>0</v>
@@ -10159,50 +10159,50 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>shardul thakur</t>
+          <t>shahrukh khan</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>14</v>
+        <v>43</v>
       </c>
       <c r="C142" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>shashank singh</t>
+          <t>shardul thakur</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>70</v>
+        <v>14</v>
       </c>
       <c r="C143" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>sherfane rutherford</t>
+          <t>shashank singh</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>103</v>
+        <v>70</v>
       </c>
       <c r="C144" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>shimron hetmyer</t>
+          <t>sherfane rutherford</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>72</v>
+        <v>103</v>
       </c>
       <c r="C145" t="n">
         <v>0</v>
@@ -10211,50 +10211,50 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>shivam dube</t>
+          <t>shimron hetmyer</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>150</v>
+        <v>72</v>
       </c>
       <c r="C146" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>shivang kumar</t>
+          <t>shivam dube</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>21</v>
+        <v>150</v>
       </c>
       <c r="C147" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>shreyas iyer</t>
+          <t>shivang kumar</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>309</v>
+        <v>21</v>
       </c>
       <c r="C148" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>shubham badriprasad dubey</t>
+          <t>shreyas iyer</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>50</v>
+        <v>309</v>
       </c>
       <c r="C149" t="n">
         <v>0</v>
@@ -10263,11 +10263,11 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>shubman gill</t>
+          <t>shubham badriprasad dubey</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>373</v>
+        <v>56</v>
       </c>
       <c r="C150" t="n">
         <v>0</v>
@@ -10276,37 +10276,37 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>sunil narine</t>
+          <t>shubman gill</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>40</v>
+        <v>373</v>
       </c>
       <c r="C151" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>suryakumar yadav</t>
+          <t>sunil narine</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>162</v>
+        <v>40</v>
       </c>
       <c r="C152" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>suryansh shedge</t>
+          <t>suryakumar yadav</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>3</v>
+        <v>162</v>
       </c>
       <c r="C153" t="n">
         <v>0</v>
@@ -10315,50 +10315,50 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>suyash sharma</t>
+          <t>suryansh shedge</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C154" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>t natarajan</t>
+          <t>suyash sharma</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C155" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>tilak varma</t>
+          <t>t natarajan</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>188</v>
+        <v>1</v>
       </c>
       <c r="C156" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>tim david</t>
+          <t>tilak varma</t>
         </is>
       </c>
       <c r="B157" t="n">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="C157" t="n">
         <v>0</v>
@@ -10367,11 +10367,11 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>tim seifert</t>
+          <t>tim david</t>
         </is>
       </c>
       <c r="B158" t="n">
-        <v>19</v>
+        <v>192</v>
       </c>
       <c r="C158" t="n">
         <v>0</v>
@@ -10380,11 +10380,11 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>travis head</t>
+          <t>tim seifert</t>
         </is>
       </c>
       <c r="B159" t="n">
-        <v>262</v>
+        <v>19</v>
       </c>
       <c r="C159" t="n">
         <v>0</v>
@@ -10393,221 +10393,234 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>trent boult</t>
+          <t>travis head</t>
         </is>
       </c>
       <c r="B160" t="n">
-        <v>1</v>
+        <v>262</v>
       </c>
       <c r="C160" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>tristan stubbs</t>
+          <t>trent boult</t>
         </is>
       </c>
       <c r="B161" t="n">
-        <v>201</v>
+        <v>1</v>
       </c>
       <c r="C161" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>tushar deshpande</t>
+          <t>tristan stubbs</t>
         </is>
       </c>
       <c r="B162" t="n">
-        <v>25</v>
+        <v>219</v>
       </c>
       <c r="C162" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>urvil patel</t>
+          <t>tushar deshpande</t>
         </is>
       </c>
       <c r="B163" t="n">
+        <v>25</v>
+      </c>
+      <c r="C163" t="n">
         <v>4</v>
-      </c>
-      <c r="C163" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>vaibhav arora</t>
+          <t>urvil patel</t>
         </is>
       </c>
       <c r="B164" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C164" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>vaibhav suryavanshi</t>
+          <t>vaibhav arora</t>
         </is>
       </c>
       <c r="B165" t="n">
-        <v>400</v>
+        <v>1</v>
       </c>
       <c r="C165" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>varun chakravarthy</t>
+          <t>vaibhav suryavanshi</t>
         </is>
       </c>
       <c r="B166" t="n">
-        <v>0</v>
+        <v>404</v>
       </c>
       <c r="C166" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>venkatesh iyer</t>
+          <t>varun chakravarthy</t>
         </is>
       </c>
       <c r="B167" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="C167" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>vijaykumar vyshak</t>
+          <t>venkatesh iyer</t>
         </is>
       </c>
       <c r="B168" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="C168" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>vipraj nigam</t>
+          <t>vijaykumar vyshak</t>
         </is>
       </c>
       <c r="B169" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="C169" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>virat kohli</t>
+          <t>vipraj nigam</t>
         </is>
       </c>
       <c r="B170" t="n">
-        <v>379</v>
+        <v>12</v>
       </c>
       <c r="C170" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>washington sundar</t>
+          <t>virat kohli</t>
         </is>
       </c>
       <c r="B171" t="n">
-        <v>169</v>
+        <v>379</v>
       </c>
       <c r="C171" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>will jacks</t>
+          <t>washington sundar</t>
         </is>
       </c>
       <c r="B172" t="n">
-        <v>46</v>
+        <v>169</v>
       </c>
       <c r="C172" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>xavier bartlett</t>
+          <t>will jacks</t>
         </is>
       </c>
       <c r="B173" t="n">
-        <v>11</v>
+        <v>46</v>
       </c>
       <c r="C173" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>yash raj punja</t>
+          <t>xavier bartlett</t>
         </is>
       </c>
       <c r="B174" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="C174" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>yashasvi jaiswal</t>
+          <t>yash raj punja</t>
         </is>
       </c>
       <c r="B175" t="n">
-        <v>306</v>
+        <v>0</v>
       </c>
       <c r="C175" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
+          <t>yashasvi jaiswal</t>
+        </is>
+      </c>
+      <c r="B176" t="n">
+        <v>312</v>
+      </c>
+      <c r="C176" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
           <t>yuzvendra chahal</t>
         </is>
       </c>
-      <c r="B176" t="n">
-        <v>0</v>
-      </c>
-      <c r="C176" t="n">
+      <c r="B177" t="n">
+        <v>0</v>
+      </c>
+      <c r="C177" t="n">
         <v>7</v>
       </c>
     </row>
@@ -10622,7 +10635,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K40"/>
+  <dimension ref="A1:K39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11287,17 +11300,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Mitchell Starc</t>
+          <t>Mitchel Owen</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>BABA11</t>
+          <t>DIPESH11</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -11330,7 +11343,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Mitchel Owen</t>
+          <t>Auqib Dar</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -11340,13 +11353,13 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>mitchell santner</t>
+          <t>auqib nabi</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -11373,23 +11386,23 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Auqib Dar</t>
+          <t>Arshin Kulkarni</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>DIPESH11</t>
+          <t>NAKUL11</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>auqib nabi</t>
+          <t>ashwani kumar</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -11416,7 +11429,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Arshin Kulkarni</t>
+          <t>Nishant Sindhu</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -11426,13 +11439,13 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>ashwani kumar</t>
+          <t>shashank singh</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -11459,7 +11472,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Nishant Sindhu</t>
+          <t>Jayant Yadav</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -11475,7 +11488,7 @@
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>shashank singh</t>
+          <t>mayank yadav</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -11502,7 +11515,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Jayant Yadav</t>
+          <t>Ajay Mandal</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -11518,7 +11531,7 @@
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>mayank yadav</t>
+          <t>rajat patidar</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -11545,7 +11558,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Ajay Mandal</t>
+          <t>Matheesha Pathirana</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -11555,13 +11568,13 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>rajat patidar</t>
+          <t>eshan malinga</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -11588,7 +11601,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Matheesha Pathirana</t>
+          <t>Ben Dwarshuis</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -11604,7 +11617,7 @@
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>eshan malinga</t>
+          <t>b sai sudharshan</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -11631,23 +11644,23 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Ben Dwarshuis</t>
+          <t>Manish Pandey</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>NAKUL11</t>
+          <t>SKY11</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>b sai sudharshan</t>
+          <t>hardik pandya</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -11674,7 +11687,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Manish Pandey</t>
+          <t>Arjun Tendulkar</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -11684,13 +11697,13 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>hardik pandya</t>
+          <t>karun nair</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -11717,7 +11730,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Arjun Tendulkar</t>
+          <t>Kwena Maphaka</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -11733,7 +11746,7 @@
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>karun nair</t>
+          <t>aiden markram</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -11760,23 +11773,23 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Kwena Maphaka</t>
+          <t>Ramkrishna Ghosh</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>SKY11</t>
+          <t>HARSH11</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>aiden markram</t>
+          <t>angkrish raghuvanshi</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -11803,7 +11816,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Ramkrishna Ghosh</t>
+          <t>Azmatullah Omarzai</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -11813,13 +11826,13 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>angkrish raghuvanshi</t>
+          <t>mitchell marsh</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -11846,23 +11859,23 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Azmatullah Omarzai</t>
+          <t>akshat raghuwanshi</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>HARSH11</t>
+          <t>AMEY11</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
-          <t>mitchell marsh</t>
+          <t>angkrish raghuvanshi</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -11889,7 +11902,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>akshat raghuwanshi</t>
+          <t>Suryansh Shegde</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -11905,7 +11918,7 @@
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
-          <t>angkrish raghuvanshi</t>
+          <t>suryansh shedge</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -11932,7 +11945,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Suryansh Shegde</t>
+          <t>Tejasvi Singh</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -11948,7 +11961,7 @@
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
-          <t>suryansh shedge</t>
+          <t>prabhsimran singh</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -11975,7 +11988,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Tejasvi Singh</t>
+          <t>Sai Kishor</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -11985,13 +11998,13 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
-          <t>prabhsimran singh</t>
+          <t>ishan kishan</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -12018,7 +12031,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Sai Kishor</t>
+          <t>Akash Deep</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -12034,7 +12047,7 @@
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>ishan kishan</t>
+          <t>arshdeep singh</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -12061,23 +12074,23 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Akash Deep</t>
+          <t>Ben Duckett</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>AMEY11</t>
+          <t>PRATIK11</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
-          <t>arshdeep singh</t>
+          <t>ryan rickelton</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -12104,7 +12117,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Ben Duckett</t>
+          <t>Rahul Tripathi</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -12120,7 +12133,7 @@
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
-          <t>ryan rickelton</t>
+          <t>rahul tewatia</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -12147,7 +12160,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Rahul Tripathi</t>
+          <t>Dre Pretorius</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -12163,7 +12176,7 @@
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
-          <t>rahul tewatia</t>
+          <t>lhuan dre pretorius</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -12190,7 +12203,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Dre Pretorius</t>
+          <t>Matthew Breetzke</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -12206,7 +12219,7 @@
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
-          <t>lhuan dre pretorius</t>
+          <t>matt henry</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -12233,7 +12246,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Matthew Breetzke</t>
+          <t>Anuj Rawat</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -12249,7 +12262,7 @@
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
-          <t>matt henry</t>
+          <t>mayank rawat</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -12276,7 +12289,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Anuj Rawat</t>
+          <t>Wanindu Hasaranga</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -12286,13 +12299,13 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr">
         <is>
-          <t>mayank rawat</t>
+          <t>sandeep sharma</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -12313,49 +12326,6 @@
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>Wanindu Hasaranga</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>PRATIK11</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>AR</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr"/>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>sandeep sharma</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>no_stats_yet</t>
-        </is>
-      </c>
-      <c r="G40" t="n">
-        <v>0</v>
-      </c>
-      <c r="H40" t="n">
-        <v>0</v>
-      </c>
-      <c r="I40" t="n">
-        <v>0</v>
-      </c>
-      <c r="J40" t="n">
-        <v>0</v>
-      </c>
-      <c r="K40" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12529,19 +12499,19 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>182</v>
+        <v>229</v>
       </c>
       <c r="H2" t="n">
         <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>182</v>
+        <v>229</v>
       </c>
       <c r="J2" t="n">
         <v>20</v>
       </c>
       <c r="K2" t="n">
-        <v>202</v>
+        <v>249</v>
       </c>
     </row>
     <row r="3">

--- a/IPL_Fantasy_Points.xlsx
+++ b/IPL_Fantasy_Points.xlsx
@@ -776,19 +776,19 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>58</v>
+        <v>112</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>58</v>
+        <v>112</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>58</v>
+        <v>112</v>
       </c>
     </row>
     <row r="9">
@@ -819,19 +819,19 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>176</v>
+        <v>233</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>176</v>
+        <v>233</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>176</v>
+        <v>233</v>
       </c>
     </row>
     <row r="10">
@@ -1811,16 +1811,16 @@
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I32" t="n">
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>200</v>
+        <v>220</v>
       </c>
       <c r="K32" t="n">
-        <v>200</v>
+        <v>220</v>
       </c>
     </row>
     <row r="33">
@@ -1854,16 +1854,16 @@
         <v>39</v>
       </c>
       <c r="H33" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I33" t="n">
         <v>0</v>
       </c>
       <c r="J33" t="n">
-        <v>280</v>
+        <v>340</v>
       </c>
       <c r="K33" t="n">
-        <v>280</v>
+        <v>340</v>
       </c>
     </row>
     <row r="34">
@@ -2754,19 +2754,19 @@
         </is>
       </c>
       <c r="G54" t="n">
-        <v>304</v>
+        <v>315</v>
       </c>
       <c r="H54" t="n">
         <v>0</v>
       </c>
       <c r="I54" t="n">
-        <v>304</v>
+        <v>315</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
       </c>
       <c r="K54" t="n">
-        <v>304</v>
+        <v>315</v>
       </c>
     </row>
     <row r="55">
@@ -3012,19 +3012,19 @@
         </is>
       </c>
       <c r="G60" t="n">
-        <v>260</v>
+        <v>297</v>
       </c>
       <c r="H60" t="n">
         <v>0</v>
       </c>
       <c r="I60" t="n">
-        <v>260</v>
+        <v>297</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
       </c>
       <c r="K60" t="n">
-        <v>260</v>
+        <v>297</v>
       </c>
     </row>
     <row r="61">
@@ -3528,19 +3528,19 @@
         </is>
       </c>
       <c r="G72" t="n">
-        <v>178</v>
+        <v>245</v>
       </c>
       <c r="H72" t="n">
         <v>0</v>
       </c>
       <c r="I72" t="n">
-        <v>178</v>
+        <v>245</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
       </c>
       <c r="K72" t="n">
-        <v>178</v>
+        <v>245</v>
       </c>
     </row>
     <row r="73">
@@ -4474,19 +4474,19 @@
         </is>
       </c>
       <c r="G94" t="n">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="H94" t="n">
         <v>0</v>
       </c>
       <c r="I94" t="n">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
       </c>
       <c r="K94" t="n">
-        <v>4</v>
+        <v>28</v>
       </c>
     </row>
     <row r="95">
@@ -4689,19 +4689,19 @@
         </is>
       </c>
       <c r="G99" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H99" t="n">
         <v>0</v>
       </c>
       <c r="I99" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
       </c>
       <c r="K99" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="100">
@@ -5334,19 +5334,19 @@
         </is>
       </c>
       <c r="G114" t="n">
-        <v>128</v>
+        <v>146</v>
       </c>
       <c r="H114" t="n">
         <v>4</v>
       </c>
       <c r="I114" t="n">
-        <v>128</v>
+        <v>146</v>
       </c>
       <c r="J114" t="n">
         <v>80</v>
       </c>
       <c r="K114" t="n">
-        <v>208</v>
+        <v>226</v>
       </c>
     </row>
     <row r="115">
@@ -5380,16 +5380,16 @@
         <v>136</v>
       </c>
       <c r="H115" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I115" t="n">
         <v>136</v>
       </c>
       <c r="J115" t="n">
-        <v>180</v>
+        <v>200</v>
       </c>
       <c r="K115" t="n">
-        <v>316</v>
+        <v>336</v>
       </c>
     </row>
     <row r="116">
@@ -5881,22 +5881,22 @@
           <t>BAT</t>
         </is>
       </c>
-      <c r="D127" t="inlineStr"/>
-      <c r="E127" t="inlineStr">
-        <is>
-          <t>angkrish raghuvanshi</t>
-        </is>
-      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>ramakrishna ghosh</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr"/>
       <c r="F127" t="inlineStr">
         <is>
-          <t>no_stats_yet</t>
+          <t>ai_structured</t>
         </is>
       </c>
       <c r="G127" t="n">
         <v>0</v>
       </c>
       <c r="H127" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I127" t="n">
         <v>0</v>
@@ -6065,19 +6065,19 @@
         </is>
       </c>
       <c r="G131" t="n">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="H131" t="n">
         <v>0</v>
       </c>
       <c r="I131" t="n">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
       </c>
       <c r="K131" t="n">
-        <v>188</v>
+        <v>193</v>
       </c>
     </row>
     <row r="132">
@@ -6455,16 +6455,16 @@
         <v>7</v>
       </c>
       <c r="H140" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I140" t="n">
         <v>0</v>
       </c>
       <c r="J140" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="K140" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
     </row>
     <row r="141">
@@ -6581,7 +6581,7 @@
         </is>
       </c>
       <c r="G143" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="H143" t="n">
         <v>2</v>
@@ -6667,19 +6667,19 @@
         </is>
       </c>
       <c r="G145" t="n">
-        <v>162</v>
+        <v>183</v>
       </c>
       <c r="H145" t="n">
         <v>0</v>
       </c>
       <c r="I145" t="n">
-        <v>162</v>
+        <v>183</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
       </c>
       <c r="K145" t="n">
-        <v>162</v>
+        <v>183</v>
       </c>
     </row>
     <row r="146">
@@ -8132,16 +8132,16 @@
         <v>10</v>
       </c>
       <c r="H179" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I179" t="n">
         <v>0</v>
       </c>
       <c r="J179" t="n">
-        <v>140</v>
+        <v>180</v>
       </c>
       <c r="K179" t="n">
-        <v>140</v>
+        <v>180</v>
       </c>
     </row>
   </sheetData>
@@ -8185,7 +8185,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2835</v>
+        <v>2902</v>
       </c>
     </row>
     <row r="3">
@@ -8198,7 +8198,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2541</v>
+        <v>2621</v>
       </c>
     </row>
     <row r="4">
@@ -8211,7 +8211,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2400</v>
+        <v>2425</v>
       </c>
     </row>
     <row r="5">
@@ -8224,7 +8224,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2273</v>
+        <v>2321</v>
       </c>
     </row>
     <row r="6">
@@ -8237,7 +8237,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2268</v>
+        <v>2289</v>
       </c>
     </row>
     <row r="7">
@@ -8250,7 +8250,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2165</v>
+        <v>2203</v>
       </c>
     </row>
     <row r="8">
@@ -8263,7 +8263,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1926</v>
+        <v>2037</v>
       </c>
     </row>
     <row r="9">
@@ -8276,7 +8276,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1922</v>
+        <v>1947</v>
       </c>
     </row>
     <row r="10">
@@ -8302,7 +8302,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1507</v>
+        <v>1547</v>
       </c>
     </row>
   </sheetData>
@@ -8316,7 +8316,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C177"/>
+  <dimension ref="A1:C179"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8437,7 +8437,7 @@
         <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10">
@@ -8489,7 +8489,7 @@
         <v>39</v>
       </c>
       <c r="C13" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="14">
@@ -8954,7 +8954,7 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>128</v>
+        <v>146</v>
       </c>
       <c r="C49" t="n">
         <v>4</v>
@@ -9074,7 +9074,7 @@
         <v>136</v>
       </c>
       <c r="C58" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="59">
@@ -9100,7 +9100,7 @@
         <v>7</v>
       </c>
       <c r="C60" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="61">
@@ -9188,7 +9188,7 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>58</v>
+        <v>112</v>
       </c>
       <c r="C67" t="n">
         <v>0</v>
@@ -9240,7 +9240,7 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C71" t="n">
         <v>0</v>
@@ -9604,7 +9604,7 @@
         </is>
       </c>
       <c r="B99" t="n">
-        <v>176</v>
+        <v>233</v>
       </c>
       <c r="C99" t="n">
         <v>0</v>
@@ -9698,7 +9698,7 @@
         <v>10</v>
       </c>
       <c r="C106" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="107">
@@ -9834,7 +9834,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>rahul chahar</t>
+          <t>raghu sharma</t>
         </is>
       </c>
       <c r="B117" t="n">
@@ -9847,11 +9847,11 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>rahul tewatia</t>
+          <t>rahul chahar</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>76</v>
+        <v>0</v>
       </c>
       <c r="C118" t="n">
         <v>0</v>
@@ -9860,11 +9860,11 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>rajat patidar</t>
+          <t>rahul tewatia</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>257</v>
+        <v>76</v>
       </c>
       <c r="C119" t="n">
         <v>0</v>
@@ -9873,115 +9873,115 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>ramandeep singh</t>
+          <t>rajat patidar</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>82</v>
+        <v>257</v>
       </c>
       <c r="C120" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>rashid khan</t>
+          <t>ramakrishna ghosh</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="C121" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>rasikh salam</t>
+          <t>ramandeep singh</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="C122" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>ravi bishnoi</t>
+          <t>rashid khan</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="C123" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>ravindra jadeja</t>
+          <t>rasikh salam</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>152</v>
+        <v>0</v>
       </c>
       <c r="C124" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>rinku singh</t>
+          <t>ravi bishnoi</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="C125" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>rishabh pant</t>
+          <t>ravindra jadeja</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>189</v>
+        <v>152</v>
       </c>
       <c r="C126" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>riyan parag</t>
+          <t>rinku singh</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>207</v>
+        <v>215</v>
       </c>
       <c r="C127" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>robin minz</t>
+          <t>rishabh pant</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>1</v>
+        <v>189</v>
       </c>
       <c r="C128" t="n">
         <v>0</v>
@@ -9990,37 +9990,37 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>rohit sharma</t>
+          <t>riyan parag</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>137</v>
+        <v>207</v>
       </c>
       <c r="C129" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>romario shepherd</t>
+          <t>robin minz</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>56</v>
+        <v>6</v>
       </c>
       <c r="C130" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>rovman powell</t>
+          <t>rohit sharma</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>121</v>
+        <v>137</v>
       </c>
       <c r="C131" t="n">
         <v>0</v>
@@ -10029,24 +10029,24 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>ruturaj gaikwad</t>
+          <t>romario shepherd</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>178</v>
+        <v>56</v>
       </c>
       <c r="C132" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>ryan rickelton</t>
+          <t>rovman powell</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>260</v>
+        <v>121</v>
       </c>
       <c r="C133" t="n">
         <v>0</v>
@@ -10055,11 +10055,11 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>sahil parakh</t>
+          <t>ruturaj gaikwad</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>0</v>
+        <v>245</v>
       </c>
       <c r="C134" t="n">
         <v>0</v>
@@ -10068,24 +10068,24 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>sakib hussain</t>
+          <t>ryan rickelton</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>0</v>
+        <v>297</v>
       </c>
       <c r="C135" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>salil arora</t>
+          <t>sahil parakh</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>93</v>
+        <v>0</v>
       </c>
       <c r="C136" t="n">
         <v>0</v>
@@ -10094,37 +10094,37 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>sameer rizvi</t>
+          <t>sakib hussain</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>209</v>
+        <v>0</v>
       </c>
       <c r="C137" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>sandeep sharma</t>
+          <t>salil arora</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>0</v>
+        <v>93</v>
       </c>
       <c r="C138" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>sanju samson</t>
+          <t>sameer rizvi</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>304</v>
+        <v>209</v>
       </c>
       <c r="C139" t="n">
         <v>0</v>
@@ -10133,24 +10133,24 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>sarfaraz khan</t>
+          <t>sandeep sharma</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>161</v>
+        <v>0</v>
       </c>
       <c r="C140" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>shahbaz ahmed</t>
+          <t>sanju samson</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>15</v>
+        <v>315</v>
       </c>
       <c r="C141" t="n">
         <v>0</v>
@@ -10159,11 +10159,11 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>shahrukh khan</t>
+          <t>sarfaraz khan</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>43</v>
+        <v>161</v>
       </c>
       <c r="C142" t="n">
         <v>0</v>
@@ -10172,115 +10172,115 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>shardul thakur</t>
+          <t>shahbaz ahmed</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C143" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>shashank singh</t>
+          <t>shahrukh khan</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>70</v>
+        <v>43</v>
       </c>
       <c r="C144" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>sherfane rutherford</t>
+          <t>shardul thakur</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>103</v>
+        <v>14</v>
       </c>
       <c r="C145" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>shimron hetmyer</t>
+          <t>shashank singh</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C146" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>shivam dube</t>
+          <t>sherfane rutherford</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>150</v>
+        <v>103</v>
       </c>
       <c r="C147" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>shivang kumar</t>
+          <t>shimron hetmyer</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>21</v>
+        <v>72</v>
       </c>
       <c r="C148" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>shreyas iyer</t>
+          <t>shivam dube</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>309</v>
+        <v>150</v>
       </c>
       <c r="C149" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>shubham badriprasad dubey</t>
+          <t>shivang kumar</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>56</v>
+        <v>21</v>
       </c>
       <c r="C150" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>shubman gill</t>
+          <t>shreyas iyer</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>373</v>
+        <v>309</v>
       </c>
       <c r="C151" t="n">
         <v>0</v>
@@ -10289,24 +10289,24 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>sunil narine</t>
+          <t>shubham badriprasad dubey</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="C152" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>suryakumar yadav</t>
+          <t>shubman gill</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>162</v>
+        <v>373</v>
       </c>
       <c r="C153" t="n">
         <v>0</v>
@@ -10315,76 +10315,76 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>suryansh shedge</t>
+          <t>sunil narine</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>3</v>
+        <v>40</v>
       </c>
       <c r="C154" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>suyash sharma</t>
+          <t>suryakumar yadav</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>0</v>
+        <v>183</v>
       </c>
       <c r="C155" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>t natarajan</t>
+          <t>suryansh shedge</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C156" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>tilak varma</t>
+          <t>suyash sharma</t>
         </is>
       </c>
       <c r="B157" t="n">
-        <v>188</v>
+        <v>0</v>
       </c>
       <c r="C157" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>tim david</t>
+          <t>t natarajan</t>
         </is>
       </c>
       <c r="B158" t="n">
-        <v>192</v>
+        <v>1</v>
       </c>
       <c r="C158" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>tim seifert</t>
+          <t>tilak varma</t>
         </is>
       </c>
       <c r="B159" t="n">
-        <v>19</v>
+        <v>193</v>
       </c>
       <c r="C159" t="n">
         <v>0</v>
@@ -10393,11 +10393,11 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>travis head</t>
+          <t>tim david</t>
         </is>
       </c>
       <c r="B160" t="n">
-        <v>262</v>
+        <v>192</v>
       </c>
       <c r="C160" t="n">
         <v>0</v>
@@ -10406,24 +10406,24 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>trent boult</t>
+          <t>tim seifert</t>
         </is>
       </c>
       <c r="B161" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="C161" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>tristan stubbs</t>
+          <t>travis head</t>
         </is>
       </c>
       <c r="B162" t="n">
-        <v>219</v>
+        <v>262</v>
       </c>
       <c r="C162" t="n">
         <v>0</v>
@@ -10432,24 +10432,24 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>tushar deshpande</t>
+          <t>trent boult</t>
         </is>
       </c>
       <c r="B163" t="n">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="C163" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>urvil patel</t>
+          <t>tristan stubbs</t>
         </is>
       </c>
       <c r="B164" t="n">
-        <v>4</v>
+        <v>219</v>
       </c>
       <c r="C164" t="n">
         <v>0</v>
@@ -10458,24 +10458,24 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>vaibhav arora</t>
+          <t>tushar deshpande</t>
         </is>
       </c>
       <c r="B165" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="C165" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>vaibhav suryavanshi</t>
+          <t>urvil patel</t>
         </is>
       </c>
       <c r="B166" t="n">
-        <v>404</v>
+        <v>28</v>
       </c>
       <c r="C166" t="n">
         <v>0</v>
@@ -10484,24 +10484,24 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>varun chakravarthy</t>
+          <t>vaibhav arora</t>
         </is>
       </c>
       <c r="B167" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C167" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>venkatesh iyer</t>
+          <t>vaibhav suryavanshi</t>
         </is>
       </c>
       <c r="B168" t="n">
-        <v>41</v>
+        <v>404</v>
       </c>
       <c r="C168" t="n">
         <v>0</v>
@@ -10510,63 +10510,63 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>vijaykumar vyshak</t>
+          <t>varun chakravarthy</t>
         </is>
       </c>
       <c r="B169" t="n">
         <v>0</v>
       </c>
       <c r="C169" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>vipraj nigam</t>
+          <t>venkatesh iyer</t>
         </is>
       </c>
       <c r="B170" t="n">
-        <v>12</v>
+        <v>41</v>
       </c>
       <c r="C170" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>virat kohli</t>
+          <t>vijaykumar vyshak</t>
         </is>
       </c>
       <c r="B171" t="n">
-        <v>379</v>
+        <v>0</v>
       </c>
       <c r="C171" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>washington sundar</t>
+          <t>vipraj nigam</t>
         </is>
       </c>
       <c r="B172" t="n">
-        <v>169</v>
+        <v>12</v>
       </c>
       <c r="C172" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>will jacks</t>
+          <t>virat kohli</t>
         </is>
       </c>
       <c r="B173" t="n">
-        <v>46</v>
+        <v>379</v>
       </c>
       <c r="C173" t="n">
         <v>0</v>
@@ -10575,52 +10575,78 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>xavier bartlett</t>
+          <t>washington sundar</t>
         </is>
       </c>
       <c r="B174" t="n">
-        <v>11</v>
+        <v>169</v>
       </c>
       <c r="C174" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>yash raj punja</t>
+          <t>will jacks</t>
         </is>
       </c>
       <c r="B175" t="n">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="C175" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>yashasvi jaiswal</t>
+          <t>xavier bartlett</t>
         </is>
       </c>
       <c r="B176" t="n">
-        <v>312</v>
+        <v>11</v>
       </c>
       <c r="C176" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
+          <t>yash raj punja</t>
+        </is>
+      </c>
+      <c r="B177" t="n">
+        <v>0</v>
+      </c>
+      <c r="C177" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>yashasvi jaiswal</t>
+        </is>
+      </c>
+      <c r="B178" t="n">
+        <v>312</v>
+      </c>
+      <c r="C178" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
           <t>yuzvendra chahal</t>
         </is>
       </c>
-      <c r="B177" t="n">
-        <v>0</v>
-      </c>
-      <c r="C177" t="n">
+      <c r="B179" t="n">
+        <v>0</v>
+      </c>
+      <c r="C179" t="n">
         <v>7</v>
       </c>
     </row>
@@ -10635,7 +10661,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K39"/>
+  <dimension ref="A1:K38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11773,7 +11799,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Ramkrishna Ghosh</t>
+          <t>Azmatullah Omarzai</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -11783,13 +11809,13 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>angkrish raghuvanshi</t>
+          <t>mitchell marsh</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -11816,23 +11842,23 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Azmatullah Omarzai</t>
+          <t>akshat raghuwanshi</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>HARSH11</t>
+          <t>AMEY11</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>mitchell marsh</t>
+          <t>angkrish raghuvanshi</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -11859,7 +11885,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>akshat raghuwanshi</t>
+          <t>Suryansh Shegde</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -11875,7 +11901,7 @@
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
-          <t>angkrish raghuvanshi</t>
+          <t>suryansh shedge</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -11902,7 +11928,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Suryansh Shegde</t>
+          <t>Tejasvi Singh</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -11918,7 +11944,7 @@
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
-          <t>suryansh shedge</t>
+          <t>prabhsimran singh</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -11945,7 +11971,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Tejasvi Singh</t>
+          <t>Sai Kishor</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -11955,13 +11981,13 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
-          <t>prabhsimran singh</t>
+          <t>ishan kishan</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -11988,7 +12014,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Sai Kishor</t>
+          <t>Akash Deep</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -12004,7 +12030,7 @@
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
-          <t>ishan kishan</t>
+          <t>arshdeep singh</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -12031,23 +12057,23 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Akash Deep</t>
+          <t>Ben Duckett</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>AMEY11</t>
+          <t>PRATIK11</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>arshdeep singh</t>
+          <t>ryan rickelton</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -12074,7 +12100,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Ben Duckett</t>
+          <t>Rahul Tripathi</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -12090,7 +12116,7 @@
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
-          <t>ryan rickelton</t>
+          <t>rahul tewatia</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -12117,7 +12143,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Rahul Tripathi</t>
+          <t>Dre Pretorius</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -12133,7 +12159,7 @@
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
-          <t>rahul tewatia</t>
+          <t>lhuan dre pretorius</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -12160,7 +12186,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Dre Pretorius</t>
+          <t>Matthew Breetzke</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -12176,7 +12202,7 @@
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
-          <t>lhuan dre pretorius</t>
+          <t>matt henry</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -12203,7 +12229,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Matthew Breetzke</t>
+          <t>Anuj Rawat</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -12219,7 +12245,7 @@
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
-          <t>matt henry</t>
+          <t>mayank rawat</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -12246,7 +12272,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Anuj Rawat</t>
+          <t>Wanindu Hasaranga</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -12256,13 +12282,13 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
-          <t>mayank rawat</t>
+          <t>sandeep sharma</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -12283,49 +12309,6 @@
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>Wanindu Hasaranga</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>PRATIK11</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>AR</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr"/>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>sandeep sharma</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>no_stats_yet</t>
-        </is>
-      </c>
-      <c r="G39" t="n">
-        <v>0</v>
-      </c>
-      <c r="H39" t="n">
-        <v>0</v>
-      </c>
-      <c r="I39" t="n">
-        <v>0</v>
-      </c>
-      <c r="J39" t="n">
-        <v>0</v>
-      </c>
-      <c r="K39" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12411,7 +12394,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K3"/>
+  <dimension ref="A1:K4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12517,12 +12500,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Abhishek Porel</t>
+          <t>Ramkrishna Ghosh</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>PRATIK11</t>
+          <t>HARSH11</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -12532,7 +12515,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>abishek porel</t>
+          <t>ramakrishna ghosh</t>
         </is>
       </c>
       <c r="E3" t="inlineStr"/>
@@ -12542,18 +12525,61 @@
         </is>
       </c>
       <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Abhishek Porel</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>PRATIK11</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>BAT</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>abishek porel</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>ai_structured</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
         <v>30</v>
       </c>
-      <c r="H3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" t="n">
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
         <v>30</v>
       </c>
-      <c r="J3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K3" t="n">
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
         <v>30</v>
       </c>
     </row>

--- a/IPL_Fantasy_Points.xlsx
+++ b/IPL_Fantasy_Points.xlsx
@@ -604,19 +604,19 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>262</v>
+        <v>323</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>262</v>
+        <v>323</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>262</v>
+        <v>323</v>
       </c>
     </row>
     <row r="5">
@@ -862,19 +862,19 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="H10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I10" t="n">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="J10" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="K10" t="n">
-        <v>236</v>
+        <v>259</v>
       </c>
     </row>
     <row r="11">
@@ -951,16 +951,16 @@
         <v>39</v>
       </c>
       <c r="H12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I12" t="n">
         <v>39</v>
       </c>
       <c r="J12" t="n">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="K12" t="n">
-        <v>139</v>
+        <v>159</v>
       </c>
     </row>
     <row r="13">
@@ -994,16 +994,16 @@
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>180</v>
+        <v>220</v>
       </c>
       <c r="K13" t="n">
-        <v>180</v>
+        <v>220</v>
       </c>
     </row>
     <row r="14">
@@ -1206,19 +1206,19 @@
         </is>
       </c>
       <c r="G18" t="n">
-        <v>312</v>
+        <v>354</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>312</v>
+        <v>354</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>312</v>
+        <v>354</v>
       </c>
     </row>
     <row r="19">
@@ -1249,19 +1249,19 @@
         </is>
       </c>
       <c r="G19" t="n">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>373</v>
+        <v>378</v>
       </c>
     </row>
     <row r="20">
@@ -1292,19 +1292,19 @@
         </is>
       </c>
       <c r="G20" t="n">
-        <v>162</v>
+        <v>205</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>162</v>
+        <v>205</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>162</v>
+        <v>205</v>
       </c>
     </row>
     <row r="21">
@@ -1439,7 +1439,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>jacob bethel</t>
+          <t>jacob bethell</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1452,31 +1452,31 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t>jacob bethell</t>
         </is>
       </c>
+      <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
-          <t>no_stats_yet</t>
+          <t>exact/alias</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
     </row>
     <row r="25">
@@ -1550,19 +1550,19 @@
         </is>
       </c>
       <c r="G26" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
     </row>
     <row r="27">
@@ -1593,19 +1593,19 @@
         </is>
       </c>
       <c r="G27" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="H27" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="I27" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="J27" t="n">
-        <v>60</v>
+        <v>140</v>
       </c>
       <c r="K27" t="n">
-        <v>95</v>
+        <v>180</v>
       </c>
     </row>
     <row r="28">
@@ -2023,19 +2023,19 @@
         </is>
       </c>
       <c r="G37" t="n">
-        <v>414</v>
+        <v>425</v>
       </c>
       <c r="H37" t="n">
         <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>414</v>
+        <v>425</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>414</v>
+        <v>425</v>
       </c>
     </row>
     <row r="38">
@@ -2127,7 +2127,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Tim Siefert</t>
+          <t>Tim Seifert</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2140,31 +2140,31 @@
           <t>BAT</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr"/>
-      <c r="E40" t="inlineStr">
+      <c r="D40" t="inlineStr">
         <is>
           <t>tim seifert</t>
         </is>
       </c>
+      <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr">
         <is>
-          <t>no_stats_yet</t>
+          <t>exact/alias</t>
         </is>
       </c>
       <c r="G40" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="H40" t="n">
         <v>0</v>
       </c>
       <c r="I40" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
     </row>
     <row r="41">
@@ -2367,19 +2367,19 @@
         </is>
       </c>
       <c r="G45" t="n">
-        <v>110</v>
+        <v>150</v>
       </c>
       <c r="H45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I45" t="n">
-        <v>110</v>
+        <v>150</v>
       </c>
       <c r="J45" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K45" t="n">
-        <v>110</v>
+        <v>170</v>
       </c>
     </row>
     <row r="46">
@@ -3055,19 +3055,19 @@
         </is>
       </c>
       <c r="G61" t="n">
-        <v>215</v>
+        <v>237</v>
       </c>
       <c r="H61" t="n">
         <v>0</v>
       </c>
       <c r="I61" t="n">
-        <v>215</v>
+        <v>237</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
       </c>
       <c r="K61" t="n">
-        <v>215</v>
+        <v>237</v>
       </c>
     </row>
     <row r="62">
@@ -3187,16 +3187,16 @@
         <v>35</v>
       </c>
       <c r="H64" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I64" t="n">
         <v>35</v>
       </c>
       <c r="J64" t="n">
-        <v>200</v>
+        <v>220</v>
       </c>
       <c r="K64" t="n">
-        <v>235</v>
+        <v>255</v>
       </c>
     </row>
     <row r="65">
@@ -3261,7 +3261,7 @@
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr">
         <is>
-          <t>rashid khan</t>
+          <t>ravichandran smaran</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -3359,16 +3359,16 @@
         <v>0</v>
       </c>
       <c r="H68" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="I68" t="n">
         <v>0</v>
       </c>
       <c r="J68" t="n">
-        <v>140</v>
+        <v>200</v>
       </c>
       <c r="K68" t="n">
-        <v>140</v>
+        <v>200</v>
       </c>
     </row>
     <row r="69">
@@ -3571,19 +3571,19 @@
         </is>
       </c>
       <c r="G73" t="n">
-        <v>328</v>
+        <v>385</v>
       </c>
       <c r="H73" t="n">
         <v>0</v>
       </c>
       <c r="I73" t="n">
-        <v>328</v>
+        <v>385</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
       </c>
       <c r="K73" t="n">
-        <v>328</v>
+        <v>385</v>
       </c>
     </row>
     <row r="74">
@@ -3614,19 +3614,19 @@
         </is>
       </c>
       <c r="G74" t="n">
-        <v>346</v>
+        <v>361</v>
       </c>
       <c r="H74" t="n">
         <v>0</v>
       </c>
       <c r="I74" t="n">
-        <v>346</v>
+        <v>361</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
       </c>
       <c r="K74" t="n">
-        <v>346</v>
+        <v>361</v>
       </c>
     </row>
     <row r="75">
@@ -3657,19 +3657,19 @@
         </is>
       </c>
       <c r="G75" t="n">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="H75" t="n">
         <v>0</v>
       </c>
       <c r="I75" t="n">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
       </c>
       <c r="K75" t="n">
-        <v>283</v>
+        <v>285</v>
       </c>
     </row>
     <row r="76">
@@ -3872,19 +3872,19 @@
         </is>
       </c>
       <c r="G80" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H80" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I80" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J80" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="K80" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
     </row>
     <row r="81">
@@ -4044,19 +4044,19 @@
         </is>
       </c>
       <c r="G84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H84" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I84" t="n">
         <v>0</v>
       </c>
       <c r="J84" t="n">
-        <v>160</v>
+        <v>200</v>
       </c>
       <c r="K84" t="n">
-        <v>160</v>
+        <v>200</v>
       </c>
     </row>
     <row r="85">
@@ -4148,7 +4148,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Auqib Dar</t>
+          <t>Auqib Nabi</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -4161,19 +4161,19 @@
           <t>BOWL</t>
         </is>
       </c>
-      <c r="D87" t="inlineStr"/>
-      <c r="E87" t="inlineStr">
+      <c r="D87" t="inlineStr">
         <is>
           <t>auqib nabi</t>
         </is>
       </c>
+      <c r="E87" t="inlineStr"/>
       <c r="F87" t="inlineStr">
         <is>
-          <t>no_stats_yet</t>
+          <t>exact/alias</t>
         </is>
       </c>
       <c r="G87" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H87" t="n">
         <v>0</v>
@@ -4388,19 +4388,19 @@
         </is>
       </c>
       <c r="G92" t="n">
-        <v>309</v>
+        <v>328</v>
       </c>
       <c r="H92" t="n">
         <v>0</v>
       </c>
       <c r="I92" t="n">
-        <v>309</v>
+        <v>328</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
       </c>
       <c r="K92" t="n">
-        <v>309</v>
+        <v>328</v>
       </c>
     </row>
     <row r="93">
@@ -4431,19 +4431,19 @@
         </is>
       </c>
       <c r="G93" t="n">
-        <v>309</v>
+        <v>335</v>
       </c>
       <c r="H93" t="n">
         <v>0</v>
       </c>
       <c r="I93" t="n">
-        <v>309</v>
+        <v>335</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
       </c>
       <c r="K93" t="n">
-        <v>309</v>
+        <v>335</v>
       </c>
     </row>
     <row r="94">
@@ -4548,31 +4548,31 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="D96" t="inlineStr"/>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>shashank singh</t>
-        </is>
-      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>nishant sindhu</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr"/>
       <c r="F96" t="inlineStr">
         <is>
-          <t>no_stats_yet</t>
+          <t>exact/alias</t>
         </is>
       </c>
       <c r="G96" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="H96" t="n">
         <v>0</v>
       </c>
       <c r="I96" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
       </c>
       <c r="K96" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
     </row>
     <row r="97">
@@ -4778,16 +4778,16 @@
         <v>35</v>
       </c>
       <c r="H101" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I101" t="n">
         <v>0</v>
       </c>
       <c r="J101" t="n">
-        <v>280</v>
+        <v>320</v>
       </c>
       <c r="K101" t="n">
-        <v>280</v>
+        <v>320</v>
       </c>
     </row>
     <row r="102">
@@ -5236,15 +5236,15 @@
           <t>BAT</t>
         </is>
       </c>
-      <c r="D112" t="inlineStr"/>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>hardik pandya</t>
-        </is>
-      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>manish pandey</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr"/>
       <c r="F112" t="inlineStr">
         <is>
-          <t>no_stats_yet</t>
+          <t>exact/alias</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -5463,7 +5463,7 @@
         </is>
       </c>
       <c r="G117" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="H117" t="n">
         <v>0</v>
@@ -5509,16 +5509,16 @@
         <v>11</v>
       </c>
       <c r="H118" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I118" t="n">
         <v>0</v>
       </c>
       <c r="J118" t="n">
-        <v>180</v>
+        <v>220</v>
       </c>
       <c r="K118" t="n">
-        <v>180</v>
+        <v>220</v>
       </c>
     </row>
     <row r="119">
@@ -5592,19 +5592,19 @@
         </is>
       </c>
       <c r="G120" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H120" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I120" t="n">
         <v>0</v>
       </c>
       <c r="J120" t="n">
-        <v>120</v>
+        <v>160</v>
       </c>
       <c r="K120" t="n">
-        <v>120</v>
+        <v>160</v>
       </c>
     </row>
     <row r="121">
@@ -6194,19 +6194,19 @@
         </is>
       </c>
       <c r="G134" t="n">
-        <v>209</v>
+        <v>268</v>
       </c>
       <c r="H134" t="n">
         <v>0</v>
       </c>
       <c r="I134" t="n">
-        <v>209</v>
+        <v>268</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
       </c>
       <c r="K134" t="n">
-        <v>209</v>
+        <v>268</v>
       </c>
     </row>
     <row r="135">
@@ -6280,19 +6280,19 @@
         </is>
       </c>
       <c r="G136" t="n">
-        <v>169</v>
+        <v>209</v>
       </c>
       <c r="H136" t="n">
         <v>1</v>
       </c>
       <c r="I136" t="n">
-        <v>169</v>
+        <v>209</v>
       </c>
       <c r="J136" t="n">
         <v>20</v>
       </c>
       <c r="K136" t="n">
-        <v>189</v>
+        <v>229</v>
       </c>
     </row>
     <row r="137">
@@ -6409,19 +6409,19 @@
         </is>
       </c>
       <c r="G139" t="n">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="H139" t="n">
         <v>0</v>
       </c>
       <c r="I139" t="n">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
       </c>
       <c r="K139" t="n">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
     <row r="140">
@@ -6796,19 +6796,19 @@
         </is>
       </c>
       <c r="G148" t="n">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="H148" t="n">
         <v>0</v>
       </c>
       <c r="I148" t="n">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
       </c>
       <c r="K148" t="n">
-        <v>73</v>
+        <v>79</v>
       </c>
     </row>
     <row r="149">
@@ -6900,7 +6900,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Suryansh Shegde</t>
+          <t>Suryansh Shedge</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -6913,31 +6913,31 @@
           <t>BAT</t>
         </is>
       </c>
-      <c r="D151" t="inlineStr"/>
-      <c r="E151" t="inlineStr">
+      <c r="D151" t="inlineStr">
         <is>
           <t>suryansh shedge</t>
         </is>
       </c>
+      <c r="E151" t="inlineStr"/>
       <c r="F151" t="inlineStr">
         <is>
-          <t>no_stats_yet</t>
+          <t>exact/alias</t>
         </is>
       </c>
       <c r="G151" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="H151" t="n">
         <v>0</v>
       </c>
       <c r="I151" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
       </c>
       <c r="K151" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="152">
@@ -7229,16 +7229,16 @@
         <v>1</v>
       </c>
       <c r="H158" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I158" t="n">
         <v>0</v>
       </c>
       <c r="J158" t="n">
-        <v>180</v>
+        <v>200</v>
       </c>
       <c r="K158" t="n">
-        <v>180</v>
+        <v>200</v>
       </c>
     </row>
     <row r="159">
@@ -7398,19 +7398,19 @@
         </is>
       </c>
       <c r="G162" t="n">
-        <v>425</v>
+        <v>440</v>
       </c>
       <c r="H162" t="n">
         <v>0</v>
       </c>
       <c r="I162" t="n">
-        <v>425</v>
+        <v>440</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
       </c>
       <c r="K162" t="n">
-        <v>425</v>
+        <v>440</v>
       </c>
     </row>
     <row r="163">
@@ -7570,19 +7570,19 @@
         </is>
       </c>
       <c r="G166" t="n">
-        <v>81</v>
+        <v>110</v>
       </c>
       <c r="H166" t="n">
         <v>0</v>
       </c>
       <c r="I166" t="n">
-        <v>81</v>
+        <v>110</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
       </c>
       <c r="K166" t="n">
-        <v>81</v>
+        <v>110</v>
       </c>
     </row>
     <row r="167">
@@ -7785,19 +7785,19 @@
         </is>
       </c>
       <c r="G171" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="H171" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I171" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="J171" t="n">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="K171" t="n">
-        <v>110</v>
+        <v>150</v>
       </c>
     </row>
     <row r="172">
@@ -7831,16 +7831,16 @@
         <v>40</v>
       </c>
       <c r="H172" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I172" t="n">
         <v>40</v>
       </c>
       <c r="J172" t="n">
-        <v>140</v>
+        <v>180</v>
       </c>
       <c r="K172" t="n">
-        <v>180</v>
+        <v>220</v>
       </c>
     </row>
     <row r="173">
@@ -7862,7 +7862,7 @@
       <c r="D173" t="inlineStr"/>
       <c r="E173" t="inlineStr">
         <is>
-          <t>sandeep sharma</t>
+          <t>ravichandran smaran</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
@@ -8185,7 +8185,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2902</v>
+        <v>3046</v>
       </c>
     </row>
     <row r="3">
@@ -8198,7 +8198,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2621</v>
+        <v>2837</v>
       </c>
     </row>
     <row r="4">
@@ -8211,7 +8211,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2425</v>
+        <v>2525</v>
       </c>
     </row>
     <row r="5">
@@ -8224,7 +8224,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2321</v>
+        <v>2423</v>
       </c>
     </row>
     <row r="6">
@@ -8237,7 +8237,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2289</v>
+        <v>2375</v>
       </c>
     </row>
     <row r="7">
@@ -8250,7 +8250,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2203</v>
+        <v>2283</v>
       </c>
     </row>
     <row r="8">
@@ -8263,7 +8263,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2037</v>
+        <v>2181</v>
       </c>
     </row>
     <row r="9">
@@ -8276,7 +8276,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1947</v>
+        <v>2048</v>
       </c>
     </row>
     <row r="10">
@@ -8289,7 +8289,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1898</v>
+        <v>1988</v>
       </c>
     </row>
     <row r="11">
@@ -8302,7 +8302,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1547</v>
+        <v>1671</v>
       </c>
     </row>
   </sheetData>
@@ -8316,7 +8316,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C179"/>
+  <dimension ref="A1:C182"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8369,7 +8369,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>425</v>
+        <v>440</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
@@ -8408,7 +8408,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>162</v>
+        <v>205</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
@@ -8447,7 +8447,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>209</v>
+        <v>268</v>
       </c>
       <c r="C10" t="n">
         <v>0</v>
@@ -8460,7 +8460,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="C11" t="n">
         <v>0</v>
@@ -8502,7 +8502,7 @@
         <v>39</v>
       </c>
       <c r="C14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15">
@@ -8512,7 +8512,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="C15" t="n">
         <v>5</v>
@@ -8525,10 +8525,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="17">
@@ -8642,7 +8642,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>328</v>
+        <v>385</v>
       </c>
       <c r="C25" t="n">
         <v>0</v>
@@ -8694,10 +8694,10 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="C29" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="30">
@@ -8889,7 +8889,7 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C44" t="n">
         <v>15</v>
@@ -8902,7 +8902,7 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>81</v>
+        <v>110</v>
       </c>
       <c r="C45" t="n">
         <v>0</v>
@@ -8993,7 +8993,7 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="C52" t="n">
         <v>0</v>
@@ -9006,7 +9006,7 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>414</v>
+        <v>425</v>
       </c>
       <c r="C53" t="n">
         <v>0</v>
@@ -9032,7 +9032,7 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>312</v>
+        <v>354</v>
       </c>
       <c r="C55" t="n">
         <v>0</v>
@@ -9084,10 +9084,10 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="C59" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="60">
@@ -9149,7 +9149,7 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>309</v>
+        <v>335</v>
       </c>
       <c r="C64" t="n">
         <v>0</v>
@@ -9178,7 +9178,7 @@
         <v>35</v>
       </c>
       <c r="C66" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="67">
@@ -9204,7 +9204,7 @@
         <v>11</v>
       </c>
       <c r="C68" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="69">
@@ -9392,63 +9392,63 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>marco jansen</t>
+          <t>manish pandey</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="C83" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>marcus stoinis</t>
+          <t>marco jansen</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>110</v>
+        <v>30</v>
       </c>
       <c r="C84" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>matt henry</t>
+          <t>marcus stoinis</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>7</v>
+        <v>150</v>
       </c>
       <c r="C85" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>matt short</t>
+          <t>matt henry</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>36</v>
+        <v>7</v>
       </c>
       <c r="C86" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>mayank markande</t>
+          <t>matt short</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="C87" t="n">
         <v>0</v>
@@ -9457,7 +9457,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>mayank rawat</t>
+          <t>mayank markande</t>
         </is>
       </c>
       <c r="B88" t="n">
@@ -9470,11 +9470,11 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>mayank yadav</t>
+          <t>mayank rawat</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C89" t="n">
         <v>0</v>
@@ -9483,11 +9483,11 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>mitchell marsh</t>
+          <t>mayank yadav</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>212</v>
+        <v>5</v>
       </c>
       <c r="C90" t="n">
         <v>0</v>
@@ -9496,115 +9496,115 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>mitchell santner</t>
+          <t>mitchell marsh</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>26</v>
+        <v>212</v>
       </c>
       <c r="C91" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>mitchell starc</t>
+          <t>mitchell santner</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="C92" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>mohammed shami</t>
+          <t>mitchell starc</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="C93" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>mohammed siraj</t>
+          <t>mohammed shami</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="C94" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>mohsin khan</t>
+          <t>mohammed siraj</t>
         </is>
       </c>
       <c r="B95" t="n">
         <v>0</v>
       </c>
       <c r="C95" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>mukesh choudhary</t>
+          <t>mohsin khan</t>
         </is>
       </c>
       <c r="B96" t="n">
         <v>0</v>
       </c>
       <c r="C96" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>mukesh kumar</t>
+          <t>mukesh choudhary</t>
         </is>
       </c>
       <c r="B97" t="n">
         <v>0</v>
       </c>
       <c r="C97" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>mukul choudhary</t>
+          <t>mukesh kumar</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>156</v>
+        <v>0</v>
       </c>
       <c r="C98" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>naman dhir</t>
+          <t>mukul choudhary</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>233</v>
+        <v>156</v>
       </c>
       <c r="C99" t="n">
         <v>0</v>
@@ -9613,37 +9613,37 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>nandre burger</t>
+          <t>naman dhir</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>3</v>
+        <v>233</v>
       </c>
       <c r="C100" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>navdeep saini</t>
+          <t>nandre burger</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C101" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>nehal wadhera</t>
+          <t>navdeep saini</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="C102" t="n">
         <v>0</v>
@@ -9652,11 +9652,11 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>nicholas pooran</t>
+          <t>nehal wadhera</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>82</v>
+        <v>65</v>
       </c>
       <c r="C103" t="n">
         <v>0</v>
@@ -9665,24 +9665,24 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>nitish kumar reddy</t>
+          <t>nicholas pooran</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>193</v>
+        <v>82</v>
       </c>
       <c r="C104" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>nitish rana</t>
+          <t>nishant sindhu</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>202</v>
+        <v>15</v>
       </c>
       <c r="C105" t="n">
         <v>0</v>
@@ -9691,63 +9691,63 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>noor ahmad</t>
+          <t>nitish kumar reddy</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>10</v>
+        <v>193</v>
       </c>
       <c r="C106" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>pat cummins</t>
+          <t>nitish rana</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>0</v>
+        <v>202</v>
       </c>
       <c r="C107" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>pathum nissanka</t>
+          <t>noor ahmad</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>209</v>
+        <v>10</v>
       </c>
       <c r="C108" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>philip salt</t>
+          <t>pat cummins</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>202</v>
+        <v>10</v>
       </c>
       <c r="C109" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>prabhsimran singh</t>
+          <t>pathum nissanka</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>346</v>
+        <v>209</v>
       </c>
       <c r="C110" t="n">
         <v>0</v>
@@ -9756,24 +9756,24 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>praful hinge</t>
+          <t>philip salt</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>0</v>
+        <v>202</v>
       </c>
       <c r="C111" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>prashant veer</t>
+          <t>prabhsimran singh</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>49</v>
+        <v>361</v>
       </c>
       <c r="C112" t="n">
         <v>0</v>
@@ -9782,63 +9782,63 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>prasidh krishna</t>
+          <t>praful hinge</t>
         </is>
       </c>
       <c r="B113" t="n">
         <v>0</v>
       </c>
       <c r="C113" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>prince yadav</t>
+          <t>prashant veer</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="C114" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>priyansh arya</t>
+          <t>prasidh krishna</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>283</v>
+        <v>0</v>
       </c>
       <c r="C115" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>quinton de kock</t>
+          <t>prince yadav</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>132</v>
+        <v>0</v>
       </c>
       <c r="C116" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>raghu sharma</t>
+          <t>priyansh arya</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>0</v>
+        <v>285</v>
       </c>
       <c r="C117" t="n">
         <v>0</v>
@@ -9847,11 +9847,11 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>rahul chahar</t>
+          <t>quinton de kock</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>0</v>
+        <v>132</v>
       </c>
       <c r="C118" t="n">
         <v>0</v>
@@ -9860,11 +9860,11 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>rahul tewatia</t>
+          <t>raghu sharma</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>76</v>
+        <v>0</v>
       </c>
       <c r="C119" t="n">
         <v>0</v>
@@ -9873,11 +9873,11 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>rajat patidar</t>
+          <t>rahul chahar</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>257</v>
+        <v>0</v>
       </c>
       <c r="C120" t="n">
         <v>0</v>
@@ -9886,63 +9886,63 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>ramakrishna ghosh</t>
+          <t>rahul tewatia</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="C121" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>ramandeep singh</t>
+          <t>rajat patidar</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>82</v>
+        <v>257</v>
       </c>
       <c r="C122" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>rashid khan</t>
+          <t>ramakrishna ghosh</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="C123" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>rasikh salam</t>
+          <t>ramandeep singh</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="C124" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>ravi bishnoi</t>
+          <t>rashid khan</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="C125" t="n">
         <v>11</v>
@@ -9951,37 +9951,37 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>ravindra jadeja</t>
+          <t>rasikh salam</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>152</v>
+        <v>0</v>
       </c>
       <c r="C126" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>rinku singh</t>
+          <t>ravi bishnoi</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="C127" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>rishabh pant</t>
+          <t>ravichandran smaran</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>189</v>
+        <v>4</v>
       </c>
       <c r="C128" t="n">
         <v>0</v>
@@ -9990,24 +9990,24 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>riyan parag</t>
+          <t>ravindra jadeja</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>207</v>
+        <v>152</v>
       </c>
       <c r="C129" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>robin minz</t>
+          <t>rinku singh</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>6</v>
+        <v>237</v>
       </c>
       <c r="C130" t="n">
         <v>0</v>
@@ -10016,11 +10016,11 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>rohit sharma</t>
+          <t>rishabh pant</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>137</v>
+        <v>189</v>
       </c>
       <c r="C131" t="n">
         <v>0</v>
@@ -10029,24 +10029,24 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>romario shepherd</t>
+          <t>riyan parag</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>56</v>
+        <v>207</v>
       </c>
       <c r="C132" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>rovman powell</t>
+          <t>robin minz</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>121</v>
+        <v>6</v>
       </c>
       <c r="C133" t="n">
         <v>0</v>
@@ -10055,11 +10055,11 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>ruturaj gaikwad</t>
+          <t>rohit sharma</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>245</v>
+        <v>137</v>
       </c>
       <c r="C134" t="n">
         <v>0</v>
@@ -10068,24 +10068,24 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>ryan rickelton</t>
+          <t>romario shepherd</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>297</v>
+        <v>56</v>
       </c>
       <c r="C135" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>sahil parakh</t>
+          <t>rovman powell</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>0</v>
+        <v>121</v>
       </c>
       <c r="C136" t="n">
         <v>0</v>
@@ -10094,24 +10094,24 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>sakib hussain</t>
+          <t>ruturaj gaikwad</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>0</v>
+        <v>245</v>
       </c>
       <c r="C137" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>salil arora</t>
+          <t>ryan rickelton</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>93</v>
+        <v>297</v>
       </c>
       <c r="C138" t="n">
         <v>0</v>
@@ -10120,11 +10120,11 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>sameer rizvi</t>
+          <t>sahil parakh</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>209</v>
+        <v>0</v>
       </c>
       <c r="C139" t="n">
         <v>0</v>
@@ -10133,24 +10133,24 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>sandeep sharma</t>
+          <t>sakib hussain</t>
         </is>
       </c>
       <c r="B140" t="n">
         <v>0</v>
       </c>
       <c r="C140" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>sanju samson</t>
+          <t>salil arora</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>315</v>
+        <v>95</v>
       </c>
       <c r="C141" t="n">
         <v>0</v>
@@ -10159,11 +10159,11 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>sarfaraz khan</t>
+          <t>sameer rizvi</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>161</v>
+        <v>209</v>
       </c>
       <c r="C142" t="n">
         <v>0</v>
@@ -10172,24 +10172,24 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>shahbaz ahmed</t>
+          <t>sandeep sharma</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="C143" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>shahrukh khan</t>
+          <t>sanju samson</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>43</v>
+        <v>315</v>
       </c>
       <c r="C144" t="n">
         <v>0</v>
@@ -10198,37 +10198,37 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>shardul thakur</t>
+          <t>sarfaraz khan</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>14</v>
+        <v>161</v>
       </c>
       <c r="C145" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>shashank singh</t>
+          <t>shahbaz ahmed</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>70</v>
+        <v>15</v>
       </c>
       <c r="C146" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>sherfane rutherford</t>
+          <t>shahrukh khan</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>103</v>
+        <v>43</v>
       </c>
       <c r="C147" t="n">
         <v>0</v>
@@ -10237,50 +10237,50 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>shimron hetmyer</t>
+          <t>shardul thakur</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>72</v>
+        <v>14</v>
       </c>
       <c r="C148" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>shivam dube</t>
+          <t>shashank singh</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>150</v>
+        <v>70</v>
       </c>
       <c r="C149" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>shivang kumar</t>
+          <t>sherfane rutherford</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>21</v>
+        <v>103</v>
       </c>
       <c r="C150" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>shreyas iyer</t>
+          <t>shimron hetmyer</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>309</v>
+        <v>72</v>
       </c>
       <c r="C151" t="n">
         <v>0</v>
@@ -10289,50 +10289,50 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>shubham badriprasad dubey</t>
+          <t>shivam dube</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>56</v>
+        <v>150</v>
       </c>
       <c r="C152" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>shubman gill</t>
+          <t>shivang kumar</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>373</v>
+        <v>22</v>
       </c>
       <c r="C153" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>sunil narine</t>
+          <t>shreyas iyer</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>40</v>
+        <v>328</v>
       </c>
       <c r="C154" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>suryakumar yadav</t>
+          <t>shubham badriprasad dubey</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>183</v>
+        <v>56</v>
       </c>
       <c r="C155" t="n">
         <v>0</v>
@@ -10341,11 +10341,11 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>suryansh shedge</t>
+          <t>shubman gill</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>3</v>
+        <v>378</v>
       </c>
       <c r="C156" t="n">
         <v>0</v>
@@ -10354,37 +10354,37 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>suyash sharma</t>
+          <t>sunil narine</t>
         </is>
       </c>
       <c r="B157" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="C157" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>t natarajan</t>
+          <t>suryakumar yadav</t>
         </is>
       </c>
       <c r="B158" t="n">
-        <v>1</v>
+        <v>183</v>
       </c>
       <c r="C158" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>tilak varma</t>
+          <t>suryansh shedge</t>
         </is>
       </c>
       <c r="B159" t="n">
-        <v>193</v>
+        <v>60</v>
       </c>
       <c r="C159" t="n">
         <v>0</v>
@@ -10393,37 +10393,37 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>tim david</t>
+          <t>suyash sharma</t>
         </is>
       </c>
       <c r="B160" t="n">
-        <v>192</v>
+        <v>0</v>
       </c>
       <c r="C160" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>tim seifert</t>
+          <t>t natarajan</t>
         </is>
       </c>
       <c r="B161" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="C161" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>travis head</t>
+          <t>tilak varma</t>
         </is>
       </c>
       <c r="B162" t="n">
-        <v>262</v>
+        <v>193</v>
       </c>
       <c r="C162" t="n">
         <v>0</v>
@@ -10432,24 +10432,24 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>trent boult</t>
+          <t>tim david</t>
         </is>
       </c>
       <c r="B163" t="n">
-        <v>8</v>
+        <v>192</v>
       </c>
       <c r="C163" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>tristan stubbs</t>
+          <t>tim seifert</t>
         </is>
       </c>
       <c r="B164" t="n">
-        <v>219</v>
+        <v>19</v>
       </c>
       <c r="C164" t="n">
         <v>0</v>
@@ -10458,115 +10458,115 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>tushar deshpande</t>
+          <t>travis head</t>
         </is>
       </c>
       <c r="B165" t="n">
-        <v>25</v>
+        <v>323</v>
       </c>
       <c r="C165" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>urvil patel</t>
+          <t>trent boult</t>
         </is>
       </c>
       <c r="B166" t="n">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="C166" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>vaibhav arora</t>
+          <t>tristan stubbs</t>
         </is>
       </c>
       <c r="B167" t="n">
-        <v>1</v>
+        <v>219</v>
       </c>
       <c r="C167" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>vaibhav suryavanshi</t>
+          <t>tushar deshpande</t>
         </is>
       </c>
       <c r="B168" t="n">
-        <v>404</v>
+        <v>25</v>
       </c>
       <c r="C168" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>varun chakravarthy</t>
+          <t>urvil patel</t>
         </is>
       </c>
       <c r="B169" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="C169" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>venkatesh iyer</t>
+          <t>vaibhav arora</t>
         </is>
       </c>
       <c r="B170" t="n">
-        <v>41</v>
+        <v>1</v>
       </c>
       <c r="C170" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>vijaykumar vyshak</t>
+          <t>vaibhav suryavanshi</t>
         </is>
       </c>
       <c r="B171" t="n">
-        <v>0</v>
+        <v>404</v>
       </c>
       <c r="C171" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>vipraj nigam</t>
+          <t>varun chakravarthy</t>
         </is>
       </c>
       <c r="B172" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="C172" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>virat kohli</t>
+          <t>venkatesh iyer</t>
         </is>
       </c>
       <c r="B173" t="n">
-        <v>379</v>
+        <v>41</v>
       </c>
       <c r="C173" t="n">
         <v>0</v>
@@ -10575,63 +10575,63 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>washington sundar</t>
+          <t>vijaykumar vyshak</t>
         </is>
       </c>
       <c r="B174" t="n">
-        <v>169</v>
+        <v>1</v>
       </c>
       <c r="C174" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>will jacks</t>
+          <t>vipraj nigam</t>
         </is>
       </c>
       <c r="B175" t="n">
-        <v>47</v>
+        <v>12</v>
       </c>
       <c r="C175" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>xavier bartlett</t>
+          <t>virat kohli</t>
         </is>
       </c>
       <c r="B176" t="n">
-        <v>11</v>
+        <v>379</v>
       </c>
       <c r="C176" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>yash raj punja</t>
+          <t>washington sundar</t>
         </is>
       </c>
       <c r="B177" t="n">
-        <v>0</v>
+        <v>209</v>
       </c>
       <c r="C177" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>yashasvi jaiswal</t>
+          <t>will jacks</t>
         </is>
       </c>
       <c r="B178" t="n">
-        <v>312</v>
+        <v>47</v>
       </c>
       <c r="C178" t="n">
         <v>0</v>
@@ -10640,13 +10640,52 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
+          <t>xavier bartlett</t>
+        </is>
+      </c>
+      <c r="B179" t="n">
+        <v>11</v>
+      </c>
+      <c r="C179" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>yash raj punja</t>
+        </is>
+      </c>
+      <c r="B180" t="n">
+        <v>0</v>
+      </c>
+      <c r="C180" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>yashasvi jaiswal</t>
+        </is>
+      </c>
+      <c r="B181" t="n">
+        <v>312</v>
+      </c>
+      <c r="C181" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
           <t>yuzvendra chahal</t>
         </is>
       </c>
-      <c r="B179" t="n">
-        <v>0</v>
-      </c>
-      <c r="C179" t="n">
+      <c r="B182" t="n">
+        <v>0</v>
+      </c>
+      <c r="C182" t="n">
         <v>7</v>
       </c>
     </row>
@@ -10661,7 +10700,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K38"/>
+  <dimension ref="A1:K32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10853,7 +10892,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>jacob bethel</t>
+          <t>kamindu mendis</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -10863,13 +10902,13 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>jacob bethell</t>
+          <t>karun nair</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -10896,7 +10935,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>kamindu mendis</t>
+          <t>Kuldeep sen</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -10912,7 +10951,7 @@
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>karun nair</t>
+          <t>kuldeep yadav</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -10939,23 +10978,23 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Kuldeep sen</t>
+          <t>Tom Banton</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>MEET11</t>
+          <t>VATSAL11</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>kuldeep yadav</t>
+          <t>t natarajan</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -10982,7 +11021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Tom Banton</t>
+          <t>Adam Milne</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -10992,13 +11031,13 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>t natarajan</t>
+          <t>david miller</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -11025,12 +11064,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Tim Siefert</t>
+          <t>Jos Inglis</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>VATSAL11</t>
+          <t>BABA11</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -11041,7 +11080,7 @@
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>tim seifert</t>
+          <t>marcus stoinis</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -11068,23 +11107,23 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Adam Milne</t>
+          <t>Prithvi Shaw</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>VATSAL11</t>
+          <t>BABA11</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>david miller</t>
+          <t>prasidh krishna</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -11111,7 +11150,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Jos Inglis</t>
+          <t>liam livingston</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -11121,13 +11160,13 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>marcus stoinis</t>
+          <t>liam livingstone</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -11154,7 +11193,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Prithvi Shaw</t>
+          <t>rachin ravindra</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -11164,13 +11203,13 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>prasidh krishna</t>
+          <t>ravichandran smaran</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -11197,7 +11236,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>liam livingston</t>
+          <t>Zeeshan Ansari</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -11207,13 +11246,13 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>liam livingstone</t>
+          <t>eshan malinga</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -11240,23 +11279,23 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>rachin ravindra</t>
+          <t>Mitchel Owen</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>BABA11</t>
+          <t>DIPESH11</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>rashid khan</t>
+          <t>mitchell santner</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -11283,23 +11322,23 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Zeeshan Ansari</t>
+          <t>Arshin Kulkarni</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>BABA11</t>
+          <t>NAKUL11</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>eshan malinga</t>
+          <t>ashwani kumar</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -11326,23 +11365,23 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Mitchel Owen</t>
+          <t>Jayant Yadav</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>DIPESH11</t>
+          <t>NAKUL11</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>mitchell santner</t>
+          <t>mayank yadav</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -11369,23 +11408,23 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Auqib Dar</t>
+          <t>Ajay Mandal</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>DIPESH11</t>
+          <t>NAKUL11</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>auqib nabi</t>
+          <t>rajat patidar</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -11412,7 +11451,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Arshin Kulkarni</t>
+          <t>Matheesha Pathirana</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -11422,13 +11461,13 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>ashwani kumar</t>
+          <t>eshan malinga</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -11455,7 +11494,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Nishant Sindhu</t>
+          <t>Ben Dwarshuis</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -11465,13 +11504,13 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>shashank singh</t>
+          <t>b sai sudharshan</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -11498,23 +11537,23 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Jayant Yadav</t>
+          <t>Arjun Tendulkar</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>NAKUL11</t>
+          <t>SKY11</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>mayank yadav</t>
+          <t>karun nair</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -11541,23 +11580,23 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Ajay Mandal</t>
+          <t>Kwena Maphaka</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>NAKUL11</t>
+          <t>SKY11</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>rajat patidar</t>
+          <t>aiden markram</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -11584,23 +11623,23 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Matheesha Pathirana</t>
+          <t>Azmatullah Omarzai</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>NAKUL11</t>
+          <t>HARSH11</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>eshan malinga</t>
+          <t>mitchell marsh</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -11627,23 +11666,23 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Ben Dwarshuis</t>
+          <t>akshat raghuwanshi</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>NAKUL11</t>
+          <t>AMEY11</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>b sai sudharshan</t>
+          <t>angkrish raghuvanshi</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -11670,12 +11709,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Manish Pandey</t>
+          <t>Tejasvi Singh</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>SKY11</t>
+          <t>AMEY11</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -11686,7 +11725,7 @@
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>hardik pandya</t>
+          <t>prabhsimran singh</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -11713,12 +11752,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Arjun Tendulkar</t>
+          <t>Sai Kishor</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>SKY11</t>
+          <t>AMEY11</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -11729,7 +11768,7 @@
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>karun nair</t>
+          <t>ishan kishan</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -11756,12 +11795,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Kwena Maphaka</t>
+          <t>Akash Deep</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>SKY11</t>
+          <t>AMEY11</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -11772,7 +11811,7 @@
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>aiden markram</t>
+          <t>arshdeep singh</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -11799,23 +11838,23 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Azmatullah Omarzai</t>
+          <t>Ben Duckett</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>HARSH11</t>
+          <t>PRATIK11</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>mitchell marsh</t>
+          <t>ryan rickelton</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -11842,12 +11881,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>akshat raghuwanshi</t>
+          <t>Rahul Tripathi</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>AMEY11</t>
+          <t>PRATIK11</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -11858,7 +11897,7 @@
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>angkrish raghuvanshi</t>
+          <t>rahul tewatia</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -11885,12 +11924,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Suryansh Shegde</t>
+          <t>Dre Pretorius</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>AMEY11</t>
+          <t>PRATIK11</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -11901,7 +11940,7 @@
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
-          <t>suryansh shedge</t>
+          <t>lhuan dre pretorius</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -11928,12 +11967,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Tejasvi Singh</t>
+          <t>Matthew Breetzke</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>AMEY11</t>
+          <t>PRATIK11</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -11944,7 +11983,7 @@
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
-          <t>prabhsimran singh</t>
+          <t>matt henry</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -11971,23 +12010,23 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Sai Kishor</t>
+          <t>Anuj Rawat</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>AMEY11</t>
+          <t>PRATIK11</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
-          <t>ishan kishan</t>
+          <t>mayank rawat</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -12014,23 +12053,23 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Akash Deep</t>
+          <t>Wanindu Hasaranga</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>AMEY11</t>
+          <t>PRATIK11</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
-          <t>arshdeep singh</t>
+          <t>ravichandran smaran</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -12051,264 +12090,6 @@
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Ben Duckett</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>PRATIK11</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>BAT</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>ryan rickelton</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>no_stats_yet</t>
-        </is>
-      </c>
-      <c r="G33" t="n">
-        <v>0</v>
-      </c>
-      <c r="H33" t="n">
-        <v>0</v>
-      </c>
-      <c r="I33" t="n">
-        <v>0</v>
-      </c>
-      <c r="J33" t="n">
-        <v>0</v>
-      </c>
-      <c r="K33" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Rahul Tripathi</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>PRATIK11</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>BAT</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>rahul tewatia</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>no_stats_yet</t>
-        </is>
-      </c>
-      <c r="G34" t="n">
-        <v>0</v>
-      </c>
-      <c r="H34" t="n">
-        <v>0</v>
-      </c>
-      <c r="I34" t="n">
-        <v>0</v>
-      </c>
-      <c r="J34" t="n">
-        <v>0</v>
-      </c>
-      <c r="K34" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Dre Pretorius</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>PRATIK11</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>BAT</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr"/>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>lhuan dre pretorius</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>no_stats_yet</t>
-        </is>
-      </c>
-      <c r="G35" t="n">
-        <v>0</v>
-      </c>
-      <c r="H35" t="n">
-        <v>0</v>
-      </c>
-      <c r="I35" t="n">
-        <v>0</v>
-      </c>
-      <c r="J35" t="n">
-        <v>0</v>
-      </c>
-      <c r="K35" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Matthew Breetzke</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>PRATIK11</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>BAT</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr"/>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>matt henry</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>no_stats_yet</t>
-        </is>
-      </c>
-      <c r="G36" t="n">
-        <v>0</v>
-      </c>
-      <c r="H36" t="n">
-        <v>0</v>
-      </c>
-      <c r="I36" t="n">
-        <v>0</v>
-      </c>
-      <c r="J36" t="n">
-        <v>0</v>
-      </c>
-      <c r="K36" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Anuj Rawat</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>PRATIK11</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>BAT</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr"/>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>mayank rawat</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>no_stats_yet</t>
-        </is>
-      </c>
-      <c r="G37" t="n">
-        <v>0</v>
-      </c>
-      <c r="H37" t="n">
-        <v>0</v>
-      </c>
-      <c r="I37" t="n">
-        <v>0</v>
-      </c>
-      <c r="J37" t="n">
-        <v>0</v>
-      </c>
-      <c r="K37" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>Wanindu Hasaranga</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>PRATIK11</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>AR</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr"/>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>sandeep sharma</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>no_stats_yet</t>
-        </is>
-      </c>
-      <c r="G38" t="n">
-        <v>0</v>
-      </c>
-      <c r="H38" t="n">
-        <v>0</v>
-      </c>
-      <c r="I38" t="n">
-        <v>0</v>
-      </c>
-      <c r="J38" t="n">
-        <v>0</v>
-      </c>
-      <c r="K38" t="n">
         <v>0</v>
       </c>
     </row>

--- a/IPL_Fantasy_Points.xlsx
+++ b/IPL_Fantasy_Points.xlsx
@@ -561,19 +561,19 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>189</v>
+        <v>204</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>189</v>
+        <v>204</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>189</v>
+        <v>204</v>
       </c>
     </row>
     <row r="4">
@@ -819,19 +819,19 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>233</v>
+        <v>256</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>233</v>
+        <v>256</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>233</v>
+        <v>256</v>
       </c>
     </row>
     <row r="10">
@@ -1037,16 +1037,16 @@
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>180</v>
+        <v>200</v>
       </c>
       <c r="K14" t="n">
-        <v>180</v>
+        <v>200</v>
       </c>
     </row>
     <row r="15">
@@ -1811,16 +1811,16 @@
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I32" t="n">
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>220</v>
+        <v>240</v>
       </c>
       <c r="K32" t="n">
-        <v>220</v>
+        <v>240</v>
       </c>
     </row>
     <row r="33">
@@ -2628,16 +2628,16 @@
         <v>11</v>
       </c>
       <c r="H51" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I51" t="n">
         <v>0</v>
       </c>
       <c r="J51" t="n">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="K51" t="n">
-        <v>20</v>
+        <v>60</v>
       </c>
     </row>
     <row r="52">
@@ -2785,31 +2785,31 @@
           <t>BAT</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr"/>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>marcus stoinis</t>
-        </is>
-      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>josh inglis</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr">
         <is>
-          <t>no_stats_yet</t>
+          <t>ai_structured</t>
         </is>
       </c>
       <c r="G55" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="H55" t="n">
         <v>0</v>
       </c>
       <c r="I55" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
       </c>
       <c r="K55" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
     </row>
     <row r="56">
@@ -3012,19 +3012,19 @@
         </is>
       </c>
       <c r="G60" t="n">
-        <v>297</v>
+        <v>380</v>
       </c>
       <c r="H60" t="n">
         <v>0</v>
       </c>
       <c r="I60" t="n">
-        <v>297</v>
+        <v>380</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
       </c>
       <c r="K60" t="n">
-        <v>297</v>
+        <v>380</v>
       </c>
     </row>
     <row r="61">
@@ -3915,19 +3915,19 @@
         </is>
       </c>
       <c r="G81" t="n">
-        <v>193</v>
+        <v>224</v>
       </c>
       <c r="H81" t="n">
         <v>0</v>
       </c>
       <c r="I81" t="n">
-        <v>193</v>
+        <v>224</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
       </c>
       <c r="K81" t="n">
-        <v>193</v>
+        <v>224</v>
       </c>
     </row>
     <row r="82">
@@ -4689,19 +4689,19 @@
         </is>
       </c>
       <c r="G99" t="n">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="H99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I99" t="n">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="J99" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K99" t="n">
-        <v>47</v>
+        <v>77</v>
       </c>
     </row>
     <row r="100">
@@ -4950,16 +4950,16 @@
         <v>0</v>
       </c>
       <c r="H105" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I105" t="n">
         <v>0</v>
       </c>
       <c r="J105" t="n">
-        <v>80</v>
+        <v>120</v>
       </c>
       <c r="K105" t="n">
-        <v>80</v>
+        <v>120</v>
       </c>
     </row>
     <row r="106">
@@ -5119,19 +5119,19 @@
         </is>
       </c>
       <c r="G109" t="n">
-        <v>212</v>
+        <v>256</v>
       </c>
       <c r="H109" t="n">
         <v>0</v>
       </c>
       <c r="I109" t="n">
-        <v>212</v>
+        <v>256</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
       </c>
       <c r="K109" t="n">
-        <v>212</v>
+        <v>256</v>
       </c>
     </row>
     <row r="110">
@@ -5162,19 +5162,19 @@
         </is>
       </c>
       <c r="G110" t="n">
-        <v>137</v>
+        <v>221</v>
       </c>
       <c r="H110" t="n">
         <v>0</v>
       </c>
       <c r="I110" t="n">
-        <v>137</v>
+        <v>221</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
       </c>
       <c r="K110" t="n">
-        <v>137</v>
+        <v>221</v>
       </c>
     </row>
     <row r="111">
@@ -6065,19 +6065,19 @@
         </is>
       </c>
       <c r="G131" t="n">
-        <v>193</v>
+        <v>204</v>
       </c>
       <c r="H131" t="n">
         <v>0</v>
       </c>
       <c r="I131" t="n">
-        <v>193</v>
+        <v>204</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
       </c>
       <c r="K131" t="n">
-        <v>193</v>
+        <v>204</v>
       </c>
     </row>
     <row r="132">
@@ -6541,16 +6541,16 @@
         <v>31</v>
       </c>
       <c r="H142" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I142" t="n">
         <v>0</v>
       </c>
       <c r="J142" t="n">
-        <v>140</v>
+        <v>160</v>
       </c>
       <c r="K142" t="n">
-        <v>140</v>
+        <v>160</v>
       </c>
     </row>
     <row r="143">
@@ -6667,19 +6667,19 @@
         </is>
       </c>
       <c r="G145" t="n">
-        <v>183</v>
+        <v>195</v>
       </c>
       <c r="H145" t="n">
         <v>0</v>
       </c>
       <c r="I145" t="n">
-        <v>183</v>
+        <v>195</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
       </c>
       <c r="K145" t="n">
-        <v>183</v>
+        <v>195</v>
       </c>
     </row>
     <row r="146">
@@ -6710,19 +6710,19 @@
         </is>
       </c>
       <c r="G146" t="n">
-        <v>82</v>
+        <v>145</v>
       </c>
       <c r="H146" t="n">
         <v>0</v>
       </c>
       <c r="I146" t="n">
-        <v>82</v>
+        <v>145</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
       </c>
       <c r="K146" t="n">
-        <v>82</v>
+        <v>145</v>
       </c>
     </row>
     <row r="147">
@@ -6827,31 +6827,31 @@
           <t>BAT</t>
         </is>
       </c>
-      <c r="D149" t="inlineStr"/>
-      <c r="E149" t="inlineStr">
-        <is>
-          <t>angkrish raghuvanshi</t>
-        </is>
-      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>akshat raghuwanshi</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr"/>
       <c r="F149" t="inlineStr">
         <is>
-          <t>no_stats_yet</t>
+          <t>exact/alias</t>
         </is>
       </c>
       <c r="G149" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="H149" t="n">
         <v>0</v>
       </c>
       <c r="I149" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
       </c>
       <c r="K149" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="150">
@@ -6882,19 +6882,19 @@
         </is>
       </c>
       <c r="G150" t="n">
-        <v>35</v>
+        <v>75</v>
       </c>
       <c r="H150" t="n">
         <v>0</v>
       </c>
       <c r="I150" t="n">
-        <v>35</v>
+        <v>75</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
       </c>
       <c r="K150" t="n">
-        <v>35</v>
+        <v>75</v>
       </c>
     </row>
     <row r="151">
@@ -8185,7 +8185,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>3046</v>
+        <v>3077</v>
       </c>
     </row>
     <row r="3">
@@ -8198,7 +8198,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2837</v>
+        <v>2857</v>
       </c>
     </row>
     <row r="4">
@@ -8211,7 +8211,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2525</v>
+        <v>2595</v>
       </c>
     </row>
     <row r="5">
@@ -8224,7 +8224,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2423</v>
+        <v>2519</v>
       </c>
     </row>
     <row r="6">
@@ -8237,7 +8237,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2375</v>
+        <v>2501</v>
       </c>
     </row>
     <row r="7">
@@ -8250,7 +8250,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2283</v>
+        <v>2411</v>
       </c>
     </row>
     <row r="8">
@@ -8263,7 +8263,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2181</v>
+        <v>2239</v>
       </c>
     </row>
     <row r="9">
@@ -8276,7 +8276,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2048</v>
+        <v>2079</v>
       </c>
     </row>
     <row r="10">
@@ -8289,7 +8289,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1988</v>
+        <v>2028</v>
       </c>
     </row>
     <row r="11">
@@ -8316,7 +8316,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C182"/>
+  <dimension ref="A1:C185"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8395,7 +8395,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>193</v>
+        <v>224</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
@@ -8430,37 +8430,37 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>am ghazanfar</t>
+          <t>akshat raghuwanshi</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="C9" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>angkrish raghuvanshi</t>
+          <t>am ghazanfar</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>268</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>aniket verma</t>
+          <t>angkrish raghuvanshi</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>79</v>
+        <v>268</v>
       </c>
       <c r="C11" t="n">
         <v>0</v>
@@ -8469,11 +8469,11 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>anrich nortje</t>
+          <t>aniket verma</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="C12" t="n">
         <v>0</v>
@@ -8482,154 +8482,154 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>anshul kamboj</t>
+          <t>anrich nortje</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>anukul roy</t>
+          <t>anshul kamboj</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>39</v>
       </c>
       <c r="C14" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>arshad khan</t>
+          <t>anukul roy</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>8</v>
+        <v>39</v>
       </c>
       <c r="C15" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>arshdeep singh</t>
+          <t>arshad khan</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C16" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ashok sharma</t>
+          <t>arshdeep singh</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>1</v>
       </c>
       <c r="C17" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ashutosh sharma</t>
+          <t>ashok sharma</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>58</v>
+        <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ashwani kumar</t>
+          <t>ashutosh sharma</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>58</v>
       </c>
       <c r="C19" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>auqib nabi</t>
+          <t>ashwani kumar</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>avesh khan</t>
+          <t>auqib nabi</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C21" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>axar patel</t>
+          <t>avesh khan</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="C22" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ayush badoni</t>
+          <t>axar patel</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>172</v>
+        <v>31</v>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ayush mhatre</t>
+          <t>ayush badoni</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>201</v>
+        <v>172</v>
       </c>
       <c r="C24" t="n">
         <v>0</v>
@@ -8638,11 +8638,11 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>b sai sudharshan</t>
+          <t>ayush mhatre</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>385</v>
+        <v>201</v>
       </c>
       <c r="C25" t="n">
         <v>0</v>
@@ -8651,102 +8651,102 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>bhuvneshwar kumar</t>
+          <t>b sai sudharshan</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>27</v>
+        <v>385</v>
       </c>
       <c r="C26" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>blessing muzarabani</t>
+          <t>bhuvneshwar kumar</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="C27" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>brijesh sharma</t>
+          <t>blessing muzarabani</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C28" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>cameron green</t>
+          <t>brijesh sharma</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>199</v>
+        <v>1</v>
       </c>
       <c r="C29" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>cooper connolly</t>
+          <t>cameron green</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>270</v>
+        <v>199</v>
       </c>
       <c r="C30" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>corbin bosch</t>
+          <t>cooper connolly</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>11</v>
+        <v>270</v>
       </c>
       <c r="C31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>danish malewar</t>
+          <t>corbin bosch</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="C32" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>dasun shanaka</t>
+          <t>danish malewar</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C33" t="n">
         <v>0</v>
@@ -8755,11 +8755,11 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>david miller</t>
+          <t>dasun shanaka</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>123</v>
+        <v>0</v>
       </c>
       <c r="C34" t="n">
         <v>0</v>
@@ -8768,50 +8768,50 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>david payne</t>
+          <t>david miller</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>6</v>
+        <v>123</v>
       </c>
       <c r="C35" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>deepak chahar</t>
+          <t>david payne</t>
         </is>
       </c>
       <c r="B36" t="n">
         <v>6</v>
       </c>
       <c r="C36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>devdutt padikkal</t>
+          <t>deepak chahar</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>282</v>
+        <v>6</v>
       </c>
       <c r="C37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>dewald brevis</t>
+          <t>devdutt padikkal</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>64</v>
+        <v>282</v>
       </c>
       <c r="C38" t="n">
         <v>0</v>
@@ -8820,11 +8820,11 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>dhruv chand jurel</t>
+          <t>dewald brevis</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>290</v>
+        <v>64</v>
       </c>
       <c r="C39" t="n">
         <v>0</v>
@@ -8833,37 +8833,37 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>digvesh rathi</t>
+          <t>dhruv chand jurel</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>2</v>
+        <v>290</v>
       </c>
       <c r="C40" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>dilshan madushanka</t>
+          <t>digvesh rathi</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C41" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>donavon ferreira</t>
+          <t>dilshan madushanka</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>229</v>
+        <v>0</v>
       </c>
       <c r="C42" t="n">
         <v>1</v>
@@ -8872,141 +8872,141 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>dushmantha chameera</t>
+          <t>donavon ferreira</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0</v>
+        <v>229</v>
       </c>
       <c r="C43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>eshan malinga</t>
+          <t>dushmantha chameera</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C44" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>finn allen</t>
+          <t>eshan malinga</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>110</v>
+        <v>2</v>
       </c>
       <c r="C45" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>george linde</t>
+          <t>finn allen</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>31</v>
+        <v>110</v>
       </c>
       <c r="C46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>glenn phillips</t>
+          <t>george linde</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>67</v>
+        <v>31</v>
       </c>
       <c r="C47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>gurjapneet singh</t>
+          <t>glenn phillips</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="C48" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>hardik pandya</t>
+          <t>gurjapneet singh</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>146</v>
+        <v>0</v>
       </c>
       <c r="C49" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>harpreet brar</t>
+          <t>hardik pandya</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0</v>
+        <v>146</v>
       </c>
       <c r="C50" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>harsh dubey</t>
+          <t>harpreet brar</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="C51" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>harshal patel</t>
+          <t>harsh dubey</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C52" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>heinrich klaasen</t>
+          <t>harshal patel</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>425</v>
+        <v>10</v>
       </c>
       <c r="C53" t="n">
         <v>0</v>
@@ -9015,11 +9015,11 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>himmat singh</t>
+          <t>heinrich klaasen</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>35</v>
+        <v>425</v>
       </c>
       <c r="C54" t="n">
         <v>0</v>
@@ -9028,11 +9028,11 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>ishan kishan</t>
+          <t>himmat singh</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>354</v>
+        <v>75</v>
       </c>
       <c r="C55" t="n">
         <v>0</v>
@@ -9041,11 +9041,11 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>jacob bethell</t>
+          <t>ishan kishan</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>39</v>
+        <v>354</v>
       </c>
       <c r="C56" t="n">
         <v>0</v>
@@ -9054,141 +9054,141 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>jacob duffy</t>
+          <t>jacob bethell</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="C57" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>jamie overton</t>
+          <t>jacob duffy</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>136</v>
+        <v>0</v>
       </c>
       <c r="C58" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>jason holder</t>
+          <t>jamie overton</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>40</v>
+        <v>136</v>
       </c>
       <c r="C59" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>jasprit bumrah</t>
+          <t>jason holder</t>
         </is>
       </c>
       <c r="B60" t="n">
+        <v>40</v>
+      </c>
+      <c r="C60" t="n">
         <v>7</v>
-      </c>
-      <c r="C60" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>jaydev unadkat</t>
+          <t>jasprit bumrah</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C61" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>jitesh sharma</t>
+          <t>jaydev unadkat</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>63</v>
+        <v>4</v>
       </c>
       <c r="C62" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>jofra archer</t>
+          <t>jitesh sharma</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>14</v>
+        <v>63</v>
       </c>
       <c r="C63" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>jos buttler</t>
+          <t>jofra archer</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>335</v>
+        <v>14</v>
       </c>
       <c r="C64" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>josh hazlewood</t>
+          <t>jos buttler</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0</v>
+        <v>335</v>
       </c>
       <c r="C65" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>kagiso rabada</t>
+          <t>josh hazlewood</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="C66" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>kartik sharma</t>
+          <t>josh inglis</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>112</v>
+        <v>13</v>
       </c>
       <c r="C67" t="n">
         <v>0</v>
@@ -9197,24 +9197,24 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>kartik tyagi</t>
+          <t>kagiso rabada</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="C68" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>karun nair</t>
+          <t>kartik sharma</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>5</v>
+        <v>112</v>
       </c>
       <c r="C69" t="n">
         <v>0</v>
@@ -9223,24 +9223,24 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>khaleel ahmed</t>
+          <t>kartik tyagi</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="C70" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>krish bhagat</t>
+          <t>karun nair</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C71" t="n">
         <v>0</v>
@@ -9249,63 +9249,63 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>krunal pandya</t>
+          <t>khaleel ahmed</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C72" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>kuldeep yadav</t>
+          <t>krish bhagat</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C73" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>kumar kushagra</t>
+          <t>krunal pandya</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="C74" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>kyle jamieson</t>
+          <t>kuldeep yadav</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C75" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>lhuan dre pretorius</t>
+          <t>kumar kushagra</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="C76" t="n">
         <v>0</v>
@@ -9314,20 +9314,20 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>liam livingstone</t>
+          <t>kyle jamieson</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C77" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>lockie ferguson</t>
+          <t>lhuan dre pretorius</t>
         </is>
       </c>
       <c r="B78" t="n">
@@ -9340,11 +9340,11 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>lokesh rahul</t>
+          <t>liam livingstone</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>433</v>
+        <v>15</v>
       </c>
       <c r="C79" t="n">
         <v>0</v>
@@ -9353,63 +9353,63 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>lungi ngidi</t>
+          <t>lockie ferguson</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C80" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>manav suthar</t>
+          <t>lokesh rahul</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0</v>
+        <v>433</v>
       </c>
       <c r="C81" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>manimaran siddharth</t>
+          <t>lungi ngidi</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C82" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>manish pandey</t>
+          <t>manav suthar</t>
         </is>
       </c>
       <c r="B83" t="n">
         <v>0</v>
       </c>
       <c r="C83" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>marco jansen</t>
+          <t>manimaran siddharth</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="C84" t="n">
         <v>6</v>
@@ -9418,63 +9418,63 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>marcus stoinis</t>
+          <t>manish pandey</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="C85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>matt henry</t>
+          <t>marco jansen</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="C86" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>matt short</t>
+          <t>marcus stoinis</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>36</v>
+        <v>150</v>
       </c>
       <c r="C87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>mayank markande</t>
+          <t>matt henry</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C88" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>mayank rawat</t>
+          <t>matt short</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="C89" t="n">
         <v>0</v>
@@ -9483,11 +9483,11 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>mayank yadav</t>
+          <t>mayank markande</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C90" t="n">
         <v>0</v>
@@ -9496,11 +9496,11 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>mitchell marsh</t>
+          <t>mayank rawat</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>212</v>
+        <v>0</v>
       </c>
       <c r="C91" t="n">
         <v>0</v>
@@ -9509,141 +9509,141 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>mitchell santner</t>
+          <t>mayank yadav</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="C92" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>mitchell starc</t>
+          <t>mitchell marsh</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>0</v>
+        <v>256</v>
       </c>
       <c r="C93" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>mohammed shami</t>
+          <t>mitchell santner</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="C94" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>mohammed siraj</t>
+          <t>mitchell starc</t>
         </is>
       </c>
       <c r="B95" t="n">
         <v>0</v>
       </c>
       <c r="C95" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>mohsin khan</t>
+          <t>mohammed shami</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="C96" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>mukesh choudhary</t>
+          <t>mohammed siraj</t>
         </is>
       </c>
       <c r="B97" t="n">
         <v>0</v>
       </c>
       <c r="C97" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>mukesh kumar</t>
+          <t>mohsin khan</t>
         </is>
       </c>
       <c r="B98" t="n">
         <v>0</v>
       </c>
       <c r="C98" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>mukul choudhary</t>
+          <t>mukesh choudhary</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>156</v>
+        <v>0</v>
       </c>
       <c r="C99" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>naman dhir</t>
+          <t>mukesh kumar</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>233</v>
+        <v>0</v>
       </c>
       <c r="C100" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>nandre burger</t>
+          <t>mukul choudhary</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>3</v>
+        <v>156</v>
       </c>
       <c r="C101" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>navdeep saini</t>
+          <t>naman dhir</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>0</v>
+        <v>256</v>
       </c>
       <c r="C102" t="n">
         <v>0</v>
@@ -9652,24 +9652,24 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>nehal wadhera</t>
+          <t>nandre burger</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>65</v>
+        <v>3</v>
       </c>
       <c r="C103" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>nicholas pooran</t>
+          <t>navdeep saini</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="C104" t="n">
         <v>0</v>
@@ -9678,11 +9678,11 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>nishant sindhu</t>
+          <t>nehal wadhera</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>15</v>
+        <v>65</v>
       </c>
       <c r="C105" t="n">
         <v>0</v>
@@ -9691,24 +9691,24 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>nitish kumar reddy</t>
+          <t>nicholas pooran</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>193</v>
+        <v>145</v>
       </c>
       <c r="C106" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>nitish rana</t>
+          <t>nishant sindhu</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>202</v>
+        <v>15</v>
       </c>
       <c r="C107" t="n">
         <v>0</v>
@@ -9717,63 +9717,63 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>noor ahmad</t>
+          <t>nitish kumar reddy</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>10</v>
+        <v>193</v>
       </c>
       <c r="C108" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>pat cummins</t>
+          <t>nitish rana</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>10</v>
+        <v>202</v>
       </c>
       <c r="C109" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>pathum nissanka</t>
+          <t>noor ahmad</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>209</v>
+        <v>10</v>
       </c>
       <c r="C110" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>philip salt</t>
+          <t>pat cummins</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>202</v>
+        <v>10</v>
       </c>
       <c r="C111" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>prabhsimran singh</t>
+          <t>pathum nissanka</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>361</v>
+        <v>209</v>
       </c>
       <c r="C112" t="n">
         <v>0</v>
@@ -9782,24 +9782,24 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>praful hinge</t>
+          <t>philip salt</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>0</v>
+        <v>202</v>
       </c>
       <c r="C113" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>prashant veer</t>
+          <t>prabhsimran singh</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>49</v>
+        <v>361</v>
       </c>
       <c r="C114" t="n">
         <v>0</v>
@@ -9808,63 +9808,63 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>prasidh krishna</t>
+          <t>praful hinge</t>
         </is>
       </c>
       <c r="B115" t="n">
         <v>0</v>
       </c>
       <c r="C115" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>prince yadav</t>
+          <t>prashant veer</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="C116" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>priyansh arya</t>
+          <t>prasidh krishna</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>285</v>
+        <v>0</v>
       </c>
       <c r="C117" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>quinton de kock</t>
+          <t>prince yadav</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>132</v>
+        <v>0</v>
       </c>
       <c r="C118" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>raghu sharma</t>
+          <t>priyansh arya</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>0</v>
+        <v>285</v>
       </c>
       <c r="C119" t="n">
         <v>0</v>
@@ -9873,11 +9873,11 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>rahul chahar</t>
+          <t>quinton de kock</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>0</v>
+        <v>132</v>
       </c>
       <c r="C120" t="n">
         <v>0</v>
@@ -9886,24 +9886,24 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>rahul tewatia</t>
+          <t>raghu sharma</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>78</v>
+        <v>0</v>
       </c>
       <c r="C121" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>rajat patidar</t>
+          <t>rahul chahar</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>257</v>
+        <v>0</v>
       </c>
       <c r="C122" t="n">
         <v>0</v>
@@ -9912,115 +9912,115 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>ramakrishna ghosh</t>
+          <t>rahul tewatia</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="C123" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>ramandeep singh</t>
+          <t>raj angad bawa</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="C124" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>rashid khan</t>
+          <t>rajat patidar</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>35</v>
+        <v>257</v>
       </c>
       <c r="C125" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>rasikh salam</t>
+          <t>ramakrishna ghosh</t>
         </is>
       </c>
       <c r="B126" t="n">
         <v>0</v>
       </c>
       <c r="C126" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>ravi bishnoi</t>
+          <t>ramandeep singh</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="C127" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>ravichandran smaran</t>
+          <t>rashid khan</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>4</v>
+        <v>35</v>
       </c>
       <c r="C128" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>ravindra jadeja</t>
+          <t>rasikh salam</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>152</v>
+        <v>0</v>
       </c>
       <c r="C129" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>rinku singh</t>
+          <t>ravi bishnoi</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>237</v>
+        <v>0</v>
       </c>
       <c r="C130" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>rishabh pant</t>
+          <t>ravichandran smaran</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>189</v>
+        <v>4</v>
       </c>
       <c r="C131" t="n">
         <v>0</v>
@@ -10029,24 +10029,24 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>riyan parag</t>
+          <t>ravindra jadeja</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>207</v>
+        <v>152</v>
       </c>
       <c r="C132" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>robin minz</t>
+          <t>rinku singh</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>6</v>
+        <v>237</v>
       </c>
       <c r="C133" t="n">
         <v>0</v>
@@ -10055,11 +10055,11 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>rohit sharma</t>
+          <t>rishabh pant</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>137</v>
+        <v>204</v>
       </c>
       <c r="C134" t="n">
         <v>0</v>
@@ -10068,24 +10068,24 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>romario shepherd</t>
+          <t>riyan parag</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>56</v>
+        <v>207</v>
       </c>
       <c r="C135" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>rovman powell</t>
+          <t>robin minz</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>121</v>
+        <v>6</v>
       </c>
       <c r="C136" t="n">
         <v>0</v>
@@ -10094,11 +10094,11 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>ruturaj gaikwad</t>
+          <t>rohit sharma</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>245</v>
+        <v>221</v>
       </c>
       <c r="C137" t="n">
         <v>0</v>
@@ -10107,24 +10107,24 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>ryan rickelton</t>
+          <t>romario shepherd</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>297</v>
+        <v>56</v>
       </c>
       <c r="C138" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>sahil parakh</t>
+          <t>rovman powell</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>0</v>
+        <v>121</v>
       </c>
       <c r="C139" t="n">
         <v>0</v>
@@ -10133,24 +10133,24 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>sakib hussain</t>
+          <t>ruturaj gaikwad</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>0</v>
+        <v>245</v>
       </c>
       <c r="C140" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>salil arora</t>
+          <t>ryan rickelton</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>95</v>
+        <v>380</v>
       </c>
       <c r="C141" t="n">
         <v>0</v>
@@ -10159,11 +10159,11 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>sameer rizvi</t>
+          <t>sahil parakh</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>209</v>
+        <v>0</v>
       </c>
       <c r="C142" t="n">
         <v>0</v>
@@ -10172,24 +10172,24 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>sandeep sharma</t>
+          <t>sakib hussain</t>
         </is>
       </c>
       <c r="B143" t="n">
         <v>0</v>
       </c>
       <c r="C143" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>sanju samson</t>
+          <t>salil arora</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>315</v>
+        <v>95</v>
       </c>
       <c r="C144" t="n">
         <v>0</v>
@@ -10198,11 +10198,11 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>sarfaraz khan</t>
+          <t>sameer rizvi</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>161</v>
+        <v>209</v>
       </c>
       <c r="C145" t="n">
         <v>0</v>
@@ -10211,24 +10211,24 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>shahbaz ahmed</t>
+          <t>sandeep sharma</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="C146" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>shahrukh khan</t>
+          <t>sanju samson</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>43</v>
+        <v>315</v>
       </c>
       <c r="C147" t="n">
         <v>0</v>
@@ -10237,37 +10237,37 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>shardul thakur</t>
+          <t>sarfaraz khan</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>14</v>
+        <v>161</v>
       </c>
       <c r="C148" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>shashank singh</t>
+          <t>shahbaz ahmed</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>70</v>
+        <v>15</v>
       </c>
       <c r="C149" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>sherfane rutherford</t>
+          <t>shahrukh khan</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>103</v>
+        <v>43</v>
       </c>
       <c r="C150" t="n">
         <v>0</v>
@@ -10276,50 +10276,50 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>shimron hetmyer</t>
+          <t>shardul thakur</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>72</v>
+        <v>14</v>
       </c>
       <c r="C151" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>shivam dube</t>
+          <t>shashank singh</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>150</v>
+        <v>70</v>
       </c>
       <c r="C152" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>shivang kumar</t>
+          <t>sherfane rutherford</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>22</v>
+        <v>103</v>
       </c>
       <c r="C153" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>shreyas iyer</t>
+          <t>shimron hetmyer</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>328</v>
+        <v>72</v>
       </c>
       <c r="C154" t="n">
         <v>0</v>
@@ -10328,50 +10328,50 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>shubham badriprasad dubey</t>
+          <t>shivam dube</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>56</v>
+        <v>150</v>
       </c>
       <c r="C155" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>shubman gill</t>
+          <t>shivang kumar</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>378</v>
+        <v>22</v>
       </c>
       <c r="C156" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>sunil narine</t>
+          <t>shreyas iyer</t>
         </is>
       </c>
       <c r="B157" t="n">
-        <v>40</v>
+        <v>328</v>
       </c>
       <c r="C157" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>suryakumar yadav</t>
+          <t>shubham badriprasad dubey</t>
         </is>
       </c>
       <c r="B158" t="n">
-        <v>183</v>
+        <v>56</v>
       </c>
       <c r="C158" t="n">
         <v>0</v>
@@ -10380,11 +10380,11 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>suryansh shedge</t>
+          <t>shubman gill</t>
         </is>
       </c>
       <c r="B159" t="n">
-        <v>60</v>
+        <v>378</v>
       </c>
       <c r="C159" t="n">
         <v>0</v>
@@ -10393,37 +10393,37 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>suyash sharma</t>
+          <t>sunil narine</t>
         </is>
       </c>
       <c r="B160" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="C160" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>t natarajan</t>
+          <t>suryakumar yadav</t>
         </is>
       </c>
       <c r="B161" t="n">
-        <v>1</v>
+        <v>195</v>
       </c>
       <c r="C161" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>tilak varma</t>
+          <t>suryansh shedge</t>
         </is>
       </c>
       <c r="B162" t="n">
-        <v>193</v>
+        <v>60</v>
       </c>
       <c r="C162" t="n">
         <v>0</v>
@@ -10432,37 +10432,37 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>tim david</t>
+          <t>suyash sharma</t>
         </is>
       </c>
       <c r="B163" t="n">
-        <v>192</v>
+        <v>0</v>
       </c>
       <c r="C163" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>tim seifert</t>
+          <t>t natarajan</t>
         </is>
       </c>
       <c r="B164" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="C164" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>travis head</t>
+          <t>tilak varma</t>
         </is>
       </c>
       <c r="B165" t="n">
-        <v>323</v>
+        <v>204</v>
       </c>
       <c r="C165" t="n">
         <v>0</v>
@@ -10471,24 +10471,24 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>trent boult</t>
+          <t>tim david</t>
         </is>
       </c>
       <c r="B166" t="n">
-        <v>8</v>
+        <v>192</v>
       </c>
       <c r="C166" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>tristan stubbs</t>
+          <t>tim seifert</t>
         </is>
       </c>
       <c r="B167" t="n">
-        <v>219</v>
+        <v>19</v>
       </c>
       <c r="C167" t="n">
         <v>0</v>
@@ -10497,115 +10497,115 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>tushar deshpande</t>
+          <t>travis head</t>
         </is>
       </c>
       <c r="B168" t="n">
-        <v>25</v>
+        <v>323</v>
       </c>
       <c r="C168" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>urvil patel</t>
+          <t>trent boult</t>
         </is>
       </c>
       <c r="B169" t="n">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="C169" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>vaibhav arora</t>
+          <t>tristan stubbs</t>
         </is>
       </c>
       <c r="B170" t="n">
-        <v>1</v>
+        <v>219</v>
       </c>
       <c r="C170" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>vaibhav suryavanshi</t>
+          <t>tushar deshpande</t>
         </is>
       </c>
       <c r="B171" t="n">
-        <v>404</v>
+        <v>25</v>
       </c>
       <c r="C171" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>varun chakravarthy</t>
+          <t>urvil patel</t>
         </is>
       </c>
       <c r="B172" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="C172" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>venkatesh iyer</t>
+          <t>vaibhav arora</t>
         </is>
       </c>
       <c r="B173" t="n">
-        <v>41</v>
+        <v>1</v>
       </c>
       <c r="C173" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>vijaykumar vyshak</t>
+          <t>vaibhav suryavanshi</t>
         </is>
       </c>
       <c r="B174" t="n">
-        <v>1</v>
+        <v>404</v>
       </c>
       <c r="C174" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>vipraj nigam</t>
+          <t>varun chakravarthy</t>
         </is>
       </c>
       <c r="B175" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="C175" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>virat kohli</t>
+          <t>venkatesh iyer</t>
         </is>
       </c>
       <c r="B176" t="n">
-        <v>379</v>
+        <v>41</v>
       </c>
       <c r="C176" t="n">
         <v>0</v>
@@ -10614,78 +10614,117 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>washington sundar</t>
+          <t>vijaykumar vyshak</t>
         </is>
       </c>
       <c r="B177" t="n">
-        <v>209</v>
+        <v>1</v>
       </c>
       <c r="C177" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>will jacks</t>
+          <t>vipraj nigam</t>
         </is>
       </c>
       <c r="B178" t="n">
-        <v>47</v>
+        <v>12</v>
       </c>
       <c r="C178" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>xavier bartlett</t>
+          <t>virat kohli</t>
         </is>
       </c>
       <c r="B179" t="n">
-        <v>11</v>
+        <v>379</v>
       </c>
       <c r="C179" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>yash raj punja</t>
+          <t>washington sundar</t>
         </is>
       </c>
       <c r="B180" t="n">
-        <v>0</v>
+        <v>209</v>
       </c>
       <c r="C180" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>yashasvi jaiswal</t>
+          <t>will jacks</t>
         </is>
       </c>
       <c r="B181" t="n">
-        <v>312</v>
+        <v>57</v>
       </c>
       <c r="C181" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
+          <t>xavier bartlett</t>
+        </is>
+      </c>
+      <c r="B182" t="n">
+        <v>11</v>
+      </c>
+      <c r="C182" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>yash raj punja</t>
+        </is>
+      </c>
+      <c r="B183" t="n">
+        <v>0</v>
+      </c>
+      <c r="C183" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>yashasvi jaiswal</t>
+        </is>
+      </c>
+      <c r="B184" t="n">
+        <v>312</v>
+      </c>
+      <c r="C184" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
           <t>yuzvendra chahal</t>
         </is>
       </c>
-      <c r="B182" t="n">
-        <v>0</v>
-      </c>
-      <c r="C182" t="n">
+      <c r="B185" t="n">
+        <v>0</v>
+      </c>
+      <c r="C185" t="n">
         <v>7</v>
       </c>
     </row>
@@ -10700,7 +10739,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K32"/>
+  <dimension ref="A1:K30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11064,7 +11103,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Jos Inglis</t>
+          <t>Prithvi Shaw</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -11080,7 +11119,7 @@
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>marcus stoinis</t>
+          <t>prasidh krishna</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -11107,7 +11146,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Prithvi Shaw</t>
+          <t>liam livingston</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -11117,13 +11156,13 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>prasidh krishna</t>
+          <t>liam livingstone</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -11150,7 +11189,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>liam livingston</t>
+          <t>rachin ravindra</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -11166,7 +11205,7 @@
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>liam livingstone</t>
+          <t>ravichandran smaran</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -11193,7 +11232,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>rachin ravindra</t>
+          <t>Zeeshan Ansari</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -11203,13 +11242,13 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>ravichandran smaran</t>
+          <t>eshan malinga</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -11236,23 +11275,23 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Zeeshan Ansari</t>
+          <t>Mitchel Owen</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>BABA11</t>
+          <t>DIPESH11</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>eshan malinga</t>
+          <t>mitchell santner</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -11279,12 +11318,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Mitchel Owen</t>
+          <t>Arshin Kulkarni</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>DIPESH11</t>
+          <t>NAKUL11</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -11295,7 +11334,7 @@
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>mitchell santner</t>
+          <t>ashwani kumar</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -11322,7 +11361,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Arshin Kulkarni</t>
+          <t>Jayant Yadav</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -11332,13 +11371,13 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>ashwani kumar</t>
+          <t>mayank yadav</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -11365,7 +11404,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Jayant Yadav</t>
+          <t>Ajay Mandal</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -11381,7 +11420,7 @@
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>mayank yadav</t>
+          <t>rajat patidar</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -11408,7 +11447,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Ajay Mandal</t>
+          <t>Matheesha Pathirana</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -11418,13 +11457,13 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>rajat patidar</t>
+          <t>eshan malinga</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -11451,7 +11490,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Matheesha Pathirana</t>
+          <t>Ben Dwarshuis</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -11467,7 +11506,7 @@
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>eshan malinga</t>
+          <t>b sai sudharshan</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -11494,12 +11533,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Ben Dwarshuis</t>
+          <t>Arjun Tendulkar</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>NAKUL11</t>
+          <t>SKY11</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -11510,7 +11549,7 @@
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>b sai sudharshan</t>
+          <t>karun nair</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -11537,7 +11576,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Arjun Tendulkar</t>
+          <t>Kwena Maphaka</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -11553,7 +11592,7 @@
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>karun nair</t>
+          <t>aiden markram</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -11580,23 +11619,23 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Kwena Maphaka</t>
+          <t>Azmatullah Omarzai</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>SKY11</t>
+          <t>HARSH11</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>aiden markram</t>
+          <t>mitchell marsh</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -11623,23 +11662,23 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Azmatullah Omarzai</t>
+          <t>Tejasvi Singh</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>HARSH11</t>
+          <t>AMEY11</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>mitchell marsh</t>
+          <t>prabhsimran singh</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -11666,7 +11705,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>akshat raghuwanshi</t>
+          <t>Sai Kishor</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -11676,13 +11715,13 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>angkrish raghuvanshi</t>
+          <t>ishan kishan</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -11709,7 +11748,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Tejasvi Singh</t>
+          <t>Akash Deep</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -11719,13 +11758,13 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>prabhsimran singh</t>
+          <t>arshdeep singh</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -11752,23 +11791,23 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Sai Kishor</t>
+          <t>Ben Duckett</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>AMEY11</t>
+          <t>PRATIK11</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>ishan kishan</t>
+          <t>ryan rickelton</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -11795,23 +11834,23 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Akash Deep</t>
+          <t>Rahul Tripathi</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>AMEY11</t>
+          <t>PRATIK11</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>arshdeep singh</t>
+          <t>rahul tewatia</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -11838,7 +11877,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Ben Duckett</t>
+          <t>Dre Pretorius</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -11854,7 +11893,7 @@
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>ryan rickelton</t>
+          <t>lhuan dre pretorius</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -11881,7 +11920,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rahul Tripathi</t>
+          <t>Matthew Breetzke</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -11897,7 +11936,7 @@
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>rahul tewatia</t>
+          <t>matt henry</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -11924,7 +11963,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Dre Pretorius</t>
+          <t>Anuj Rawat</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -11940,7 +11979,7 @@
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
-          <t>lhuan dre pretorius</t>
+          <t>mayank rawat</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -11967,7 +12006,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Matthew Breetzke</t>
+          <t>Wanindu Hasaranga</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -11977,13 +12016,13 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
-          <t>matt henry</t>
+          <t>ravichandran smaran</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -12004,92 +12043,6 @@
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Anuj Rawat</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>PRATIK11</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>BAT</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>mayank rawat</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>no_stats_yet</t>
-        </is>
-      </c>
-      <c r="G31" t="n">
-        <v>0</v>
-      </c>
-      <c r="H31" t="n">
-        <v>0</v>
-      </c>
-      <c r="I31" t="n">
-        <v>0</v>
-      </c>
-      <c r="J31" t="n">
-        <v>0</v>
-      </c>
-      <c r="K31" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Wanindu Hasaranga</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>PRATIK11</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>AR</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>ravichandran smaran</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>no_stats_yet</t>
-        </is>
-      </c>
-      <c r="G32" t="n">
-        <v>0</v>
-      </c>
-      <c r="H32" t="n">
-        <v>0</v>
-      </c>
-      <c r="I32" t="n">
-        <v>0</v>
-      </c>
-      <c r="J32" t="n">
-        <v>0</v>
-      </c>
-      <c r="K32" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12175,7 +12128,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K4"/>
+  <dimension ref="A1:K5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12238,22 +12191,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Donavan Ferreira</t>
+          <t>Jos Inglis</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>SKY11</t>
+          <t>BABA11</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>donavon ferreira</t>
+          <t>josh inglis</t>
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
@@ -12263,40 +12216,40 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>229</v>
+        <v>13</v>
       </c>
       <c r="H2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>229</v>
+        <v>13</v>
       </c>
       <c r="J2" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>249</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Ramkrishna Ghosh</t>
+          <t>Donavan Ferreira</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>HARSH11</t>
+          <t>SKY11</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>ramakrishna ghosh</t>
+          <t>donavon ferreira</t>
         </is>
       </c>
       <c r="E3" t="inlineStr"/>
@@ -12306,30 +12259,30 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>229</v>
       </c>
       <c r="H3" t="n">
         <v>1</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>229</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>249</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Abhishek Porel</t>
+          <t>Ramkrishna Ghosh</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>PRATIK11</t>
+          <t>HARSH11</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -12339,7 +12292,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>abishek porel</t>
+          <t>ramakrishna ghosh</t>
         </is>
       </c>
       <c r="E4" t="inlineStr"/>
@@ -12349,18 +12302,61 @@
         </is>
       </c>
       <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Abhishek Porel</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>PRATIK11</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>BAT</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>abishek porel</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>ai_structured</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
         <v>30</v>
       </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
         <v>30</v>
       </c>
-      <c r="J4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" t="n">
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
         <v>30</v>
       </c>
     </row>

--- a/IPL_Fantasy_Points.xlsx
+++ b/IPL_Fantasy_Points.xlsx
@@ -776,19 +776,19 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>112</v>
+        <v>153</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>112</v>
+        <v>153</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>112</v>
+        <v>153</v>
       </c>
     </row>
     <row r="9">
@@ -908,16 +908,16 @@
         <v>2</v>
       </c>
       <c r="H11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I11" t="n">
         <v>2</v>
       </c>
       <c r="J11" t="n">
-        <v>120</v>
+        <v>140</v>
       </c>
       <c r="K11" t="n">
-        <v>122</v>
+        <v>142</v>
       </c>
     </row>
     <row r="12">
@@ -1421,19 +1421,19 @@
         </is>
       </c>
       <c r="G23" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
     </row>
     <row r="24">
@@ -2754,19 +2754,19 @@
         </is>
       </c>
       <c r="G54" t="n">
-        <v>315</v>
+        <v>402</v>
       </c>
       <c r="H54" t="n">
         <v>0</v>
       </c>
       <c r="I54" t="n">
-        <v>315</v>
+        <v>402</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
       </c>
       <c r="K54" t="n">
-        <v>315</v>
+        <v>402</v>
       </c>
     </row>
     <row r="55">
@@ -3528,19 +3528,19 @@
         </is>
       </c>
       <c r="G72" t="n">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="H72" t="n">
         <v>0</v>
       </c>
       <c r="I72" t="n">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
       </c>
       <c r="K72" t="n">
-        <v>245</v>
+        <v>251</v>
       </c>
     </row>
     <row r="73">
@@ -3786,19 +3786,19 @@
         </is>
       </c>
       <c r="G78" t="n">
-        <v>219</v>
+        <v>257</v>
       </c>
       <c r="H78" t="n">
         <v>0</v>
       </c>
       <c r="I78" t="n">
-        <v>219</v>
+        <v>257</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
       </c>
       <c r="K78" t="n">
-        <v>219</v>
+        <v>257</v>
       </c>
     </row>
     <row r="79">
@@ -4345,19 +4345,19 @@
         </is>
       </c>
       <c r="G91" t="n">
-        <v>433</v>
+        <v>445</v>
       </c>
       <c r="H91" t="n">
         <v>0</v>
       </c>
       <c r="I91" t="n">
-        <v>433</v>
+        <v>445</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
       </c>
       <c r="K91" t="n">
-        <v>433</v>
+        <v>445</v>
       </c>
     </row>
     <row r="92">
@@ -4474,19 +4474,19 @@
         </is>
       </c>
       <c r="G94" t="n">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H94" t="n">
         <v>0</v>
       </c>
       <c r="I94" t="n">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
       </c>
       <c r="K94" t="n">
-        <v>28</v>
+        <v>45</v>
       </c>
     </row>
     <row r="95">
@@ -5291,19 +5291,19 @@
         </is>
       </c>
       <c r="G113" t="n">
-        <v>209</v>
+        <v>228</v>
       </c>
       <c r="H113" t="n">
         <v>0</v>
       </c>
       <c r="I113" t="n">
-        <v>209</v>
+        <v>228</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
       </c>
       <c r="K113" t="n">
-        <v>209</v>
+        <v>228</v>
       </c>
     </row>
     <row r="114">
@@ -5380,16 +5380,16 @@
         <v>136</v>
       </c>
       <c r="H115" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I115" t="n">
         <v>136</v>
       </c>
       <c r="J115" t="n">
-        <v>200</v>
+        <v>220</v>
       </c>
       <c r="K115" t="n">
-        <v>336</v>
+        <v>356</v>
       </c>
     </row>
     <row r="116">
@@ -5552,16 +5552,16 @@
         <v>3</v>
       </c>
       <c r="H119" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I119" t="n">
         <v>0</v>
       </c>
       <c r="J119" t="n">
-        <v>140</v>
+        <v>160</v>
       </c>
       <c r="K119" t="n">
-        <v>140</v>
+        <v>160</v>
       </c>
     </row>
     <row r="120">
@@ -5638,16 +5638,16 @@
         <v>0</v>
       </c>
       <c r="H121" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I121" t="n">
         <v>0</v>
       </c>
       <c r="J121" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="K121" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
     </row>
     <row r="122">
@@ -5681,16 +5681,16 @@
         <v>0</v>
       </c>
       <c r="H122" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I122" t="n">
         <v>0</v>
       </c>
       <c r="J122" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="K122" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
     </row>
     <row r="123">
@@ -6022,19 +6022,19 @@
         </is>
       </c>
       <c r="G130" t="n">
-        <v>58</v>
+        <v>72</v>
       </c>
       <c r="H130" t="n">
         <v>0</v>
       </c>
       <c r="I130" t="n">
-        <v>58</v>
+        <v>72</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
       </c>
       <c r="K130" t="n">
-        <v>58</v>
+        <v>72</v>
       </c>
     </row>
     <row r="131">
@@ -6151,19 +6151,19 @@
         </is>
       </c>
       <c r="G133" t="n">
-        <v>209</v>
+        <v>249</v>
       </c>
       <c r="H133" t="n">
         <v>0</v>
       </c>
       <c r="I133" t="n">
-        <v>209</v>
+        <v>249</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
       </c>
       <c r="K133" t="n">
-        <v>209</v>
+        <v>249</v>
       </c>
     </row>
     <row r="134">
@@ -6323,19 +6323,19 @@
         </is>
       </c>
       <c r="G137" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H137" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I137" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="J137" t="n">
-        <v>160</v>
+        <v>180</v>
       </c>
       <c r="K137" t="n">
-        <v>191</v>
+        <v>213</v>
       </c>
     </row>
     <row r="138">
@@ -6753,19 +6753,19 @@
         </is>
       </c>
       <c r="G147" t="n">
-        <v>202</v>
+        <v>217</v>
       </c>
       <c r="H147" t="n">
         <v>0</v>
       </c>
       <c r="I147" t="n">
-        <v>202</v>
+        <v>217</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
       </c>
       <c r="K147" t="n">
-        <v>202</v>
+        <v>217</v>
       </c>
     </row>
     <row r="148">
@@ -8132,16 +8132,16 @@
         <v>10</v>
       </c>
       <c r="H179" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I179" t="n">
         <v>0</v>
       </c>
       <c r="J179" t="n">
-        <v>180</v>
+        <v>220</v>
       </c>
       <c r="K179" t="n">
-        <v>180</v>
+        <v>220</v>
       </c>
     </row>
   </sheetData>
@@ -8185,7 +8185,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>3077</v>
+        <v>3121</v>
       </c>
     </row>
     <row r="3">
@@ -8198,7 +8198,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2857</v>
+        <v>2870</v>
       </c>
     </row>
     <row r="4">
@@ -8211,7 +8211,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2595</v>
+        <v>2624</v>
       </c>
     </row>
     <row r="5">
@@ -8224,7 +8224,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2519</v>
+        <v>2606</v>
       </c>
     </row>
     <row r="6">
@@ -8237,7 +8237,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2501</v>
+        <v>2516</v>
       </c>
     </row>
     <row r="7">
@@ -8250,7 +8250,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2411</v>
+        <v>2510</v>
       </c>
     </row>
     <row r="8">
@@ -8263,7 +8263,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2239</v>
+        <v>2300</v>
       </c>
     </row>
     <row r="9">
@@ -8276,7 +8276,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2079</v>
+        <v>2155</v>
       </c>
     </row>
     <row r="10">
@@ -8302,7 +8302,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1671</v>
+        <v>1711</v>
       </c>
     </row>
   </sheetData>
@@ -8424,7 +8424,7 @@
         <v>2</v>
       </c>
       <c r="C8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9">
@@ -8564,7 +8564,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>58</v>
+        <v>72</v>
       </c>
       <c r="C19" t="n">
         <v>0</v>
@@ -8616,10 +8616,10 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C23" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="24">
@@ -8957,7 +8957,7 @@
         <v>0</v>
       </c>
       <c r="C49" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="50">
@@ -9087,7 +9087,7 @@
         <v>136</v>
       </c>
       <c r="C59" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="60">
@@ -9214,7 +9214,7 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>112</v>
+        <v>153</v>
       </c>
       <c r="C69" t="n">
         <v>0</v>
@@ -9240,7 +9240,7 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="C71" t="n">
         <v>0</v>
@@ -9370,7 +9370,7 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>433</v>
+        <v>445</v>
       </c>
       <c r="C81" t="n">
         <v>0</v>
@@ -9386,7 +9386,7 @@
         <v>3</v>
       </c>
       <c r="C82" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="83">
@@ -9607,7 +9607,7 @@
         <v>0</v>
       </c>
       <c r="C99" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="100">
@@ -9734,7 +9734,7 @@
         </is>
       </c>
       <c r="B109" t="n">
-        <v>202</v>
+        <v>217</v>
       </c>
       <c r="C109" t="n">
         <v>0</v>
@@ -9750,7 +9750,7 @@
         <v>10</v>
       </c>
       <c r="C110" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="111">
@@ -9773,7 +9773,7 @@
         </is>
       </c>
       <c r="B112" t="n">
-        <v>209</v>
+        <v>228</v>
       </c>
       <c r="C112" t="n">
         <v>0</v>
@@ -10137,7 +10137,7 @@
         </is>
       </c>
       <c r="B140" t="n">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="C140" t="n">
         <v>0</v>
@@ -10202,7 +10202,7 @@
         </is>
       </c>
       <c r="B145" t="n">
-        <v>209</v>
+        <v>249</v>
       </c>
       <c r="C145" t="n">
         <v>0</v>
@@ -10228,7 +10228,7 @@
         </is>
       </c>
       <c r="B147" t="n">
-        <v>315</v>
+        <v>402</v>
       </c>
       <c r="C147" t="n">
         <v>0</v>
@@ -10527,7 +10527,7 @@
         </is>
       </c>
       <c r="B170" t="n">
-        <v>219</v>
+        <v>257</v>
       </c>
       <c r="C170" t="n">
         <v>0</v>
@@ -10553,7 +10553,7 @@
         </is>
       </c>
       <c r="B172" t="n">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="C172" t="n">
         <v>0</v>

--- a/IPL_Fantasy_Points.xlsx
+++ b/IPL_Fantasy_Points.xlsx
@@ -604,19 +604,19 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>323</v>
+        <v>361</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>323</v>
+        <v>361</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>323</v>
+        <v>361</v>
       </c>
     </row>
     <row r="5">
@@ -1206,19 +1206,19 @@
         </is>
       </c>
       <c r="G18" t="n">
-        <v>354</v>
+        <v>409</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>354</v>
+        <v>409</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>354</v>
+        <v>409</v>
       </c>
     </row>
     <row r="19">
@@ -2023,19 +2023,19 @@
         </is>
       </c>
       <c r="G37" t="n">
-        <v>425</v>
+        <v>494</v>
       </c>
       <c r="H37" t="n">
         <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>425</v>
+        <v>494</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>425</v>
+        <v>494</v>
       </c>
     </row>
     <row r="38">
@@ -2109,19 +2109,19 @@
         </is>
       </c>
       <c r="G39" t="n">
-        <v>193</v>
+        <v>222</v>
       </c>
       <c r="H39" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I39" t="n">
-        <v>193</v>
+        <v>222</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>193</v>
+        <v>222</v>
       </c>
     </row>
     <row r="40">
@@ -2367,19 +2367,19 @@
         </is>
       </c>
       <c r="G45" t="n">
-        <v>150</v>
+        <v>178</v>
       </c>
       <c r="H45" t="n">
         <v>1</v>
       </c>
       <c r="I45" t="n">
-        <v>150</v>
+        <v>178</v>
       </c>
       <c r="J45" t="n">
         <v>20</v>
       </c>
       <c r="K45" t="n">
-        <v>170</v>
+        <v>198</v>
       </c>
     </row>
     <row r="46">
@@ -2456,16 +2456,16 @@
         <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I47" t="n">
         <v>0</v>
       </c>
       <c r="J47" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K47" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="48">
@@ -3614,19 +3614,19 @@
         </is>
       </c>
       <c r="G74" t="n">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="H74" t="n">
         <v>0</v>
       </c>
       <c r="I74" t="n">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
       </c>
       <c r="K74" t="n">
-        <v>361</v>
+        <v>364</v>
       </c>
     </row>
     <row r="75">
@@ -3657,19 +3657,19 @@
         </is>
       </c>
       <c r="G75" t="n">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="H75" t="n">
         <v>0</v>
       </c>
       <c r="I75" t="n">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
       </c>
       <c r="K75" t="n">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="76">
@@ -3875,16 +3875,16 @@
         <v>10</v>
       </c>
       <c r="H80" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I80" t="n">
         <v>10</v>
       </c>
       <c r="J80" t="n">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="K80" t="n">
-        <v>50</v>
+        <v>90</v>
       </c>
     </row>
     <row r="81">
@@ -4001,19 +4001,19 @@
         </is>
       </c>
       <c r="G83" t="n">
-        <v>270</v>
+        <v>377</v>
       </c>
       <c r="H83" t="n">
         <v>0</v>
       </c>
       <c r="I83" t="n">
-        <v>270</v>
+        <v>377</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
       </c>
       <c r="K83" t="n">
-        <v>270</v>
+        <v>377</v>
       </c>
     </row>
     <row r="84">
@@ -4047,16 +4047,16 @@
         <v>1</v>
       </c>
       <c r="H84" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I84" t="n">
         <v>0</v>
       </c>
       <c r="J84" t="n">
-        <v>200</v>
+        <v>220</v>
       </c>
       <c r="K84" t="n">
-        <v>200</v>
+        <v>220</v>
       </c>
     </row>
     <row r="85">
@@ -4388,19 +4388,19 @@
         </is>
       </c>
       <c r="G92" t="n">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="H92" t="n">
         <v>0</v>
       </c>
       <c r="I92" t="n">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
       </c>
       <c r="K92" t="n">
-        <v>328</v>
+        <v>333</v>
       </c>
     </row>
     <row r="93">
@@ -5592,19 +5592,19 @@
         </is>
       </c>
       <c r="G120" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H120" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I120" t="n">
         <v>0</v>
       </c>
       <c r="J120" t="n">
-        <v>160</v>
+        <v>180</v>
       </c>
       <c r="K120" t="n">
-        <v>160</v>
+        <v>180</v>
       </c>
     </row>
     <row r="121">
@@ -6108,19 +6108,19 @@
         </is>
       </c>
       <c r="G132" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="H132" t="n">
         <v>3</v>
       </c>
       <c r="I132" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
       </c>
       <c r="K132" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
     </row>
     <row r="133">
@@ -6925,19 +6925,19 @@
         </is>
       </c>
       <c r="G151" t="n">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="H151" t="n">
         <v>0</v>
       </c>
       <c r="I151" t="n">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
       </c>
       <c r="K151" t="n">
-        <v>60</v>
+        <v>85</v>
       </c>
     </row>
     <row r="152">
@@ -7143,16 +7143,16 @@
         <v>0</v>
       </c>
       <c r="H156" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I156" t="n">
         <v>0</v>
       </c>
       <c r="J156" t="n">
-        <v>140</v>
+        <v>160</v>
       </c>
       <c r="K156" t="n">
-        <v>140</v>
+        <v>160</v>
       </c>
     </row>
     <row r="157">
@@ -7398,19 +7398,19 @@
         </is>
       </c>
       <c r="G162" t="n">
-        <v>440</v>
+        <v>475</v>
       </c>
       <c r="H162" t="n">
         <v>0</v>
       </c>
       <c r="I162" t="n">
-        <v>440</v>
+        <v>475</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
       </c>
       <c r="K162" t="n">
-        <v>440</v>
+        <v>475</v>
       </c>
     </row>
     <row r="163">
@@ -7785,19 +7785,19 @@
         </is>
       </c>
       <c r="G171" t="n">
-        <v>30</v>
+        <v>49</v>
       </c>
       <c r="H171" t="n">
         <v>6</v>
       </c>
       <c r="I171" t="n">
-        <v>30</v>
+        <v>49</v>
       </c>
       <c r="J171" t="n">
         <v>120</v>
       </c>
       <c r="K171" t="n">
-        <v>150</v>
+        <v>169</v>
       </c>
     </row>
     <row r="172">
@@ -8185,7 +8185,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>3121</v>
+        <v>3292</v>
       </c>
     </row>
     <row r="3">
@@ -8198,7 +8198,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2870</v>
+        <v>2925</v>
       </c>
     </row>
     <row r="4">
@@ -8211,7 +8211,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2624</v>
+        <v>2629</v>
       </c>
     </row>
     <row r="5">
@@ -8237,7 +8237,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2516</v>
+        <v>2561</v>
       </c>
     </row>
     <row r="7">
@@ -8250,7 +8250,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2510</v>
+        <v>2530</v>
       </c>
     </row>
     <row r="8">
@@ -8263,7 +8263,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2300</v>
+        <v>2338</v>
       </c>
     </row>
     <row r="9">
@@ -8272,11 +8272,11 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>HARSH11</t>
+          <t>VATSAL11</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2155</v>
+        <v>2174</v>
       </c>
     </row>
     <row r="10">
@@ -8285,11 +8285,11 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>VATSAL11</t>
+          <t>HARSH11</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2028</v>
+        <v>2159</v>
       </c>
     </row>
     <row r="11">
@@ -8302,7 +8302,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1711</v>
+        <v>1765</v>
       </c>
     </row>
   </sheetData>
@@ -8369,7 +8369,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>440</v>
+        <v>475</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
@@ -8541,7 +8541,7 @@
         <v>1</v>
       </c>
       <c r="C17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="18">
@@ -8720,7 +8720,7 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>270</v>
+        <v>377</v>
       </c>
       <c r="C31" t="n">
         <v>0</v>
@@ -8905,7 +8905,7 @@
         <v>2</v>
       </c>
       <c r="C45" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="46">
@@ -9019,7 +9019,7 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>425</v>
+        <v>494</v>
       </c>
       <c r="C54" t="n">
         <v>0</v>
@@ -9045,7 +9045,7 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>354</v>
+        <v>409</v>
       </c>
       <c r="C56" t="n">
         <v>0</v>
@@ -9360,7 +9360,7 @@
         <v>0</v>
       </c>
       <c r="C80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="81">
@@ -9435,7 +9435,7 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>30</v>
+        <v>49</v>
       </c>
       <c r="C86" t="n">
         <v>6</v>
@@ -9448,7 +9448,7 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>150</v>
+        <v>178</v>
       </c>
       <c r="C87" t="n">
         <v>1</v>
@@ -9721,10 +9721,10 @@
         </is>
       </c>
       <c r="B108" t="n">
-        <v>193</v>
+        <v>222</v>
       </c>
       <c r="C108" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="109">
@@ -9763,7 +9763,7 @@
         <v>10</v>
       </c>
       <c r="C111" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="112">
@@ -9799,7 +9799,7 @@
         </is>
       </c>
       <c r="B114" t="n">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="C114" t="n">
         <v>0</v>
@@ -9864,7 +9864,7 @@
         </is>
       </c>
       <c r="B119" t="n">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C119" t="n">
         <v>0</v>
@@ -10179,7 +10179,7 @@
         <v>0</v>
       </c>
       <c r="C143" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="144">
@@ -10293,7 +10293,7 @@
         </is>
       </c>
       <c r="B152" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="C152" t="n">
         <v>3</v>
@@ -10348,7 +10348,7 @@
         <v>22</v>
       </c>
       <c r="C156" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="157">
@@ -10358,7 +10358,7 @@
         </is>
       </c>
       <c r="B157" t="n">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="C157" t="n">
         <v>0</v>
@@ -10423,7 +10423,7 @@
         </is>
       </c>
       <c r="B162" t="n">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="C162" t="n">
         <v>0</v>
@@ -10501,7 +10501,7 @@
         </is>
       </c>
       <c r="B168" t="n">
-        <v>323</v>
+        <v>361</v>
       </c>
       <c r="C168" t="n">
         <v>0</v>
@@ -10618,10 +10618,10 @@
         </is>
       </c>
       <c r="B177" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C177" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="178">
@@ -10725,7 +10725,7 @@
         <v>0</v>
       </c>
       <c r="C185" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/IPL_Fantasy_Points.xlsx
+++ b/IPL_Fantasy_Points.xlsx
@@ -4505,31 +4505,31 @@
           <t>BAT</t>
         </is>
       </c>
-      <c r="D95" t="inlineStr"/>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>ashwani kumar</t>
-        </is>
-      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>arshin kulkarni</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr"/>
       <c r="F95" t="inlineStr">
         <is>
-          <t>no_stats_yet</t>
+          <t>exact/alias</t>
         </is>
       </c>
       <c r="G95" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="H95" t="n">
         <v>0</v>
       </c>
       <c r="I95" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
       </c>
       <c r="K95" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
     </row>
     <row r="96">
@@ -5119,19 +5119,19 @@
         </is>
       </c>
       <c r="G109" t="n">
-        <v>256</v>
+        <v>363</v>
       </c>
       <c r="H109" t="n">
         <v>0</v>
       </c>
       <c r="I109" t="n">
-        <v>256</v>
+        <v>363</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
       </c>
       <c r="K109" t="n">
-        <v>256</v>
+        <v>363</v>
       </c>
     </row>
     <row r="110">
@@ -6710,19 +6710,19 @@
         </is>
       </c>
       <c r="G146" t="n">
-        <v>145</v>
+        <v>159</v>
       </c>
       <c r="H146" t="n">
         <v>0</v>
       </c>
       <c r="I146" t="n">
-        <v>145</v>
+        <v>159</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
       </c>
       <c r="K146" t="n">
-        <v>145</v>
+        <v>159</v>
       </c>
     </row>
     <row r="147">
@@ -7014,16 +7014,16 @@
         <v>40</v>
       </c>
       <c r="H153" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I153" t="n">
         <v>40</v>
       </c>
       <c r="J153" t="n">
-        <v>180</v>
+        <v>200</v>
       </c>
       <c r="K153" t="n">
-        <v>220</v>
+        <v>240</v>
       </c>
     </row>
     <row r="154">
@@ -8211,7 +8211,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2629</v>
+        <v>2646</v>
       </c>
     </row>
     <row r="5">
@@ -8220,11 +8220,11 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>BABA11</t>
+          <t>SKY11</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2606</v>
+        <v>2637</v>
       </c>
     </row>
     <row r="6">
@@ -8233,11 +8233,11 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>AMEY11</t>
+          <t>BABA11</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2561</v>
+        <v>2606</v>
       </c>
     </row>
     <row r="7">
@@ -8246,11 +8246,11 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>SKY11</t>
+          <t>AMEY11</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2530</v>
+        <v>2595</v>
       </c>
     </row>
     <row r="8">
@@ -8316,7 +8316,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C185"/>
+  <dimension ref="A1:C186"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8547,102 +8547,102 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ashok sharma</t>
+          <t>arshin kulkarni</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ashutosh sharma</t>
+          <t>ashok sharma</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>72</v>
+        <v>1</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ashwani kumar</t>
+          <t>ashutosh sharma</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>72</v>
       </c>
       <c r="C20" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>auqib nabi</t>
+          <t>ashwani kumar</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>avesh khan</t>
+          <t>auqib nabi</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C22" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>axar patel</t>
+          <t>avesh khan</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="C23" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ayush badoni</t>
+          <t>axar patel</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>172</v>
+        <v>33</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>ayush mhatre</t>
+          <t>ayush badoni</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>201</v>
+        <v>172</v>
       </c>
       <c r="C25" t="n">
         <v>0</v>
@@ -8651,11 +8651,11 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>b sai sudharshan</t>
+          <t>ayush mhatre</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>385</v>
+        <v>201</v>
       </c>
       <c r="C26" t="n">
         <v>0</v>
@@ -8664,102 +8664,102 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>bhuvneshwar kumar</t>
+          <t>b sai sudharshan</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>27</v>
+        <v>385</v>
       </c>
       <c r="C27" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>blessing muzarabani</t>
+          <t>bhuvneshwar kumar</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="C28" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>brijesh sharma</t>
+          <t>blessing muzarabani</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C29" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>cameron green</t>
+          <t>brijesh sharma</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>199</v>
+        <v>1</v>
       </c>
       <c r="C30" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>cooper connolly</t>
+          <t>cameron green</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>377</v>
+        <v>199</v>
       </c>
       <c r="C31" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>corbin bosch</t>
+          <t>cooper connolly</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>11</v>
+        <v>377</v>
       </c>
       <c r="C32" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>danish malewar</t>
+          <t>corbin bosch</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="C33" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>dasun shanaka</t>
+          <t>danish malewar</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C34" t="n">
         <v>0</v>
@@ -8768,11 +8768,11 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>david miller</t>
+          <t>dasun shanaka</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>123</v>
+        <v>0</v>
       </c>
       <c r="C35" t="n">
         <v>0</v>
@@ -8781,50 +8781,50 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>david payne</t>
+          <t>david miller</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>6</v>
+        <v>123</v>
       </c>
       <c r="C36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>deepak chahar</t>
+          <t>david payne</t>
         </is>
       </c>
       <c r="B37" t="n">
         <v>6</v>
       </c>
       <c r="C37" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>devdutt padikkal</t>
+          <t>deepak chahar</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>282</v>
+        <v>6</v>
       </c>
       <c r="C38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>dewald brevis</t>
+          <t>devdutt padikkal</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>64</v>
+        <v>282</v>
       </c>
       <c r="C39" t="n">
         <v>0</v>
@@ -8833,11 +8833,11 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>dhruv chand jurel</t>
+          <t>dewald brevis</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>290</v>
+        <v>64</v>
       </c>
       <c r="C40" t="n">
         <v>0</v>
@@ -8846,37 +8846,37 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>digvesh rathi</t>
+          <t>dhruv chand jurel</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>2</v>
+        <v>290</v>
       </c>
       <c r="C41" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>dilshan madushanka</t>
+          <t>digvesh rathi</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C42" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>donavon ferreira</t>
+          <t>dilshan madushanka</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>229</v>
+        <v>0</v>
       </c>
       <c r="C43" t="n">
         <v>1</v>
@@ -8885,89 +8885,89 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>dushmantha chameera</t>
+          <t>donavon ferreira</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0</v>
+        <v>229</v>
       </c>
       <c r="C44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>eshan malinga</t>
+          <t>dushmantha chameera</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C45" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>finn allen</t>
+          <t>eshan malinga</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>110</v>
+        <v>2</v>
       </c>
       <c r="C46" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>george linde</t>
+          <t>finn allen</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>31</v>
+        <v>110</v>
       </c>
       <c r="C47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>glenn phillips</t>
+          <t>george linde</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>67</v>
+        <v>31</v>
       </c>
       <c r="C48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>gurjapneet singh</t>
+          <t>glenn phillips</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="C49" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>hardik pandya</t>
+          <t>gurjapneet singh</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>146</v>
+        <v>0</v>
       </c>
       <c r="C50" t="n">
         <v>4</v>
@@ -8976,50 +8976,50 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>harpreet brar</t>
+          <t>hardik pandya</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0</v>
+        <v>146</v>
       </c>
       <c r="C51" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>harsh dubey</t>
+          <t>harpreet brar</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="C52" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>harshal patel</t>
+          <t>harsh dubey</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C53" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>heinrich klaasen</t>
+          <t>harshal patel</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>494</v>
+        <v>10</v>
       </c>
       <c r="C54" t="n">
         <v>0</v>
@@ -9028,11 +9028,11 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>himmat singh</t>
+          <t>heinrich klaasen</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>75</v>
+        <v>494</v>
       </c>
       <c r="C55" t="n">
         <v>0</v>
@@ -9041,11 +9041,11 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>ishan kishan</t>
+          <t>himmat singh</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>409</v>
+        <v>75</v>
       </c>
       <c r="C56" t="n">
         <v>0</v>
@@ -9054,11 +9054,11 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>jacob bethell</t>
+          <t>ishan kishan</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>39</v>
+        <v>409</v>
       </c>
       <c r="C57" t="n">
         <v>0</v>
@@ -9067,284 +9067,284 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>jacob duffy</t>
+          <t>jacob bethell</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="C58" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>jamie overton</t>
+          <t>jacob duffy</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>136</v>
+        <v>0</v>
       </c>
       <c r="C59" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>jason holder</t>
+          <t>jamie overton</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>40</v>
+        <v>136</v>
       </c>
       <c r="C60" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>jasprit bumrah</t>
+          <t>jason holder</t>
         </is>
       </c>
       <c r="B61" t="n">
+        <v>40</v>
+      </c>
+      <c r="C61" t="n">
         <v>7</v>
-      </c>
-      <c r="C61" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>jaydev unadkat</t>
+          <t>jasprit bumrah</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C62" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>jitesh sharma</t>
+          <t>jaydev unadkat</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>63</v>
+        <v>4</v>
       </c>
       <c r="C63" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>jofra archer</t>
+          <t>jitesh sharma</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>14</v>
+        <v>63</v>
       </c>
       <c r="C64" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>jos buttler</t>
+          <t>jofra archer</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>335</v>
+        <v>14</v>
       </c>
       <c r="C65" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>josh hazlewood</t>
+          <t>jos buttler</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0</v>
+        <v>335</v>
       </c>
       <c r="C66" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>josh inglis</t>
+          <t>josh hazlewood</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="C67" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>kagiso rabada</t>
+          <t>josh inglis</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="C68" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>kartik sharma</t>
+          <t>kagiso rabada</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>153</v>
+        <v>35</v>
       </c>
       <c r="C69" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>kartik tyagi</t>
+          <t>kartik sharma</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>11</v>
+        <v>153</v>
       </c>
       <c r="C70" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>karun nair</t>
+          <t>kartik tyagi</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="C71" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>khaleel ahmed</t>
+          <t>karun nair</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="C72" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>krish bhagat</t>
+          <t>khaleel ahmed</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="C73" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>krunal pandya</t>
+          <t>krish bhagat</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="C74" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>kuldeep yadav</t>
+          <t>krunal pandya</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="C75" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>kumar kushagra</t>
+          <t>kuldeep yadav</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="C76" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>kyle jamieson</t>
+          <t>kumar kushagra</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="C77" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>lhuan dre pretorius</t>
+          <t>kyle jamieson</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="C78" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>liam livingstone</t>
+          <t>lhuan dre pretorius</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="C79" t="n">
         <v>0</v>
@@ -9353,141 +9353,141 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>lockie ferguson</t>
+          <t>liam livingstone</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="C80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>lokesh rahul</t>
+          <t>lockie ferguson</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>445</v>
+        <v>0</v>
       </c>
       <c r="C81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>lungi ngidi</t>
+          <t>lokesh rahul</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>3</v>
+        <v>445</v>
       </c>
       <c r="C82" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>manav suthar</t>
+          <t>lungi ngidi</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C83" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>manimaran siddharth</t>
+          <t>manav suthar</t>
         </is>
       </c>
       <c r="B84" t="n">
         <v>0</v>
       </c>
       <c r="C84" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>manish pandey</t>
+          <t>manimaran siddharth</t>
         </is>
       </c>
       <c r="B85" t="n">
         <v>0</v>
       </c>
       <c r="C85" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>marco jansen</t>
+          <t>manish pandey</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="C86" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>marcus stoinis</t>
+          <t>marco jansen</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>178</v>
+        <v>49</v>
       </c>
       <c r="C87" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>matt henry</t>
+          <t>marcus stoinis</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>7</v>
+        <v>178</v>
       </c>
       <c r="C88" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>matt short</t>
+          <t>matt henry</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>36</v>
+        <v>7</v>
       </c>
       <c r="C89" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>mayank markande</t>
+          <t>matt short</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="C90" t="n">
         <v>0</v>
@@ -9496,7 +9496,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>mayank rawat</t>
+          <t>mayank markande</t>
         </is>
       </c>
       <c r="B91" t="n">
@@ -9509,11 +9509,11 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>mayank yadav</t>
+          <t>mayank rawat</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C92" t="n">
         <v>0</v>
@@ -9522,11 +9522,11 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>mitchell marsh</t>
+          <t>mayank yadav</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>256</v>
+        <v>5</v>
       </c>
       <c r="C93" t="n">
         <v>0</v>
@@ -9535,115 +9535,115 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>mitchell santner</t>
+          <t>mitchell marsh</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>26</v>
+        <v>363</v>
       </c>
       <c r="C94" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>mitchell starc</t>
+          <t>mitchell santner</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="C95" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>mohammed shami</t>
+          <t>mitchell starc</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="C96" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>mohammed siraj</t>
+          <t>mohammed shami</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="C97" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>mohsin khan</t>
+          <t>mohammed siraj</t>
         </is>
       </c>
       <c r="B98" t="n">
         <v>0</v>
       </c>
       <c r="C98" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>mukesh choudhary</t>
+          <t>mohsin khan</t>
         </is>
       </c>
       <c r="B99" t="n">
         <v>0</v>
       </c>
       <c r="C99" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>mukesh kumar</t>
+          <t>mukesh choudhary</t>
         </is>
       </c>
       <c r="B100" t="n">
         <v>0</v>
       </c>
       <c r="C100" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>mukul choudhary</t>
+          <t>mukesh kumar</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>156</v>
+        <v>0</v>
       </c>
       <c r="C101" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>naman dhir</t>
+          <t>mukul choudhary</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>256</v>
+        <v>156</v>
       </c>
       <c r="C102" t="n">
         <v>0</v>
@@ -9652,37 +9652,37 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>nandre burger</t>
+          <t>naman dhir</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>3</v>
+        <v>256</v>
       </c>
       <c r="C103" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>navdeep saini</t>
+          <t>nandre burger</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C104" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>nehal wadhera</t>
+          <t>navdeep saini</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="C105" t="n">
         <v>0</v>
@@ -9691,11 +9691,11 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>nicholas pooran</t>
+          <t>nehal wadhera</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>145</v>
+        <v>65</v>
       </c>
       <c r="C106" t="n">
         <v>0</v>
@@ -9704,11 +9704,11 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>nishant sindhu</t>
+          <t>nicholas pooran</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>15</v>
+        <v>159</v>
       </c>
       <c r="C107" t="n">
         <v>0</v>
@@ -9717,76 +9717,76 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>nitish kumar reddy</t>
+          <t>nishant sindhu</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>222</v>
+        <v>15</v>
       </c>
       <c r="C108" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>nitish rana</t>
+          <t>nitish kumar reddy</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="C109" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>noor ahmad</t>
+          <t>nitish rana</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>10</v>
+        <v>217</v>
       </c>
       <c r="C110" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>pat cummins</t>
+          <t>noor ahmad</t>
         </is>
       </c>
       <c r="B111" t="n">
         <v>10</v>
       </c>
       <c r="C111" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>pathum nissanka</t>
+          <t>pat cummins</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>228</v>
+        <v>10</v>
       </c>
       <c r="C112" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>philip salt</t>
+          <t>pathum nissanka</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>202</v>
+        <v>228</v>
       </c>
       <c r="C113" t="n">
         <v>0</v>
@@ -9795,11 +9795,11 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>prabhsimran singh</t>
+          <t>philip salt</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>364</v>
+        <v>202</v>
       </c>
       <c r="C114" t="n">
         <v>0</v>
@@ -9808,76 +9808,76 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>praful hinge</t>
+          <t>prabhsimran singh</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>0</v>
+        <v>364</v>
       </c>
       <c r="C115" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>prashant veer</t>
+          <t>praful hinge</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="C116" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>prasidh krishna</t>
+          <t>prashant veer</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="C117" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>prince yadav</t>
+          <t>prasidh krishna</t>
         </is>
       </c>
       <c r="B118" t="n">
         <v>0</v>
       </c>
       <c r="C118" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>priyansh arya</t>
+          <t>prince yadav</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>286</v>
+        <v>0</v>
       </c>
       <c r="C119" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>quinton de kock</t>
+          <t>priyansh arya</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>132</v>
+        <v>286</v>
       </c>
       <c r="C120" t="n">
         <v>0</v>
@@ -9886,37 +9886,37 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>raghu sharma</t>
+          <t>quinton de kock</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>0</v>
+        <v>132</v>
       </c>
       <c r="C121" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>rahul chahar</t>
+          <t>raghu sharma</t>
         </is>
       </c>
       <c r="B122" t="n">
         <v>0</v>
       </c>
       <c r="C122" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>rahul tewatia</t>
+          <t>rahul chahar</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>78</v>
+        <v>0</v>
       </c>
       <c r="C123" t="n">
         <v>0</v>
@@ -9925,11 +9925,11 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>raj angad bawa</t>
+          <t>rahul tewatia</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="C124" t="n">
         <v>0</v>
@@ -9938,11 +9938,11 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>rajat patidar</t>
+          <t>raj angad bawa</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>257</v>
+        <v>0</v>
       </c>
       <c r="C125" t="n">
         <v>0</v>
@@ -9951,24 +9951,24 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>ramakrishna ghosh</t>
+          <t>rajat patidar</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>0</v>
+        <v>257</v>
       </c>
       <c r="C126" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>ramandeep singh</t>
+          <t>ramakrishna ghosh</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="C127" t="n">
         <v>1</v>
@@ -9977,89 +9977,89 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>rashid khan</t>
+          <t>ramandeep singh</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>35</v>
+        <v>82</v>
       </c>
       <c r="C128" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>rasikh salam</t>
+          <t>rashid khan</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="C129" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>ravi bishnoi</t>
+          <t>rasikh salam</t>
         </is>
       </c>
       <c r="B130" t="n">
         <v>0</v>
       </c>
       <c r="C130" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>ravichandran smaran</t>
+          <t>ravi bishnoi</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C131" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>ravindra jadeja</t>
+          <t>ravichandran smaran</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>152</v>
+        <v>4</v>
       </c>
       <c r="C132" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>rinku singh</t>
+          <t>ravindra jadeja</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>237</v>
+        <v>152</v>
       </c>
       <c r="C133" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>rishabh pant</t>
+          <t>rinku singh</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>204</v>
+        <v>237</v>
       </c>
       <c r="C134" t="n">
         <v>0</v>
@@ -10068,37 +10068,37 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>riyan parag</t>
+          <t>rishabh pant</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="C135" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>robin minz</t>
+          <t>riyan parag</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>6</v>
+        <v>207</v>
       </c>
       <c r="C136" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>rohit sharma</t>
+          <t>robin minz</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>221</v>
+        <v>6</v>
       </c>
       <c r="C137" t="n">
         <v>0</v>
@@ -10107,37 +10107,37 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>romario shepherd</t>
+          <t>rohit sharma</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>56</v>
+        <v>221</v>
       </c>
       <c r="C138" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>rovman powell</t>
+          <t>romario shepherd</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>121</v>
+        <v>56</v>
       </c>
       <c r="C139" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>ruturaj gaikwad</t>
+          <t>rovman powell</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>251</v>
+        <v>121</v>
       </c>
       <c r="C140" t="n">
         <v>0</v>
@@ -10146,11 +10146,11 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>ryan rickelton</t>
+          <t>ruturaj gaikwad</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>380</v>
+        <v>251</v>
       </c>
       <c r="C141" t="n">
         <v>0</v>
@@ -10159,11 +10159,11 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>sahil parakh</t>
+          <t>ryan rickelton</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>0</v>
+        <v>380</v>
       </c>
       <c r="C142" t="n">
         <v>0</v>
@@ -10172,37 +10172,37 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>sakib hussain</t>
+          <t>sahil parakh</t>
         </is>
       </c>
       <c r="B143" t="n">
         <v>0</v>
       </c>
       <c r="C143" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>salil arora</t>
+          <t>sakib hussain</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="C144" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>sameer rizvi</t>
+          <t>salil arora</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>249</v>
+        <v>95</v>
       </c>
       <c r="C145" t="n">
         <v>0</v>
@@ -10211,37 +10211,37 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>sandeep sharma</t>
+          <t>sameer rizvi</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>0</v>
+        <v>249</v>
       </c>
       <c r="C146" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>sanju samson</t>
+          <t>sandeep sharma</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="C147" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>sarfaraz khan</t>
+          <t>sanju samson</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>161</v>
+        <v>402</v>
       </c>
       <c r="C148" t="n">
         <v>0</v>
@@ -10250,11 +10250,11 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>shahbaz ahmed</t>
+          <t>sarfaraz khan</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>15</v>
+        <v>161</v>
       </c>
       <c r="C149" t="n">
         <v>0</v>
@@ -10263,11 +10263,11 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>shahrukh khan</t>
+          <t>shahbaz ahmed</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>43</v>
+        <v>15</v>
       </c>
       <c r="C150" t="n">
         <v>0</v>
@@ -10276,50 +10276,50 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>shardul thakur</t>
+          <t>shahrukh khan</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>14</v>
+        <v>43</v>
       </c>
       <c r="C151" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>shashank singh</t>
+          <t>shardul thakur</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>74</v>
+        <v>14</v>
       </c>
       <c r="C152" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>sherfane rutherford</t>
+          <t>shashank singh</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>103</v>
+        <v>74</v>
       </c>
       <c r="C153" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>shimron hetmyer</t>
+          <t>sherfane rutherford</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>72</v>
+        <v>103</v>
       </c>
       <c r="C154" t="n">
         <v>0</v>
@@ -10328,50 +10328,50 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>shivam dube</t>
+          <t>shimron hetmyer</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>150</v>
+        <v>72</v>
       </c>
       <c r="C155" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>shivang kumar</t>
+          <t>shivam dube</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>22</v>
+        <v>150</v>
       </c>
       <c r="C156" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>shreyas iyer</t>
+          <t>shivang kumar</t>
         </is>
       </c>
       <c r="B157" t="n">
-        <v>333</v>
+        <v>22</v>
       </c>
       <c r="C157" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>shubham badriprasad dubey</t>
+          <t>shreyas iyer</t>
         </is>
       </c>
       <c r="B158" t="n">
-        <v>56</v>
+        <v>333</v>
       </c>
       <c r="C158" t="n">
         <v>0</v>
@@ -10380,11 +10380,11 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>shubman gill</t>
+          <t>shubham badriprasad dubey</t>
         </is>
       </c>
       <c r="B159" t="n">
-        <v>378</v>
+        <v>56</v>
       </c>
       <c r="C159" t="n">
         <v>0</v>
@@ -10393,37 +10393,37 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>sunil narine</t>
+          <t>shubman gill</t>
         </is>
       </c>
       <c r="B160" t="n">
-        <v>40</v>
+        <v>378</v>
       </c>
       <c r="C160" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>suryakumar yadav</t>
+          <t>sunil narine</t>
         </is>
       </c>
       <c r="B161" t="n">
-        <v>195</v>
+        <v>40</v>
       </c>
       <c r="C161" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>suryansh shedge</t>
+          <t>suryakumar yadav</t>
         </is>
       </c>
       <c r="B162" t="n">
-        <v>85</v>
+        <v>195</v>
       </c>
       <c r="C162" t="n">
         <v>0</v>
@@ -10432,50 +10432,50 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>suyash sharma</t>
+          <t>suryansh shedge</t>
         </is>
       </c>
       <c r="B163" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="C163" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>t natarajan</t>
+          <t>suyash sharma</t>
         </is>
       </c>
       <c r="B164" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C164" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>tilak varma</t>
+          <t>t natarajan</t>
         </is>
       </c>
       <c r="B165" t="n">
-        <v>204</v>
+        <v>1</v>
       </c>
       <c r="C165" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>tim david</t>
+          <t>tilak varma</t>
         </is>
       </c>
       <c r="B166" t="n">
-        <v>192</v>
+        <v>204</v>
       </c>
       <c r="C166" t="n">
         <v>0</v>
@@ -10484,11 +10484,11 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>tim seifert</t>
+          <t>tim david</t>
         </is>
       </c>
       <c r="B167" t="n">
-        <v>19</v>
+        <v>192</v>
       </c>
       <c r="C167" t="n">
         <v>0</v>
@@ -10497,11 +10497,11 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>travis head</t>
+          <t>tim seifert</t>
         </is>
       </c>
       <c r="B168" t="n">
-        <v>361</v>
+        <v>19</v>
       </c>
       <c r="C168" t="n">
         <v>0</v>
@@ -10510,167 +10510,167 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>trent boult</t>
+          <t>travis head</t>
         </is>
       </c>
       <c r="B169" t="n">
-        <v>8</v>
+        <v>361</v>
       </c>
       <c r="C169" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>tristan stubbs</t>
+          <t>trent boult</t>
         </is>
       </c>
       <c r="B170" t="n">
-        <v>257</v>
+        <v>8</v>
       </c>
       <c r="C170" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>tushar deshpande</t>
+          <t>tristan stubbs</t>
         </is>
       </c>
       <c r="B171" t="n">
-        <v>25</v>
+        <v>257</v>
       </c>
       <c r="C171" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>urvil patel</t>
+          <t>tushar deshpande</t>
         </is>
       </c>
       <c r="B172" t="n">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="C172" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>vaibhav arora</t>
+          <t>urvil patel</t>
         </is>
       </c>
       <c r="B173" t="n">
-        <v>1</v>
+        <v>45</v>
       </c>
       <c r="C173" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>vaibhav suryavanshi</t>
+          <t>vaibhav arora</t>
         </is>
       </c>
       <c r="B174" t="n">
-        <v>404</v>
+        <v>1</v>
       </c>
       <c r="C174" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>varun chakravarthy</t>
+          <t>vaibhav suryavanshi</t>
         </is>
       </c>
       <c r="B175" t="n">
-        <v>0</v>
+        <v>404</v>
       </c>
       <c r="C175" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>venkatesh iyer</t>
+          <t>varun chakravarthy</t>
         </is>
       </c>
       <c r="B176" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="C176" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>vijaykumar vyshak</t>
+          <t>venkatesh iyer</t>
         </is>
       </c>
       <c r="B177" t="n">
-        <v>2</v>
+        <v>41</v>
       </c>
       <c r="C177" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>vipraj nigam</t>
+          <t>vijaykumar vyshak</t>
         </is>
       </c>
       <c r="B178" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="C178" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>virat kohli</t>
+          <t>vipraj nigam</t>
         </is>
       </c>
       <c r="B179" t="n">
-        <v>379</v>
+        <v>12</v>
       </c>
       <c r="C179" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>washington sundar</t>
+          <t>virat kohli</t>
         </is>
       </c>
       <c r="B180" t="n">
-        <v>209</v>
+        <v>379</v>
       </c>
       <c r="C180" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>will jacks</t>
+          <t>washington sundar</t>
         </is>
       </c>
       <c r="B181" t="n">
-        <v>57</v>
+        <v>209</v>
       </c>
       <c r="C181" t="n">
         <v>1</v>
@@ -10679,52 +10679,65 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>xavier bartlett</t>
+          <t>will jacks</t>
         </is>
       </c>
       <c r="B182" t="n">
-        <v>11</v>
+        <v>57</v>
       </c>
       <c r="C182" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>yash raj punja</t>
+          <t>xavier bartlett</t>
         </is>
       </c>
       <c r="B183" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="C183" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>yashasvi jaiswal</t>
+          <t>yash raj punja</t>
         </is>
       </c>
       <c r="B184" t="n">
-        <v>312</v>
+        <v>0</v>
       </c>
       <c r="C184" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
+          <t>yashasvi jaiswal</t>
+        </is>
+      </c>
+      <c r="B185" t="n">
+        <v>312</v>
+      </c>
+      <c r="C185" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
           <t>yuzvendra chahal</t>
         </is>
       </c>
-      <c r="B185" t="n">
-        <v>0</v>
-      </c>
-      <c r="C185" t="n">
+      <c r="B186" t="n">
+        <v>0</v>
+      </c>
+      <c r="C186" t="n">
         <v>8</v>
       </c>
     </row>
@@ -10739,7 +10752,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K30"/>
+  <dimension ref="A1:K29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11318,7 +11331,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Arshin Kulkarni</t>
+          <t>Jayant Yadav</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -11328,13 +11341,13 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>ashwani kumar</t>
+          <t>mayank yadav</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -11361,7 +11374,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Jayant Yadav</t>
+          <t>Ajay Mandal</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -11377,7 +11390,7 @@
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>mayank yadav</t>
+          <t>rajat patidar</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -11404,7 +11417,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Ajay Mandal</t>
+          <t>Matheesha Pathirana</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -11414,13 +11427,13 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>rajat patidar</t>
+          <t>eshan malinga</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -11447,7 +11460,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Matheesha Pathirana</t>
+          <t>Ben Dwarshuis</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -11463,7 +11476,7 @@
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>eshan malinga</t>
+          <t>b sai sudharshan</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -11490,12 +11503,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Ben Dwarshuis</t>
+          <t>Arjun Tendulkar</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>NAKUL11</t>
+          <t>SKY11</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -11506,7 +11519,7 @@
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>b sai sudharshan</t>
+          <t>karun nair</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -11533,7 +11546,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Arjun Tendulkar</t>
+          <t>Kwena Maphaka</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -11549,7 +11562,7 @@
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>karun nair</t>
+          <t>aiden markram</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -11576,23 +11589,23 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Kwena Maphaka</t>
+          <t>Azmatullah Omarzai</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>SKY11</t>
+          <t>HARSH11</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>aiden markram</t>
+          <t>mitchell marsh</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -11619,23 +11632,23 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Azmatullah Omarzai</t>
+          <t>Tejasvi Singh</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>HARSH11</t>
+          <t>AMEY11</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>mitchell marsh</t>
+          <t>prabhsimran singh</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -11662,7 +11675,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Tejasvi Singh</t>
+          <t>Sai Kishor</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -11672,13 +11685,13 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>prabhsimran singh</t>
+          <t>ishan kishan</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -11705,7 +11718,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Sai Kishor</t>
+          <t>Akash Deep</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -11721,7 +11734,7 @@
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>ishan kishan</t>
+          <t>arshdeep singh</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -11748,23 +11761,23 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Akash Deep</t>
+          <t>Ben Duckett</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>AMEY11</t>
+          <t>PRATIK11</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>arshdeep singh</t>
+          <t>ryan rickelton</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -11791,7 +11804,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Ben Duckett</t>
+          <t>Rahul Tripathi</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -11807,7 +11820,7 @@
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>ryan rickelton</t>
+          <t>rahul tewatia</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -11834,7 +11847,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rahul Tripathi</t>
+          <t>Dre Pretorius</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -11850,7 +11863,7 @@
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>rahul tewatia</t>
+          <t>lhuan dre pretorius</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -11877,7 +11890,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Dre Pretorius</t>
+          <t>Matthew Breetzke</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -11893,7 +11906,7 @@
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>lhuan dre pretorius</t>
+          <t>matt henry</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -11920,7 +11933,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Matthew Breetzke</t>
+          <t>Anuj Rawat</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -11936,7 +11949,7 @@
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>matt henry</t>
+          <t>mayank rawat</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -11963,7 +11976,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Anuj Rawat</t>
+          <t>Wanindu Hasaranga</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -11973,13 +11986,13 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
-          <t>mayank rawat</t>
+          <t>ravichandran smaran</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -12000,49 +12013,6 @@
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Wanindu Hasaranga</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>PRATIK11</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>AR</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>ravichandran smaran</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>no_stats_yet</t>
-        </is>
-      </c>
-      <c r="G30" t="n">
-        <v>0</v>
-      </c>
-      <c r="H30" t="n">
-        <v>0</v>
-      </c>
-      <c r="I30" t="n">
-        <v>0</v>
-      </c>
-      <c r="J30" t="n">
-        <v>0</v>
-      </c>
-      <c r="K30" t="n">
         <v>0</v>
       </c>
     </row>

--- a/IPL_Fantasy_Points.xlsx
+++ b/IPL_Fantasy_Points.xlsx
@@ -561,19 +561,19 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>204</v>
+        <v>236</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>204</v>
+        <v>236</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>204</v>
+        <v>236</v>
       </c>
     </row>
     <row r="4">
@@ -647,19 +647,19 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="6">
@@ -690,19 +690,19 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>257</v>
+        <v>318</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>257</v>
+        <v>318</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>257</v>
+        <v>318</v>
       </c>
     </row>
     <row r="7">
@@ -862,19 +862,19 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>199</v>
+        <v>232</v>
       </c>
       <c r="H10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I10" t="n">
-        <v>199</v>
+        <v>232</v>
       </c>
       <c r="J10" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="K10" t="n">
-        <v>259</v>
+        <v>312</v>
       </c>
     </row>
     <row r="11">
@@ -951,16 +951,16 @@
         <v>39</v>
       </c>
       <c r="H12" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I12" t="n">
         <v>39</v>
       </c>
       <c r="J12" t="n">
-        <v>120</v>
+        <v>160</v>
       </c>
       <c r="K12" t="n">
-        <v>159</v>
+        <v>199</v>
       </c>
     </row>
     <row r="13">
@@ -1292,19 +1292,19 @@
         </is>
       </c>
       <c r="G20" t="n">
-        <v>205</v>
+        <v>218</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>205</v>
+        <v>218</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>205</v>
+        <v>218</v>
       </c>
     </row>
     <row r="21">
@@ -1464,19 +1464,19 @@
         </is>
       </c>
       <c r="G24" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
     </row>
     <row r="25">
@@ -1507,19 +1507,19 @@
         </is>
       </c>
       <c r="G25" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="H25" t="n">
         <v>2</v>
       </c>
       <c r="I25" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="J25" t="n">
         <v>40</v>
       </c>
       <c r="K25" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
     </row>
     <row r="26">
@@ -2238,19 +2238,19 @@
         </is>
       </c>
       <c r="G42" t="n">
-        <v>56</v>
+        <v>79</v>
       </c>
       <c r="H42" t="n">
         <v>5</v>
       </c>
       <c r="I42" t="n">
-        <v>56</v>
+        <v>79</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>56</v>
+        <v>79</v>
       </c>
     </row>
     <row r="43">
@@ -3786,19 +3786,19 @@
         </is>
       </c>
       <c r="G78" t="n">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="H78" t="n">
         <v>0</v>
       </c>
       <c r="I78" t="n">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
       </c>
       <c r="K78" t="n">
-        <v>257</v>
+        <v>259</v>
       </c>
     </row>
     <row r="79">
@@ -3915,19 +3915,19 @@
         </is>
       </c>
       <c r="G81" t="n">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="H81" t="n">
         <v>0</v>
       </c>
       <c r="I81" t="n">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
       </c>
       <c r="K81" t="n">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="82">
@@ -3958,19 +3958,19 @@
         </is>
       </c>
       <c r="G82" t="n">
-        <v>192</v>
+        <v>232</v>
       </c>
       <c r="H82" t="n">
         <v>0</v>
       </c>
       <c r="I82" t="n">
-        <v>192</v>
+        <v>232</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
       </c>
       <c r="K82" t="n">
-        <v>192</v>
+        <v>232</v>
       </c>
     </row>
     <row r="83">
@@ -4219,16 +4219,16 @@
         <v>0</v>
       </c>
       <c r="H88" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I88" t="n">
         <v>0</v>
       </c>
       <c r="J88" t="n">
-        <v>120</v>
+        <v>140</v>
       </c>
       <c r="K88" t="n">
-        <v>120</v>
+        <v>140</v>
       </c>
     </row>
     <row r="89">
@@ -4345,19 +4345,19 @@
         </is>
       </c>
       <c r="G91" t="n">
-        <v>445</v>
+        <v>468</v>
       </c>
       <c r="H91" t="n">
         <v>0</v>
       </c>
       <c r="I91" t="n">
-        <v>445</v>
+        <v>468</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
       </c>
       <c r="K91" t="n">
-        <v>445</v>
+        <v>468</v>
       </c>
     </row>
     <row r="92">
@@ -4821,16 +4821,16 @@
         <v>0</v>
       </c>
       <c r="H102" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I102" t="n">
         <v>0</v>
       </c>
       <c r="J102" t="n">
-        <v>160</v>
+        <v>180</v>
       </c>
       <c r="K102" t="n">
-        <v>160</v>
+        <v>180</v>
       </c>
     </row>
     <row r="103">
@@ -5119,19 +5119,19 @@
         </is>
       </c>
       <c r="G109" t="n">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="H109" t="n">
         <v>0</v>
       </c>
       <c r="I109" t="n">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
       </c>
       <c r="K109" t="n">
-        <v>363</v>
+        <v>367</v>
       </c>
     </row>
     <row r="110">
@@ -5291,19 +5291,19 @@
         </is>
       </c>
       <c r="G113" t="n">
-        <v>228</v>
+        <v>278</v>
       </c>
       <c r="H113" t="n">
         <v>0</v>
       </c>
       <c r="I113" t="n">
-        <v>228</v>
+        <v>278</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
       </c>
       <c r="K113" t="n">
-        <v>228</v>
+        <v>278</v>
       </c>
     </row>
     <row r="114">
@@ -5509,16 +5509,16 @@
         <v>11</v>
       </c>
       <c r="H118" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="I118" t="n">
         <v>0</v>
       </c>
       <c r="J118" t="n">
-        <v>220</v>
+        <v>260</v>
       </c>
       <c r="K118" t="n">
-        <v>220</v>
+        <v>260</v>
       </c>
     </row>
     <row r="119">
@@ -5549,7 +5549,7 @@
         </is>
       </c>
       <c r="G119" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H119" t="n">
         <v>8</v>
@@ -5850,19 +5850,19 @@
         </is>
       </c>
       <c r="G126" t="n">
-        <v>282</v>
+        <v>316</v>
       </c>
       <c r="H126" t="n">
         <v>0</v>
       </c>
       <c r="I126" t="n">
-        <v>282</v>
+        <v>316</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
       </c>
       <c r="K126" t="n">
-        <v>282</v>
+        <v>316</v>
       </c>
     </row>
     <row r="127">
@@ -6022,19 +6022,19 @@
         </is>
       </c>
       <c r="G130" t="n">
-        <v>72</v>
+        <v>111</v>
       </c>
       <c r="H130" t="n">
         <v>0</v>
       </c>
       <c r="I130" t="n">
-        <v>72</v>
+        <v>111</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
       </c>
       <c r="K130" t="n">
-        <v>72</v>
+        <v>111</v>
       </c>
     </row>
     <row r="131">
@@ -6151,19 +6151,19 @@
         </is>
       </c>
       <c r="G133" t="n">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="H133" t="n">
         <v>0</v>
       </c>
       <c r="I133" t="n">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
       </c>
       <c r="K133" t="n">
-        <v>249</v>
+        <v>252</v>
       </c>
     </row>
     <row r="134">
@@ -6194,19 +6194,19 @@
         </is>
       </c>
       <c r="G134" t="n">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H134" t="n">
         <v>0</v>
       </c>
       <c r="I134" t="n">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
       </c>
       <c r="K134" t="n">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="135">
@@ -6323,19 +6323,19 @@
         </is>
       </c>
       <c r="G137" t="n">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="H137" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I137" t="n">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="J137" t="n">
-        <v>180</v>
+        <v>200</v>
       </c>
       <c r="K137" t="n">
-        <v>213</v>
+        <v>244</v>
       </c>
     </row>
     <row r="138">
@@ -6541,16 +6541,16 @@
         <v>31</v>
       </c>
       <c r="H142" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I142" t="n">
         <v>0</v>
       </c>
       <c r="J142" t="n">
-        <v>160</v>
+        <v>180</v>
       </c>
       <c r="K142" t="n">
-        <v>160</v>
+        <v>180</v>
       </c>
     </row>
     <row r="143">
@@ -6710,19 +6710,19 @@
         </is>
       </c>
       <c r="G146" t="n">
-        <v>159</v>
+        <v>183</v>
       </c>
       <c r="H146" t="n">
         <v>0</v>
       </c>
       <c r="I146" t="n">
-        <v>159</v>
+        <v>183</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
       </c>
       <c r="K146" t="n">
-        <v>159</v>
+        <v>183</v>
       </c>
     </row>
     <row r="147">
@@ -6753,19 +6753,19 @@
         </is>
       </c>
       <c r="G147" t="n">
-        <v>217</v>
+        <v>225</v>
       </c>
       <c r="H147" t="n">
         <v>0</v>
       </c>
       <c r="I147" t="n">
-        <v>217</v>
+        <v>225</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
       </c>
       <c r="K147" t="n">
-        <v>217</v>
+        <v>225</v>
       </c>
     </row>
     <row r="148">
@@ -7011,19 +7011,19 @@
         </is>
       </c>
       <c r="G153" t="n">
-        <v>40</v>
+        <v>68</v>
       </c>
       <c r="H153" t="n">
         <v>10</v>
       </c>
       <c r="I153" t="n">
-        <v>40</v>
+        <v>68</v>
       </c>
       <c r="J153" t="n">
         <v>200</v>
       </c>
       <c r="K153" t="n">
-        <v>240</v>
+        <v>268</v>
       </c>
     </row>
     <row r="154">
@@ -7229,16 +7229,16 @@
         <v>1</v>
       </c>
       <c r="H158" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I158" t="n">
         <v>0</v>
       </c>
       <c r="J158" t="n">
-        <v>200</v>
+        <v>220</v>
       </c>
       <c r="K158" t="n">
-        <v>200</v>
+        <v>220</v>
       </c>
     </row>
     <row r="159">
@@ -7570,19 +7570,19 @@
         </is>
       </c>
       <c r="G166" t="n">
-        <v>110</v>
+        <v>210</v>
       </c>
       <c r="H166" t="n">
         <v>0</v>
       </c>
       <c r="I166" t="n">
-        <v>110</v>
+        <v>210</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
       </c>
       <c r="K166" t="n">
-        <v>110</v>
+        <v>210</v>
       </c>
     </row>
     <row r="167">
@@ -7831,16 +7831,16 @@
         <v>40</v>
       </c>
       <c r="H172" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I172" t="n">
         <v>40</v>
       </c>
       <c r="J172" t="n">
-        <v>180</v>
+        <v>200</v>
       </c>
       <c r="K172" t="n">
-        <v>220</v>
+        <v>240</v>
       </c>
     </row>
     <row r="173">
@@ -8185,7 +8185,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>3292</v>
+        <v>3355</v>
       </c>
     </row>
     <row r="3">
@@ -8198,7 +8198,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2925</v>
+        <v>2945</v>
       </c>
     </row>
     <row r="4">
@@ -8207,11 +8207,11 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>NAKUL11</t>
+          <t>SKY11</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2646</v>
+        <v>2731</v>
       </c>
     </row>
     <row r="5">
@@ -8220,11 +8220,11 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>SKY11</t>
+          <t>NAKUL11</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2637</v>
+        <v>2689</v>
       </c>
     </row>
     <row r="6">
@@ -8233,11 +8233,11 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>BABA11</t>
+          <t>AMEY11</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2606</v>
+        <v>2675</v>
       </c>
     </row>
     <row r="7">
@@ -8246,11 +8246,11 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>AMEY11</t>
+          <t>BABA11</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2595</v>
+        <v>2606</v>
       </c>
     </row>
     <row r="8">
@@ -8263,7 +8263,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2338</v>
+        <v>2525</v>
       </c>
     </row>
     <row r="9">
@@ -8272,11 +8272,11 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>VATSAL11</t>
+          <t>HARSH11</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2174</v>
+        <v>2287</v>
       </c>
     </row>
     <row r="10">
@@ -8285,11 +8285,11 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>HARSH11</t>
+          <t>VATSAL11</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2159</v>
+        <v>2197</v>
       </c>
     </row>
     <row r="11">
@@ -8302,7 +8302,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1765</v>
+        <v>1885</v>
       </c>
     </row>
   </sheetData>
@@ -8395,7 +8395,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
@@ -8408,7 +8408,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>205</v>
+        <v>218</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
@@ -8460,7 +8460,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C11" t="n">
         <v>0</v>
@@ -8515,7 +8515,7 @@
         <v>39</v>
       </c>
       <c r="C15" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16">
@@ -8577,7 +8577,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>72</v>
+        <v>111</v>
       </c>
       <c r="C20" t="n">
         <v>0</v>
@@ -8629,10 +8629,10 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="C24" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="25">
@@ -8720,10 +8720,10 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>199</v>
+        <v>232</v>
       </c>
       <c r="C31" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="32">
@@ -8824,7 +8824,7 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>282</v>
+        <v>316</v>
       </c>
       <c r="C39" t="n">
         <v>0</v>
@@ -8928,7 +8928,7 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>110</v>
+        <v>210</v>
       </c>
       <c r="C47" t="n">
         <v>0</v>
@@ -9071,7 +9071,7 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="C58" t="n">
         <v>0</v>
@@ -9149,7 +9149,7 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C64" t="n">
         <v>0</v>
@@ -9191,7 +9191,7 @@
         <v>0</v>
       </c>
       <c r="C67" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="68">
@@ -9243,7 +9243,7 @@
         <v>11</v>
       </c>
       <c r="C71" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="72">
@@ -9292,7 +9292,7 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>40</v>
+        <v>68</v>
       </c>
       <c r="C75" t="n">
         <v>10</v>
@@ -9383,7 +9383,7 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>445</v>
+        <v>468</v>
       </c>
       <c r="C82" t="n">
         <v>0</v>
@@ -9396,7 +9396,7 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C83" t="n">
         <v>8</v>
@@ -9539,7 +9539,7 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="C94" t="n">
         <v>0</v>
@@ -9581,7 +9581,7 @@
         <v>31</v>
       </c>
       <c r="C97" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="98">
@@ -9708,7 +9708,7 @@
         </is>
       </c>
       <c r="B107" t="n">
-        <v>159</v>
+        <v>183</v>
       </c>
       <c r="C107" t="n">
         <v>0</v>
@@ -9747,7 +9747,7 @@
         </is>
       </c>
       <c r="B110" t="n">
-        <v>217</v>
+        <v>225</v>
       </c>
       <c r="C110" t="n">
         <v>0</v>
@@ -9786,7 +9786,7 @@
         </is>
       </c>
       <c r="B113" t="n">
-        <v>228</v>
+        <v>278</v>
       </c>
       <c r="C113" t="n">
         <v>0</v>
@@ -9867,7 +9867,7 @@
         <v>0</v>
       </c>
       <c r="C119" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="120">
@@ -9955,7 +9955,7 @@
         </is>
       </c>
       <c r="B126" t="n">
-        <v>257</v>
+        <v>318</v>
       </c>
       <c r="C126" t="n">
         <v>0</v>
@@ -10010,7 +10010,7 @@
         <v>0</v>
       </c>
       <c r="C130" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="131">
@@ -10072,7 +10072,7 @@
         </is>
       </c>
       <c r="B135" t="n">
-        <v>204</v>
+        <v>236</v>
       </c>
       <c r="C135" t="n">
         <v>0</v>
@@ -10124,7 +10124,7 @@
         </is>
       </c>
       <c r="B139" t="n">
-        <v>56</v>
+        <v>79</v>
       </c>
       <c r="C139" t="n">
         <v>5</v>
@@ -10215,7 +10215,7 @@
         </is>
       </c>
       <c r="B146" t="n">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="C146" t="n">
         <v>0</v>
@@ -10270,7 +10270,7 @@
         <v>15</v>
       </c>
       <c r="C150" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="151">
@@ -10413,7 +10413,7 @@
         <v>40</v>
       </c>
       <c r="C161" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="162">
@@ -10488,7 +10488,7 @@
         </is>
       </c>
       <c r="B167" t="n">
-        <v>192</v>
+        <v>232</v>
       </c>
       <c r="C167" t="n">
         <v>0</v>
@@ -10540,7 +10540,7 @@
         </is>
       </c>
       <c r="B171" t="n">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="C171" t="n">
         <v>0</v>
@@ -10582,7 +10582,7 @@
         <v>1</v>
       </c>
       <c r="C174" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="175">
@@ -10644,7 +10644,7 @@
         </is>
       </c>
       <c r="B179" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C179" t="n">
         <v>2</v>

--- a/IPL_Fantasy_Points.xlsx
+++ b/IPL_Fantasy_Points.xlsx
@@ -994,16 +994,16 @@
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>220</v>
+        <v>240</v>
       </c>
       <c r="K13" t="n">
-        <v>220</v>
+        <v>240</v>
       </c>
     </row>
     <row r="14">
@@ -1249,19 +1249,19 @@
         </is>
       </c>
       <c r="G19" t="n">
-        <v>378</v>
+        <v>462</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>378</v>
+        <v>462</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>378</v>
+        <v>462</v>
       </c>
     </row>
     <row r="20">
@@ -1335,19 +1335,19 @@
         </is>
       </c>
       <c r="G21" t="n">
-        <v>404</v>
+        <v>440</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>404</v>
+        <v>440</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>404</v>
+        <v>440</v>
       </c>
     </row>
     <row r="22">
@@ -1550,19 +1550,19 @@
         </is>
       </c>
       <c r="G26" t="n">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>78</v>
+        <v>92</v>
       </c>
     </row>
     <row r="27">
@@ -1593,19 +1593,19 @@
         </is>
       </c>
       <c r="G27" t="n">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="H27" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="I27" t="n">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="J27" t="n">
-        <v>140</v>
+        <v>200</v>
       </c>
       <c r="K27" t="n">
-        <v>180</v>
+        <v>247</v>
       </c>
     </row>
     <row r="28">
@@ -1679,7 +1679,7 @@
         </is>
       </c>
       <c r="G29" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H29" t="n">
         <v>4</v>
@@ -2281,19 +2281,19 @@
         </is>
       </c>
       <c r="G43" t="n">
-        <v>152</v>
+        <v>190</v>
       </c>
       <c r="H43" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I43" t="n">
-        <v>152</v>
+        <v>190</v>
       </c>
       <c r="J43" t="n">
-        <v>140</v>
+        <v>160</v>
       </c>
       <c r="K43" t="n">
-        <v>292</v>
+        <v>350</v>
       </c>
     </row>
     <row r="44">
@@ -2883,19 +2883,19 @@
         </is>
       </c>
       <c r="G57" t="n">
-        <v>290</v>
+        <v>314</v>
       </c>
       <c r="H57" t="n">
         <v>0</v>
       </c>
       <c r="I57" t="n">
-        <v>290</v>
+        <v>314</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
       </c>
       <c r="K57" t="n">
-        <v>290</v>
+        <v>314</v>
       </c>
     </row>
     <row r="58">
@@ -3187,16 +3187,16 @@
         <v>35</v>
       </c>
       <c r="H64" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="I64" t="n">
         <v>35</v>
       </c>
       <c r="J64" t="n">
-        <v>220</v>
+        <v>300</v>
       </c>
       <c r="K64" t="n">
-        <v>255</v>
+        <v>335</v>
       </c>
     </row>
     <row r="65">
@@ -3571,19 +3571,19 @@
         </is>
       </c>
       <c r="G73" t="n">
-        <v>385</v>
+        <v>440</v>
       </c>
       <c r="H73" t="n">
         <v>0</v>
       </c>
       <c r="I73" t="n">
-        <v>385</v>
+        <v>440</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
       </c>
       <c r="K73" t="n">
-        <v>385</v>
+        <v>440</v>
       </c>
     </row>
     <row r="74">
@@ -4302,19 +4302,19 @@
         </is>
       </c>
       <c r="G90" t="n">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="H90" t="n">
         <v>0</v>
       </c>
       <c r="I90" t="n">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
       </c>
       <c r="K90" t="n">
-        <v>312</v>
+        <v>315</v>
       </c>
     </row>
     <row r="91">
@@ -4431,19 +4431,19 @@
         </is>
       </c>
       <c r="G93" t="n">
-        <v>335</v>
+        <v>348</v>
       </c>
       <c r="H93" t="n">
         <v>0</v>
       </c>
       <c r="I93" t="n">
-        <v>335</v>
+        <v>348</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
       </c>
       <c r="K93" t="n">
-        <v>335</v>
+        <v>348</v>
       </c>
     </row>
     <row r="94">
@@ -4778,16 +4778,16 @@
         <v>35</v>
       </c>
       <c r="H101" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="I101" t="n">
         <v>0</v>
       </c>
       <c r="J101" t="n">
-        <v>320</v>
+        <v>360</v>
       </c>
       <c r="K101" t="n">
-        <v>320</v>
+        <v>360</v>
       </c>
     </row>
     <row r="102">
@@ -5205,19 +5205,19 @@
         </is>
       </c>
       <c r="G111" t="n">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="H111" t="n">
         <v>0</v>
       </c>
       <c r="I111" t="n">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
       </c>
       <c r="K111" t="n">
-        <v>72</v>
+        <v>78</v>
       </c>
     </row>
     <row r="112">
@@ -5420,19 +5420,19 @@
         </is>
       </c>
       <c r="G116" t="n">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="H116" t="n">
         <v>1</v>
       </c>
       <c r="I116" t="n">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="J116" t="n">
         <v>20</v>
       </c>
       <c r="K116" t="n">
-        <v>249</v>
+        <v>253</v>
       </c>
     </row>
     <row r="117">
@@ -6280,19 +6280,19 @@
         </is>
       </c>
       <c r="G136" t="n">
-        <v>209</v>
+        <v>246</v>
       </c>
       <c r="H136" t="n">
         <v>1</v>
       </c>
       <c r="I136" t="n">
-        <v>209</v>
+        <v>246</v>
       </c>
       <c r="J136" t="n">
         <v>20</v>
       </c>
       <c r="K136" t="n">
-        <v>229</v>
+        <v>266</v>
       </c>
     </row>
     <row r="137">
@@ -7054,19 +7054,19 @@
         </is>
       </c>
       <c r="G154" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="H154" t="n">
         <v>15</v>
       </c>
       <c r="I154" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="J154" t="n">
         <v>300</v>
       </c>
       <c r="K154" t="n">
-        <v>314</v>
+        <v>319</v>
       </c>
     </row>
     <row r="155">
@@ -8185,7 +8185,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>3355</v>
+        <v>3410</v>
       </c>
     </row>
     <row r="3">
@@ -8198,7 +8198,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2945</v>
+        <v>3146</v>
       </c>
     </row>
     <row r="4">
@@ -8207,11 +8207,11 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>SKY11</t>
+          <t>NAKUL11</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2731</v>
+        <v>2745</v>
       </c>
     </row>
     <row r="5">
@@ -8220,11 +8220,11 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>NAKUL11</t>
+          <t>SKY11</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2689</v>
+        <v>2741</v>
       </c>
     </row>
     <row r="6">
@@ -8233,11 +8233,11 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>AMEY11</t>
+          <t>BABA11</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2675</v>
+        <v>2710</v>
       </c>
     </row>
     <row r="7">
@@ -8246,11 +8246,11 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>BABA11</t>
+          <t>AMEY11</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2606</v>
+        <v>2680</v>
       </c>
     </row>
     <row r="8">
@@ -8263,7 +8263,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2525</v>
+        <v>2545</v>
       </c>
     </row>
     <row r="9">
@@ -8276,7 +8276,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2287</v>
+        <v>2324</v>
       </c>
     </row>
     <row r="10">
@@ -8289,7 +8289,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2197</v>
+        <v>2255</v>
       </c>
     </row>
     <row r="11">
@@ -8316,7 +8316,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C186"/>
+  <dimension ref="A1:C187"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8668,7 +8668,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>385</v>
+        <v>440</v>
       </c>
       <c r="C27" t="n">
         <v>0</v>
@@ -8707,10 +8707,10 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C30" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="31">
@@ -8772,7 +8772,7 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="C35" t="n">
         <v>0</v>
@@ -8850,7 +8850,7 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>290</v>
+        <v>314</v>
       </c>
       <c r="C41" t="n">
         <v>0</v>
@@ -8889,7 +8889,7 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="C44" t="n">
         <v>1</v>
@@ -9110,10 +9110,10 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="C61" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="62">
@@ -9162,7 +9162,7 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="C65" t="n">
         <v>15</v>
@@ -9175,7 +9175,7 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>335</v>
+        <v>348</v>
       </c>
       <c r="C66" t="n">
         <v>0</v>
@@ -9217,7 +9217,7 @@
         <v>35</v>
       </c>
       <c r="C69" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="70">
@@ -9594,7 +9594,7 @@
         <v>0</v>
       </c>
       <c r="C98" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="99">
@@ -9929,7 +9929,7 @@
         </is>
       </c>
       <c r="B124" t="n">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="C124" t="n">
         <v>0</v>
@@ -9997,7 +9997,7 @@
         <v>35</v>
       </c>
       <c r="C129" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="130">
@@ -10046,20 +10046,20 @@
         </is>
       </c>
       <c r="B133" t="n">
-        <v>152</v>
+        <v>190</v>
       </c>
       <c r="C133" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>rinku singh</t>
+          <t>ravisrinivasan sai kishore</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>237</v>
+        <v>0</v>
       </c>
       <c r="C134" t="n">
         <v>0</v>
@@ -10068,11 +10068,11 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>rishabh pant</t>
+          <t>rinku singh</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C135" t="n">
         <v>0</v>
@@ -10081,37 +10081,37 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>riyan parag</t>
+          <t>rishabh pant</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>207</v>
+        <v>236</v>
       </c>
       <c r="C136" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>robin minz</t>
+          <t>riyan parag</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>6</v>
+        <v>207</v>
       </c>
       <c r="C137" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>rohit sharma</t>
+          <t>robin minz</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>221</v>
+        <v>6</v>
       </c>
       <c r="C138" t="n">
         <v>0</v>
@@ -10120,37 +10120,37 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>romario shepherd</t>
+          <t>rohit sharma</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>79</v>
+        <v>221</v>
       </c>
       <c r="C139" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>rovman powell</t>
+          <t>romario shepherd</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>121</v>
+        <v>79</v>
       </c>
       <c r="C140" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>ruturaj gaikwad</t>
+          <t>rovman powell</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>251</v>
+        <v>121</v>
       </c>
       <c r="C141" t="n">
         <v>0</v>
@@ -10159,11 +10159,11 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>ryan rickelton</t>
+          <t>ruturaj gaikwad</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>380</v>
+        <v>251</v>
       </c>
       <c r="C142" t="n">
         <v>0</v>
@@ -10172,11 +10172,11 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>sahil parakh</t>
+          <t>ryan rickelton</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>0</v>
+        <v>380</v>
       </c>
       <c r="C143" t="n">
         <v>0</v>
@@ -10185,37 +10185,37 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>sakib hussain</t>
+          <t>sahil parakh</t>
         </is>
       </c>
       <c r="B144" t="n">
         <v>0</v>
       </c>
       <c r="C144" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>salil arora</t>
+          <t>sakib hussain</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="C145" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>sameer rizvi</t>
+          <t>salil arora</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>252</v>
+        <v>95</v>
       </c>
       <c r="C146" t="n">
         <v>0</v>
@@ -10224,37 +10224,37 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>sandeep sharma</t>
+          <t>sameer rizvi</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>0</v>
+        <v>252</v>
       </c>
       <c r="C147" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>sanju samson</t>
+          <t>sandeep sharma</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="C148" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>sarfaraz khan</t>
+          <t>sanju samson</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>161</v>
+        <v>402</v>
       </c>
       <c r="C149" t="n">
         <v>0</v>
@@ -10263,76 +10263,76 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>shahbaz ahmed</t>
+          <t>sarfaraz khan</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>15</v>
+        <v>161</v>
       </c>
       <c r="C150" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>shahrukh khan</t>
+          <t>shahbaz ahmed</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>43</v>
+        <v>15</v>
       </c>
       <c r="C151" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>shardul thakur</t>
+          <t>shahrukh khan</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>14</v>
+        <v>43</v>
       </c>
       <c r="C152" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>shashank singh</t>
+          <t>shardul thakur</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>74</v>
+        <v>14</v>
       </c>
       <c r="C153" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>sherfane rutherford</t>
+          <t>shashank singh</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>103</v>
+        <v>74</v>
       </c>
       <c r="C154" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>shimron hetmyer</t>
+          <t>sherfane rutherford</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>72</v>
+        <v>103</v>
       </c>
       <c r="C155" t="n">
         <v>0</v>
@@ -10341,50 +10341,50 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>shivam dube</t>
+          <t>shimron hetmyer</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>150</v>
+        <v>78</v>
       </c>
       <c r="C156" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>shivang kumar</t>
+          <t>shivam dube</t>
         </is>
       </c>
       <c r="B157" t="n">
-        <v>22</v>
+        <v>150</v>
       </c>
       <c r="C157" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>shreyas iyer</t>
+          <t>shivang kumar</t>
         </is>
       </c>
       <c r="B158" t="n">
-        <v>333</v>
+        <v>22</v>
       </c>
       <c r="C158" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>shubham badriprasad dubey</t>
+          <t>shreyas iyer</t>
         </is>
       </c>
       <c r="B159" t="n">
-        <v>56</v>
+        <v>333</v>
       </c>
       <c r="C159" t="n">
         <v>0</v>
@@ -10393,11 +10393,11 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>shubman gill</t>
+          <t>shubham badriprasad dubey</t>
         </is>
       </c>
       <c r="B160" t="n">
-        <v>378</v>
+        <v>71</v>
       </c>
       <c r="C160" t="n">
         <v>0</v>
@@ -10406,37 +10406,37 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>sunil narine</t>
+          <t>shubman gill</t>
         </is>
       </c>
       <c r="B161" t="n">
-        <v>40</v>
+        <v>462</v>
       </c>
       <c r="C161" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>suryakumar yadav</t>
+          <t>sunil narine</t>
         </is>
       </c>
       <c r="B162" t="n">
-        <v>195</v>
+        <v>40</v>
       </c>
       <c r="C162" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>suryansh shedge</t>
+          <t>suryakumar yadav</t>
         </is>
       </c>
       <c r="B163" t="n">
-        <v>85</v>
+        <v>195</v>
       </c>
       <c r="C163" t="n">
         <v>0</v>
@@ -10445,50 +10445,50 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>suyash sharma</t>
+          <t>suryansh shedge</t>
         </is>
       </c>
       <c r="B164" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="C164" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>t natarajan</t>
+          <t>suyash sharma</t>
         </is>
       </c>
       <c r="B165" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C165" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>tilak varma</t>
+          <t>t natarajan</t>
         </is>
       </c>
       <c r="B166" t="n">
-        <v>204</v>
+        <v>1</v>
       </c>
       <c r="C166" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>tim david</t>
+          <t>tilak varma</t>
         </is>
       </c>
       <c r="B167" t="n">
-        <v>232</v>
+        <v>204</v>
       </c>
       <c r="C167" t="n">
         <v>0</v>
@@ -10497,11 +10497,11 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>tim seifert</t>
+          <t>tim david</t>
         </is>
       </c>
       <c r="B168" t="n">
-        <v>19</v>
+        <v>232</v>
       </c>
       <c r="C168" t="n">
         <v>0</v>
@@ -10510,11 +10510,11 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>travis head</t>
+          <t>tim seifert</t>
         </is>
       </c>
       <c r="B169" t="n">
-        <v>361</v>
+        <v>19</v>
       </c>
       <c r="C169" t="n">
         <v>0</v>
@@ -10523,167 +10523,167 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>trent boult</t>
+          <t>travis head</t>
         </is>
       </c>
       <c r="B170" t="n">
-        <v>8</v>
+        <v>361</v>
       </c>
       <c r="C170" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>tristan stubbs</t>
+          <t>trent boult</t>
         </is>
       </c>
       <c r="B171" t="n">
-        <v>259</v>
+        <v>8</v>
       </c>
       <c r="C171" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>tushar deshpande</t>
+          <t>tristan stubbs</t>
         </is>
       </c>
       <c r="B172" t="n">
-        <v>25</v>
+        <v>259</v>
       </c>
       <c r="C172" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>urvil patel</t>
+          <t>tushar deshpande</t>
         </is>
       </c>
       <c r="B173" t="n">
-        <v>45</v>
+        <v>26</v>
       </c>
       <c r="C173" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>vaibhav arora</t>
+          <t>urvil patel</t>
         </is>
       </c>
       <c r="B174" t="n">
-        <v>1</v>
+        <v>45</v>
       </c>
       <c r="C174" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>vaibhav suryavanshi</t>
+          <t>vaibhav arora</t>
         </is>
       </c>
       <c r="B175" t="n">
-        <v>404</v>
+        <v>1</v>
       </c>
       <c r="C175" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>varun chakravarthy</t>
+          <t>vaibhav suryavanshi</t>
         </is>
       </c>
       <c r="B176" t="n">
-        <v>0</v>
+        <v>440</v>
       </c>
       <c r="C176" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>venkatesh iyer</t>
+          <t>varun chakravarthy</t>
         </is>
       </c>
       <c r="B177" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="C177" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>vijaykumar vyshak</t>
+          <t>venkatesh iyer</t>
         </is>
       </c>
       <c r="B178" t="n">
-        <v>2</v>
+        <v>41</v>
       </c>
       <c r="C178" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>vipraj nigam</t>
+          <t>vijaykumar vyshak</t>
         </is>
       </c>
       <c r="B179" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="C179" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>virat kohli</t>
+          <t>vipraj nigam</t>
         </is>
       </c>
       <c r="B180" t="n">
-        <v>379</v>
+        <v>15</v>
       </c>
       <c r="C180" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>washington sundar</t>
+          <t>virat kohli</t>
         </is>
       </c>
       <c r="B181" t="n">
-        <v>209</v>
+        <v>379</v>
       </c>
       <c r="C181" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>will jacks</t>
+          <t>washington sundar</t>
         </is>
       </c>
       <c r="B182" t="n">
-        <v>57</v>
+        <v>246</v>
       </c>
       <c r="C182" t="n">
         <v>1</v>
@@ -10692,52 +10692,65 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>xavier bartlett</t>
+          <t>will jacks</t>
         </is>
       </c>
       <c r="B183" t="n">
-        <v>11</v>
+        <v>57</v>
       </c>
       <c r="C183" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>yash raj punja</t>
+          <t>xavier bartlett</t>
         </is>
       </c>
       <c r="B184" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="C184" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>yashasvi jaiswal</t>
+          <t>yash raj punja</t>
         </is>
       </c>
       <c r="B185" t="n">
-        <v>312</v>
+        <v>0</v>
       </c>
       <c r="C185" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
+          <t>yashasvi jaiswal</t>
+        </is>
+      </c>
+      <c r="B186" t="n">
+        <v>315</v>
+      </c>
+      <c r="C186" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
           <t>yuzvendra chahal</t>
         </is>
       </c>
-      <c r="B186" t="n">
-        <v>0</v>
-      </c>
-      <c r="C186" t="n">
+      <c r="B187" t="n">
+        <v>0</v>
+      </c>
+      <c r="C187" t="n">
         <v>8</v>
       </c>
     </row>
@@ -12229,19 +12242,19 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="H3" t="n">
         <v>1</v>
       </c>
       <c r="I3" t="n">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="J3" t="n">
         <v>20</v>
       </c>
       <c r="K3" t="n">
-        <v>249</v>
+        <v>253</v>
       </c>
     </row>
     <row r="4">

--- a/IPL_Fantasy_Points.xlsx
+++ b/IPL_Fantasy_Points.xlsx
@@ -561,19 +561,19 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>236</v>
+        <v>251</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>236</v>
+        <v>251</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>236</v>
+        <v>251</v>
       </c>
     </row>
     <row r="4">
@@ -647,19 +647,19 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>64</v>
+        <v>82</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>64</v>
+        <v>82</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>64</v>
+        <v>82</v>
       </c>
     </row>
     <row r="6">
@@ -690,19 +690,19 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>318</v>
+        <v>326</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>318</v>
+        <v>326</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>318</v>
+        <v>326</v>
       </c>
     </row>
     <row r="7">
@@ -733,19 +733,19 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>64</v>
+        <v>74</v>
       </c>
     </row>
     <row r="8">
@@ -776,19 +776,19 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>153</v>
+        <v>173</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>153</v>
+        <v>173</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>153</v>
+        <v>173</v>
       </c>
     </row>
     <row r="9">
@@ -819,19 +819,19 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>256</v>
+        <v>303</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>256</v>
+        <v>303</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>256</v>
+        <v>303</v>
       </c>
     </row>
     <row r="10">
@@ -1464,19 +1464,19 @@
         </is>
       </c>
       <c r="G24" t="n">
-        <v>43</v>
+        <v>70</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>43</v>
+        <v>70</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>43</v>
+        <v>70</v>
       </c>
     </row>
     <row r="25">
@@ -1811,16 +1811,16 @@
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I32" t="n">
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>240</v>
+        <v>260</v>
       </c>
       <c r="K32" t="n">
-        <v>240</v>
+        <v>260</v>
       </c>
     </row>
     <row r="33">
@@ -1854,16 +1854,16 @@
         <v>39</v>
       </c>
       <c r="H33" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I33" t="n">
         <v>0</v>
       </c>
       <c r="J33" t="n">
-        <v>340</v>
+        <v>380</v>
       </c>
       <c r="K33" t="n">
-        <v>340</v>
+        <v>380</v>
       </c>
     </row>
     <row r="34">
@@ -2238,19 +2238,19 @@
         </is>
       </c>
       <c r="G42" t="n">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="H42" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I42" t="n">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>79</v>
+        <v>83</v>
       </c>
     </row>
     <row r="43">
@@ -2625,19 +2625,19 @@
         </is>
       </c>
       <c r="G51" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="H51" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="I51" t="n">
         <v>0</v>
       </c>
       <c r="J51" t="n">
-        <v>60</v>
+        <v>140</v>
       </c>
       <c r="K51" t="n">
-        <v>60</v>
+        <v>140</v>
       </c>
     </row>
     <row r="52">
@@ -2668,19 +2668,19 @@
         </is>
       </c>
       <c r="G52" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H52" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I52" t="n">
         <v>0</v>
       </c>
       <c r="J52" t="n">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="K52" t="n">
-        <v>20</v>
+        <v>60</v>
       </c>
     </row>
     <row r="53">
@@ -2754,19 +2754,19 @@
         </is>
       </c>
       <c r="G54" t="n">
-        <v>402</v>
+        <v>430</v>
       </c>
       <c r="H54" t="n">
         <v>0</v>
       </c>
       <c r="I54" t="n">
-        <v>402</v>
+        <v>430</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
       </c>
       <c r="K54" t="n">
-        <v>402</v>
+        <v>430</v>
       </c>
     </row>
     <row r="55">
@@ -2797,19 +2797,19 @@
         </is>
       </c>
       <c r="G55" t="n">
-        <v>13</v>
+        <v>98</v>
       </c>
       <c r="H55" t="n">
         <v>0</v>
       </c>
       <c r="I55" t="n">
-        <v>13</v>
+        <v>98</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
       </c>
       <c r="K55" t="n">
-        <v>13</v>
+        <v>98</v>
       </c>
     </row>
     <row r="56">
@@ -3012,19 +3012,19 @@
         </is>
       </c>
       <c r="G60" t="n">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="H60" t="n">
         <v>0</v>
       </c>
       <c r="I60" t="n">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
       </c>
       <c r="K60" t="n">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="61">
@@ -3098,19 +3098,19 @@
         </is>
       </c>
       <c r="G62" t="n">
-        <v>150</v>
+        <v>165</v>
       </c>
       <c r="H62" t="n">
         <v>1</v>
       </c>
       <c r="I62" t="n">
-        <v>150</v>
+        <v>165</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
       </c>
       <c r="K62" t="n">
-        <v>150</v>
+        <v>165</v>
       </c>
     </row>
     <row r="63">
@@ -3528,19 +3528,19 @@
         </is>
       </c>
       <c r="G72" t="n">
-        <v>251</v>
+        <v>293</v>
       </c>
       <c r="H72" t="n">
         <v>0</v>
       </c>
       <c r="I72" t="n">
-        <v>251</v>
+        <v>293</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
       </c>
       <c r="K72" t="n">
-        <v>251</v>
+        <v>293</v>
       </c>
     </row>
     <row r="73">
@@ -3915,19 +3915,19 @@
         </is>
       </c>
       <c r="G81" t="n">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="H81" t="n">
         <v>0</v>
       </c>
       <c r="I81" t="n">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
       </c>
       <c r="K81" t="n">
-        <v>225</v>
+        <v>231</v>
       </c>
     </row>
     <row r="82">
@@ -4090,16 +4090,16 @@
         <v>6</v>
       </c>
       <c r="H85" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I85" t="n">
         <v>0</v>
       </c>
       <c r="J85" t="n">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="K85" t="n">
-        <v>100</v>
+        <v>120</v>
       </c>
     </row>
     <row r="86">
@@ -4216,19 +4216,19 @@
         </is>
       </c>
       <c r="G88" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H88" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I88" t="n">
         <v>0</v>
       </c>
       <c r="J88" t="n">
-        <v>140</v>
+        <v>160</v>
       </c>
       <c r="K88" t="n">
-        <v>140</v>
+        <v>160</v>
       </c>
     </row>
     <row r="89">
@@ -4474,19 +4474,19 @@
         </is>
       </c>
       <c r="G94" t="n">
-        <v>45</v>
+        <v>110</v>
       </c>
       <c r="H94" t="n">
         <v>0</v>
       </c>
       <c r="I94" t="n">
-        <v>45</v>
+        <v>110</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
       </c>
       <c r="K94" t="n">
-        <v>45</v>
+        <v>110</v>
       </c>
     </row>
     <row r="95">
@@ -4689,19 +4689,19 @@
         </is>
       </c>
       <c r="G99" t="n">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="H99" t="n">
         <v>1</v>
       </c>
       <c r="I99" t="n">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="J99" t="n">
         <v>20</v>
       </c>
       <c r="K99" t="n">
-        <v>77</v>
+        <v>87</v>
       </c>
     </row>
     <row r="100">
@@ -4821,16 +4821,16 @@
         <v>0</v>
       </c>
       <c r="H102" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I102" t="n">
         <v>0</v>
       </c>
       <c r="J102" t="n">
-        <v>180</v>
+        <v>200</v>
       </c>
       <c r="K102" t="n">
-        <v>180</v>
+        <v>200</v>
       </c>
     </row>
     <row r="103">
@@ -5119,19 +5119,19 @@
         </is>
       </c>
       <c r="G109" t="n">
-        <v>367</v>
+        <v>377</v>
       </c>
       <c r="H109" t="n">
         <v>0</v>
       </c>
       <c r="I109" t="n">
-        <v>367</v>
+        <v>377</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
       </c>
       <c r="K109" t="n">
-        <v>367</v>
+        <v>377</v>
       </c>
     </row>
     <row r="110">
@@ -5162,19 +5162,19 @@
         </is>
       </c>
       <c r="G110" t="n">
-        <v>221</v>
+        <v>243</v>
       </c>
       <c r="H110" t="n">
         <v>0</v>
       </c>
       <c r="I110" t="n">
-        <v>221</v>
+        <v>243</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
       </c>
       <c r="K110" t="n">
-        <v>221</v>
+        <v>243</v>
       </c>
     </row>
     <row r="111">
@@ -5380,16 +5380,16 @@
         <v>136</v>
       </c>
       <c r="H115" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="I115" t="n">
         <v>136</v>
       </c>
       <c r="J115" t="n">
-        <v>220</v>
+        <v>280</v>
       </c>
       <c r="K115" t="n">
-        <v>356</v>
+        <v>416</v>
       </c>
     </row>
     <row r="116">
@@ -5850,19 +5850,19 @@
         </is>
       </c>
       <c r="G126" t="n">
-        <v>316</v>
+        <v>328</v>
       </c>
       <c r="H126" t="n">
         <v>0</v>
       </c>
       <c r="I126" t="n">
-        <v>316</v>
+        <v>328</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
       </c>
       <c r="K126" t="n">
-        <v>316</v>
+        <v>328</v>
       </c>
     </row>
     <row r="127">
@@ -6065,19 +6065,19 @@
         </is>
       </c>
       <c r="G131" t="n">
-        <v>204</v>
+        <v>261</v>
       </c>
       <c r="H131" t="n">
         <v>0</v>
       </c>
       <c r="I131" t="n">
-        <v>204</v>
+        <v>261</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
       </c>
       <c r="K131" t="n">
-        <v>204</v>
+        <v>261</v>
       </c>
     </row>
     <row r="132">
@@ -6237,19 +6237,19 @@
         </is>
       </c>
       <c r="G135" t="n">
-        <v>49</v>
+        <v>66</v>
       </c>
       <c r="H135" t="n">
         <v>0</v>
       </c>
       <c r="I135" t="n">
-        <v>49</v>
+        <v>66</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
       </c>
       <c r="K135" t="n">
-        <v>49</v>
+        <v>66</v>
       </c>
     </row>
     <row r="136">
@@ -6710,19 +6710,19 @@
         </is>
       </c>
       <c r="G146" t="n">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H146" t="n">
         <v>0</v>
       </c>
       <c r="I146" t="n">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
       </c>
       <c r="K146" t="n">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="147">
@@ -6839,19 +6839,19 @@
         </is>
       </c>
       <c r="G149" t="n">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="H149" t="n">
         <v>0</v>
       </c>
       <c r="I149" t="n">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
       </c>
       <c r="K149" t="n">
-        <v>11</v>
+        <v>29</v>
       </c>
     </row>
     <row r="150">
@@ -6882,19 +6882,19 @@
         </is>
       </c>
       <c r="G150" t="n">
-        <v>75</v>
+        <v>92</v>
       </c>
       <c r="H150" t="n">
         <v>0</v>
       </c>
       <c r="I150" t="n">
-        <v>75</v>
+        <v>92</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
       </c>
       <c r="K150" t="n">
-        <v>75</v>
+        <v>92</v>
       </c>
     </row>
     <row r="151">
@@ -7011,19 +7011,19 @@
         </is>
       </c>
       <c r="G153" t="n">
-        <v>68</v>
+        <v>141</v>
       </c>
       <c r="H153" t="n">
         <v>10</v>
       </c>
       <c r="I153" t="n">
-        <v>68</v>
+        <v>141</v>
       </c>
       <c r="J153" t="n">
         <v>200</v>
       </c>
       <c r="K153" t="n">
-        <v>268</v>
+        <v>341</v>
       </c>
     </row>
     <row r="154">
@@ -7183,19 +7183,19 @@
         </is>
       </c>
       <c r="G157" t="n">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="H157" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="I157" t="n">
         <v>0</v>
       </c>
       <c r="J157" t="n">
-        <v>340</v>
+        <v>420</v>
       </c>
       <c r="K157" t="n">
-        <v>340</v>
+        <v>420</v>
       </c>
     </row>
     <row r="158">
@@ -8046,16 +8046,16 @@
         <v>2</v>
       </c>
       <c r="H177" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I177" t="n">
         <v>0</v>
       </c>
       <c r="J177" t="n">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="K177" t="n">
-        <v>60</v>
+        <v>100</v>
       </c>
     </row>
     <row r="178">
@@ -8132,16 +8132,16 @@
         <v>10</v>
       </c>
       <c r="H179" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I179" t="n">
         <v>0</v>
       </c>
       <c r="J179" t="n">
-        <v>220</v>
+        <v>240</v>
       </c>
       <c r="K179" t="n">
-        <v>220</v>
+        <v>240</v>
       </c>
     </row>
   </sheetData>
@@ -8185,7 +8185,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>3410</v>
+        <v>3498</v>
       </c>
     </row>
     <row r="3">
@@ -8198,7 +8198,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>3146</v>
+        <v>3233</v>
       </c>
     </row>
     <row r="4">
@@ -8207,11 +8207,11 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>NAKUL11</t>
+          <t>AMEY11</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2745</v>
+        <v>2869</v>
       </c>
     </row>
     <row r="5">
@@ -8220,11 +8220,11 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>SKY11</t>
+          <t>BABA11</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2741</v>
+        <v>2840</v>
       </c>
     </row>
     <row r="6">
@@ -8233,11 +8233,11 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>BABA11</t>
+          <t>NAKUL11</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2710</v>
+        <v>2840</v>
       </c>
     </row>
     <row r="7">
@@ -8246,11 +8246,11 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>AMEY11</t>
+          <t>SKY11</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2680</v>
+        <v>2833</v>
       </c>
     </row>
     <row r="8">
@@ -8263,7 +8263,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2545</v>
+        <v>2663</v>
       </c>
     </row>
     <row r="9">
@@ -8276,7 +8276,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2324</v>
+        <v>2410</v>
       </c>
     </row>
     <row r="10">
@@ -8289,7 +8289,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2255</v>
+        <v>2379</v>
       </c>
     </row>
     <row r="11">
@@ -8302,7 +8302,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1885</v>
+        <v>1945</v>
       </c>
     </row>
   </sheetData>
@@ -8395,7 +8395,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
@@ -8434,7 +8434,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>
@@ -8450,7 +8450,7 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11">
@@ -8502,7 +8502,7 @@
         <v>39</v>
       </c>
       <c r="C14" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="15">
@@ -8619,7 +8619,7 @@
         <v>6</v>
       </c>
       <c r="C23" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="24">
@@ -8681,10 +8681,10 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="C28" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="29">
@@ -8746,10 +8746,10 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="C33" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="34">
@@ -8811,10 +8811,10 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C38" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="39">
@@ -8824,7 +8824,7 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>316</v>
+        <v>328</v>
       </c>
       <c r="C39" t="n">
         <v>0</v>
@@ -8837,7 +8837,7 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="C40" t="n">
         <v>0</v>
@@ -8866,7 +8866,7 @@
         <v>2</v>
       </c>
       <c r="C42" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="43">
@@ -9045,7 +9045,7 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>75</v>
+        <v>92</v>
       </c>
       <c r="C56" t="n">
         <v>0</v>
@@ -9071,7 +9071,7 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>43</v>
+        <v>70</v>
       </c>
       <c r="C58" t="n">
         <v>0</v>
@@ -9100,7 +9100,7 @@
         <v>136</v>
       </c>
       <c r="C60" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="61">
@@ -9149,7 +9149,7 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>64</v>
+        <v>82</v>
       </c>
       <c r="C64" t="n">
         <v>0</v>
@@ -9191,7 +9191,7 @@
         <v>0</v>
       </c>
       <c r="C67" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="68">
@@ -9201,7 +9201,7 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>13</v>
+        <v>98</v>
       </c>
       <c r="C68" t="n">
         <v>0</v>
@@ -9227,7 +9227,7 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>153</v>
+        <v>173</v>
       </c>
       <c r="C70" t="n">
         <v>0</v>
@@ -9292,7 +9292,7 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>68</v>
+        <v>141</v>
       </c>
       <c r="C75" t="n">
         <v>10</v>
@@ -9539,7 +9539,7 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>367</v>
+        <v>377</v>
       </c>
       <c r="C94" t="n">
         <v>0</v>
@@ -9656,7 +9656,7 @@
         </is>
       </c>
       <c r="B103" t="n">
-        <v>256</v>
+        <v>303</v>
       </c>
       <c r="C103" t="n">
         <v>0</v>
@@ -9708,7 +9708,7 @@
         </is>
       </c>
       <c r="B107" t="n">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C107" t="n">
         <v>0</v>
@@ -9763,7 +9763,7 @@
         <v>10</v>
       </c>
       <c r="C111" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="112">
@@ -9838,7 +9838,7 @@
         </is>
       </c>
       <c r="B117" t="n">
-        <v>49</v>
+        <v>66</v>
       </c>
       <c r="C117" t="n">
         <v>0</v>
@@ -9942,10 +9942,10 @@
         </is>
       </c>
       <c r="B125" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="C125" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="126">
@@ -9955,7 +9955,7 @@
         </is>
       </c>
       <c r="B126" t="n">
-        <v>318</v>
+        <v>326</v>
       </c>
       <c r="C126" t="n">
         <v>0</v>
@@ -10007,10 +10007,10 @@
         </is>
       </c>
       <c r="B130" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C130" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="131">
@@ -10085,7 +10085,7 @@
         </is>
       </c>
       <c r="B136" t="n">
-        <v>236</v>
+        <v>251</v>
       </c>
       <c r="C136" t="n">
         <v>0</v>
@@ -10124,7 +10124,7 @@
         </is>
       </c>
       <c r="B139" t="n">
-        <v>221</v>
+        <v>243</v>
       </c>
       <c r="C139" t="n">
         <v>0</v>
@@ -10137,10 +10137,10 @@
         </is>
       </c>
       <c r="B140" t="n">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="C140" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="141">
@@ -10163,7 +10163,7 @@
         </is>
       </c>
       <c r="B142" t="n">
-        <v>251</v>
+        <v>293</v>
       </c>
       <c r="C142" t="n">
         <v>0</v>
@@ -10176,7 +10176,7 @@
         </is>
       </c>
       <c r="B143" t="n">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="C143" t="n">
         <v>0</v>
@@ -10254,7 +10254,7 @@
         </is>
       </c>
       <c r="B149" t="n">
-        <v>402</v>
+        <v>430</v>
       </c>
       <c r="C149" t="n">
         <v>0</v>
@@ -10280,10 +10280,10 @@
         </is>
       </c>
       <c r="B151" t="n">
-        <v>15</v>
+        <v>58</v>
       </c>
       <c r="C151" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="152">
@@ -10358,7 +10358,7 @@
         </is>
       </c>
       <c r="B157" t="n">
-        <v>150</v>
+        <v>165</v>
       </c>
       <c r="C157" t="n">
         <v>1</v>
@@ -10488,7 +10488,7 @@
         </is>
       </c>
       <c r="B167" t="n">
-        <v>204</v>
+        <v>261</v>
       </c>
       <c r="C167" t="n">
         <v>0</v>
@@ -10579,7 +10579,7 @@
         </is>
       </c>
       <c r="B174" t="n">
-        <v>45</v>
+        <v>110</v>
       </c>
       <c r="C174" t="n">
         <v>0</v>
@@ -10696,7 +10696,7 @@
         </is>
       </c>
       <c r="B183" t="n">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="C183" t="n">
         <v>1</v>
@@ -12199,19 +12199,19 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>13</v>
+        <v>98</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>13</v>
+        <v>98</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>13</v>
+        <v>98</v>
       </c>
     </row>
     <row r="3">

--- a/IPL_Fantasy_Points.xlsx
+++ b/IPL_Fantasy_Points.xlsx
@@ -2367,19 +2367,19 @@
         </is>
       </c>
       <c r="G45" t="n">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H45" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I45" t="n">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="J45" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="K45" t="n">
-        <v>198</v>
+        <v>219</v>
       </c>
     </row>
     <row r="46">
@@ -2840,19 +2840,19 @@
         </is>
       </c>
       <c r="G56" t="n">
-        <v>123</v>
+        <v>174</v>
       </c>
       <c r="H56" t="n">
         <v>0</v>
       </c>
       <c r="I56" t="n">
-        <v>123</v>
+        <v>174</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
       </c>
       <c r="K56" t="n">
-        <v>123</v>
+        <v>174</v>
       </c>
     </row>
     <row r="57">
@@ -3445,16 +3445,16 @@
         <v>0</v>
       </c>
       <c r="H70" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I70" t="n">
         <v>0</v>
       </c>
       <c r="J70" t="n">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="K70" t="n">
-        <v>60</v>
+        <v>100</v>
       </c>
     </row>
     <row r="71">
@@ -3614,19 +3614,19 @@
         </is>
       </c>
       <c r="G74" t="n">
-        <v>364</v>
+        <v>382</v>
       </c>
       <c r="H74" t="n">
         <v>0</v>
       </c>
       <c r="I74" t="n">
-        <v>364</v>
+        <v>382</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
       </c>
       <c r="K74" t="n">
-        <v>364</v>
+        <v>382</v>
       </c>
     </row>
     <row r="75">
@@ -3657,19 +3657,19 @@
         </is>
       </c>
       <c r="G75" t="n">
-        <v>286</v>
+        <v>342</v>
       </c>
       <c r="H75" t="n">
         <v>0</v>
       </c>
       <c r="I75" t="n">
-        <v>286</v>
+        <v>342</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
       </c>
       <c r="K75" t="n">
-        <v>286</v>
+        <v>342</v>
       </c>
     </row>
     <row r="76">
@@ -3786,19 +3786,19 @@
         </is>
       </c>
       <c r="G78" t="n">
-        <v>259</v>
+        <v>271</v>
       </c>
       <c r="H78" t="n">
         <v>0</v>
       </c>
       <c r="I78" t="n">
-        <v>259</v>
+        <v>271</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
       </c>
       <c r="K78" t="n">
-        <v>259</v>
+        <v>271</v>
       </c>
     </row>
     <row r="79">
@@ -4001,19 +4001,19 @@
         </is>
       </c>
       <c r="G83" t="n">
-        <v>377</v>
+        <v>415</v>
       </c>
       <c r="H83" t="n">
         <v>0</v>
       </c>
       <c r="I83" t="n">
-        <v>377</v>
+        <v>415</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
       </c>
       <c r="K83" t="n">
-        <v>377</v>
+        <v>415</v>
       </c>
     </row>
     <row r="84">
@@ -4047,16 +4047,16 @@
         <v>1</v>
       </c>
       <c r="H84" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="I84" t="n">
         <v>0</v>
       </c>
       <c r="J84" t="n">
-        <v>220</v>
+        <v>260</v>
       </c>
       <c r="K84" t="n">
-        <v>220</v>
+        <v>260</v>
       </c>
     </row>
     <row r="85">
@@ -4133,16 +4133,16 @@
         <v>0</v>
       </c>
       <c r="H86" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I86" t="n">
         <v>0</v>
       </c>
       <c r="J86" t="n">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="K86" t="n">
-        <v>100</v>
+        <v>120</v>
       </c>
     </row>
     <row r="87">
@@ -4173,7 +4173,7 @@
         </is>
       </c>
       <c r="G87" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="H87" t="n">
         <v>0</v>
@@ -4345,19 +4345,19 @@
         </is>
       </c>
       <c r="G91" t="n">
-        <v>468</v>
+        <v>477</v>
       </c>
       <c r="H91" t="n">
         <v>0</v>
       </c>
       <c r="I91" t="n">
-        <v>468</v>
+        <v>477</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
       </c>
       <c r="K91" t="n">
-        <v>468</v>
+        <v>477</v>
       </c>
     </row>
     <row r="92">
@@ -4388,19 +4388,19 @@
         </is>
       </c>
       <c r="G92" t="n">
-        <v>333</v>
+        <v>392</v>
       </c>
       <c r="H92" t="n">
         <v>0</v>
       </c>
       <c r="I92" t="n">
-        <v>333</v>
+        <v>392</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
       </c>
       <c r="K92" t="n">
-        <v>333</v>
+        <v>392</v>
       </c>
     </row>
     <row r="93">
@@ -4978,31 +4978,31 @@
           <t>BOWL</t>
         </is>
       </c>
-      <c r="D106" t="inlineStr"/>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>b sai sudharshan</t>
-        </is>
-      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>ben dwarshuis</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr"/>
       <c r="F106" t="inlineStr">
         <is>
-          <t>no_stats_yet</t>
+          <t>exact/alias</t>
         </is>
       </c>
       <c r="G106" t="n">
         <v>0</v>
       </c>
       <c r="H106" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I106" t="n">
         <v>0</v>
       </c>
       <c r="J106" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K106" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="107">
@@ -6022,19 +6022,19 @@
         </is>
       </c>
       <c r="G130" t="n">
-        <v>111</v>
+        <v>135</v>
       </c>
       <c r="H130" t="n">
         <v>0</v>
       </c>
       <c r="I130" t="n">
-        <v>111</v>
+        <v>135</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
       </c>
       <c r="K130" t="n">
-        <v>111</v>
+        <v>135</v>
       </c>
     </row>
     <row r="131">
@@ -6323,19 +6323,19 @@
         </is>
       </c>
       <c r="G137" t="n">
-        <v>44</v>
+        <v>100</v>
       </c>
       <c r="H137" t="n">
         <v>10</v>
       </c>
       <c r="I137" t="n">
-        <v>44</v>
+        <v>100</v>
       </c>
       <c r="J137" t="n">
         <v>200</v>
       </c>
       <c r="K137" t="n">
-        <v>244</v>
+        <v>300</v>
       </c>
     </row>
     <row r="138">
@@ -6925,19 +6925,19 @@
         </is>
       </c>
       <c r="G151" t="n">
-        <v>85</v>
+        <v>106</v>
       </c>
       <c r="H151" t="n">
         <v>0</v>
       </c>
       <c r="I151" t="n">
-        <v>85</v>
+        <v>106</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
       </c>
       <c r="K151" t="n">
-        <v>85</v>
+        <v>106</v>
       </c>
     </row>
     <row r="152">
@@ -7432,7 +7432,7 @@
       <c r="D163" t="inlineStr"/>
       <c r="E163" t="inlineStr">
         <is>
-          <t>ryan rickelton</t>
+          <t>ben dwarshuis</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
@@ -7484,19 +7484,19 @@
         </is>
       </c>
       <c r="G164" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="H164" t="n">
         <v>0</v>
       </c>
       <c r="I164" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
       </c>
       <c r="K164" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
     </row>
     <row r="165">
@@ -8185,7 +8185,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>3498</v>
+        <v>3682</v>
       </c>
     </row>
     <row r="3">
@@ -8207,11 +8207,11 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>AMEY11</t>
+          <t>BABA11</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2869</v>
+        <v>2931</v>
       </c>
     </row>
     <row r="5">
@@ -8220,11 +8220,11 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>BABA11</t>
+          <t>NAKUL11</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2840</v>
+        <v>2928</v>
       </c>
     </row>
     <row r="6">
@@ -8233,11 +8233,11 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>NAKUL11</t>
+          <t>AMEY11</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2840</v>
+        <v>2890</v>
       </c>
     </row>
     <row r="7">
@@ -8276,7 +8276,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2410</v>
+        <v>2490</v>
       </c>
     </row>
     <row r="10">
@@ -8289,7 +8289,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2379</v>
+        <v>2400</v>
       </c>
     </row>
     <row r="11">
@@ -8302,7 +8302,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1945</v>
+        <v>1950</v>
       </c>
     </row>
   </sheetData>
@@ -8316,7 +8316,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C187"/>
+  <dimension ref="A1:C190"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8382,7 +8382,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
@@ -8541,7 +8541,7 @@
         <v>1</v>
       </c>
       <c r="C17" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="18">
@@ -8577,7 +8577,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>111</v>
+        <v>135</v>
       </c>
       <c r="C20" t="n">
         <v>0</v>
@@ -8603,7 +8603,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="C22" t="n">
         <v>0</v>
@@ -8629,7 +8629,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>44</v>
+        <v>100</v>
       </c>
       <c r="C24" t="n">
         <v>10</v>
@@ -8677,102 +8677,102 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>bhuvneshwar kumar</t>
+          <t>ben dwarshuis</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="C28" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>blessing muzarabani</t>
+          <t>bhuvneshwar kumar</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="C29" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>brijesh sharma</t>
+          <t>blessing muzarabani</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C30" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>cameron green</t>
+          <t>brijesh sharma</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>232</v>
+        <v>2</v>
       </c>
       <c r="C31" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>cooper connolly</t>
+          <t>cameron green</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>377</v>
+        <v>232</v>
       </c>
       <c r="C32" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>corbin bosch</t>
+          <t>cooper connolly</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>16</v>
+        <v>415</v>
       </c>
       <c r="C33" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>danish malewar</t>
+          <t>corbin bosch</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="C34" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>dasun shanaka</t>
+          <t>danish malewar</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="C35" t="n">
         <v>0</v>
@@ -8781,11 +8781,11 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>david miller</t>
+          <t>dasun shanaka</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>123</v>
+        <v>16</v>
       </c>
       <c r="C36" t="n">
         <v>0</v>
@@ -8794,50 +8794,50 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>david payne</t>
+          <t>david miller</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>6</v>
+        <v>174</v>
       </c>
       <c r="C37" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>deepak chahar</t>
+          <t>david payne</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C38" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>devdutt padikkal</t>
+          <t>deepak chahar</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>328</v>
+        <v>7</v>
       </c>
       <c r="C39" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>dewald brevis</t>
+          <t>devdutt padikkal</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>74</v>
+        <v>328</v>
       </c>
       <c r="C40" t="n">
         <v>0</v>
@@ -8846,11 +8846,11 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>dhruv chand jurel</t>
+          <t>dewald brevis</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>314</v>
+        <v>74</v>
       </c>
       <c r="C41" t="n">
         <v>0</v>
@@ -8859,37 +8859,37 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>digvesh rathi</t>
+          <t>dhruv chand jurel</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>2</v>
+        <v>314</v>
       </c>
       <c r="C42" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>dilshan madushanka</t>
+          <t>digvesh rathi</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C43" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>donavon ferreira</t>
+          <t>dilshan madushanka</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>233</v>
+        <v>0</v>
       </c>
       <c r="C44" t="n">
         <v>1</v>
@@ -8898,89 +8898,89 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>dushmantha chameera</t>
+          <t>donavon ferreira</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0</v>
+        <v>233</v>
       </c>
       <c r="C45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>eshan malinga</t>
+          <t>dushmantha chameera</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C46" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>finn allen</t>
+          <t>eshan malinga</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>210</v>
+        <v>2</v>
       </c>
       <c r="C47" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>george linde</t>
+          <t>finn allen</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>31</v>
+        <v>210</v>
       </c>
       <c r="C48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>glenn phillips</t>
+          <t>george linde</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>67</v>
+        <v>31</v>
       </c>
       <c r="C49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>gurjapneet singh</t>
+          <t>glenn phillips</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="C50" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>hardik pandya</t>
+          <t>gurjapneet singh</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>146</v>
+        <v>0</v>
       </c>
       <c r="C51" t="n">
         <v>4</v>
@@ -8989,50 +8989,50 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>harpreet brar</t>
+          <t>hardik pandya</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0</v>
+        <v>146</v>
       </c>
       <c r="C52" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>harsh dubey</t>
+          <t>harpreet brar</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="C53" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>harshal patel</t>
+          <t>harsh dubey</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C54" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>heinrich klaasen</t>
+          <t>harshal patel</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>494</v>
+        <v>10</v>
       </c>
       <c r="C55" t="n">
         <v>0</v>
@@ -9041,11 +9041,11 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>himmat singh</t>
+          <t>heinrich klaasen</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>92</v>
+        <v>494</v>
       </c>
       <c r="C56" t="n">
         <v>0</v>
@@ -9054,11 +9054,11 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>ishan kishan</t>
+          <t>himmat singh</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>409</v>
+        <v>92</v>
       </c>
       <c r="C57" t="n">
         <v>0</v>
@@ -9067,11 +9067,11 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>jacob bethell</t>
+          <t>ishan kishan</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>70</v>
+        <v>409</v>
       </c>
       <c r="C58" t="n">
         <v>0</v>
@@ -9080,284 +9080,284 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>jacob duffy</t>
+          <t>jacob bethell</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="C59" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>jamie overton</t>
+          <t>jacob duffy</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>136</v>
+        <v>0</v>
       </c>
       <c r="C60" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>jason holder</t>
+          <t>jamie overton</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>47</v>
+        <v>136</v>
       </c>
       <c r="C61" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>jasprit bumrah</t>
+          <t>jason holder</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>7</v>
+        <v>47</v>
       </c>
       <c r="C62" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>jaydev unadkat</t>
+          <t>jasprit bumrah</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C63" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>jitesh sharma</t>
+          <t>jaydev unadkat</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>82</v>
+        <v>4</v>
       </c>
       <c r="C64" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>jofra archer</t>
+          <t>jitesh sharma</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>19</v>
+        <v>82</v>
       </c>
       <c r="C65" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>jos buttler</t>
+          <t>jofra archer</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>348</v>
+        <v>19</v>
       </c>
       <c r="C66" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>josh hazlewood</t>
+          <t>jos buttler</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0</v>
+        <v>348</v>
       </c>
       <c r="C67" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>josh inglis</t>
+          <t>josh hazlewood</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>98</v>
+        <v>0</v>
       </c>
       <c r="C68" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>kagiso rabada</t>
+          <t>josh inglis</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>35</v>
+        <v>98</v>
       </c>
       <c r="C69" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>kartik sharma</t>
+          <t>kagiso rabada</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>173</v>
+        <v>35</v>
       </c>
       <c r="C70" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>kartik tyagi</t>
+          <t>kartik sharma</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>11</v>
+        <v>173</v>
       </c>
       <c r="C71" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>karun nair</t>
+          <t>kartik tyagi</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="C72" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>khaleel ahmed</t>
+          <t>karun nair</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="C73" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>krish bhagat</t>
+          <t>khaleel ahmed</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="C74" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>krunal pandya</t>
+          <t>krish bhagat</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>141</v>
+        <v>10</v>
       </c>
       <c r="C75" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>kuldeep yadav</t>
+          <t>krunal pandya</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>9</v>
+        <v>141</v>
       </c>
       <c r="C76" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>kumar kushagra</t>
+          <t>kuldeep yadav</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="C77" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>kyle jamieson</t>
+          <t>kumar kushagra</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="C78" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>lhuan dre pretorius</t>
+          <t>kyle jamieson</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="C79" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>liam livingstone</t>
+          <t>lhuan dre pretorius</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="C80" t="n">
         <v>0</v>
@@ -9366,89 +9366,89 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>lockie ferguson</t>
+          <t>liam livingstone</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="C81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>lokesh rahul</t>
+          <t>lockie ferguson</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>468</v>
+        <v>0</v>
       </c>
       <c r="C82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>lungi ngidi</t>
+          <t>lokesh rahul</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>4</v>
+        <v>477</v>
       </c>
       <c r="C83" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>manav suthar</t>
+          <t>lungi ngidi</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C84" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>manimaran siddharth</t>
+          <t>madhav tiwari</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="C85" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>manish pandey</t>
+          <t>manav suthar</t>
         </is>
       </c>
       <c r="B86" t="n">
         <v>0</v>
       </c>
       <c r="C86" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>marco jansen</t>
+          <t>manimaran siddharth</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="C87" t="n">
         <v>6</v>
@@ -9457,63 +9457,63 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>marcus stoinis</t>
+          <t>manish pandey</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>178</v>
+        <v>0</v>
       </c>
       <c r="C88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>matt henry</t>
+          <t>marco jansen</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>7</v>
+        <v>49</v>
       </c>
       <c r="C89" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>matt short</t>
+          <t>marcus stoinis</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>36</v>
+        <v>179</v>
       </c>
       <c r="C90" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>mayank markande</t>
+          <t>matt henry</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C91" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>mayank rawat</t>
+          <t>matt short</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="C92" t="n">
         <v>0</v>
@@ -9522,11 +9522,11 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>mayank yadav</t>
+          <t>mayank markande</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C93" t="n">
         <v>0</v>
@@ -9535,11 +9535,11 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>mitchell marsh</t>
+          <t>mayank rawat</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>377</v>
+        <v>0</v>
       </c>
       <c r="C94" t="n">
         <v>0</v>
@@ -9548,141 +9548,141 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>mitchell santner</t>
+          <t>mayank yadav</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="C95" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>mitchell starc</t>
+          <t>mitchell marsh</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>0</v>
+        <v>377</v>
       </c>
       <c r="C96" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>mohammed shami</t>
+          <t>mitchell santner</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="C97" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>mohammed siraj</t>
+          <t>mitchell starc</t>
         </is>
       </c>
       <c r="B98" t="n">
         <v>0</v>
       </c>
       <c r="C98" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>mohsin khan</t>
+          <t>mohammed shami</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="C99" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>mukesh choudhary</t>
+          <t>mohammed siraj</t>
         </is>
       </c>
       <c r="B100" t="n">
         <v>0</v>
       </c>
       <c r="C100" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>mukesh kumar</t>
+          <t>mohsin khan</t>
         </is>
       </c>
       <c r="B101" t="n">
         <v>0</v>
       </c>
       <c r="C101" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>mukul choudhary</t>
+          <t>mukesh choudhary</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>156</v>
+        <v>0</v>
       </c>
       <c r="C102" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>naman dhir</t>
+          <t>mukesh kumar</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>303</v>
+        <v>0</v>
       </c>
       <c r="C103" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>nandre burger</t>
+          <t>mukul choudhary</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>3</v>
+        <v>156</v>
       </c>
       <c r="C104" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>navdeep saini</t>
+          <t>naman dhir</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>0</v>
+        <v>303</v>
       </c>
       <c r="C105" t="n">
         <v>0</v>
@@ -9691,24 +9691,24 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>nehal wadhera</t>
+          <t>nandre burger</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>65</v>
+        <v>3</v>
       </c>
       <c r="C106" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>nicholas pooran</t>
+          <t>navdeep saini</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>184</v>
+        <v>0</v>
       </c>
       <c r="C107" t="n">
         <v>0</v>
@@ -9717,11 +9717,11 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>nishant sindhu</t>
+          <t>nehal wadhera</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>15</v>
+        <v>65</v>
       </c>
       <c r="C108" t="n">
         <v>0</v>
@@ -9730,24 +9730,24 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>nitish kumar reddy</t>
+          <t>nicholas pooran</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>222</v>
+        <v>184</v>
       </c>
       <c r="C109" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>nitish rana</t>
+          <t>nishant sindhu</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>225</v>
+        <v>15</v>
       </c>
       <c r="C110" t="n">
         <v>0</v>
@@ -9756,63 +9756,63 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>noor ahmad</t>
+          <t>nitish kumar reddy</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>10</v>
+        <v>222</v>
       </c>
       <c r="C111" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>pat cummins</t>
+          <t>nitish rana</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>10</v>
+        <v>225</v>
       </c>
       <c r="C112" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>pathum nissanka</t>
+          <t>noor ahmad</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>278</v>
+        <v>10</v>
       </c>
       <c r="C113" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>philip salt</t>
+          <t>pat cummins</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>202</v>
+        <v>10</v>
       </c>
       <c r="C114" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>prabhsimran singh</t>
+          <t>pathum nissanka</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>364</v>
+        <v>278</v>
       </c>
       <c r="C115" t="n">
         <v>0</v>
@@ -9821,24 +9821,24 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>praful hinge</t>
+          <t>philip salt</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>0</v>
+        <v>202</v>
       </c>
       <c r="C116" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>prashant veer</t>
+          <t>prabhsimran singh</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>66</v>
+        <v>382</v>
       </c>
       <c r="C117" t="n">
         <v>0</v>
@@ -9847,76 +9847,76 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>prasidh krishna</t>
+          <t>praful hinge</t>
         </is>
       </c>
       <c r="B118" t="n">
         <v>0</v>
       </c>
       <c r="C118" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>prince yadav</t>
+          <t>prashant veer</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="C119" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>priyansh arya</t>
+          <t>prasidh krishna</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>286</v>
+        <v>0</v>
       </c>
       <c r="C120" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>quinton de kock</t>
+          <t>prince yadav</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>132</v>
+        <v>0</v>
       </c>
       <c r="C121" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>raghu sharma</t>
+          <t>priyansh arya</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>0</v>
+        <v>342</v>
       </c>
       <c r="C122" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>rahul chahar</t>
+          <t>quinton de kock</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>0</v>
+        <v>132</v>
       </c>
       <c r="C123" t="n">
         <v>0</v>
@@ -9925,37 +9925,37 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>rahul tewatia</t>
+          <t>raghu sharma</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>92</v>
+        <v>0</v>
       </c>
       <c r="C124" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>raj angad bawa</t>
+          <t>rahul chahar</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="C125" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>rajat patidar</t>
+          <t>rahul tewatia</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>326</v>
+        <v>92</v>
       </c>
       <c r="C126" t="n">
         <v>0</v>
@@ -9964,11 +9964,11 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>ramakrishna ghosh</t>
+          <t>raj angad bawa</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="C127" t="n">
         <v>1</v>
@@ -9977,89 +9977,89 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>ramandeep singh</t>
+          <t>rajat patidar</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>82</v>
+        <v>326</v>
       </c>
       <c r="C128" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>rashid khan</t>
+          <t>ramakrishna ghosh</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="C129" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>rasikh salam</t>
+          <t>ramandeep singh</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>3</v>
+        <v>82</v>
       </c>
       <c r="C130" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>ravi bishnoi</t>
+          <t>rashid khan</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="C131" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>ravichandran smaran</t>
+          <t>rasikh salam</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C132" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>ravindra jadeja</t>
+          <t>ravi bishnoi</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>190</v>
+        <v>0</v>
       </c>
       <c r="C133" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>ravisrinivasan sai kishore</t>
+          <t>ravichandran smaran</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C134" t="n">
         <v>0</v>
@@ -10068,24 +10068,24 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>rinku singh</t>
+          <t>ravindra jadeja</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>237</v>
+        <v>190</v>
       </c>
       <c r="C135" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>rishabh pant</t>
+          <t>ravisrinivasan sai kishore</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>251</v>
+        <v>0</v>
       </c>
       <c r="C136" t="n">
         <v>0</v>
@@ -10094,24 +10094,24 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>riyan parag</t>
+          <t>rinku singh</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>207</v>
+        <v>237</v>
       </c>
       <c r="C137" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>robin minz</t>
+          <t>rishabh pant</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>6</v>
+        <v>251</v>
       </c>
       <c r="C138" t="n">
         <v>0</v>
@@ -10120,37 +10120,37 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>rohit sharma</t>
+          <t>riyan parag</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>243</v>
+        <v>207</v>
       </c>
       <c r="C139" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>romario shepherd</t>
+          <t>robin minz</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>83</v>
+        <v>6</v>
       </c>
       <c r="C140" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>rovman powell</t>
+          <t>rohit sharma</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>121</v>
+        <v>243</v>
       </c>
       <c r="C141" t="n">
         <v>0</v>
@@ -10159,24 +10159,24 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>ruturaj gaikwad</t>
+          <t>romario shepherd</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>293</v>
+        <v>83</v>
       </c>
       <c r="C142" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>ryan rickelton</t>
+          <t>rovman powell</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>382</v>
+        <v>121</v>
       </c>
       <c r="C143" t="n">
         <v>0</v>
@@ -10185,11 +10185,11 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>sahil parakh</t>
+          <t>ruturaj gaikwad</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>0</v>
+        <v>293</v>
       </c>
       <c r="C144" t="n">
         <v>0</v>
@@ -10198,24 +10198,24 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>sakib hussain</t>
+          <t>ryan rickelton</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>0</v>
+        <v>382</v>
       </c>
       <c r="C145" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>salil arora</t>
+          <t>sahil parakh</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>95</v>
+        <v>13</v>
       </c>
       <c r="C146" t="n">
         <v>0</v>
@@ -10224,37 +10224,37 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>sameer rizvi</t>
+          <t>sakib hussain</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>252</v>
+        <v>0</v>
       </c>
       <c r="C147" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>sandeep sharma</t>
+          <t>salil arora</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="C148" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>sanju samson</t>
+          <t>sameer rizvi</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>430</v>
+        <v>252</v>
       </c>
       <c r="C149" t="n">
         <v>0</v>
@@ -10263,37 +10263,37 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>sarfaraz khan</t>
+          <t>sandeep sharma</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>161</v>
+        <v>0</v>
       </c>
       <c r="C150" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>shahbaz ahmed</t>
+          <t>sanju samson</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>58</v>
+        <v>430</v>
       </c>
       <c r="C151" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>shahrukh khan</t>
+          <t>sarfaraz khan</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>43</v>
+        <v>161</v>
       </c>
       <c r="C152" t="n">
         <v>0</v>
@@ -10302,115 +10302,115 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>shardul thakur</t>
+          <t>shahbaz ahmed</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>14</v>
+        <v>58</v>
       </c>
       <c r="C153" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>shashank singh</t>
+          <t>shahrukh khan</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>74</v>
+        <v>43</v>
       </c>
       <c r="C154" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>sherfane rutherford</t>
+          <t>shardul thakur</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>103</v>
+        <v>14</v>
       </c>
       <c r="C155" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>shimron hetmyer</t>
+          <t>shashank singh</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="C156" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>shivam dube</t>
+          <t>sherfane rutherford</t>
         </is>
       </c>
       <c r="B157" t="n">
-        <v>165</v>
+        <v>103</v>
       </c>
       <c r="C157" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>shivang kumar</t>
+          <t>shimron hetmyer</t>
         </is>
       </c>
       <c r="B158" t="n">
-        <v>22</v>
+        <v>78</v>
       </c>
       <c r="C158" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>shreyas iyer</t>
+          <t>shivam dube</t>
         </is>
       </c>
       <c r="B159" t="n">
-        <v>333</v>
+        <v>165</v>
       </c>
       <c r="C159" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>shubham badriprasad dubey</t>
+          <t>shivang kumar</t>
         </is>
       </c>
       <c r="B160" t="n">
-        <v>71</v>
+        <v>22</v>
       </c>
       <c r="C160" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>shubman gill</t>
+          <t>shreyas iyer</t>
         </is>
       </c>
       <c r="B161" t="n">
-        <v>462</v>
+        <v>392</v>
       </c>
       <c r="C161" t="n">
         <v>0</v>
@@ -10419,24 +10419,24 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>sunil narine</t>
+          <t>shubham badriprasad dubey</t>
         </is>
       </c>
       <c r="B162" t="n">
-        <v>40</v>
+        <v>71</v>
       </c>
       <c r="C162" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>suryakumar yadav</t>
+          <t>shubman gill</t>
         </is>
       </c>
       <c r="B163" t="n">
-        <v>195</v>
+        <v>462</v>
       </c>
       <c r="C163" t="n">
         <v>0</v>
@@ -10445,76 +10445,76 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>suryansh shedge</t>
+          <t>sunil narine</t>
         </is>
       </c>
       <c r="B164" t="n">
-        <v>85</v>
+        <v>40</v>
       </c>
       <c r="C164" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>suyash sharma</t>
+          <t>suryakumar yadav</t>
         </is>
       </c>
       <c r="B165" t="n">
-        <v>0</v>
+        <v>195</v>
       </c>
       <c r="C165" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>t natarajan</t>
+          <t>suryansh shedge</t>
         </is>
       </c>
       <c r="B166" t="n">
-        <v>1</v>
+        <v>106</v>
       </c>
       <c r="C166" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>tilak varma</t>
+          <t>suyash sharma</t>
         </is>
       </c>
       <c r="B167" t="n">
-        <v>261</v>
+        <v>0</v>
       </c>
       <c r="C167" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>tim david</t>
+          <t>t natarajan</t>
         </is>
       </c>
       <c r="B168" t="n">
-        <v>232</v>
+        <v>1</v>
       </c>
       <c r="C168" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>tim seifert</t>
+          <t>tilak varma</t>
         </is>
       </c>
       <c r="B169" t="n">
-        <v>19</v>
+        <v>261</v>
       </c>
       <c r="C169" t="n">
         <v>0</v>
@@ -10523,11 +10523,11 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>travis head</t>
+          <t>tim david</t>
         </is>
       </c>
       <c r="B170" t="n">
-        <v>361</v>
+        <v>232</v>
       </c>
       <c r="C170" t="n">
         <v>0</v>
@@ -10536,24 +10536,24 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>trent boult</t>
+          <t>tim seifert</t>
         </is>
       </c>
       <c r="B171" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="C171" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>tristan stubbs</t>
+          <t>travis head</t>
         </is>
       </c>
       <c r="B172" t="n">
-        <v>259</v>
+        <v>361</v>
       </c>
       <c r="C172" t="n">
         <v>0</v>
@@ -10562,24 +10562,24 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>tushar deshpande</t>
+          <t>trent boult</t>
         </is>
       </c>
       <c r="B173" t="n">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="C173" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>urvil patel</t>
+          <t>tristan stubbs</t>
         </is>
       </c>
       <c r="B174" t="n">
-        <v>110</v>
+        <v>271</v>
       </c>
       <c r="C174" t="n">
         <v>0</v>
@@ -10588,24 +10588,24 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>vaibhav arora</t>
+          <t>tushar deshpande</t>
         </is>
       </c>
       <c r="B175" t="n">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="C175" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>vaibhav suryavanshi</t>
+          <t>urvil patel</t>
         </is>
       </c>
       <c r="B176" t="n">
-        <v>440</v>
+        <v>110</v>
       </c>
       <c r="C176" t="n">
         <v>0</v>
@@ -10614,24 +10614,24 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>varun chakravarthy</t>
+          <t>vaibhav arora</t>
         </is>
       </c>
       <c r="B177" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C177" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>venkatesh iyer</t>
+          <t>vaibhav suryavanshi</t>
         </is>
       </c>
       <c r="B178" t="n">
-        <v>41</v>
+        <v>440</v>
       </c>
       <c r="C178" t="n">
         <v>0</v>
@@ -10640,117 +10640,156 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>vijaykumar vyshak</t>
+          <t>varun chakravarthy</t>
         </is>
       </c>
       <c r="B179" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C179" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>vipraj nigam</t>
+          <t>venkatesh iyer</t>
         </is>
       </c>
       <c r="B180" t="n">
-        <v>15</v>
+        <v>41</v>
       </c>
       <c r="C180" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>virat kohli</t>
+          <t>vijaykumar vyshak</t>
         </is>
       </c>
       <c r="B181" t="n">
-        <v>379</v>
+        <v>2</v>
       </c>
       <c r="C181" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>washington sundar</t>
+          <t>vipraj nigam</t>
         </is>
       </c>
       <c r="B182" t="n">
-        <v>246</v>
+        <v>15</v>
       </c>
       <c r="C182" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>will jacks</t>
+          <t>virat kohli</t>
         </is>
       </c>
       <c r="B183" t="n">
-        <v>67</v>
+        <v>379</v>
       </c>
       <c r="C183" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>xavier bartlett</t>
+          <t>washington sundar</t>
         </is>
       </c>
       <c r="B184" t="n">
-        <v>11</v>
+        <v>246</v>
       </c>
       <c r="C184" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>yash raj punja</t>
+          <t>will jacks</t>
         </is>
       </c>
       <c r="B185" t="n">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="C185" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>yashasvi jaiswal</t>
+          <t>xavier bartlett</t>
         </is>
       </c>
       <c r="B186" t="n">
-        <v>315</v>
+        <v>11</v>
       </c>
       <c r="C186" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
+          <t>yash raj punja</t>
+        </is>
+      </c>
+      <c r="B187" t="n">
+        <v>0</v>
+      </c>
+      <c r="C187" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>yash thakur</t>
+        </is>
+      </c>
+      <c r="B188" t="n">
+        <v>0</v>
+      </c>
+      <c r="C188" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>yashasvi jaiswal</t>
+        </is>
+      </c>
+      <c r="B189" t="n">
+        <v>315</v>
+      </c>
+      <c r="C189" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
           <t>yuzvendra chahal</t>
         </is>
       </c>
-      <c r="B187" t="n">
-        <v>0</v>
-      </c>
-      <c r="C187" t="n">
+      <c r="B190" t="n">
+        <v>0</v>
+      </c>
+      <c r="C190" t="n">
         <v>8</v>
       </c>
     </row>
@@ -10765,7 +10804,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K29"/>
+  <dimension ref="A1:K28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11473,12 +11512,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Ben Dwarshuis</t>
+          <t>Arjun Tendulkar</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>NAKUL11</t>
+          <t>SKY11</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -11489,7 +11528,7 @@
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>b sai sudharshan</t>
+          <t>karun nair</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -11516,7 +11555,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Arjun Tendulkar</t>
+          <t>Kwena Maphaka</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -11532,7 +11571,7 @@
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>karun nair</t>
+          <t>aiden markram</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -11559,23 +11598,23 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Kwena Maphaka</t>
+          <t>Azmatullah Omarzai</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>SKY11</t>
+          <t>HARSH11</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>aiden markram</t>
+          <t>mitchell marsh</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -11602,23 +11641,23 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Azmatullah Omarzai</t>
+          <t>Tejasvi Singh</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>HARSH11</t>
+          <t>AMEY11</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>mitchell marsh</t>
+          <t>prabhsimran singh</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -11645,7 +11684,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Tejasvi Singh</t>
+          <t>Sai Kishor</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -11655,13 +11694,13 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>prabhsimran singh</t>
+          <t>ishan kishan</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -11688,7 +11727,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Sai Kishor</t>
+          <t>Akash Deep</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -11704,7 +11743,7 @@
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>ishan kishan</t>
+          <t>arshdeep singh</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -11731,23 +11770,23 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Akash Deep</t>
+          <t>Ben Duckett</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>AMEY11</t>
+          <t>PRATIK11</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>arshdeep singh</t>
+          <t>ben dwarshuis</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -11774,7 +11813,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Ben Duckett</t>
+          <t>Rahul Tripathi</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -11790,7 +11829,7 @@
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>ryan rickelton</t>
+          <t>rahul tewatia</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -11817,7 +11856,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rahul Tripathi</t>
+          <t>Dre Pretorius</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -11833,7 +11872,7 @@
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>rahul tewatia</t>
+          <t>lhuan dre pretorius</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -11860,7 +11899,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Dre Pretorius</t>
+          <t>Matthew Breetzke</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -11876,7 +11915,7 @@
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>lhuan dre pretorius</t>
+          <t>matt henry</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -11903,7 +11942,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Matthew Breetzke</t>
+          <t>Anuj Rawat</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -11919,7 +11958,7 @@
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>matt henry</t>
+          <t>mayank rawat</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -11946,7 +11985,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Anuj Rawat</t>
+          <t>Wanindu Hasaranga</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -11956,13 +11995,13 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>mayank rawat</t>
+          <t>ravichandran smaran</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -11983,49 +12022,6 @@
         <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Wanindu Hasaranga</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>PRATIK11</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>AR</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>ravichandran smaran</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>no_stats_yet</t>
-        </is>
-      </c>
-      <c r="G29" t="n">
-        <v>0</v>
-      </c>
-      <c r="H29" t="n">
-        <v>0</v>
-      </c>
-      <c r="I29" t="n">
-        <v>0</v>
-      </c>
-      <c r="J29" t="n">
-        <v>0</v>
-      </c>
-      <c r="K29" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12328,19 +12324,19 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>

--- a/IPL_Fantasy_Points.xlsx
+++ b/IPL_Fantasy_Points.xlsx
@@ -994,16 +994,16 @@
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>240</v>
+        <v>260</v>
       </c>
       <c r="K13" t="n">
-        <v>240</v>
+        <v>260</v>
       </c>
     </row>
     <row r="14">
@@ -1206,19 +1206,19 @@
         </is>
       </c>
       <c r="G18" t="n">
-        <v>409</v>
+        <v>420</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>409</v>
+        <v>420</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>409</v>
+        <v>420</v>
       </c>
     </row>
     <row r="19">
@@ -1249,19 +1249,19 @@
         </is>
       </c>
       <c r="G19" t="n">
-        <v>462</v>
+        <v>467</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>462</v>
+        <v>467</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>462</v>
+        <v>467</v>
       </c>
     </row>
     <row r="20">
@@ -1550,19 +1550,19 @@
         </is>
       </c>
       <c r="G26" t="n">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>92</v>
+        <v>96</v>
       </c>
     </row>
     <row r="27">
@@ -1593,19 +1593,19 @@
         </is>
       </c>
       <c r="G27" t="n">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="H27" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="I27" t="n">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="J27" t="n">
-        <v>200</v>
+        <v>260</v>
       </c>
       <c r="K27" t="n">
-        <v>247</v>
+        <v>318</v>
       </c>
     </row>
     <row r="28">
@@ -2023,19 +2023,19 @@
         </is>
       </c>
       <c r="G37" t="n">
-        <v>494</v>
+        <v>508</v>
       </c>
       <c r="H37" t="n">
         <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>494</v>
+        <v>508</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>494</v>
+        <v>508</v>
       </c>
     </row>
     <row r="38">
@@ -2109,19 +2109,19 @@
         </is>
       </c>
       <c r="G39" t="n">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="H39" t="n">
         <v>7</v>
       </c>
       <c r="I39" t="n">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>222</v>
+        <v>224</v>
       </c>
     </row>
     <row r="40">
@@ -2413,16 +2413,16 @@
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I46" t="n">
         <v>0</v>
       </c>
       <c r="J46" t="n">
-        <v>240</v>
+        <v>280</v>
       </c>
       <c r="K46" t="n">
-        <v>240</v>
+        <v>280</v>
       </c>
     </row>
     <row r="47">
@@ -3187,16 +3187,16 @@
         <v>35</v>
       </c>
       <c r="H64" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I64" t="n">
         <v>35</v>
       </c>
       <c r="J64" t="n">
-        <v>300</v>
+        <v>320</v>
       </c>
       <c r="K64" t="n">
-        <v>335</v>
+        <v>355</v>
       </c>
     </row>
     <row r="65">
@@ -3571,19 +3571,19 @@
         </is>
       </c>
       <c r="G73" t="n">
-        <v>440</v>
+        <v>501</v>
       </c>
       <c r="H73" t="n">
         <v>0</v>
       </c>
       <c r="I73" t="n">
-        <v>440</v>
+        <v>501</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
       </c>
       <c r="K73" t="n">
-        <v>440</v>
+        <v>501</v>
       </c>
     </row>
     <row r="74">
@@ -3872,19 +3872,19 @@
         </is>
       </c>
       <c r="G80" t="n">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="H80" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I80" t="n">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="J80" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="K80" t="n">
-        <v>90</v>
+        <v>129</v>
       </c>
     </row>
     <row r="81">
@@ -4431,19 +4431,19 @@
         </is>
       </c>
       <c r="G93" t="n">
-        <v>348</v>
+        <v>355</v>
       </c>
       <c r="H93" t="n">
         <v>0</v>
       </c>
       <c r="I93" t="n">
-        <v>348</v>
+        <v>355</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
       </c>
       <c r="K93" t="n">
-        <v>348</v>
+        <v>355</v>
       </c>
     </row>
     <row r="94">
@@ -4560,19 +4560,19 @@
         </is>
       </c>
       <c r="G96" t="n">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="H96" t="n">
         <v>0</v>
       </c>
       <c r="I96" t="n">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
       </c>
       <c r="K96" t="n">
-        <v>15</v>
+        <v>37</v>
       </c>
     </row>
     <row r="97">
@@ -4778,16 +4778,16 @@
         <v>35</v>
       </c>
       <c r="H101" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="I101" t="n">
         <v>0</v>
       </c>
       <c r="J101" t="n">
-        <v>360</v>
+        <v>420</v>
       </c>
       <c r="K101" t="n">
-        <v>360</v>
+        <v>420</v>
       </c>
     </row>
     <row r="102">
@@ -6280,19 +6280,19 @@
         </is>
       </c>
       <c r="G136" t="n">
-        <v>246</v>
+        <v>296</v>
       </c>
       <c r="H136" t="n">
         <v>1</v>
       </c>
       <c r="I136" t="n">
-        <v>246</v>
+        <v>296</v>
       </c>
       <c r="J136" t="n">
         <v>20</v>
       </c>
       <c r="K136" t="n">
-        <v>266</v>
+        <v>316</v>
       </c>
     </row>
     <row r="137">
@@ -6409,19 +6409,19 @@
         </is>
       </c>
       <c r="G139" t="n">
-        <v>95</v>
+        <v>111</v>
       </c>
       <c r="H139" t="n">
         <v>0</v>
       </c>
       <c r="I139" t="n">
-        <v>95</v>
+        <v>111</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
       </c>
       <c r="K139" t="n">
-        <v>95</v>
+        <v>111</v>
       </c>
     </row>
     <row r="140">
@@ -7398,19 +7398,19 @@
         </is>
       </c>
       <c r="G162" t="n">
-        <v>475</v>
+        <v>481</v>
       </c>
       <c r="H162" t="n">
         <v>0</v>
       </c>
       <c r="I162" t="n">
-        <v>475</v>
+        <v>481</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
       </c>
       <c r="K162" t="n">
-        <v>475</v>
+        <v>481</v>
       </c>
     </row>
     <row r="163">
@@ -8185,7 +8185,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>3682</v>
+        <v>3782</v>
       </c>
     </row>
     <row r="3">
@@ -8198,7 +8198,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>3233</v>
+        <v>3324</v>
       </c>
     </row>
     <row r="4">
@@ -8207,11 +8207,11 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>BABA11</t>
+          <t>NAKUL11</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2931</v>
+        <v>3017</v>
       </c>
     </row>
     <row r="5">
@@ -8220,11 +8220,11 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>NAKUL11</t>
+          <t>BABA11</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2928</v>
+        <v>2951</v>
       </c>
     </row>
     <row r="6">
@@ -8263,7 +8263,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2663</v>
+        <v>2683</v>
       </c>
     </row>
     <row r="9">
@@ -8276,7 +8276,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2490</v>
+        <v>2556</v>
       </c>
     </row>
     <row r="10">
@@ -8289,7 +8289,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2400</v>
+        <v>2456</v>
       </c>
     </row>
     <row r="11">
@@ -8302,7 +8302,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1950</v>
+        <v>1956</v>
       </c>
     </row>
   </sheetData>
@@ -8369,7 +8369,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>475</v>
+        <v>481</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
@@ -8668,7 +8668,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>440</v>
+        <v>501</v>
       </c>
       <c r="C27" t="n">
         <v>0</v>
@@ -9045,7 +9045,7 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>494</v>
+        <v>508</v>
       </c>
       <c r="C56" t="n">
         <v>0</v>
@@ -9071,7 +9071,7 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>409</v>
+        <v>420</v>
       </c>
       <c r="C58" t="n">
         <v>0</v>
@@ -9123,10 +9123,10 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="C62" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="63">
@@ -9188,7 +9188,7 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>348</v>
+        <v>355</v>
       </c>
       <c r="C67" t="n">
         <v>0</v>
@@ -9230,7 +9230,7 @@
         <v>35</v>
       </c>
       <c r="C70" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="71">
@@ -9620,7 +9620,7 @@
         <v>0</v>
       </c>
       <c r="C100" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="101">
@@ -9747,7 +9747,7 @@
         </is>
       </c>
       <c r="B110" t="n">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="C110" t="n">
         <v>0</v>
@@ -9760,7 +9760,7 @@
         </is>
       </c>
       <c r="B111" t="n">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="C111" t="n">
         <v>7</v>
@@ -9799,10 +9799,10 @@
         </is>
       </c>
       <c r="B114" t="n">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="C114" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="115">
@@ -9851,10 +9851,10 @@
         </is>
       </c>
       <c r="B118" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C118" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="119">
@@ -9880,7 +9880,7 @@
         <v>0</v>
       </c>
       <c r="C120" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="121">
@@ -9955,7 +9955,7 @@
         </is>
       </c>
       <c r="B126" t="n">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="C126" t="n">
         <v>0</v>
@@ -10023,7 +10023,7 @@
         <v>35</v>
       </c>
       <c r="C131" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="132">
@@ -10059,7 +10059,7 @@
         </is>
       </c>
       <c r="B134" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="C134" t="n">
         <v>0</v>
@@ -10231,7 +10231,7 @@
         <v>0</v>
       </c>
       <c r="C147" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="148">
@@ -10241,7 +10241,7 @@
         </is>
       </c>
       <c r="B148" t="n">
-        <v>95</v>
+        <v>111</v>
       </c>
       <c r="C148" t="n">
         <v>0</v>
@@ -10397,7 +10397,7 @@
         </is>
       </c>
       <c r="B160" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="C160" t="n">
         <v>8</v>
@@ -10436,7 +10436,7 @@
         </is>
       </c>
       <c r="B163" t="n">
-        <v>462</v>
+        <v>467</v>
       </c>
       <c r="C163" t="n">
         <v>0</v>
@@ -10709,7 +10709,7 @@
         </is>
       </c>
       <c r="B184" t="n">
-        <v>246</v>
+        <v>296</v>
       </c>
       <c r="C184" t="n">
         <v>1</v>

--- a/IPL_Fantasy_Points.xlsx
+++ b/IPL_Fantasy_Points.xlsx
@@ -647,19 +647,19 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>82</v>
+        <v>90</v>
       </c>
     </row>
     <row r="6">
@@ -690,19 +690,19 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>326</v>
+        <v>337</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>326</v>
+        <v>337</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>326</v>
+        <v>337</v>
       </c>
     </row>
     <row r="7">
@@ -819,19 +819,19 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>303</v>
+        <v>312</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>303</v>
+        <v>312</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>303</v>
+        <v>312</v>
       </c>
     </row>
     <row r="10">
@@ -862,19 +862,19 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>232</v>
+        <v>264</v>
       </c>
       <c r="H10" t="n">
         <v>4</v>
       </c>
       <c r="I10" t="n">
-        <v>232</v>
+        <v>264</v>
       </c>
       <c r="J10" t="n">
         <v>80</v>
       </c>
       <c r="K10" t="n">
-        <v>312</v>
+        <v>344</v>
       </c>
     </row>
     <row r="11">
@@ -1292,19 +1292,19 @@
         </is>
       </c>
       <c r="G20" t="n">
-        <v>218</v>
+        <v>237</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>218</v>
+        <v>237</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>218</v>
+        <v>237</v>
       </c>
     </row>
     <row r="21">
@@ -1464,19 +1464,19 @@
         </is>
       </c>
       <c r="G24" t="n">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>70</v>
+        <v>85</v>
       </c>
     </row>
     <row r="25">
@@ -2327,16 +2327,16 @@
         <v>14</v>
       </c>
       <c r="H44" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="I44" t="n">
         <v>14</v>
       </c>
       <c r="J44" t="n">
-        <v>120</v>
+        <v>200</v>
       </c>
       <c r="K44" t="n">
-        <v>134</v>
+        <v>214</v>
       </c>
     </row>
     <row r="45">
@@ -2628,16 +2628,16 @@
         <v>16</v>
       </c>
       <c r="H51" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I51" t="n">
         <v>0</v>
       </c>
       <c r="J51" t="n">
-        <v>140</v>
+        <v>160</v>
       </c>
       <c r="K51" t="n">
-        <v>140</v>
+        <v>160</v>
       </c>
     </row>
     <row r="52">
@@ -2671,16 +2671,16 @@
         <v>7</v>
       </c>
       <c r="H52" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I52" t="n">
         <v>0</v>
       </c>
       <c r="J52" t="n">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="K52" t="n">
-        <v>60</v>
+        <v>100</v>
       </c>
     </row>
     <row r="53">
@@ -3012,19 +3012,19 @@
         </is>
       </c>
       <c r="G60" t="n">
-        <v>382</v>
+        <v>430</v>
       </c>
       <c r="H60" t="n">
         <v>0</v>
       </c>
       <c r="I60" t="n">
-        <v>382</v>
+        <v>430</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
       </c>
       <c r="K60" t="n">
-        <v>382</v>
+        <v>430</v>
       </c>
     </row>
     <row r="61">
@@ -3055,19 +3055,19 @@
         </is>
       </c>
       <c r="G61" t="n">
-        <v>237</v>
+        <v>286</v>
       </c>
       <c r="H61" t="n">
         <v>0</v>
       </c>
       <c r="I61" t="n">
-        <v>237</v>
+        <v>286</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
       </c>
       <c r="K61" t="n">
-        <v>237</v>
+        <v>286</v>
       </c>
     </row>
     <row r="62">
@@ -3313,19 +3313,19 @@
         </is>
       </c>
       <c r="G67" t="n">
-        <v>103</v>
+        <v>123</v>
       </c>
       <c r="H67" t="n">
         <v>0</v>
       </c>
       <c r="I67" t="n">
-        <v>103</v>
+        <v>123</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
       </c>
       <c r="K67" t="n">
-        <v>103</v>
+        <v>123</v>
       </c>
     </row>
     <row r="68">
@@ -3614,19 +3614,19 @@
         </is>
       </c>
       <c r="G74" t="n">
-        <v>382</v>
+        <v>439</v>
       </c>
       <c r="H74" t="n">
         <v>0</v>
       </c>
       <c r="I74" t="n">
-        <v>382</v>
+        <v>439</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
       </c>
       <c r="K74" t="n">
-        <v>382</v>
+        <v>439</v>
       </c>
     </row>
     <row r="75">
@@ -3657,19 +3657,19 @@
         </is>
       </c>
       <c r="G75" t="n">
-        <v>342</v>
+        <v>364</v>
       </c>
       <c r="H75" t="n">
         <v>0</v>
       </c>
       <c r="I75" t="n">
-        <v>342</v>
+        <v>364</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
       </c>
       <c r="K75" t="n">
-        <v>342</v>
+        <v>364</v>
       </c>
     </row>
     <row r="76">
@@ -3958,19 +3958,19 @@
         </is>
       </c>
       <c r="G82" t="n">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="H82" t="n">
         <v>0</v>
       </c>
       <c r="I82" t="n">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
       </c>
       <c r="K82" t="n">
-        <v>232</v>
+        <v>234</v>
       </c>
     </row>
     <row r="83">
@@ -4001,19 +4001,19 @@
         </is>
       </c>
       <c r="G83" t="n">
-        <v>415</v>
+        <v>436</v>
       </c>
       <c r="H83" t="n">
         <v>0</v>
       </c>
       <c r="I83" t="n">
-        <v>415</v>
+        <v>436</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
       </c>
       <c r="K83" t="n">
-        <v>415</v>
+        <v>436</v>
       </c>
     </row>
     <row r="84">
@@ -4219,16 +4219,16 @@
         <v>3</v>
       </c>
       <c r="H88" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I88" t="n">
         <v>0</v>
       </c>
       <c r="J88" t="n">
-        <v>160</v>
+        <v>180</v>
       </c>
       <c r="K88" t="n">
-        <v>160</v>
+        <v>180</v>
       </c>
     </row>
     <row r="89">
@@ -4259,7 +4259,7 @@
         </is>
       </c>
       <c r="G89" t="n">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="H89" t="n">
         <v>5</v>
@@ -4388,19 +4388,19 @@
         </is>
       </c>
       <c r="G92" t="n">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="H92" t="n">
         <v>0</v>
       </c>
       <c r="I92" t="n">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
       </c>
       <c r="K92" t="n">
-        <v>392</v>
+        <v>396</v>
       </c>
     </row>
     <row r="93">
@@ -4689,19 +4689,19 @@
         </is>
       </c>
       <c r="G99" t="n">
-        <v>67</v>
+        <v>92</v>
       </c>
       <c r="H99" t="n">
         <v>1</v>
       </c>
       <c r="I99" t="n">
-        <v>67</v>
+        <v>92</v>
       </c>
       <c r="J99" t="n">
         <v>20</v>
       </c>
       <c r="K99" t="n">
-        <v>87</v>
+        <v>112</v>
       </c>
     </row>
     <row r="100">
@@ -4821,16 +4821,16 @@
         <v>0</v>
       </c>
       <c r="H102" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I102" t="n">
         <v>0</v>
       </c>
       <c r="J102" t="n">
-        <v>200</v>
+        <v>220</v>
       </c>
       <c r="K102" t="n">
-        <v>200</v>
+        <v>220</v>
       </c>
     </row>
     <row r="103">
@@ -5162,19 +5162,19 @@
         </is>
       </c>
       <c r="G110" t="n">
-        <v>243</v>
+        <v>268</v>
       </c>
       <c r="H110" t="n">
         <v>0</v>
       </c>
       <c r="I110" t="n">
-        <v>243</v>
+        <v>268</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
       </c>
       <c r="K110" t="n">
-        <v>243</v>
+        <v>268</v>
       </c>
     </row>
     <row r="111">
@@ -5509,16 +5509,16 @@
         <v>11</v>
       </c>
       <c r="H118" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="I118" t="n">
         <v>0</v>
       </c>
       <c r="J118" t="n">
-        <v>260</v>
+        <v>320</v>
       </c>
       <c r="K118" t="n">
-        <v>260</v>
+        <v>320</v>
       </c>
     </row>
     <row r="119">
@@ -5850,19 +5850,19 @@
         </is>
       </c>
       <c r="G126" t="n">
-        <v>328</v>
+        <v>367</v>
       </c>
       <c r="H126" t="n">
         <v>0</v>
       </c>
       <c r="I126" t="n">
-        <v>328</v>
+        <v>367</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
       </c>
       <c r="K126" t="n">
-        <v>328</v>
+        <v>367</v>
       </c>
     </row>
     <row r="127">
@@ -6065,19 +6065,19 @@
         </is>
       </c>
       <c r="G131" t="n">
-        <v>261</v>
+        <v>336</v>
       </c>
       <c r="H131" t="n">
         <v>0</v>
       </c>
       <c r="I131" t="n">
-        <v>261</v>
+        <v>336</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
       </c>
       <c r="K131" t="n">
-        <v>261</v>
+        <v>336</v>
       </c>
     </row>
     <row r="132">
@@ -6108,19 +6108,19 @@
         </is>
       </c>
       <c r="G132" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H132" t="n">
         <v>3</v>
       </c>
       <c r="I132" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
       </c>
       <c r="K132" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="133">
@@ -6194,19 +6194,19 @@
         </is>
       </c>
       <c r="G134" t="n">
-        <v>269</v>
+        <v>340</v>
       </c>
       <c r="H134" t="n">
         <v>0</v>
       </c>
       <c r="I134" t="n">
-        <v>269</v>
+        <v>340</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
       </c>
       <c r="K134" t="n">
-        <v>269</v>
+        <v>340</v>
       </c>
     </row>
     <row r="135">
@@ -6357,7 +6357,7 @@
       <c r="D138" t="inlineStr"/>
       <c r="E138" t="inlineStr">
         <is>
-          <t>mitchell marsh</t>
+          <t>azmatullah</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -6624,19 +6624,19 @@
         </is>
       </c>
       <c r="G144" t="n">
-        <v>379</v>
+        <v>484</v>
       </c>
       <c r="H144" t="n">
         <v>0</v>
       </c>
       <c r="I144" t="n">
-        <v>379</v>
+        <v>484</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
       </c>
       <c r="K144" t="n">
-        <v>379</v>
+        <v>484</v>
       </c>
     </row>
     <row r="145">
@@ -6925,19 +6925,19 @@
         </is>
       </c>
       <c r="G151" t="n">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="H151" t="n">
         <v>0</v>
       </c>
       <c r="I151" t="n">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
       </c>
       <c r="K151" t="n">
-        <v>106</v>
+        <v>114</v>
       </c>
     </row>
     <row r="152">
@@ -7143,16 +7143,16 @@
         <v>0</v>
       </c>
       <c r="H156" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I156" t="n">
         <v>0</v>
       </c>
       <c r="J156" t="n">
-        <v>160</v>
+        <v>180</v>
       </c>
       <c r="K156" t="n">
-        <v>160</v>
+        <v>180</v>
       </c>
     </row>
     <row r="157">
@@ -7186,16 +7186,16 @@
         <v>34</v>
       </c>
       <c r="H157" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I157" t="n">
         <v>0</v>
       </c>
       <c r="J157" t="n">
-        <v>420</v>
+        <v>440</v>
       </c>
       <c r="K157" t="n">
-        <v>420</v>
+        <v>440</v>
       </c>
     </row>
     <row r="158">
@@ -7570,19 +7570,19 @@
         </is>
       </c>
       <c r="G166" t="n">
-        <v>210</v>
+        <v>228</v>
       </c>
       <c r="H166" t="n">
         <v>0</v>
       </c>
       <c r="I166" t="n">
-        <v>210</v>
+        <v>228</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
       </c>
       <c r="K166" t="n">
-        <v>210</v>
+        <v>228</v>
       </c>
     </row>
     <row r="167">
@@ -7785,19 +7785,19 @@
         </is>
       </c>
       <c r="G171" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="H171" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I171" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="J171" t="n">
-        <v>120</v>
+        <v>140</v>
       </c>
       <c r="K171" t="n">
-        <v>169</v>
+        <v>191</v>
       </c>
     </row>
     <row r="172">
@@ -7831,16 +7831,16 @@
         <v>40</v>
       </c>
       <c r="H172" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I172" t="n">
         <v>40</v>
       </c>
       <c r="J172" t="n">
-        <v>200</v>
+        <v>220</v>
       </c>
       <c r="K172" t="n">
-        <v>240</v>
+        <v>260</v>
       </c>
     </row>
     <row r="173">
@@ -8185,7 +8185,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>3782</v>
+        <v>3904</v>
       </c>
     </row>
     <row r="3">
@@ -8198,7 +8198,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>3324</v>
+        <v>3358</v>
       </c>
     </row>
     <row r="4">
@@ -8207,11 +8207,11 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>NAKUL11</t>
+          <t>BABA11</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>3017</v>
+        <v>3068</v>
       </c>
     </row>
     <row r="5">
@@ -8220,11 +8220,11 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>BABA11</t>
+          <t>NAKUL11</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2951</v>
+        <v>3066</v>
       </c>
     </row>
     <row r="6">
@@ -8237,7 +8237,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2890</v>
+        <v>3043</v>
       </c>
     </row>
     <row r="7">
@@ -8250,7 +8250,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2833</v>
+        <v>2918</v>
       </c>
     </row>
     <row r="8">
@@ -8259,11 +8259,11 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>NIRAV11</t>
+          <t>HARSH11</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2683</v>
+        <v>2743</v>
       </c>
     </row>
     <row r="9">
@@ -8272,11 +8272,11 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>HARSH11</t>
+          <t>NIRAV11</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2556</v>
+        <v>2743</v>
       </c>
     </row>
     <row r="10">
@@ -8289,7 +8289,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2456</v>
+        <v>2596</v>
       </c>
     </row>
     <row r="11">
@@ -8302,7 +8302,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1956</v>
+        <v>2016</v>
       </c>
     </row>
   </sheetData>
@@ -8316,7 +8316,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C190"/>
+  <dimension ref="A1:C193"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8408,7 +8408,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>218</v>
+        <v>237</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
@@ -8460,7 +8460,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>269</v>
+        <v>340</v>
       </c>
       <c r="C11" t="n">
         <v>0</v>
@@ -8664,128 +8664,128 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>b sai sudharshan</t>
+          <t>azmatullah</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>501</v>
+        <v>38</v>
       </c>
       <c r="C27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ben dwarshuis</t>
+          <t>b sai sudharshan</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0</v>
+        <v>501</v>
       </c>
       <c r="C28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>bhuvneshwar kumar</t>
+          <t>ben dwarshuis</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="C29" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>blessing muzarabani</t>
+          <t>bhuvneshwar kumar</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="C30" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>brijesh sharma</t>
+          <t>blessing muzarabani</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C31" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>cameron green</t>
+          <t>brijesh sharma</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>232</v>
+        <v>2</v>
       </c>
       <c r="C32" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>cooper connolly</t>
+          <t>cameron green</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>415</v>
+        <v>264</v>
       </c>
       <c r="C33" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>corbin bosch</t>
+          <t>cooper connolly</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>16</v>
+        <v>436</v>
       </c>
       <c r="C34" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>danish malewar</t>
+          <t>corbin bosch</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="C35" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>dasun shanaka</t>
+          <t>danish malewar</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="C36" t="n">
         <v>0</v>
@@ -8794,11 +8794,11 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>david miller</t>
+          <t>dasun shanaka</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>174</v>
+        <v>16</v>
       </c>
       <c r="C37" t="n">
         <v>0</v>
@@ -8807,50 +8807,50 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>david payne</t>
+          <t>david miller</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>6</v>
+        <v>174</v>
       </c>
       <c r="C38" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>deepak chahar</t>
+          <t>david payne</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C39" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>devdutt padikkal</t>
+          <t>deepak chahar</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>328</v>
+        <v>7</v>
       </c>
       <c r="C40" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>dewald brevis</t>
+          <t>devdutt padikkal</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>74</v>
+        <v>367</v>
       </c>
       <c r="C41" t="n">
         <v>0</v>
@@ -8859,11 +8859,11 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>dhruv chand jurel</t>
+          <t>dewald brevis</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>314</v>
+        <v>74</v>
       </c>
       <c r="C42" t="n">
         <v>0</v>
@@ -8872,37 +8872,37 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>digvesh rathi</t>
+          <t>dhruv chand jurel</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>2</v>
+        <v>314</v>
       </c>
       <c r="C43" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>dilshan madushanka</t>
+          <t>digvesh rathi</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C44" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>donavon ferreira</t>
+          <t>dilshan madushanka</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>233</v>
+        <v>0</v>
       </c>
       <c r="C45" t="n">
         <v>1</v>
@@ -8911,89 +8911,89 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>dushmantha chameera</t>
+          <t>donavon ferreira</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0</v>
+        <v>233</v>
       </c>
       <c r="C46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>eshan malinga</t>
+          <t>dushmantha chameera</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C47" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>finn allen</t>
+          <t>eshan malinga</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>210</v>
+        <v>2</v>
       </c>
       <c r="C48" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>george linde</t>
+          <t>finn allen</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>31</v>
+        <v>228</v>
       </c>
       <c r="C49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>glenn phillips</t>
+          <t>george linde</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>67</v>
+        <v>31</v>
       </c>
       <c r="C50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>gurjapneet singh</t>
+          <t>glenn phillips</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="C51" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>hardik pandya</t>
+          <t>gurjapneet singh</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>146</v>
+        <v>0</v>
       </c>
       <c r="C52" t="n">
         <v>4</v>
@@ -9002,50 +9002,50 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>harpreet brar</t>
+          <t>hardik pandya</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0</v>
+        <v>146</v>
       </c>
       <c r="C53" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>harsh dubey</t>
+          <t>harpreet brar</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="C54" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>harshal patel</t>
+          <t>harsh dubey</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C55" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>heinrich klaasen</t>
+          <t>harshal patel</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>508</v>
+        <v>10</v>
       </c>
       <c r="C56" t="n">
         <v>0</v>
@@ -9054,11 +9054,11 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>himmat singh</t>
+          <t>heinrich klaasen</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>92</v>
+        <v>508</v>
       </c>
       <c r="C57" t="n">
         <v>0</v>
@@ -9067,11 +9067,11 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>ishan kishan</t>
+          <t>himmat singh</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>420</v>
+        <v>92</v>
       </c>
       <c r="C58" t="n">
         <v>0</v>
@@ -9080,11 +9080,11 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>jacob bethell</t>
+          <t>ishan kishan</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>70</v>
+        <v>420</v>
       </c>
       <c r="C59" t="n">
         <v>0</v>
@@ -9093,284 +9093,284 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>jacob duffy</t>
+          <t>jacob bethell</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="C60" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>jamie overton</t>
+          <t>jacob duffy</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>136</v>
+        <v>0</v>
       </c>
       <c r="C61" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>jason holder</t>
+          <t>jamie overton</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>58</v>
+        <v>136</v>
       </c>
       <c r="C62" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>jasprit bumrah</t>
+          <t>jason holder</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>7</v>
+        <v>58</v>
       </c>
       <c r="C63" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>jaydev unadkat</t>
+          <t>jasprit bumrah</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C64" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>jitesh sharma</t>
+          <t>jaydev unadkat</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>82</v>
+        <v>4</v>
       </c>
       <c r="C65" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>jofra archer</t>
+          <t>jitesh sharma</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>19</v>
+        <v>90</v>
       </c>
       <c r="C66" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>jos buttler</t>
+          <t>jofra archer</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>355</v>
+        <v>19</v>
       </c>
       <c r="C67" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>josh hazlewood</t>
+          <t>jos buttler</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0</v>
+        <v>355</v>
       </c>
       <c r="C68" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>josh inglis</t>
+          <t>josh hazlewood</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>98</v>
+        <v>0</v>
       </c>
       <c r="C69" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>kagiso rabada</t>
+          <t>josh inglis</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>35</v>
+        <v>98</v>
       </c>
       <c r="C70" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>kartik sharma</t>
+          <t>kagiso rabada</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>173</v>
+        <v>35</v>
       </c>
       <c r="C71" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>kartik tyagi</t>
+          <t>kartik sharma</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>11</v>
+        <v>173</v>
       </c>
       <c r="C72" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>karun nair</t>
+          <t>kartik tyagi</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="C73" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>khaleel ahmed</t>
+          <t>karun nair</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="C74" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>krish bhagat</t>
+          <t>khaleel ahmed</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="C75" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>krunal pandya</t>
+          <t>krish bhagat</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>141</v>
+        <v>10</v>
       </c>
       <c r="C76" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>kuldeep yadav</t>
+          <t>krunal pandya</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>9</v>
+        <v>141</v>
       </c>
       <c r="C77" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>kumar kushagra</t>
+          <t>kuldeep yadav</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="C78" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>kyle jamieson</t>
+          <t>kumar kushagra</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="C79" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>lhuan dre pretorius</t>
+          <t>kyle jamieson</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="C80" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>liam livingstone</t>
+          <t>lhuan dre pretorius</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="C81" t="n">
         <v>0</v>
@@ -9379,63 +9379,63 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>lockie ferguson</t>
+          <t>liam livingstone</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="C82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>lokesh rahul</t>
+          <t>lockie ferguson</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>477</v>
+        <v>0</v>
       </c>
       <c r="C83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>lungi ngidi</t>
+          <t>lokesh rahul</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>4</v>
+        <v>477</v>
       </c>
       <c r="C84" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>madhav tiwari</t>
+          <t>lungi ngidi</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="C85" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>manav suthar</t>
+          <t>madhav tiwari</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="C86" t="n">
         <v>2</v>
@@ -9444,63 +9444,63 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>manimaran siddharth</t>
+          <t>manav suthar</t>
         </is>
       </c>
       <c r="B87" t="n">
         <v>0</v>
       </c>
       <c r="C87" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>manish pandey</t>
+          <t>manimaran siddharth</t>
         </is>
       </c>
       <c r="B88" t="n">
         <v>0</v>
       </c>
       <c r="C88" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>marco jansen</t>
+          <t>manish pandey</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="C89" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>marcus stoinis</t>
+          <t>marco jansen</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>179</v>
+        <v>51</v>
       </c>
       <c r="C90" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>matt henry</t>
+          <t>marcus stoinis</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>7</v>
+        <v>179</v>
       </c>
       <c r="C91" t="n">
         <v>2</v>
@@ -9509,24 +9509,24 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>matt short</t>
+          <t>matt henry</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>36</v>
+        <v>7</v>
       </c>
       <c r="C92" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>mayank markande</t>
+          <t>matt short</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="C93" t="n">
         <v>0</v>
@@ -9535,7 +9535,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>mayank rawat</t>
+          <t>mayank markande</t>
         </is>
       </c>
       <c r="B94" t="n">
@@ -9548,11 +9548,11 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>mayank yadav</t>
+          <t>mayank rawat</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C95" t="n">
         <v>0</v>
@@ -9561,11 +9561,11 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>mitchell marsh</t>
+          <t>mayank yadav</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>377</v>
+        <v>5</v>
       </c>
       <c r="C96" t="n">
         <v>0</v>
@@ -9574,24 +9574,24 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>mitchell santner</t>
+          <t>mitchell marsh</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>26</v>
+        <v>377</v>
       </c>
       <c r="C97" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>mitchell starc</t>
+          <t>mitchell santner</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="C98" t="n">
         <v>5</v>
@@ -9600,89 +9600,89 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>mohammed shami</t>
+          <t>mitchell starc</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="C99" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>mohammed siraj</t>
+          <t>mohammed shami</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="C100" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>mohsin khan</t>
+          <t>mohammed siraj</t>
         </is>
       </c>
       <c r="B101" t="n">
         <v>0</v>
       </c>
       <c r="C101" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>mukesh choudhary</t>
+          <t>mohsin khan</t>
         </is>
       </c>
       <c r="B102" t="n">
         <v>0</v>
       </c>
       <c r="C102" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>mukesh kumar</t>
+          <t>mukesh choudhary</t>
         </is>
       </c>
       <c r="B103" t="n">
         <v>0</v>
       </c>
       <c r="C103" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>mukul choudhary</t>
+          <t>mukesh kumar</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>156</v>
+        <v>0</v>
       </c>
       <c r="C104" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>naman dhir</t>
+          <t>mukul choudhary</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>303</v>
+        <v>156</v>
       </c>
       <c r="C105" t="n">
         <v>0</v>
@@ -9691,37 +9691,37 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>nandre burger</t>
+          <t>naman dhir</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>3</v>
+        <v>312</v>
       </c>
       <c r="C106" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>navdeep saini</t>
+          <t>nandre burger</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C107" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>nehal wadhera</t>
+          <t>navdeep saini</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="C108" t="n">
         <v>0</v>
@@ -9730,11 +9730,11 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>nicholas pooran</t>
+          <t>nehal wadhera</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>184</v>
+        <v>65</v>
       </c>
       <c r="C109" t="n">
         <v>0</v>
@@ -9743,11 +9743,11 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>nishant sindhu</t>
+          <t>nicholas pooran</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>37</v>
+        <v>184</v>
       </c>
       <c r="C110" t="n">
         <v>0</v>
@@ -9756,76 +9756,76 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>nitish kumar reddy</t>
+          <t>nishant sindhu</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>224</v>
+        <v>37</v>
       </c>
       <c r="C111" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>nitish rana</t>
+          <t>nitish kumar reddy</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C112" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>noor ahmad</t>
+          <t>nitish rana</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>10</v>
+        <v>225</v>
       </c>
       <c r="C113" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>pat cummins</t>
+          <t>noor ahmad</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="C114" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>pathum nissanka</t>
+          <t>pat cummins</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>278</v>
+        <v>29</v>
       </c>
       <c r="C115" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>philip salt</t>
+          <t>pathum nissanka</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>202</v>
+        <v>278</v>
       </c>
       <c r="C116" t="n">
         <v>0</v>
@@ -9834,11 +9834,11 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>prabhsimran singh</t>
+          <t>philip salt</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>382</v>
+        <v>202</v>
       </c>
       <c r="C117" t="n">
         <v>0</v>
@@ -9847,76 +9847,76 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>praful hinge</t>
+          <t>prabhsimran singh</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>3</v>
+        <v>439</v>
       </c>
       <c r="C118" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>prashant veer</t>
+          <t>praful hinge</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>66</v>
+        <v>3</v>
       </c>
       <c r="C119" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>prasidh krishna</t>
+          <t>prashant veer</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="C120" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>prince yadav</t>
+          <t>prasidh krishna</t>
         </is>
       </c>
       <c r="B121" t="n">
         <v>0</v>
       </c>
       <c r="C121" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>priyansh arya</t>
+          <t>prince yadav</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>342</v>
+        <v>0</v>
       </c>
       <c r="C122" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>quinton de kock</t>
+          <t>priyansh arya</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>132</v>
+        <v>364</v>
       </c>
       <c r="C123" t="n">
         <v>0</v>
@@ -9925,37 +9925,37 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>raghu sharma</t>
+          <t>quinton de kock</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>0</v>
+        <v>132</v>
       </c>
       <c r="C124" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>rahul chahar</t>
+          <t>raghu sharma</t>
         </is>
       </c>
       <c r="B125" t="n">
         <v>0</v>
       </c>
       <c r="C125" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>rahul tewatia</t>
+          <t>rahul chahar</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>96</v>
+        <v>0</v>
       </c>
       <c r="C126" t="n">
         <v>0</v>
@@ -9964,50 +9964,50 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>raj angad bawa</t>
+          <t>rahul tewatia</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>16</v>
+        <v>96</v>
       </c>
       <c r="C127" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>rajat patidar</t>
+          <t>raj angad bawa</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>326</v>
+        <v>16</v>
       </c>
       <c r="C128" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>ramakrishna ghosh</t>
+          <t>rajat patidar</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>0</v>
+        <v>337</v>
       </c>
       <c r="C129" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>ramandeep singh</t>
+          <t>ramakrishna ghosh</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="C130" t="n">
         <v>1</v>
@@ -10016,89 +10016,89 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>rashid khan</t>
+          <t>ramandeep singh</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>35</v>
+        <v>82</v>
       </c>
       <c r="C131" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>rasikh salam</t>
+          <t>rashid khan</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>3</v>
+        <v>35</v>
       </c>
       <c r="C132" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>ravi bishnoi</t>
+          <t>rasikh salam</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C133" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>ravichandran smaran</t>
+          <t>ravi bishnoi</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="C134" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>ravindra jadeja</t>
+          <t>ravichandran smaran</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>190</v>
+        <v>13</v>
       </c>
       <c r="C135" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>ravisrinivasan sai kishore</t>
+          <t>ravindra jadeja</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>0</v>
+        <v>190</v>
       </c>
       <c r="C136" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>rinku singh</t>
+          <t>ravisrinivasan sai kishore</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>237</v>
+        <v>0</v>
       </c>
       <c r="C137" t="n">
         <v>0</v>
@@ -10107,11 +10107,11 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>rishabh pant</t>
+          <t>rinku singh</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>251</v>
+        <v>286</v>
       </c>
       <c r="C138" t="n">
         <v>0</v>
@@ -10120,37 +10120,37 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>riyan parag</t>
+          <t>rishabh pant</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>207</v>
+        <v>251</v>
       </c>
       <c r="C139" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>robin minz</t>
+          <t>riyan parag</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>6</v>
+        <v>207</v>
       </c>
       <c r="C140" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>rohit sharma</t>
+          <t>robin minz</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>243</v>
+        <v>6</v>
       </c>
       <c r="C141" t="n">
         <v>0</v>
@@ -10159,37 +10159,37 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>romario shepherd</t>
+          <t>rohit sharma</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>83</v>
+        <v>268</v>
       </c>
       <c r="C142" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>rovman powell</t>
+          <t>romario shepherd</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>121</v>
+        <v>83</v>
       </c>
       <c r="C143" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>ruturaj gaikwad</t>
+          <t>rovman powell</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>293</v>
+        <v>121</v>
       </c>
       <c r="C144" t="n">
         <v>0</v>
@@ -10198,11 +10198,11 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>ryan rickelton</t>
+          <t>ruturaj gaikwad</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>382</v>
+        <v>293</v>
       </c>
       <c r="C145" t="n">
         <v>0</v>
@@ -10211,11 +10211,11 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>sahil parakh</t>
+          <t>ryan rickelton</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>13</v>
+        <v>430</v>
       </c>
       <c r="C146" t="n">
         <v>0</v>
@@ -10224,37 +10224,37 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>sakib hussain</t>
+          <t>sahil parakh</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="C147" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>salil arora</t>
+          <t>sakib hussain</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>111</v>
+        <v>0</v>
       </c>
       <c r="C148" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>sameer rizvi</t>
+          <t>salil arora</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>252</v>
+        <v>111</v>
       </c>
       <c r="C149" t="n">
         <v>0</v>
@@ -10263,37 +10263,37 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>sandeep sharma</t>
+          <t>sameer rizvi</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>0</v>
+        <v>252</v>
       </c>
       <c r="C150" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>sanju samson</t>
+          <t>sandeep sharma</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>430</v>
+        <v>0</v>
       </c>
       <c r="C151" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>sarfaraz khan</t>
+          <t>sanju samson</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>161</v>
+        <v>430</v>
       </c>
       <c r="C152" t="n">
         <v>0</v>
@@ -10302,24 +10302,24 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>shahbaz ahmed</t>
+          <t>sarfaraz khan</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>58</v>
+        <v>161</v>
       </c>
       <c r="C153" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>shahrukh khan</t>
+          <t>saurabh dubey</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="C154" t="n">
         <v>0</v>
@@ -10328,115 +10328,115 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>shardul thakur</t>
+          <t>shahbaz ahmed</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>14</v>
+        <v>58</v>
       </c>
       <c r="C155" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>shashank singh</t>
+          <t>shahrukh khan</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>74</v>
+        <v>43</v>
       </c>
       <c r="C156" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>sherfane rutherford</t>
+          <t>shardul thakur</t>
         </is>
       </c>
       <c r="B157" t="n">
-        <v>103</v>
+        <v>14</v>
       </c>
       <c r="C157" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>shimron hetmyer</t>
+          <t>shashank singh</t>
         </is>
       </c>
       <c r="B158" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C158" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>shivam dube</t>
+          <t>sherfane rutherford</t>
         </is>
       </c>
       <c r="B159" t="n">
-        <v>165</v>
+        <v>123</v>
       </c>
       <c r="C159" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>shivang kumar</t>
+          <t>shimron hetmyer</t>
         </is>
       </c>
       <c r="B160" t="n">
-        <v>26</v>
+        <v>78</v>
       </c>
       <c r="C160" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>shreyas iyer</t>
+          <t>shivam dube</t>
         </is>
       </c>
       <c r="B161" t="n">
-        <v>392</v>
+        <v>165</v>
       </c>
       <c r="C161" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>shubham badriprasad dubey</t>
+          <t>shivang kumar</t>
         </is>
       </c>
       <c r="B162" t="n">
-        <v>71</v>
+        <v>26</v>
       </c>
       <c r="C162" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>shubman gill</t>
+          <t>shreyas iyer</t>
         </is>
       </c>
       <c r="B163" t="n">
-        <v>467</v>
+        <v>396</v>
       </c>
       <c r="C163" t="n">
         <v>0</v>
@@ -10445,24 +10445,24 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>sunil narine</t>
+          <t>shubham badriprasad dubey</t>
         </is>
       </c>
       <c r="B164" t="n">
-        <v>40</v>
+        <v>71</v>
       </c>
       <c r="C164" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>suryakumar yadav</t>
+          <t>shubman gill</t>
         </is>
       </c>
       <c r="B165" t="n">
-        <v>195</v>
+        <v>467</v>
       </c>
       <c r="C165" t="n">
         <v>0</v>
@@ -10471,76 +10471,76 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>suryansh shedge</t>
+          <t>sunil narine</t>
         </is>
       </c>
       <c r="B166" t="n">
-        <v>106</v>
+        <v>40</v>
       </c>
       <c r="C166" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>suyash sharma</t>
+          <t>suryakumar yadav</t>
         </is>
       </c>
       <c r="B167" t="n">
-        <v>0</v>
+        <v>195</v>
       </c>
       <c r="C167" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>t natarajan</t>
+          <t>suryansh shedge</t>
         </is>
       </c>
       <c r="B168" t="n">
-        <v>1</v>
+        <v>114</v>
       </c>
       <c r="C168" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>tilak varma</t>
+          <t>suyash sharma</t>
         </is>
       </c>
       <c r="B169" t="n">
-        <v>261</v>
+        <v>0</v>
       </c>
       <c r="C169" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>tim david</t>
+          <t>t natarajan</t>
         </is>
       </c>
       <c r="B170" t="n">
-        <v>232</v>
+        <v>1</v>
       </c>
       <c r="C170" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>tim seifert</t>
+          <t>tilak varma</t>
         </is>
       </c>
       <c r="B171" t="n">
-        <v>19</v>
+        <v>336</v>
       </c>
       <c r="C171" t="n">
         <v>0</v>
@@ -10549,11 +10549,11 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>travis head</t>
+          <t>tim david</t>
         </is>
       </c>
       <c r="B172" t="n">
-        <v>361</v>
+        <v>234</v>
       </c>
       <c r="C172" t="n">
         <v>0</v>
@@ -10562,24 +10562,24 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>trent boult</t>
+          <t>tim seifert</t>
         </is>
       </c>
       <c r="B173" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="C173" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>tristan stubbs</t>
+          <t>travis head</t>
         </is>
       </c>
       <c r="B174" t="n">
-        <v>271</v>
+        <v>361</v>
       </c>
       <c r="C174" t="n">
         <v>0</v>
@@ -10588,24 +10588,24 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>tushar deshpande</t>
+          <t>trent boult</t>
         </is>
       </c>
       <c r="B175" t="n">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="C175" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>urvil patel</t>
+          <t>tristan stubbs</t>
         </is>
       </c>
       <c r="B176" t="n">
-        <v>110</v>
+        <v>271</v>
       </c>
       <c r="C176" t="n">
         <v>0</v>
@@ -10614,24 +10614,24 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>vaibhav arora</t>
+          <t>tushar deshpande</t>
         </is>
       </c>
       <c r="B177" t="n">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="C177" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>vaibhav suryavanshi</t>
+          <t>urvil patel</t>
         </is>
       </c>
       <c r="B178" t="n">
-        <v>440</v>
+        <v>110</v>
       </c>
       <c r="C178" t="n">
         <v>0</v>
@@ -10640,24 +10640,24 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>varun chakravarthy</t>
+          <t>vaibhav arora</t>
         </is>
       </c>
       <c r="B179" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C179" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>venkatesh iyer</t>
+          <t>vaibhav suryavanshi</t>
         </is>
       </c>
       <c r="B180" t="n">
-        <v>41</v>
+        <v>440</v>
       </c>
       <c r="C180" t="n">
         <v>0</v>
@@ -10666,131 +10666,170 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>vijaykumar vyshak</t>
+          <t>varun chakravarthy</t>
         </is>
       </c>
       <c r="B181" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C181" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>vipraj nigam</t>
+          <t>venkatesh iyer</t>
         </is>
       </c>
       <c r="B182" t="n">
-        <v>15</v>
+        <v>41</v>
       </c>
       <c r="C182" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>virat kohli</t>
+          <t>vijaykumar vyshak</t>
         </is>
       </c>
       <c r="B183" t="n">
-        <v>379</v>
+        <v>2</v>
       </c>
       <c r="C183" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>washington sundar</t>
+          <t>vipraj nigam</t>
         </is>
       </c>
       <c r="B184" t="n">
-        <v>296</v>
+        <v>15</v>
       </c>
       <c r="C184" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>will jacks</t>
+          <t>virat kohli</t>
         </is>
       </c>
       <c r="B185" t="n">
-        <v>67</v>
+        <v>484</v>
       </c>
       <c r="C185" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>xavier bartlett</t>
+          <t>vishnu vinod</t>
         </is>
       </c>
       <c r="B186" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C186" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>yash raj punja</t>
+          <t>washington sundar</t>
         </is>
       </c>
       <c r="B187" t="n">
-        <v>0</v>
+        <v>296</v>
       </c>
       <c r="C187" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>yash thakur</t>
+          <t>will jacks</t>
         </is>
       </c>
       <c r="B188" t="n">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="C188" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>yashasvi jaiswal</t>
+          <t>xavier bartlett</t>
         </is>
       </c>
       <c r="B189" t="n">
-        <v>315</v>
+        <v>29</v>
       </c>
       <c r="C189" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
+          <t>yash raj punja</t>
+        </is>
+      </c>
+      <c r="B190" t="n">
+        <v>0</v>
+      </c>
+      <c r="C190" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>yash thakur</t>
+        </is>
+      </c>
+      <c r="B191" t="n">
+        <v>0</v>
+      </c>
+      <c r="C191" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>yashasvi jaiswal</t>
+        </is>
+      </c>
+      <c r="B192" t="n">
+        <v>315</v>
+      </c>
+      <c r="C192" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
           <t>yuzvendra chahal</t>
         </is>
       </c>
-      <c r="B190" t="n">
-        <v>0</v>
-      </c>
-      <c r="C190" t="n">
-        <v>8</v>
+      <c r="B193" t="n">
+        <v>0</v>
+      </c>
+      <c r="C193" t="n">
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -11614,7 +11653,7 @@
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>mitchell marsh</t>
+          <t>azmatullah</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">

--- a/IPL_Fantasy_Points.xlsx
+++ b/IPL_Fantasy_Points.xlsx
@@ -733,19 +733,19 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>74</v>
+        <v>99</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>74</v>
+        <v>99</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>74</v>
+        <v>99</v>
       </c>
     </row>
     <row r="8">
@@ -776,19 +776,19 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>173</v>
+        <v>244</v>
       </c>
     </row>
     <row r="9">
@@ -2754,19 +2754,19 @@
         </is>
       </c>
       <c r="G54" t="n">
-        <v>430</v>
+        <v>450</v>
       </c>
       <c r="H54" t="n">
         <v>0</v>
       </c>
       <c r="I54" t="n">
-        <v>430</v>
+        <v>450</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
       </c>
       <c r="K54" t="n">
-        <v>430</v>
+        <v>450</v>
       </c>
     </row>
     <row r="55">
@@ -2797,19 +2797,19 @@
         </is>
       </c>
       <c r="G55" t="n">
-        <v>98</v>
+        <v>134</v>
       </c>
       <c r="H55" t="n">
         <v>0</v>
       </c>
       <c r="I55" t="n">
-        <v>98</v>
+        <v>134</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
       </c>
       <c r="K55" t="n">
-        <v>98</v>
+        <v>134</v>
       </c>
     </row>
     <row r="56">
@@ -3098,19 +3098,19 @@
         </is>
       </c>
       <c r="G62" t="n">
-        <v>165</v>
+        <v>197</v>
       </c>
       <c r="H62" t="n">
         <v>1</v>
       </c>
       <c r="I62" t="n">
-        <v>165</v>
+        <v>197</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
       </c>
       <c r="K62" t="n">
-        <v>165</v>
+        <v>197</v>
       </c>
     </row>
     <row r="63">
@@ -3528,19 +3528,19 @@
         </is>
       </c>
       <c r="G72" t="n">
-        <v>293</v>
+        <v>306</v>
       </c>
       <c r="H72" t="n">
         <v>0</v>
       </c>
       <c r="I72" t="n">
-        <v>293</v>
+        <v>306</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
       </c>
       <c r="K72" t="n">
-        <v>293</v>
+        <v>306</v>
       </c>
     </row>
     <row r="73">
@@ -4474,19 +4474,19 @@
         </is>
       </c>
       <c r="G94" t="n">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="H94" t="n">
         <v>0</v>
       </c>
       <c r="I94" t="n">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
       </c>
       <c r="K94" t="n">
-        <v>110</v>
+        <v>116</v>
       </c>
     </row>
     <row r="95">
@@ -5119,19 +5119,19 @@
         </is>
       </c>
       <c r="G109" t="n">
-        <v>377</v>
+        <v>467</v>
       </c>
       <c r="H109" t="n">
         <v>0</v>
       </c>
       <c r="I109" t="n">
-        <v>377</v>
+        <v>467</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
       </c>
       <c r="K109" t="n">
-        <v>377</v>
+        <v>467</v>
       </c>
     </row>
     <row r="110">
@@ -5638,16 +5638,16 @@
         <v>0</v>
       </c>
       <c r="H121" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I121" t="n">
         <v>0</v>
       </c>
       <c r="J121" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="K121" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
     </row>
     <row r="122">
@@ -6237,19 +6237,19 @@
         </is>
       </c>
       <c r="G135" t="n">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="H135" t="n">
         <v>0</v>
       </c>
       <c r="I135" t="n">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
       </c>
       <c r="K135" t="n">
-        <v>66</v>
+        <v>79</v>
       </c>
     </row>
     <row r="136">
@@ -6541,16 +6541,16 @@
         <v>31</v>
       </c>
       <c r="H142" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I142" t="n">
         <v>0</v>
       </c>
       <c r="J142" t="n">
-        <v>180</v>
+        <v>200</v>
       </c>
       <c r="K142" t="n">
-        <v>180</v>
+        <v>200</v>
       </c>
     </row>
     <row r="143">
@@ -6710,19 +6710,19 @@
         </is>
       </c>
       <c r="G146" t="n">
-        <v>184</v>
+        <v>216</v>
       </c>
       <c r="H146" t="n">
         <v>0</v>
       </c>
       <c r="I146" t="n">
-        <v>184</v>
+        <v>216</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
       </c>
       <c r="K146" t="n">
-        <v>184</v>
+        <v>216</v>
       </c>
     </row>
     <row r="147">
@@ -6959,7 +6959,7 @@
       <c r="D152" t="inlineStr"/>
       <c r="E152" t="inlineStr">
         <is>
-          <t>prabhsimran singh</t>
+          <t>akash singh</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
@@ -8185,7 +8185,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>3904</v>
+        <v>3917</v>
       </c>
     </row>
     <row r="3">
@@ -8211,7 +8211,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>3068</v>
+        <v>3156</v>
       </c>
     </row>
     <row r="5">
@@ -8220,11 +8220,11 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>NAKUL11</t>
+          <t>AMEY11</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>3066</v>
+        <v>3075</v>
       </c>
     </row>
     <row r="6">
@@ -8233,11 +8233,11 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>AMEY11</t>
+          <t>NAKUL11</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>3043</v>
+        <v>3072</v>
       </c>
     </row>
     <row r="7">
@@ -8250,7 +8250,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2918</v>
+        <v>3028</v>
       </c>
     </row>
     <row r="8">
@@ -8259,11 +8259,11 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>HARSH11</t>
+          <t>NIRAV11</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2743</v>
+        <v>2839</v>
       </c>
     </row>
     <row r="9">
@@ -8272,11 +8272,11 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>NIRAV11</t>
+          <t>HARSH11</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2743</v>
+        <v>2776</v>
       </c>
     </row>
     <row r="10">
@@ -8316,7 +8316,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C193"/>
+  <dimension ref="A1:C195"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8343,7 +8343,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
@@ -8417,63 +8417,63 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>akeal hosein</t>
+          <t>akash singh</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C8" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>akshat raghuwanshi</t>
+          <t>akeal hosein</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>am ghazanfar</t>
+          <t>akshat raghuwanshi</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="C10" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>angkrish raghuvanshi</t>
+          <t>am ghazanfar</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>340</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>aniket verma</t>
+          <t>angkrish raghuvanshi</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>79</v>
+        <v>340</v>
       </c>
       <c r="C12" t="n">
         <v>0</v>
@@ -8482,11 +8482,11 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>anrich nortje</t>
+          <t>aniket verma</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="C13" t="n">
         <v>0</v>
@@ -8495,167 +8495,167 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>anshul kamboj</t>
+          <t>anrich nortje</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>anukul roy</t>
+          <t>anshul kamboj</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>39</v>
       </c>
       <c r="C15" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>arshad khan</t>
+          <t>anukul roy</t>
         </is>
       </c>
       <c r="B16" t="n">
+        <v>39</v>
+      </c>
+      <c r="C16" t="n">
         <v>8</v>
-      </c>
-      <c r="C16" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>arshdeep singh</t>
+          <t>arshad khan</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C17" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>arshin kulkarni</t>
+          <t>arshdeep singh</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ashok sharma</t>
+          <t>arshin kulkarni</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="C19" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ashutosh sharma</t>
+          <t>ashok sharma</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>135</v>
+        <v>1</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ashwani kumar</t>
+          <t>ashutosh sharma</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1</v>
+        <v>135</v>
       </c>
       <c r="C21" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>auqib nabi</t>
+          <t>ashwani kumar</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>avesh khan</t>
+          <t>auqib nabi</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="C23" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>axar patel</t>
+          <t>avesh khan</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>100</v>
+        <v>6</v>
       </c>
       <c r="C24" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>ayush badoni</t>
+          <t>axar patel</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>172</v>
+        <v>100</v>
       </c>
       <c r="C25" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ayush mhatre</t>
+          <t>ayush badoni</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>201</v>
+        <v>172</v>
       </c>
       <c r="C26" t="n">
         <v>0</v>
@@ -8664,141 +8664,141 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>azmatullah</t>
+          <t>ayush mhatre</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>38</v>
+        <v>201</v>
       </c>
       <c r="C27" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>b sai sudharshan</t>
+          <t>azmatullah</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>501</v>
+        <v>38</v>
       </c>
       <c r="C28" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>ben dwarshuis</t>
+          <t>b sai sudharshan</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0</v>
+        <v>501</v>
       </c>
       <c r="C29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>bhuvneshwar kumar</t>
+          <t>ben dwarshuis</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="C30" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>blessing muzarabani</t>
+          <t>bhuvneshwar kumar</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="C31" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>brijesh sharma</t>
+          <t>blessing muzarabani</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C32" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>cameron green</t>
+          <t>brijesh sharma</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>264</v>
+        <v>2</v>
       </c>
       <c r="C33" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>cooper connolly</t>
+          <t>cameron green</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>436</v>
+        <v>264</v>
       </c>
       <c r="C34" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>corbin bosch</t>
+          <t>cooper connolly</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>16</v>
+        <v>436</v>
       </c>
       <c r="C35" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>danish malewar</t>
+          <t>corbin bosch</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="C36" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>dasun shanaka</t>
+          <t>danish malewar</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="C37" t="n">
         <v>0</v>
@@ -8807,11 +8807,11 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>david miller</t>
+          <t>dasun shanaka</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>174</v>
+        <v>16</v>
       </c>
       <c r="C38" t="n">
         <v>0</v>
@@ -8820,50 +8820,50 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>david payne</t>
+          <t>david miller</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>6</v>
+        <v>174</v>
       </c>
       <c r="C39" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>deepak chahar</t>
+          <t>david payne</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C40" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>devdutt padikkal</t>
+          <t>deepak chahar</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>367</v>
+        <v>7</v>
       </c>
       <c r="C41" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>dewald brevis</t>
+          <t>devdutt padikkal</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>74</v>
+        <v>367</v>
       </c>
       <c r="C42" t="n">
         <v>0</v>
@@ -8872,11 +8872,11 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>dhruv chand jurel</t>
+          <t>dewald brevis</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>314</v>
+        <v>99</v>
       </c>
       <c r="C43" t="n">
         <v>0</v>
@@ -8885,37 +8885,37 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>digvesh rathi</t>
+          <t>dhruv chand jurel</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>2</v>
+        <v>314</v>
       </c>
       <c r="C44" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>dilshan madushanka</t>
+          <t>digvesh rathi</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C45" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>donavon ferreira</t>
+          <t>dilshan madushanka</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>233</v>
+        <v>0</v>
       </c>
       <c r="C46" t="n">
         <v>1</v>
@@ -8924,89 +8924,89 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>dushmantha chameera</t>
+          <t>donavon ferreira</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0</v>
+        <v>233</v>
       </c>
       <c r="C47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>eshan malinga</t>
+          <t>dushmantha chameera</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C48" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>finn allen</t>
+          <t>eshan malinga</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>228</v>
+        <v>2</v>
       </c>
       <c r="C49" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>george linde</t>
+          <t>finn allen</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>31</v>
+        <v>228</v>
       </c>
       <c r="C50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>glenn phillips</t>
+          <t>george linde</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>67</v>
+        <v>31</v>
       </c>
       <c r="C51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>gurjapneet singh</t>
+          <t>glenn phillips</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="C52" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>hardik pandya</t>
+          <t>gurjapneet singh</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>146</v>
+        <v>0</v>
       </c>
       <c r="C53" t="n">
         <v>4</v>
@@ -9015,50 +9015,50 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>harpreet brar</t>
+          <t>hardik pandya</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0</v>
+        <v>146</v>
       </c>
       <c r="C54" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>harsh dubey</t>
+          <t>harpreet brar</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="C55" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>harshal patel</t>
+          <t>harsh dubey</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C56" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>heinrich klaasen</t>
+          <t>harshal patel</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>508</v>
+        <v>10</v>
       </c>
       <c r="C57" t="n">
         <v>0</v>
@@ -9067,11 +9067,11 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>himmat singh</t>
+          <t>heinrich klaasen</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>92</v>
+        <v>508</v>
       </c>
       <c r="C58" t="n">
         <v>0</v>
@@ -9080,11 +9080,11 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>ishan kishan</t>
+          <t>himmat singh</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>420</v>
+        <v>92</v>
       </c>
       <c r="C59" t="n">
         <v>0</v>
@@ -9093,11 +9093,11 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>jacob bethell</t>
+          <t>ishan kishan</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>85</v>
+        <v>420</v>
       </c>
       <c r="C60" t="n">
         <v>0</v>
@@ -9106,284 +9106,284 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>jacob duffy</t>
+          <t>jacob bethell</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="C61" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>jamie overton</t>
+          <t>jacob duffy</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>136</v>
+        <v>0</v>
       </c>
       <c r="C62" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>jason holder</t>
+          <t>jamie overton</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>58</v>
+        <v>136</v>
       </c>
       <c r="C63" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>jasprit bumrah</t>
+          <t>jason holder</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>7</v>
+        <v>58</v>
       </c>
       <c r="C64" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>jaydev unadkat</t>
+          <t>jasprit bumrah</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C65" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>jitesh sharma</t>
+          <t>jaydev unadkat</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>90</v>
+        <v>4</v>
       </c>
       <c r="C66" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>jofra archer</t>
+          <t>jitesh sharma</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>19</v>
+        <v>90</v>
       </c>
       <c r="C67" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>jos buttler</t>
+          <t>jofra archer</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>355</v>
+        <v>19</v>
       </c>
       <c r="C68" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>josh hazlewood</t>
+          <t>jos buttler</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0</v>
+        <v>355</v>
       </c>
       <c r="C69" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>josh inglis</t>
+          <t>josh hazlewood</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>98</v>
+        <v>0</v>
       </c>
       <c r="C70" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>kagiso rabada</t>
+          <t>josh inglis</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>35</v>
+        <v>134</v>
       </c>
       <c r="C71" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>kartik sharma</t>
+          <t>kagiso rabada</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>173</v>
+        <v>35</v>
       </c>
       <c r="C72" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>kartik tyagi</t>
+          <t>kartik sharma</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>11</v>
+        <v>244</v>
       </c>
       <c r="C73" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>karun nair</t>
+          <t>kartik tyagi</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="C74" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>khaleel ahmed</t>
+          <t>karun nair</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="C75" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>krish bhagat</t>
+          <t>khaleel ahmed</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="C76" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>krunal pandya</t>
+          <t>krish bhagat</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>141</v>
+        <v>10</v>
       </c>
       <c r="C77" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>kuldeep yadav</t>
+          <t>krunal pandya</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>9</v>
+        <v>141</v>
       </c>
       <c r="C78" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>kumar kushagra</t>
+          <t>kuldeep yadav</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="C79" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>kyle jamieson</t>
+          <t>kumar kushagra</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="C80" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>lhuan dre pretorius</t>
+          <t>kyle jamieson</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="C81" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>liam livingstone</t>
+          <t>lhuan dre pretorius</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="C82" t="n">
         <v>0</v>
@@ -9392,63 +9392,63 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>lockie ferguson</t>
+          <t>liam livingstone</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="C83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>lokesh rahul</t>
+          <t>lockie ferguson</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>477</v>
+        <v>0</v>
       </c>
       <c r="C84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>lungi ngidi</t>
+          <t>lokesh rahul</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>4</v>
+        <v>477</v>
       </c>
       <c r="C85" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>madhav tiwari</t>
+          <t>lungi ngidi</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="C86" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>manav suthar</t>
+          <t>madhav tiwari</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="C87" t="n">
         <v>2</v>
@@ -9457,63 +9457,63 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>manimaran siddharth</t>
+          <t>manav suthar</t>
         </is>
       </c>
       <c r="B88" t="n">
         <v>0</v>
       </c>
       <c r="C88" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>manish pandey</t>
+          <t>manimaran siddharth</t>
         </is>
       </c>
       <c r="B89" t="n">
         <v>0</v>
       </c>
       <c r="C89" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>marco jansen</t>
+          <t>manish pandey</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="C90" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>marcus stoinis</t>
+          <t>marco jansen</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>179</v>
+        <v>51</v>
       </c>
       <c r="C91" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>matt henry</t>
+          <t>marcus stoinis</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>7</v>
+        <v>179</v>
       </c>
       <c r="C92" t="n">
         <v>2</v>
@@ -9522,24 +9522,24 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>matt short</t>
+          <t>matt henry</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>36</v>
+        <v>7</v>
       </c>
       <c r="C93" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>mayank markande</t>
+          <t>matt short</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="C94" t="n">
         <v>0</v>
@@ -9548,7 +9548,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>mayank rawat</t>
+          <t>mayank markande</t>
         </is>
       </c>
       <c r="B95" t="n">
@@ -9561,11 +9561,11 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>mayank yadav</t>
+          <t>mayank rawat</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C96" t="n">
         <v>0</v>
@@ -9574,11 +9574,11 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>mitchell marsh</t>
+          <t>mayank yadav</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>377</v>
+        <v>5</v>
       </c>
       <c r="C97" t="n">
         <v>0</v>
@@ -9587,24 +9587,24 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>mitchell santner</t>
+          <t>mitchell marsh</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>26</v>
+        <v>467</v>
       </c>
       <c r="C98" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>mitchell starc</t>
+          <t>mitchell santner</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="C99" t="n">
         <v>5</v>
@@ -9613,89 +9613,89 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>mohammed shami</t>
+          <t>mitchell starc</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="C100" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>mohammed siraj</t>
+          <t>mohammed shami</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="C101" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>mohsin khan</t>
+          <t>mohammed siraj</t>
         </is>
       </c>
       <c r="B102" t="n">
         <v>0</v>
       </c>
       <c r="C102" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>mukesh choudhary</t>
+          <t>mohsin khan</t>
         </is>
       </c>
       <c r="B103" t="n">
         <v>0</v>
       </c>
       <c r="C103" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>mukesh kumar</t>
+          <t>mukesh choudhary</t>
         </is>
       </c>
       <c r="B104" t="n">
         <v>0</v>
       </c>
       <c r="C104" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>mukul choudhary</t>
+          <t>mukesh kumar</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>156</v>
+        <v>0</v>
       </c>
       <c r="C105" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>naman dhir</t>
+          <t>mukul choudhary</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>312</v>
+        <v>169</v>
       </c>
       <c r="C106" t="n">
         <v>0</v>
@@ -9704,37 +9704,37 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>nandre burger</t>
+          <t>naman dhir</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>3</v>
+        <v>312</v>
       </c>
       <c r="C107" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>navdeep saini</t>
+          <t>nandre burger</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C108" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>nehal wadhera</t>
+          <t>navdeep saini</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="C109" t="n">
         <v>0</v>
@@ -9743,11 +9743,11 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>nicholas pooran</t>
+          <t>nehal wadhera</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>184</v>
+        <v>65</v>
       </c>
       <c r="C110" t="n">
         <v>0</v>
@@ -9756,11 +9756,11 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>nishant sindhu</t>
+          <t>nicholas pooran</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>37</v>
+        <v>216</v>
       </c>
       <c r="C111" t="n">
         <v>0</v>
@@ -9769,76 +9769,76 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>nitish kumar reddy</t>
+          <t>nishant sindhu</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>224</v>
+        <v>37</v>
       </c>
       <c r="C112" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>nitish rana</t>
+          <t>nitish kumar reddy</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C113" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>noor ahmad</t>
+          <t>nitish rana</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>10</v>
+        <v>225</v>
       </c>
       <c r="C114" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>pat cummins</t>
+          <t>noor ahmad</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="C115" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>pathum nissanka</t>
+          <t>pat cummins</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>278</v>
+        <v>29</v>
       </c>
       <c r="C116" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>philip salt</t>
+          <t>pathum nissanka</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>202</v>
+        <v>278</v>
       </c>
       <c r="C117" t="n">
         <v>0</v>
@@ -9847,11 +9847,11 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>prabhsimran singh</t>
+          <t>philip salt</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>439</v>
+        <v>202</v>
       </c>
       <c r="C118" t="n">
         <v>0</v>
@@ -9860,76 +9860,76 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>praful hinge</t>
+          <t>prabhsimran singh</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>3</v>
+        <v>439</v>
       </c>
       <c r="C119" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>prashant veer</t>
+          <t>praful hinge</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>66</v>
+        <v>3</v>
       </c>
       <c r="C120" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>prasidh krishna</t>
+          <t>prashant veer</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="C121" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>prince yadav</t>
+          <t>prasidh krishna</t>
         </is>
       </c>
       <c r="B122" t="n">
         <v>0</v>
       </c>
       <c r="C122" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>priyansh arya</t>
+          <t>prince yadav</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>364</v>
+        <v>0</v>
       </c>
       <c r="C123" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>quinton de kock</t>
+          <t>priyansh arya</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>132</v>
+        <v>364</v>
       </c>
       <c r="C124" t="n">
         <v>0</v>
@@ -9938,37 +9938,37 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>raghu sharma</t>
+          <t>quinton de kock</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>0</v>
+        <v>132</v>
       </c>
       <c r="C125" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>rahul chahar</t>
+          <t>raghu sharma</t>
         </is>
       </c>
       <c r="B126" t="n">
         <v>0</v>
       </c>
       <c r="C126" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>rahul tewatia</t>
+          <t>rahul chahar</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>96</v>
+        <v>0</v>
       </c>
       <c r="C127" t="n">
         <v>0</v>
@@ -9977,50 +9977,50 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>raj angad bawa</t>
+          <t>rahul tewatia</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>16</v>
+        <v>96</v>
       </c>
       <c r="C128" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>rajat patidar</t>
+          <t>raj angad bawa</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>337</v>
+        <v>16</v>
       </c>
       <c r="C129" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>ramakrishna ghosh</t>
+          <t>rajat patidar</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>0</v>
+        <v>337</v>
       </c>
       <c r="C130" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>ramandeep singh</t>
+          <t>ramakrishna ghosh</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="C131" t="n">
         <v>1</v>
@@ -10029,89 +10029,89 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>rashid khan</t>
+          <t>ramandeep singh</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>35</v>
+        <v>82</v>
       </c>
       <c r="C132" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>rasikh salam</t>
+          <t>rashid khan</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>3</v>
+        <v>35</v>
       </c>
       <c r="C133" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>ravi bishnoi</t>
+          <t>rasikh salam</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C134" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>ravichandran smaran</t>
+          <t>ravi bishnoi</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="C135" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>ravindra jadeja</t>
+          <t>ravichandran smaran</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>190</v>
+        <v>13</v>
       </c>
       <c r="C136" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>ravisrinivasan sai kishore</t>
+          <t>ravindra jadeja</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>0</v>
+        <v>190</v>
       </c>
       <c r="C137" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>rinku singh</t>
+          <t>ravisrinivasan sai kishore</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>286</v>
+        <v>0</v>
       </c>
       <c r="C138" t="n">
         <v>0</v>
@@ -10120,11 +10120,11 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>rishabh pant</t>
+          <t>rinku singh</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>251</v>
+        <v>286</v>
       </c>
       <c r="C139" t="n">
         <v>0</v>
@@ -10133,37 +10133,37 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>riyan parag</t>
+          <t>rishabh pant</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>207</v>
+        <v>251</v>
       </c>
       <c r="C140" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>robin minz</t>
+          <t>riyan parag</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>6</v>
+        <v>207</v>
       </c>
       <c r="C141" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>rohit sharma</t>
+          <t>robin minz</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>268</v>
+        <v>6</v>
       </c>
       <c r="C142" t="n">
         <v>0</v>
@@ -10172,37 +10172,37 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>romario shepherd</t>
+          <t>rohit sharma</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>83</v>
+        <v>268</v>
       </c>
       <c r="C143" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>rovman powell</t>
+          <t>romario shepherd</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>121</v>
+        <v>83</v>
       </c>
       <c r="C144" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>ruturaj gaikwad</t>
+          <t>rovman powell</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>293</v>
+        <v>121</v>
       </c>
       <c r="C145" t="n">
         <v>0</v>
@@ -10211,11 +10211,11 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>ryan rickelton</t>
+          <t>ruturaj gaikwad</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>430</v>
+        <v>306</v>
       </c>
       <c r="C146" t="n">
         <v>0</v>
@@ -10224,11 +10224,11 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>sahil parakh</t>
+          <t>ryan rickelton</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>13</v>
+        <v>430</v>
       </c>
       <c r="C147" t="n">
         <v>0</v>
@@ -10237,37 +10237,37 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>sakib hussain</t>
+          <t>sahil parakh</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="C148" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>salil arora</t>
+          <t>sakib hussain</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>111</v>
+        <v>0</v>
       </c>
       <c r="C149" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>sameer rizvi</t>
+          <t>salil arora</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>252</v>
+        <v>111</v>
       </c>
       <c r="C150" t="n">
         <v>0</v>
@@ -10276,37 +10276,37 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>sandeep sharma</t>
+          <t>sameer rizvi</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>0</v>
+        <v>252</v>
       </c>
       <c r="C151" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>sanju samson</t>
+          <t>sandeep sharma</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>430</v>
+        <v>0</v>
       </c>
       <c r="C152" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>sarfaraz khan</t>
+          <t>sanju samson</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>161</v>
+        <v>450</v>
       </c>
       <c r="C153" t="n">
         <v>0</v>
@@ -10315,11 +10315,11 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>saurabh dubey</t>
+          <t>sarfaraz khan</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>0</v>
+        <v>161</v>
       </c>
       <c r="C154" t="n">
         <v>0</v>
@@ -10328,76 +10328,76 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>shahbaz ahmed</t>
+          <t>saurabh dubey</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="C155" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>shahrukh khan</t>
+          <t>shahbaz ahmed</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>43</v>
+        <v>58</v>
       </c>
       <c r="C156" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>shardul thakur</t>
+          <t>shahrukh khan</t>
         </is>
       </c>
       <c r="B157" t="n">
-        <v>14</v>
+        <v>43</v>
       </c>
       <c r="C157" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>shashank singh</t>
+          <t>shardul thakur</t>
         </is>
       </c>
       <c r="B158" t="n">
-        <v>76</v>
+        <v>14</v>
       </c>
       <c r="C158" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>sherfane rutherford</t>
+          <t>shashank singh</t>
         </is>
       </c>
       <c r="B159" t="n">
-        <v>123</v>
+        <v>76</v>
       </c>
       <c r="C159" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>shimron hetmyer</t>
+          <t>sherfane rutherford</t>
         </is>
       </c>
       <c r="B160" t="n">
-        <v>78</v>
+        <v>123</v>
       </c>
       <c r="C160" t="n">
         <v>0</v>
@@ -10406,50 +10406,50 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>shivam dube</t>
+          <t>shimron hetmyer</t>
         </is>
       </c>
       <c r="B161" t="n">
-        <v>165</v>
+        <v>78</v>
       </c>
       <c r="C161" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>shivang kumar</t>
+          <t>shivam dube</t>
         </is>
       </c>
       <c r="B162" t="n">
-        <v>26</v>
+        <v>197</v>
       </c>
       <c r="C162" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>shreyas iyer</t>
+          <t>shivang kumar</t>
         </is>
       </c>
       <c r="B163" t="n">
-        <v>396</v>
+        <v>26</v>
       </c>
       <c r="C163" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>shubham badriprasad dubey</t>
+          <t>shreyas iyer</t>
         </is>
       </c>
       <c r="B164" t="n">
-        <v>71</v>
+        <v>396</v>
       </c>
       <c r="C164" t="n">
         <v>0</v>
@@ -10458,11 +10458,11 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>shubman gill</t>
+          <t>shubham badriprasad dubey</t>
         </is>
       </c>
       <c r="B165" t="n">
-        <v>467</v>
+        <v>71</v>
       </c>
       <c r="C165" t="n">
         <v>0</v>
@@ -10471,102 +10471,102 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>sunil narine</t>
+          <t>shubman gill</t>
         </is>
       </c>
       <c r="B166" t="n">
-        <v>40</v>
+        <v>467</v>
       </c>
       <c r="C166" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>suryakumar yadav</t>
+          <t>spencer johnson</t>
         </is>
       </c>
       <c r="B167" t="n">
-        <v>195</v>
+        <v>0</v>
       </c>
       <c r="C167" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>suryansh shedge</t>
+          <t>sunil narine</t>
         </is>
       </c>
       <c r="B168" t="n">
-        <v>114</v>
+        <v>40</v>
       </c>
       <c r="C168" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>suyash sharma</t>
+          <t>suryakumar yadav</t>
         </is>
       </c>
       <c r="B169" t="n">
-        <v>0</v>
+        <v>195</v>
       </c>
       <c r="C169" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>t natarajan</t>
+          <t>suryansh shedge</t>
         </is>
       </c>
       <c r="B170" t="n">
-        <v>1</v>
+        <v>114</v>
       </c>
       <c r="C170" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>tilak varma</t>
+          <t>suyash sharma</t>
         </is>
       </c>
       <c r="B171" t="n">
-        <v>336</v>
+        <v>0</v>
       </c>
       <c r="C171" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>tim david</t>
+          <t>t natarajan</t>
         </is>
       </c>
       <c r="B172" t="n">
-        <v>234</v>
+        <v>1</v>
       </c>
       <c r="C172" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>tim seifert</t>
+          <t>tilak varma</t>
         </is>
       </c>
       <c r="B173" t="n">
-        <v>19</v>
+        <v>336</v>
       </c>
       <c r="C173" t="n">
         <v>0</v>
@@ -10575,11 +10575,11 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>travis head</t>
+          <t>tim david</t>
         </is>
       </c>
       <c r="B174" t="n">
-        <v>361</v>
+        <v>234</v>
       </c>
       <c r="C174" t="n">
         <v>0</v>
@@ -10588,24 +10588,24 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>trent boult</t>
+          <t>tim seifert</t>
         </is>
       </c>
       <c r="B175" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="C175" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>tristan stubbs</t>
+          <t>travis head</t>
         </is>
       </c>
       <c r="B176" t="n">
-        <v>271</v>
+        <v>361</v>
       </c>
       <c r="C176" t="n">
         <v>0</v>
@@ -10614,24 +10614,24 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>tushar deshpande</t>
+          <t>trent boult</t>
         </is>
       </c>
       <c r="B177" t="n">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="C177" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>urvil patel</t>
+          <t>tristan stubbs</t>
         </is>
       </c>
       <c r="B178" t="n">
-        <v>110</v>
+        <v>271</v>
       </c>
       <c r="C178" t="n">
         <v>0</v>
@@ -10640,24 +10640,24 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>vaibhav arora</t>
+          <t>tushar deshpande</t>
         </is>
       </c>
       <c r="B179" t="n">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="C179" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>vaibhav suryavanshi</t>
+          <t>urvil patel</t>
         </is>
       </c>
       <c r="B180" t="n">
-        <v>440</v>
+        <v>116</v>
       </c>
       <c r="C180" t="n">
         <v>0</v>
@@ -10666,24 +10666,24 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>varun chakravarthy</t>
+          <t>vaibhav arora</t>
         </is>
       </c>
       <c r="B181" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C181" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>venkatesh iyer</t>
+          <t>vaibhav suryavanshi</t>
         </is>
       </c>
       <c r="B182" t="n">
-        <v>41</v>
+        <v>440</v>
       </c>
       <c r="C182" t="n">
         <v>0</v>
@@ -10692,143 +10692,169 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>vijaykumar vyshak</t>
+          <t>varun chakravarthy</t>
         </is>
       </c>
       <c r="B183" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C183" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>vipraj nigam</t>
+          <t>venkatesh iyer</t>
         </is>
       </c>
       <c r="B184" t="n">
-        <v>15</v>
+        <v>41</v>
       </c>
       <c r="C184" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>virat kohli</t>
+          <t>vijaykumar vyshak</t>
         </is>
       </c>
       <c r="B185" t="n">
-        <v>484</v>
+        <v>2</v>
       </c>
       <c r="C185" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>vishnu vinod</t>
+          <t>vipraj nigam</t>
         </is>
       </c>
       <c r="B186" t="n">
         <v>15</v>
       </c>
       <c r="C186" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>washington sundar</t>
+          <t>virat kohli</t>
         </is>
       </c>
       <c r="B187" t="n">
-        <v>296</v>
+        <v>484</v>
       </c>
       <c r="C187" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>will jacks</t>
+          <t>vishnu vinod</t>
         </is>
       </c>
       <c r="B188" t="n">
-        <v>92</v>
+        <v>15</v>
       </c>
       <c r="C188" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>xavier bartlett</t>
+          <t>washington sundar</t>
         </is>
       </c>
       <c r="B189" t="n">
-        <v>29</v>
+        <v>296</v>
       </c>
       <c r="C189" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>yash raj punja</t>
+          <t>will jacks</t>
         </is>
       </c>
       <c r="B190" t="n">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="C190" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>yash thakur</t>
+          <t>xavier bartlett</t>
         </is>
       </c>
       <c r="B191" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="C191" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>yashasvi jaiswal</t>
+          <t>yash raj punja</t>
         </is>
       </c>
       <c r="B192" t="n">
-        <v>315</v>
+        <v>0</v>
       </c>
       <c r="C192" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
+          <t>yash thakur</t>
+        </is>
+      </c>
+      <c r="B193" t="n">
+        <v>0</v>
+      </c>
+      <c r="C193" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>yashasvi jaiswal</t>
+        </is>
+      </c>
+      <c r="B194" t="n">
+        <v>315</v>
+      </c>
+      <c r="C194" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
           <t>yuzvendra chahal</t>
         </is>
       </c>
-      <c r="B193" t="n">
-        <v>0</v>
-      </c>
-      <c r="C193" t="n">
+      <c r="B195" t="n">
+        <v>0</v>
+      </c>
+      <c r="C195" t="n">
         <v>9</v>
       </c>
     </row>
@@ -11696,7 +11722,7 @@
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>prabhsimran singh</t>
+          <t>akash singh</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -12234,19 +12260,19 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>98</v>
+        <v>134</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>98</v>
+        <v>134</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>98</v>
+        <v>134</v>
       </c>
     </row>
     <row r="3">

--- a/IPL_Fantasy_Points.xlsx
+++ b/IPL_Fantasy_Points.xlsx
@@ -862,19 +862,19 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>264</v>
+        <v>316</v>
       </c>
       <c r="H10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I10" t="n">
-        <v>264</v>
+        <v>316</v>
       </c>
       <c r="J10" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="K10" t="n">
-        <v>344</v>
+        <v>416</v>
       </c>
     </row>
     <row r="11">
@@ -994,16 +994,16 @@
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>260</v>
+        <v>280</v>
       </c>
       <c r="K13" t="n">
-        <v>260</v>
+        <v>280</v>
       </c>
     </row>
     <row r="14">
@@ -1249,19 +1249,19 @@
         </is>
       </c>
       <c r="G19" t="n">
-        <v>467</v>
+        <v>552</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>467</v>
+        <v>552</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>467</v>
+        <v>552</v>
       </c>
     </row>
     <row r="20">
@@ -1292,19 +1292,19 @@
         </is>
       </c>
       <c r="G20" t="n">
-        <v>237</v>
+        <v>251</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>237</v>
+        <v>251</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>237</v>
+        <v>251</v>
       </c>
     </row>
     <row r="21">
@@ -1550,19 +1550,19 @@
         </is>
       </c>
       <c r="G26" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
     </row>
     <row r="27">
@@ -3571,19 +3571,19 @@
         </is>
       </c>
       <c r="G73" t="n">
-        <v>501</v>
+        <v>554</v>
       </c>
       <c r="H73" t="n">
         <v>0</v>
       </c>
       <c r="I73" t="n">
-        <v>501</v>
+        <v>554</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
       </c>
       <c r="K73" t="n">
-        <v>501</v>
+        <v>554</v>
       </c>
     </row>
     <row r="74">
@@ -4431,19 +4431,19 @@
         </is>
       </c>
       <c r="G93" t="n">
-        <v>355</v>
+        <v>412</v>
       </c>
       <c r="H93" t="n">
         <v>0</v>
       </c>
       <c r="I93" t="n">
-        <v>355</v>
+        <v>412</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
       </c>
       <c r="K93" t="n">
-        <v>355</v>
+        <v>412</v>
       </c>
     </row>
     <row r="94">
@@ -4560,19 +4560,19 @@
         </is>
       </c>
       <c r="G96" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H96" t="n">
         <v>0</v>
       </c>
       <c r="I96" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
       </c>
       <c r="K96" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="97">
@@ -4892,15 +4892,15 @@
           <t>BOWL</t>
         </is>
       </c>
-      <c r="D104" t="inlineStr"/>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>eshan malinga</t>
-        </is>
-      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>matheesha pathirana</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr"/>
       <c r="F104" t="inlineStr">
         <is>
-          <t>no_stats_yet</t>
+          <t>exact/alias</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -6194,19 +6194,19 @@
         </is>
       </c>
       <c r="G134" t="n">
-        <v>340</v>
+        <v>422</v>
       </c>
       <c r="H134" t="n">
         <v>0</v>
       </c>
       <c r="I134" t="n">
-        <v>340</v>
+        <v>422</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
       </c>
       <c r="K134" t="n">
-        <v>340</v>
+        <v>422</v>
       </c>
     </row>
     <row r="135">
@@ -7570,19 +7570,19 @@
         </is>
       </c>
       <c r="G166" t="n">
-        <v>228</v>
+        <v>321</v>
       </c>
       <c r="H166" t="n">
         <v>0</v>
       </c>
       <c r="I166" t="n">
-        <v>228</v>
+        <v>321</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
       </c>
       <c r="K166" t="n">
-        <v>228</v>
+        <v>321</v>
       </c>
     </row>
     <row r="167">
@@ -7831,16 +7831,16 @@
         <v>40</v>
       </c>
       <c r="H172" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="I172" t="n">
         <v>40</v>
       </c>
       <c r="J172" t="n">
-        <v>220</v>
+        <v>260</v>
       </c>
       <c r="K172" t="n">
-        <v>260</v>
+        <v>300</v>
       </c>
     </row>
     <row r="173">
@@ -8185,7 +8185,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>3917</v>
+        <v>3970</v>
       </c>
     </row>
     <row r="3">
@@ -8198,7 +8198,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>3358</v>
+        <v>3459</v>
       </c>
     </row>
     <row r="4">
@@ -8220,11 +8220,11 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>AMEY11</t>
+          <t>NAKUL11</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>3075</v>
+        <v>3130</v>
       </c>
     </row>
     <row r="6">
@@ -8233,11 +8233,11 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>NAKUL11</t>
+          <t>AMEY11</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>3072</v>
+        <v>3075</v>
       </c>
     </row>
     <row r="7">
@@ -8263,7 +8263,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2839</v>
+        <v>2931</v>
       </c>
     </row>
     <row r="9">
@@ -8276,7 +8276,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2776</v>
+        <v>2858</v>
       </c>
     </row>
     <row r="10">
@@ -8302,7 +8302,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2016</v>
+        <v>2149</v>
       </c>
     </row>
   </sheetData>
@@ -8316,7 +8316,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C195"/>
+  <dimension ref="A1:C196"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8408,7 +8408,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>237</v>
+        <v>251</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
@@ -8473,7 +8473,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>340</v>
+        <v>422</v>
       </c>
       <c r="C12" t="n">
         <v>0</v>
@@ -8694,7 +8694,7 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>501</v>
+        <v>554</v>
       </c>
       <c r="C29" t="n">
         <v>0</v>
@@ -8759,10 +8759,10 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>264</v>
+        <v>316</v>
       </c>
       <c r="C34" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="35">
@@ -8967,7 +8967,7 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>228</v>
+        <v>321</v>
       </c>
       <c r="C50" t="n">
         <v>0</v>
@@ -9214,7 +9214,7 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>355</v>
+        <v>412</v>
       </c>
       <c r="C69" t="n">
         <v>0</v>
@@ -9522,37 +9522,37 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>matt henry</t>
+          <t>matheesha pathirana</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C93" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>matt short</t>
+          <t>matt henry</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>36</v>
+        <v>7</v>
       </c>
       <c r="C94" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>mayank markande</t>
+          <t>matt short</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="C95" t="n">
         <v>0</v>
@@ -9561,7 +9561,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>mayank rawat</t>
+          <t>mayank markande</t>
         </is>
       </c>
       <c r="B96" t="n">
@@ -9574,11 +9574,11 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>mayank yadav</t>
+          <t>mayank rawat</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C97" t="n">
         <v>0</v>
@@ -9587,11 +9587,11 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>mitchell marsh</t>
+          <t>mayank yadav</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>467</v>
+        <v>5</v>
       </c>
       <c r="C98" t="n">
         <v>0</v>
@@ -9600,24 +9600,24 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>mitchell santner</t>
+          <t>mitchell marsh</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>26</v>
+        <v>467</v>
       </c>
       <c r="C99" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>mitchell starc</t>
+          <t>mitchell santner</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="C100" t="n">
         <v>5</v>
@@ -9626,89 +9626,89 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>mohammed shami</t>
+          <t>mitchell starc</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="C101" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>mohammed siraj</t>
+          <t>mohammed shami</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="C102" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>mohsin khan</t>
+          <t>mohammed siraj</t>
         </is>
       </c>
       <c r="B103" t="n">
         <v>0</v>
       </c>
       <c r="C103" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>mukesh choudhary</t>
+          <t>mohsin khan</t>
         </is>
       </c>
       <c r="B104" t="n">
         <v>0</v>
       </c>
       <c r="C104" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>mukesh kumar</t>
+          <t>mukesh choudhary</t>
         </is>
       </c>
       <c r="B105" t="n">
         <v>0</v>
       </c>
       <c r="C105" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>mukul choudhary</t>
+          <t>mukesh kumar</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>169</v>
+        <v>0</v>
       </c>
       <c r="C106" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>naman dhir</t>
+          <t>mukul choudhary</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>312</v>
+        <v>169</v>
       </c>
       <c r="C107" t="n">
         <v>0</v>
@@ -9717,37 +9717,37 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>nandre burger</t>
+          <t>naman dhir</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>3</v>
+        <v>312</v>
       </c>
       <c r="C108" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>navdeep saini</t>
+          <t>nandre burger</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C109" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>nehal wadhera</t>
+          <t>navdeep saini</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="C110" t="n">
         <v>0</v>
@@ -9756,11 +9756,11 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>nicholas pooran</t>
+          <t>nehal wadhera</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>216</v>
+        <v>65</v>
       </c>
       <c r="C111" t="n">
         <v>0</v>
@@ -9769,11 +9769,11 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>nishant sindhu</t>
+          <t>nicholas pooran</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>37</v>
+        <v>216</v>
       </c>
       <c r="C112" t="n">
         <v>0</v>
@@ -9782,76 +9782,76 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>nitish kumar reddy</t>
+          <t>nishant sindhu</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>224</v>
+        <v>38</v>
       </c>
       <c r="C113" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>nitish rana</t>
+          <t>nitish kumar reddy</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C114" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>noor ahmad</t>
+          <t>nitish rana</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>10</v>
+        <v>225</v>
       </c>
       <c r="C115" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>pat cummins</t>
+          <t>noor ahmad</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="C116" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>pathum nissanka</t>
+          <t>pat cummins</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>278</v>
+        <v>29</v>
       </c>
       <c r="C117" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>philip salt</t>
+          <t>pathum nissanka</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>202</v>
+        <v>278</v>
       </c>
       <c r="C118" t="n">
         <v>0</v>
@@ -9860,11 +9860,11 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>prabhsimran singh</t>
+          <t>philip salt</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>439</v>
+        <v>202</v>
       </c>
       <c r="C119" t="n">
         <v>0</v>
@@ -9873,76 +9873,76 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>praful hinge</t>
+          <t>prabhsimran singh</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>3</v>
+        <v>439</v>
       </c>
       <c r="C120" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>prashant veer</t>
+          <t>praful hinge</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>79</v>
+        <v>3</v>
       </c>
       <c r="C121" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>prasidh krishna</t>
+          <t>prashant veer</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="C122" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>prince yadav</t>
+          <t>prasidh krishna</t>
         </is>
       </c>
       <c r="B123" t="n">
         <v>0</v>
       </c>
       <c r="C123" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>priyansh arya</t>
+          <t>prince yadav</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>364</v>
+        <v>0</v>
       </c>
       <c r="C124" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>quinton de kock</t>
+          <t>priyansh arya</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>132</v>
+        <v>364</v>
       </c>
       <c r="C125" t="n">
         <v>0</v>
@@ -9951,37 +9951,37 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>raghu sharma</t>
+          <t>quinton de kock</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>0</v>
+        <v>132</v>
       </c>
       <c r="C126" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>rahul chahar</t>
+          <t>raghu sharma</t>
         </is>
       </c>
       <c r="B127" t="n">
         <v>0</v>
       </c>
       <c r="C127" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>rahul tewatia</t>
+          <t>rahul chahar</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>96</v>
+        <v>0</v>
       </c>
       <c r="C128" t="n">
         <v>0</v>
@@ -9990,50 +9990,50 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>raj angad bawa</t>
+          <t>rahul tewatia</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>16</v>
+        <v>98</v>
       </c>
       <c r="C129" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>rajat patidar</t>
+          <t>raj angad bawa</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>337</v>
+        <v>16</v>
       </c>
       <c r="C130" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>ramakrishna ghosh</t>
+          <t>rajat patidar</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>0</v>
+        <v>337</v>
       </c>
       <c r="C131" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>ramandeep singh</t>
+          <t>ramakrishna ghosh</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="C132" t="n">
         <v>1</v>
@@ -10042,102 +10042,102 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>rashid khan</t>
+          <t>ramandeep singh</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>35</v>
+        <v>82</v>
       </c>
       <c r="C133" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>rasikh salam</t>
+          <t>rashid khan</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>3</v>
+        <v>35</v>
       </c>
       <c r="C134" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>ravi bishnoi</t>
+          <t>rasikh salam</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C135" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>ravichandran smaran</t>
+          <t>ravi bishnoi</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="C136" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>ravindra jadeja</t>
+          <t>ravichandran smaran</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>190</v>
+        <v>13</v>
       </c>
       <c r="C137" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>ravisrinivasan sai kishore</t>
+          <t>ravindra jadeja</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>0</v>
+        <v>190</v>
       </c>
       <c r="C138" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>rinku singh</t>
+          <t>ravisrinivasan sai kishore</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>286</v>
+        <v>0</v>
       </c>
       <c r="C139" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>rishabh pant</t>
+          <t>rinku singh</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>251</v>
+        <v>286</v>
       </c>
       <c r="C140" t="n">
         <v>0</v>
@@ -10146,37 +10146,37 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>riyan parag</t>
+          <t>rishabh pant</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>207</v>
+        <v>251</v>
       </c>
       <c r="C141" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>robin minz</t>
+          <t>riyan parag</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>6</v>
+        <v>207</v>
       </c>
       <c r="C142" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>rohit sharma</t>
+          <t>robin minz</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>268</v>
+        <v>6</v>
       </c>
       <c r="C143" t="n">
         <v>0</v>
@@ -10185,37 +10185,37 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>romario shepherd</t>
+          <t>rohit sharma</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>83</v>
+        <v>268</v>
       </c>
       <c r="C144" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>rovman powell</t>
+          <t>romario shepherd</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>121</v>
+        <v>83</v>
       </c>
       <c r="C145" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>ruturaj gaikwad</t>
+          <t>rovman powell</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>306</v>
+        <v>121</v>
       </c>
       <c r="C146" t="n">
         <v>0</v>
@@ -10224,11 +10224,11 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>ryan rickelton</t>
+          <t>ruturaj gaikwad</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>430</v>
+        <v>306</v>
       </c>
       <c r="C147" t="n">
         <v>0</v>
@@ -10237,11 +10237,11 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>sahil parakh</t>
+          <t>ryan rickelton</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>13</v>
+        <v>430</v>
       </c>
       <c r="C148" t="n">
         <v>0</v>
@@ -10250,37 +10250,37 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>sakib hussain</t>
+          <t>sahil parakh</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="C149" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>salil arora</t>
+          <t>sakib hussain</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>111</v>
+        <v>0</v>
       </c>
       <c r="C150" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>sameer rizvi</t>
+          <t>salil arora</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>252</v>
+        <v>111</v>
       </c>
       <c r="C151" t="n">
         <v>0</v>
@@ -10289,37 +10289,37 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>sandeep sharma</t>
+          <t>sameer rizvi</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>0</v>
+        <v>252</v>
       </c>
       <c r="C152" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>sanju samson</t>
+          <t>sandeep sharma</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>450</v>
+        <v>0</v>
       </c>
       <c r="C153" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>sarfaraz khan</t>
+          <t>sanju samson</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>161</v>
+        <v>450</v>
       </c>
       <c r="C154" t="n">
         <v>0</v>
@@ -10328,11 +10328,11 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>saurabh dubey</t>
+          <t>sarfaraz khan</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>0</v>
+        <v>161</v>
       </c>
       <c r="C155" t="n">
         <v>0</v>
@@ -10341,76 +10341,76 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>shahbaz ahmed</t>
+          <t>saurabh dubey</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="C156" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>shahrukh khan</t>
+          <t>shahbaz ahmed</t>
         </is>
       </c>
       <c r="B157" t="n">
-        <v>43</v>
+        <v>58</v>
       </c>
       <c r="C157" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>shardul thakur</t>
+          <t>shahrukh khan</t>
         </is>
       </c>
       <c r="B158" t="n">
-        <v>14</v>
+        <v>43</v>
       </c>
       <c r="C158" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>shashank singh</t>
+          <t>shardul thakur</t>
         </is>
       </c>
       <c r="B159" t="n">
-        <v>76</v>
+        <v>14</v>
       </c>
       <c r="C159" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>sherfane rutherford</t>
+          <t>shashank singh</t>
         </is>
       </c>
       <c r="B160" t="n">
-        <v>123</v>
+        <v>76</v>
       </c>
       <c r="C160" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>shimron hetmyer</t>
+          <t>sherfane rutherford</t>
         </is>
       </c>
       <c r="B161" t="n">
-        <v>78</v>
+        <v>123</v>
       </c>
       <c r="C161" t="n">
         <v>0</v>
@@ -10419,50 +10419,50 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>shivam dube</t>
+          <t>shimron hetmyer</t>
         </is>
       </c>
       <c r="B162" t="n">
-        <v>197</v>
+        <v>78</v>
       </c>
       <c r="C162" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>shivang kumar</t>
+          <t>shivam dube</t>
         </is>
       </c>
       <c r="B163" t="n">
-        <v>26</v>
+        <v>197</v>
       </c>
       <c r="C163" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>shreyas iyer</t>
+          <t>shivang kumar</t>
         </is>
       </c>
       <c r="B164" t="n">
-        <v>396</v>
+        <v>26</v>
       </c>
       <c r="C164" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>shubham badriprasad dubey</t>
+          <t>shreyas iyer</t>
         </is>
       </c>
       <c r="B165" t="n">
-        <v>71</v>
+        <v>396</v>
       </c>
       <c r="C165" t="n">
         <v>0</v>
@@ -10471,11 +10471,11 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>shubman gill</t>
+          <t>shubham badriprasad dubey</t>
         </is>
       </c>
       <c r="B166" t="n">
-        <v>467</v>
+        <v>71</v>
       </c>
       <c r="C166" t="n">
         <v>0</v>
@@ -10484,50 +10484,50 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>spencer johnson</t>
+          <t>shubman gill</t>
         </is>
       </c>
       <c r="B167" t="n">
-        <v>0</v>
+        <v>552</v>
       </c>
       <c r="C167" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>sunil narine</t>
+          <t>spencer johnson</t>
         </is>
       </c>
       <c r="B168" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C168" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>suryakumar yadav</t>
+          <t>sunil narine</t>
         </is>
       </c>
       <c r="B169" t="n">
-        <v>195</v>
+        <v>40</v>
       </c>
       <c r="C169" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>suryansh shedge</t>
+          <t>suryakumar yadav</t>
         </is>
       </c>
       <c r="B170" t="n">
-        <v>114</v>
+        <v>195</v>
       </c>
       <c r="C170" t="n">
         <v>0</v>
@@ -10536,50 +10536,50 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>suyash sharma</t>
+          <t>suryansh shedge</t>
         </is>
       </c>
       <c r="B171" t="n">
-        <v>0</v>
+        <v>114</v>
       </c>
       <c r="C171" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>t natarajan</t>
+          <t>suyash sharma</t>
         </is>
       </c>
       <c r="B172" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C172" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>tilak varma</t>
+          <t>t natarajan</t>
         </is>
       </c>
       <c r="B173" t="n">
-        <v>336</v>
+        <v>1</v>
       </c>
       <c r="C173" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>tim david</t>
+          <t>tilak varma</t>
         </is>
       </c>
       <c r="B174" t="n">
-        <v>234</v>
+        <v>336</v>
       </c>
       <c r="C174" t="n">
         <v>0</v>
@@ -10588,11 +10588,11 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>tim seifert</t>
+          <t>tim david</t>
         </is>
       </c>
       <c r="B175" t="n">
-        <v>19</v>
+        <v>234</v>
       </c>
       <c r="C175" t="n">
         <v>0</v>
@@ -10601,11 +10601,11 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>travis head</t>
+          <t>tim seifert</t>
         </is>
       </c>
       <c r="B176" t="n">
-        <v>361</v>
+        <v>19</v>
       </c>
       <c r="C176" t="n">
         <v>0</v>
@@ -10614,154 +10614,154 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>trent boult</t>
+          <t>travis head</t>
         </is>
       </c>
       <c r="B177" t="n">
-        <v>8</v>
+        <v>361</v>
       </c>
       <c r="C177" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>tristan stubbs</t>
+          <t>trent boult</t>
         </is>
       </c>
       <c r="B178" t="n">
-        <v>271</v>
+        <v>8</v>
       </c>
       <c r="C178" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>tushar deshpande</t>
+          <t>tristan stubbs</t>
         </is>
       </c>
       <c r="B179" t="n">
-        <v>26</v>
+        <v>271</v>
       </c>
       <c r="C179" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>urvil patel</t>
+          <t>tushar deshpande</t>
         </is>
       </c>
       <c r="B180" t="n">
-        <v>116</v>
+        <v>26</v>
       </c>
       <c r="C180" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>vaibhav arora</t>
+          <t>urvil patel</t>
         </is>
       </c>
       <c r="B181" t="n">
-        <v>1</v>
+        <v>116</v>
       </c>
       <c r="C181" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>vaibhav suryavanshi</t>
+          <t>vaibhav arora</t>
         </is>
       </c>
       <c r="B182" t="n">
-        <v>440</v>
+        <v>1</v>
       </c>
       <c r="C182" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>varun chakravarthy</t>
+          <t>vaibhav suryavanshi</t>
         </is>
       </c>
       <c r="B183" t="n">
-        <v>0</v>
+        <v>440</v>
       </c>
       <c r="C183" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>venkatesh iyer</t>
+          <t>varun chakravarthy</t>
         </is>
       </c>
       <c r="B184" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="C184" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>vijaykumar vyshak</t>
+          <t>venkatesh iyer</t>
         </is>
       </c>
       <c r="B185" t="n">
-        <v>2</v>
+        <v>41</v>
       </c>
       <c r="C185" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>vipraj nigam</t>
+          <t>vijaykumar vyshak</t>
         </is>
       </c>
       <c r="B186" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="C186" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>virat kohli</t>
+          <t>vipraj nigam</t>
         </is>
       </c>
       <c r="B187" t="n">
-        <v>484</v>
+        <v>15</v>
       </c>
       <c r="C187" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>vishnu vinod</t>
+          <t>virat kohli</t>
         </is>
       </c>
       <c r="B188" t="n">
-        <v>15</v>
+        <v>484</v>
       </c>
       <c r="C188" t="n">
         <v>0</v>
@@ -10770,24 +10770,24 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>washington sundar</t>
+          <t>vishnu vinod</t>
         </is>
       </c>
       <c r="B189" t="n">
-        <v>296</v>
+        <v>15</v>
       </c>
       <c r="C189" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>will jacks</t>
+          <t>washington sundar</t>
         </is>
       </c>
       <c r="B190" t="n">
-        <v>92</v>
+        <v>296</v>
       </c>
       <c r="C190" t="n">
         <v>1</v>
@@ -10796,65 +10796,78 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>xavier bartlett</t>
+          <t>will jacks</t>
         </is>
       </c>
       <c r="B191" t="n">
-        <v>29</v>
+        <v>92</v>
       </c>
       <c r="C191" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>yash raj punja</t>
+          <t>xavier bartlett</t>
         </is>
       </c>
       <c r="B192" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="C192" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>yash thakur</t>
+          <t>yash raj punja</t>
         </is>
       </c>
       <c r="B193" t="n">
         <v>0</v>
       </c>
       <c r="C193" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>yashasvi jaiswal</t>
+          <t>yash thakur</t>
         </is>
       </c>
       <c r="B194" t="n">
-        <v>315</v>
+        <v>0</v>
       </c>
       <c r="C194" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
+          <t>yashasvi jaiswal</t>
+        </is>
+      </c>
+      <c r="B195" t="n">
+        <v>315</v>
+      </c>
+      <c r="C195" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
           <t>yuzvendra chahal</t>
         </is>
       </c>
-      <c r="B195" t="n">
-        <v>0</v>
-      </c>
-      <c r="C195" t="n">
+      <c r="B196" t="n">
+        <v>0</v>
+      </c>
+      <c r="C196" t="n">
         <v>9</v>
       </c>
     </row>
@@ -10869,7 +10882,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K28"/>
+  <dimension ref="A1:K27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11534,12 +11547,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Matheesha Pathirana</t>
+          <t>Arjun Tendulkar</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>NAKUL11</t>
+          <t>SKY11</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -11550,7 +11563,7 @@
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>eshan malinga</t>
+          <t>karun nair</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -11577,7 +11590,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Arjun Tendulkar</t>
+          <t>Kwena Maphaka</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -11593,7 +11606,7 @@
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>karun nair</t>
+          <t>aiden markram</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -11620,23 +11633,23 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Kwena Maphaka</t>
+          <t>Azmatullah Omarzai</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>SKY11</t>
+          <t>HARSH11</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>aiden markram</t>
+          <t>azmatullah</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -11663,23 +11676,23 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Azmatullah Omarzai</t>
+          <t>Tejasvi Singh</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>HARSH11</t>
+          <t>AMEY11</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>azmatullah</t>
+          <t>akash singh</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -11706,7 +11719,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Tejasvi Singh</t>
+          <t>Sai Kishor</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -11716,13 +11729,13 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>akash singh</t>
+          <t>ishan kishan</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -11749,7 +11762,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Sai Kishor</t>
+          <t>Akash Deep</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -11765,7 +11778,7 @@
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>ishan kishan</t>
+          <t>arshdeep singh</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -11792,23 +11805,23 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Akash Deep</t>
+          <t>Ben Duckett</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>AMEY11</t>
+          <t>PRATIK11</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>arshdeep singh</t>
+          <t>ben dwarshuis</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -11835,7 +11848,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Ben Duckett</t>
+          <t>Rahul Tripathi</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -11851,7 +11864,7 @@
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>ben dwarshuis</t>
+          <t>rahul tewatia</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -11878,7 +11891,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rahul Tripathi</t>
+          <t>Dre Pretorius</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -11894,7 +11907,7 @@
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>rahul tewatia</t>
+          <t>lhuan dre pretorius</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -11921,7 +11934,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Dre Pretorius</t>
+          <t>Matthew Breetzke</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -11937,7 +11950,7 @@
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>lhuan dre pretorius</t>
+          <t>matt henry</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -11964,7 +11977,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Matthew Breetzke</t>
+          <t>Anuj Rawat</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -11980,7 +11993,7 @@
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>matt henry</t>
+          <t>mayank rawat</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -12007,7 +12020,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Anuj Rawat</t>
+          <t>Wanindu Hasaranga</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -12017,13 +12030,13 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>mayank rawat</t>
+          <t>ravichandran smaran</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -12044,49 +12057,6 @@
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Wanindu Hasaranga</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>PRATIK11</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>AR</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>ravichandran smaran</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>no_stats_yet</t>
-        </is>
-      </c>
-      <c r="G28" t="n">
-        <v>0</v>
-      </c>
-      <c r="H28" t="n">
-        <v>0</v>
-      </c>
-      <c r="I28" t="n">
-        <v>0</v>
-      </c>
-      <c r="J28" t="n">
-        <v>0</v>
-      </c>
-      <c r="K28" t="n">
         <v>0</v>
       </c>
     </row>

--- a/IPL_Fantasy_Points.xlsx
+++ b/IPL_Fantasy_Points.xlsx
@@ -1335,19 +1335,19 @@
         </is>
       </c>
       <c r="G21" t="n">
-        <v>440</v>
+        <v>486</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>440</v>
+        <v>486</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>440</v>
+        <v>486</v>
       </c>
     </row>
     <row r="22">
@@ -1464,19 +1464,19 @@
         </is>
       </c>
       <c r="G24" t="n">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>85</v>
+        <v>96</v>
       </c>
     </row>
     <row r="25">
@@ -2241,7 +2241,7 @@
         <v>83</v>
       </c>
       <c r="H42" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I42" t="n">
         <v>83</v>
@@ -2367,19 +2367,19 @@
         </is>
       </c>
       <c r="G45" t="n">
-        <v>179</v>
+        <v>216</v>
       </c>
       <c r="H45" t="n">
         <v>2</v>
       </c>
       <c r="I45" t="n">
-        <v>179</v>
+        <v>216</v>
       </c>
       <c r="J45" t="n">
         <v>40</v>
       </c>
       <c r="K45" t="n">
-        <v>219</v>
+        <v>256</v>
       </c>
     </row>
     <row r="46">
@@ -2570,19 +2570,19 @@
           <t>BOWL</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr"/>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>david miller</t>
-        </is>
-      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>adam milne</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr">
         <is>
-          <t>no_stats_yet</t>
+          <t>exact/alias</t>
         </is>
       </c>
       <c r="G50" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H50" t="n">
         <v>0</v>
@@ -2840,19 +2840,19 @@
         </is>
       </c>
       <c r="G56" t="n">
-        <v>174</v>
+        <v>183</v>
       </c>
       <c r="H56" t="n">
         <v>0</v>
       </c>
       <c r="I56" t="n">
-        <v>174</v>
+        <v>183</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
       </c>
       <c r="K56" t="n">
-        <v>174</v>
+        <v>183</v>
       </c>
     </row>
     <row r="57">
@@ -2883,19 +2883,19 @@
         </is>
       </c>
       <c r="G57" t="n">
-        <v>314</v>
+        <v>367</v>
       </c>
       <c r="H57" t="n">
         <v>0</v>
       </c>
       <c r="I57" t="n">
-        <v>314</v>
+        <v>367</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
       </c>
       <c r="K57" t="n">
-        <v>314</v>
+        <v>367</v>
       </c>
     </row>
     <row r="58">
@@ -3445,16 +3445,16 @@
         <v>0</v>
       </c>
       <c r="H70" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="I70" t="n">
         <v>0</v>
       </c>
       <c r="J70" t="n">
-        <v>100</v>
+        <v>180</v>
       </c>
       <c r="K70" t="n">
-        <v>100</v>
+        <v>180</v>
       </c>
     </row>
     <row r="71">
@@ -3614,19 +3614,19 @@
         </is>
       </c>
       <c r="G74" t="n">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="H74" t="n">
         <v>0</v>
       </c>
       <c r="I74" t="n">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
       </c>
       <c r="K74" t="n">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
     <row r="75">
@@ -3786,19 +3786,19 @@
         </is>
       </c>
       <c r="G78" t="n">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="H78" t="n">
         <v>0</v>
       </c>
       <c r="I78" t="n">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
       </c>
       <c r="K78" t="n">
-        <v>271</v>
+        <v>275</v>
       </c>
     </row>
     <row r="79">
@@ -3958,19 +3958,19 @@
         </is>
       </c>
       <c r="G82" t="n">
-        <v>234</v>
+        <v>262</v>
       </c>
       <c r="H82" t="n">
         <v>0</v>
       </c>
       <c r="I82" t="n">
-        <v>234</v>
+        <v>262</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
       </c>
       <c r="K82" t="n">
-        <v>234</v>
+        <v>262</v>
       </c>
     </row>
     <row r="83">
@@ -4001,19 +4001,19 @@
         </is>
       </c>
       <c r="G83" t="n">
-        <v>436</v>
+        <v>473</v>
       </c>
       <c r="H83" t="n">
         <v>0</v>
       </c>
       <c r="I83" t="n">
-        <v>436</v>
+        <v>473</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
       </c>
       <c r="K83" t="n">
-        <v>436</v>
+        <v>473</v>
       </c>
     </row>
     <row r="84">
@@ -4047,16 +4047,16 @@
         <v>1</v>
       </c>
       <c r="H84" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I84" t="n">
         <v>0</v>
       </c>
       <c r="J84" t="n">
-        <v>260</v>
+        <v>280</v>
       </c>
       <c r="K84" t="n">
-        <v>260</v>
+        <v>280</v>
       </c>
     </row>
     <row r="85">
@@ -4219,16 +4219,16 @@
         <v>3</v>
       </c>
       <c r="H88" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="I88" t="n">
         <v>0</v>
       </c>
       <c r="J88" t="n">
-        <v>180</v>
+        <v>240</v>
       </c>
       <c r="K88" t="n">
-        <v>180</v>
+        <v>240</v>
       </c>
     </row>
     <row r="89">
@@ -4302,19 +4302,19 @@
         </is>
       </c>
       <c r="G90" t="n">
-        <v>315</v>
+        <v>327</v>
       </c>
       <c r="H90" t="n">
         <v>0</v>
       </c>
       <c r="I90" t="n">
-        <v>315</v>
+        <v>327</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
       </c>
       <c r="K90" t="n">
-        <v>315</v>
+        <v>327</v>
       </c>
     </row>
     <row r="91">
@@ -4345,19 +4345,19 @@
         </is>
       </c>
       <c r="G91" t="n">
-        <v>477</v>
+        <v>533</v>
       </c>
       <c r="H91" t="n">
         <v>0</v>
       </c>
       <c r="I91" t="n">
-        <v>477</v>
+        <v>533</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
       </c>
       <c r="K91" t="n">
-        <v>477</v>
+        <v>533</v>
       </c>
     </row>
     <row r="92">
@@ -4388,19 +4388,19 @@
         </is>
       </c>
       <c r="G92" t="n">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="H92" t="n">
         <v>0</v>
       </c>
       <c r="I92" t="n">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
       </c>
       <c r="K92" t="n">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="93">
@@ -4732,19 +4732,19 @@
         </is>
       </c>
       <c r="G100" t="n">
-        <v>207</v>
+        <v>258</v>
       </c>
       <c r="H100" t="n">
         <v>2</v>
       </c>
       <c r="I100" t="n">
-        <v>207</v>
+        <v>258</v>
       </c>
       <c r="J100" t="n">
         <v>40</v>
       </c>
       <c r="K100" t="n">
-        <v>247</v>
+        <v>298</v>
       </c>
     </row>
     <row r="101">
@@ -4821,16 +4821,16 @@
         <v>0</v>
       </c>
       <c r="H102" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I102" t="n">
         <v>0</v>
       </c>
       <c r="J102" t="n">
-        <v>220</v>
+        <v>240</v>
       </c>
       <c r="K102" t="n">
-        <v>220</v>
+        <v>240</v>
       </c>
     </row>
     <row r="103">
@@ -5552,16 +5552,16 @@
         <v>4</v>
       </c>
       <c r="H119" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I119" t="n">
         <v>0</v>
       </c>
       <c r="J119" t="n">
-        <v>160</v>
+        <v>200</v>
       </c>
       <c r="K119" t="n">
-        <v>160</v>
+        <v>200</v>
       </c>
     </row>
     <row r="120">
@@ -5850,19 +5850,19 @@
         </is>
       </c>
       <c r="G126" t="n">
-        <v>367</v>
+        <v>412</v>
       </c>
       <c r="H126" t="n">
         <v>0</v>
       </c>
       <c r="I126" t="n">
-        <v>367</v>
+        <v>412</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
       </c>
       <c r="K126" t="n">
-        <v>367</v>
+        <v>412</v>
       </c>
     </row>
     <row r="127">
@@ -5936,19 +5936,19 @@
         </is>
       </c>
       <c r="G128" t="n">
-        <v>41</v>
+        <v>114</v>
       </c>
       <c r="H128" t="n">
         <v>0</v>
       </c>
       <c r="I128" t="n">
-        <v>41</v>
+        <v>114</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
       </c>
       <c r="K128" t="n">
-        <v>41</v>
+        <v>114</v>
       </c>
     </row>
     <row r="129">
@@ -6022,19 +6022,19 @@
         </is>
       </c>
       <c r="G130" t="n">
-        <v>135</v>
+        <v>153</v>
       </c>
       <c r="H130" t="n">
         <v>0</v>
       </c>
       <c r="I130" t="n">
-        <v>135</v>
+        <v>153</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
       </c>
       <c r="K130" t="n">
-        <v>135</v>
+        <v>153</v>
       </c>
     </row>
     <row r="131">
@@ -6108,19 +6108,19 @@
         </is>
       </c>
       <c r="G132" t="n">
-        <v>76</v>
+        <v>132</v>
       </c>
       <c r="H132" t="n">
         <v>3</v>
       </c>
       <c r="I132" t="n">
-        <v>76</v>
+        <v>132</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
       </c>
       <c r="K132" t="n">
-        <v>76</v>
+        <v>132</v>
       </c>
     </row>
     <row r="133">
@@ -6323,19 +6323,19 @@
         </is>
       </c>
       <c r="G137" t="n">
-        <v>100</v>
+        <v>134</v>
       </c>
       <c r="H137" t="n">
         <v>10</v>
       </c>
       <c r="I137" t="n">
-        <v>100</v>
+        <v>134</v>
       </c>
       <c r="J137" t="n">
         <v>200</v>
       </c>
       <c r="K137" t="n">
-        <v>300</v>
+        <v>334</v>
       </c>
     </row>
     <row r="138">
@@ -6624,19 +6624,19 @@
         </is>
       </c>
       <c r="G144" t="n">
-        <v>484</v>
+        <v>542</v>
       </c>
       <c r="H144" t="n">
         <v>0</v>
       </c>
       <c r="I144" t="n">
-        <v>484</v>
+        <v>542</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
       </c>
       <c r="K144" t="n">
-        <v>484</v>
+        <v>542</v>
       </c>
     </row>
     <row r="145">
@@ -6925,19 +6925,19 @@
         </is>
       </c>
       <c r="G151" t="n">
-        <v>114</v>
+        <v>149</v>
       </c>
       <c r="H151" t="n">
         <v>0</v>
       </c>
       <c r="I151" t="n">
-        <v>114</v>
+        <v>149</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
       </c>
       <c r="K151" t="n">
-        <v>114</v>
+        <v>149</v>
       </c>
     </row>
     <row r="152">
@@ -6959,7 +6959,7 @@
       <c r="D152" t="inlineStr"/>
       <c r="E152" t="inlineStr">
         <is>
-          <t>akash singh</t>
+          <t>ravi singh</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
@@ -7054,19 +7054,19 @@
         </is>
       </c>
       <c r="G154" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="H154" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="I154" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J154" t="n">
-        <v>300</v>
+        <v>340</v>
       </c>
       <c r="K154" t="n">
-        <v>319</v>
+        <v>361</v>
       </c>
     </row>
     <row r="155">
@@ -7143,16 +7143,16 @@
         <v>0</v>
       </c>
       <c r="H156" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I156" t="n">
         <v>0</v>
       </c>
       <c r="J156" t="n">
-        <v>180</v>
+        <v>200</v>
       </c>
       <c r="K156" t="n">
-        <v>180</v>
+        <v>200</v>
       </c>
     </row>
     <row r="157">
@@ -7186,16 +7186,16 @@
         <v>34</v>
       </c>
       <c r="H157" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I157" t="n">
         <v>0</v>
       </c>
       <c r="J157" t="n">
-        <v>440</v>
+        <v>480</v>
       </c>
       <c r="K157" t="n">
-        <v>440</v>
+        <v>480</v>
       </c>
     </row>
     <row r="158">
@@ -7484,19 +7484,19 @@
         </is>
       </c>
       <c r="G164" t="n">
-        <v>35</v>
+        <v>86</v>
       </c>
       <c r="H164" t="n">
         <v>0</v>
       </c>
       <c r="I164" t="n">
-        <v>35</v>
+        <v>86</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
       </c>
       <c r="K164" t="n">
-        <v>35</v>
+        <v>86</v>
       </c>
     </row>
     <row r="165">
@@ -7914,19 +7914,19 @@
         </is>
       </c>
       <c r="G174" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H174" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I174" t="n">
         <v>0</v>
       </c>
       <c r="J174" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="K174" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="175">
@@ -8003,16 +8003,16 @@
         <v>0</v>
       </c>
       <c r="H176" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I176" t="n">
         <v>0</v>
       </c>
       <c r="J176" t="n">
-        <v>140</v>
+        <v>160</v>
       </c>
       <c r="K176" t="n">
-        <v>140</v>
+        <v>160</v>
       </c>
     </row>
     <row r="177">
@@ -8185,7 +8185,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>3970</v>
+        <v>4121</v>
       </c>
     </row>
     <row r="3">
@@ -8198,7 +8198,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>3459</v>
+        <v>3516</v>
       </c>
     </row>
     <row r="4">
@@ -8211,7 +8211,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>3156</v>
+        <v>3298</v>
       </c>
     </row>
     <row r="5">
@@ -8220,11 +8220,11 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>NAKUL11</t>
+          <t>AMEY11</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>3130</v>
+        <v>3270</v>
       </c>
     </row>
     <row r="6">
@@ -8233,11 +8233,11 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>AMEY11</t>
+          <t>NAKUL11</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>3075</v>
+        <v>3270</v>
       </c>
     </row>
     <row r="7">
@@ -8246,11 +8246,11 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>SKY11</t>
+          <t>HARSH11</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>3028</v>
+        <v>3084</v>
       </c>
     </row>
     <row r="8">
@@ -8259,11 +8259,11 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>NIRAV11</t>
+          <t>SKY11</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2931</v>
+        <v>3068</v>
       </c>
     </row>
     <row r="9">
@@ -8272,11 +8272,11 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>HARSH11</t>
+          <t>NIRAV11</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2858</v>
+        <v>2931</v>
       </c>
     </row>
     <row r="10">
@@ -8289,7 +8289,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2596</v>
+        <v>2633</v>
       </c>
     </row>
     <row r="11">
@@ -8302,7 +8302,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2149</v>
+        <v>2260</v>
       </c>
     </row>
   </sheetData>
@@ -8316,7 +8316,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C196"/>
+  <dimension ref="A1:C199"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8382,7 +8382,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>35</v>
+        <v>86</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
@@ -8391,11 +8391,11 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>aiden markram</t>
+          <t>adam milne</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>231</v>
+        <v>2</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
@@ -8404,11 +8404,11 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ajinkya rahane</t>
+          <t>aiden markram</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>251</v>
+        <v>231</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
@@ -8417,76 +8417,76 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>akash singh</t>
+          <t>ajinkya rahane</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0</v>
+        <v>251</v>
       </c>
       <c r="C8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>akeal hosein</t>
+          <t>akash singh</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>akshat raghuwanshi</t>
+          <t>akeal hosein</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>am ghazanfar</t>
+          <t>akshat raghuwanshi</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="C11" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>angkrish raghuvanshi</t>
+          <t>am ghazanfar</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>422</v>
+        <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>aniket verma</t>
+          <t>angkrish raghuvanshi</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>79</v>
+        <v>422</v>
       </c>
       <c r="C13" t="n">
         <v>0</v>
@@ -8495,11 +8495,11 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>anrich nortje</t>
+          <t>aniket verma</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="C14" t="n">
         <v>0</v>
@@ -8508,167 +8508,167 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>anshul kamboj</t>
+          <t>anrich nortje</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>anukul roy</t>
+          <t>anshul kamboj</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>39</v>
       </c>
       <c r="C16" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>arshad khan</t>
+          <t>anukul roy</t>
         </is>
       </c>
       <c r="B17" t="n">
+        <v>39</v>
+      </c>
+      <c r="C17" t="n">
         <v>8</v>
-      </c>
-      <c r="C17" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>arshdeep singh</t>
+          <t>arshad khan</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C18" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>arshin kulkarni</t>
+          <t>arshdeep singh</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ashok sharma</t>
+          <t>arshin kulkarni</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="C20" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ashutosh sharma</t>
+          <t>ashok sharma</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>135</v>
+        <v>1</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ashwani kumar</t>
+          <t>ashutosh sharma</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1</v>
+        <v>153</v>
       </c>
       <c r="C22" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>auqib nabi</t>
+          <t>ashwani kumar</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>avesh khan</t>
+          <t>auqib nabi</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="C24" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>axar patel</t>
+          <t>avesh khan</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>100</v>
+        <v>6</v>
       </c>
       <c r="C25" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ayush badoni</t>
+          <t>axar patel</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>172</v>
+        <v>134</v>
       </c>
       <c r="C26" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>ayush mhatre</t>
+          <t>ayush badoni</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>201</v>
+        <v>172</v>
       </c>
       <c r="C27" t="n">
         <v>0</v>
@@ -8677,141 +8677,141 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>azmatullah</t>
+          <t>ayush mhatre</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>38</v>
+        <v>201</v>
       </c>
       <c r="C28" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>b sai sudharshan</t>
+          <t>azmatullah</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>554</v>
+        <v>52</v>
       </c>
       <c r="C29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>ben dwarshuis</t>
+          <t>b sai sudharshan</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0</v>
+        <v>554</v>
       </c>
       <c r="C30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>bhuvneshwar kumar</t>
+          <t>ben dwarshuis</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="C31" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>blessing muzarabani</t>
+          <t>bhuvneshwar kumar</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="C32" t="n">
-        <v>4</v>
+        <v>24</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>brijesh sharma</t>
+          <t>blessing muzarabani</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C33" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>cameron green</t>
+          <t>brijesh sharma</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>316</v>
+        <v>2</v>
       </c>
       <c r="C34" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>cooper connolly</t>
+          <t>cameron green</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>436</v>
+        <v>316</v>
       </c>
       <c r="C35" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>corbin bosch</t>
+          <t>cooper connolly</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>16</v>
+        <v>473</v>
       </c>
       <c r="C36" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>danish malewar</t>
+          <t>corbin bosch</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="C37" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>dasun shanaka</t>
+          <t>danish malewar</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="C38" t="n">
         <v>0</v>
@@ -8820,63 +8820,63 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>david miller</t>
+          <t>dasun shanaka</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>174</v>
+        <v>26</v>
       </c>
       <c r="C39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>david payne</t>
+          <t>david miller</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>6</v>
+        <v>183</v>
       </c>
       <c r="C40" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>deepak chahar</t>
+          <t>david payne</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C41" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>devdutt padikkal</t>
+          <t>deepak chahar</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>367</v>
+        <v>7</v>
       </c>
       <c r="C42" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>dewald brevis</t>
+          <t>devdutt padikkal</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>99</v>
+        <v>412</v>
       </c>
       <c r="C43" t="n">
         <v>0</v>
@@ -8885,11 +8885,11 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>dhruv chand jurel</t>
+          <t>dewald brevis</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>314</v>
+        <v>99</v>
       </c>
       <c r="C44" t="n">
         <v>0</v>
@@ -8898,37 +8898,37 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>digvesh rathi</t>
+          <t>dhruv chand jurel</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>2</v>
+        <v>367</v>
       </c>
       <c r="C45" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>dilshan madushanka</t>
+          <t>digvesh rathi</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C46" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>donavon ferreira</t>
+          <t>dilshan madushanka</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>233</v>
+        <v>0</v>
       </c>
       <c r="C47" t="n">
         <v>1</v>
@@ -8937,89 +8937,89 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>dushmantha chameera</t>
+          <t>donavon ferreira</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0</v>
+        <v>233</v>
       </c>
       <c r="C48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>eshan malinga</t>
+          <t>dushmantha chameera</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C49" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>finn allen</t>
+          <t>eshan malinga</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>321</v>
+        <v>2</v>
       </c>
       <c r="C50" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>george linde</t>
+          <t>finn allen</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>31</v>
+        <v>321</v>
       </c>
       <c r="C51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>glenn phillips</t>
+          <t>george linde</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>67</v>
+        <v>31</v>
       </c>
       <c r="C52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>gurjapneet singh</t>
+          <t>glenn phillips</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="C53" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>hardik pandya</t>
+          <t>gurjapneet singh</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>146</v>
+        <v>0</v>
       </c>
       <c r="C54" t="n">
         <v>4</v>
@@ -9028,50 +9028,50 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>harpreet brar</t>
+          <t>hardik pandya</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0</v>
+        <v>146</v>
       </c>
       <c r="C55" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>harsh dubey</t>
+          <t>harpreet brar</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C56" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>harshal patel</t>
+          <t>harsh dubey</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C57" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>heinrich klaasen</t>
+          <t>harshal patel</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>508</v>
+        <v>10</v>
       </c>
       <c r="C58" t="n">
         <v>0</v>
@@ -9080,11 +9080,11 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>himmat singh</t>
+          <t>heinrich klaasen</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>92</v>
+        <v>508</v>
       </c>
       <c r="C59" t="n">
         <v>0</v>
@@ -9093,11 +9093,11 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>ishan kishan</t>
+          <t>himmat singh</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>420</v>
+        <v>92</v>
       </c>
       <c r="C60" t="n">
         <v>0</v>
@@ -9106,11 +9106,11 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>jacob bethell</t>
+          <t>ishan kishan</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>85</v>
+        <v>420</v>
       </c>
       <c r="C61" t="n">
         <v>0</v>
@@ -9119,284 +9119,284 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>jacob duffy</t>
+          <t>jacob bethell</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="C62" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>jamie overton</t>
+          <t>jacob duffy</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>136</v>
+        <v>0</v>
       </c>
       <c r="C63" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>jason holder</t>
+          <t>jamie overton</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>58</v>
+        <v>136</v>
       </c>
       <c r="C64" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>jasprit bumrah</t>
+          <t>jason holder</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>7</v>
+        <v>58</v>
       </c>
       <c r="C65" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>jaydev unadkat</t>
+          <t>jasprit bumrah</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C66" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>jitesh sharma</t>
+          <t>jaydev unadkat</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>90</v>
+        <v>4</v>
       </c>
       <c r="C67" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>jofra archer</t>
+          <t>jitesh sharma</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>19</v>
+        <v>90</v>
       </c>
       <c r="C68" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>jos buttler</t>
+          <t>jofra archer</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>412</v>
+        <v>21</v>
       </c>
       <c r="C69" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>josh hazlewood</t>
+          <t>jos buttler</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0</v>
+        <v>412</v>
       </c>
       <c r="C70" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>josh inglis</t>
+          <t>josh hazlewood</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>134</v>
+        <v>0</v>
       </c>
       <c r="C71" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>kagiso rabada</t>
+          <t>josh inglis</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>35</v>
+        <v>134</v>
       </c>
       <c r="C72" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>kartik sharma</t>
+          <t>kagiso rabada</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>244</v>
+        <v>35</v>
       </c>
       <c r="C73" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>kartik tyagi</t>
+          <t>kartik sharma</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>11</v>
+        <v>244</v>
       </c>
       <c r="C74" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>karun nair</t>
+          <t>kartik tyagi</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="C75" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>khaleel ahmed</t>
+          <t>karun nair</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="C76" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>krish bhagat</t>
+          <t>khaleel ahmed</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="C77" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>krunal pandya</t>
+          <t>krish bhagat</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>141</v>
+        <v>10</v>
       </c>
       <c r="C78" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>kuldeep yadav</t>
+          <t>krunal pandya</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>9</v>
+        <v>141</v>
       </c>
       <c r="C79" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>kumar kushagra</t>
+          <t>kuldeep yadav</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="C80" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>kyle jamieson</t>
+          <t>kumar kushagra</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="C81" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>lhuan dre pretorius</t>
+          <t>kyle jamieson</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="C82" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>liam livingstone</t>
+          <t>lhuan dre pretorius</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="C83" t="n">
         <v>0</v>
@@ -9405,167 +9405,167 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>lockie ferguson</t>
+          <t>liam livingstone</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="C84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>lokesh rahul</t>
+          <t>lockie ferguson</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>477</v>
+        <v>0</v>
       </c>
       <c r="C85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>lungi ngidi</t>
+          <t>lokesh rahul</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>4</v>
+        <v>533</v>
       </c>
       <c r="C86" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>madhav tiwari</t>
+          <t>lungi ngidi</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="C87" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>manav suthar</t>
+          <t>madhav tiwari</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="C88" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>manimaran siddharth</t>
+          <t>manav suthar</t>
         </is>
       </c>
       <c r="B89" t="n">
         <v>0</v>
       </c>
       <c r="C89" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>manish pandey</t>
+          <t>manimaran siddharth</t>
         </is>
       </c>
       <c r="B90" t="n">
         <v>0</v>
       </c>
       <c r="C90" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>marco jansen</t>
+          <t>manish pandey</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="C91" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>marcus stoinis</t>
+          <t>marco jansen</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>179</v>
+        <v>51</v>
       </c>
       <c r="C92" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>matheesha pathirana</t>
+          <t>marcus stoinis</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>0</v>
+        <v>216</v>
       </c>
       <c r="C93" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>matt henry</t>
+          <t>matheesha pathirana</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C94" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>matt short</t>
+          <t>matt henry</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>36</v>
+        <v>7</v>
       </c>
       <c r="C95" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>mayank markande</t>
+          <t>matt short</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="C96" t="n">
         <v>0</v>
@@ -9574,7 +9574,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>mayank rawat</t>
+          <t>mayank markande</t>
         </is>
       </c>
       <c r="B97" t="n">
@@ -9587,11 +9587,11 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>mayank yadav</t>
+          <t>mayank rawat</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C98" t="n">
         <v>0</v>
@@ -9600,11 +9600,11 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>mitchell marsh</t>
+          <t>mayank yadav</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>467</v>
+        <v>5</v>
       </c>
       <c r="C99" t="n">
         <v>0</v>
@@ -9613,24 +9613,24 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>mitchell santner</t>
+          <t>mitchell marsh</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>26</v>
+        <v>467</v>
       </c>
       <c r="C100" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>mitchell starc</t>
+          <t>mitchell santner</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="C101" t="n">
         <v>5</v>
@@ -9639,89 +9639,89 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>mohammed shami</t>
+          <t>mitchell starc</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="C102" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>mohammed siraj</t>
+          <t>mohammed shami</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="C103" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>mohsin khan</t>
+          <t>mohammed siraj</t>
         </is>
       </c>
       <c r="B104" t="n">
         <v>0</v>
       </c>
       <c r="C104" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>mukesh choudhary</t>
+          <t>mohsin khan</t>
         </is>
       </c>
       <c r="B105" t="n">
         <v>0</v>
       </c>
       <c r="C105" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>mukesh kumar</t>
+          <t>mukesh choudhary</t>
         </is>
       </c>
       <c r="B106" t="n">
         <v>0</v>
       </c>
       <c r="C106" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>mukul choudhary</t>
+          <t>mukesh kumar</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>169</v>
+        <v>0</v>
       </c>
       <c r="C107" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>naman dhir</t>
+          <t>mukul choudhary</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>312</v>
+        <v>169</v>
       </c>
       <c r="C108" t="n">
         <v>0</v>
@@ -9730,37 +9730,37 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>nandre burger</t>
+          <t>naman dhir</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>3</v>
+        <v>312</v>
       </c>
       <c r="C109" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>navdeep saini</t>
+          <t>nandre burger</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C110" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>nehal wadhera</t>
+          <t>navdeep saini</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="C111" t="n">
         <v>0</v>
@@ -9769,11 +9769,11 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>nicholas pooran</t>
+          <t>nehal wadhera</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>216</v>
+        <v>65</v>
       </c>
       <c r="C112" t="n">
         <v>0</v>
@@ -9782,11 +9782,11 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>nishant sindhu</t>
+          <t>nicholas pooran</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>38</v>
+        <v>216</v>
       </c>
       <c r="C113" t="n">
         <v>0</v>
@@ -9795,76 +9795,76 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>nitish kumar reddy</t>
+          <t>nishant sindhu</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>224</v>
+        <v>38</v>
       </c>
       <c r="C114" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>nitish rana</t>
+          <t>nitish kumar reddy</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C115" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>noor ahmad</t>
+          <t>nitish rana</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>10</v>
+        <v>225</v>
       </c>
       <c r="C116" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>pat cummins</t>
+          <t>noor ahmad</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="C117" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>pathum nissanka</t>
+          <t>pat cummins</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>278</v>
+        <v>29</v>
       </c>
       <c r="C118" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>philip salt</t>
+          <t>pathum nissanka</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>202</v>
+        <v>278</v>
       </c>
       <c r="C119" t="n">
         <v>0</v>
@@ -9873,11 +9873,11 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>prabhsimran singh</t>
+          <t>philip salt</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>439</v>
+        <v>202</v>
       </c>
       <c r="C120" t="n">
         <v>0</v>
@@ -9886,76 +9886,76 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>praful hinge</t>
+          <t>prabhsimran singh</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>3</v>
+        <v>441</v>
       </c>
       <c r="C121" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>prashant veer</t>
+          <t>praful hinge</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>79</v>
+        <v>3</v>
       </c>
       <c r="C122" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>prasidh krishna</t>
+          <t>prashant veer</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="C123" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>prince yadav</t>
+          <t>prasidh krishna</t>
         </is>
       </c>
       <c r="B124" t="n">
         <v>0</v>
       </c>
       <c r="C124" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>priyansh arya</t>
+          <t>prince yadav</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>364</v>
+        <v>0</v>
       </c>
       <c r="C125" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>quinton de kock</t>
+          <t>priyansh arya</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>132</v>
+        <v>364</v>
       </c>
       <c r="C126" t="n">
         <v>0</v>
@@ -9964,37 +9964,37 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>raghu sharma</t>
+          <t>quinton de kock</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>0</v>
+        <v>132</v>
       </c>
       <c r="C127" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>rahul chahar</t>
+          <t>raghu sharma</t>
         </is>
       </c>
       <c r="B128" t="n">
         <v>0</v>
       </c>
       <c r="C128" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>rahul tewatia</t>
+          <t>rahul chahar</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>98</v>
+        <v>0</v>
       </c>
       <c r="C129" t="n">
         <v>0</v>
@@ -10003,50 +10003,50 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>raj angad bawa</t>
+          <t>rahul tewatia</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>16</v>
+        <v>98</v>
       </c>
       <c r="C130" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>rajat patidar</t>
+          <t>raj angad bawa</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>337</v>
+        <v>16</v>
       </c>
       <c r="C131" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>ramakrishna ghosh</t>
+          <t>rajat patidar</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>0</v>
+        <v>337</v>
       </c>
       <c r="C132" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>ramandeep singh</t>
+          <t>ramakrishna ghosh</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="C133" t="n">
         <v>1</v>
@@ -10055,128 +10055,128 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>rashid khan</t>
+          <t>ramandeep singh</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>35</v>
+        <v>82</v>
       </c>
       <c r="C134" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>rasikh salam</t>
+          <t>rashid khan</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>3</v>
+        <v>35</v>
       </c>
       <c r="C135" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>ravi bishnoi</t>
+          <t>rasikh salam</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C136" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>ravichandran smaran</t>
+          <t>ravi bishnoi</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="C137" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>ravindra jadeja</t>
+          <t>ravi singh</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>190</v>
+        <v>4</v>
       </c>
       <c r="C138" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>ravisrinivasan sai kishore</t>
+          <t>ravichandran smaran</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="C139" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>rinku singh</t>
+          <t>ravindra jadeja</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>286</v>
+        <v>190</v>
       </c>
       <c r="C140" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>rishabh pant</t>
+          <t>ravisrinivasan sai kishore</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>251</v>
+        <v>0</v>
       </c>
       <c r="C141" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>riyan parag</t>
+          <t>rinku singh</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>207</v>
+        <v>286</v>
       </c>
       <c r="C142" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>robin minz</t>
+          <t>rishabh pant</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>6</v>
+        <v>251</v>
       </c>
       <c r="C143" t="n">
         <v>0</v>
@@ -10185,37 +10185,37 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>rohit sharma</t>
+          <t>riyan parag</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>268</v>
+        <v>258</v>
       </c>
       <c r="C144" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>romario shepherd</t>
+          <t>robin minz</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>83</v>
+        <v>6</v>
       </c>
       <c r="C145" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>rovman powell</t>
+          <t>rohit sharma</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>121</v>
+        <v>268</v>
       </c>
       <c r="C146" t="n">
         <v>0</v>
@@ -10224,24 +10224,24 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>ruturaj gaikwad</t>
+          <t>romario shepherd</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>306</v>
+        <v>83</v>
       </c>
       <c r="C147" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>ryan rickelton</t>
+          <t>rovman powell</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>430</v>
+        <v>121</v>
       </c>
       <c r="C148" t="n">
         <v>0</v>
@@ -10250,11 +10250,11 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>sahil parakh</t>
+          <t>ruturaj gaikwad</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>13</v>
+        <v>306</v>
       </c>
       <c r="C149" t="n">
         <v>0</v>
@@ -10263,24 +10263,24 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>sakib hussain</t>
+          <t>ryan rickelton</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>0</v>
+        <v>430</v>
       </c>
       <c r="C150" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>salil arora</t>
+          <t>sahil parakh</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>111</v>
+        <v>22</v>
       </c>
       <c r="C151" t="n">
         <v>0</v>
@@ -10289,37 +10289,37 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>sameer rizvi</t>
+          <t>sakib hussain</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>252</v>
+        <v>0</v>
       </c>
       <c r="C152" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>sandeep sharma</t>
+          <t>salil arora</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>0</v>
+        <v>111</v>
       </c>
       <c r="C153" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>sanju samson</t>
+          <t>sameer rizvi</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>450</v>
+        <v>252</v>
       </c>
       <c r="C154" t="n">
         <v>0</v>
@@ -10328,167 +10328,167 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>sarfaraz khan</t>
+          <t>sandeep sharma</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>161</v>
+        <v>0</v>
       </c>
       <c r="C155" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>saurabh dubey</t>
+          <t>sanju samson</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>0</v>
+        <v>450</v>
       </c>
       <c r="C156" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>shahbaz ahmed</t>
+          <t>sarfaraz khan</t>
         </is>
       </c>
       <c r="B157" t="n">
-        <v>58</v>
+        <v>161</v>
       </c>
       <c r="C157" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>shahrukh khan</t>
+          <t>saurabh dubey</t>
         </is>
       </c>
       <c r="B158" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="C158" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>shardul thakur</t>
+          <t>shahbaz ahmed</t>
         </is>
       </c>
       <c r="B159" t="n">
-        <v>14</v>
+        <v>58</v>
       </c>
       <c r="C159" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>shashank singh</t>
+          <t>shahrukh khan</t>
         </is>
       </c>
       <c r="B160" t="n">
-        <v>76</v>
+        <v>43</v>
       </c>
       <c r="C160" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>sherfane rutherford</t>
+          <t>shardul thakur</t>
         </is>
       </c>
       <c r="B161" t="n">
-        <v>123</v>
+        <v>14</v>
       </c>
       <c r="C161" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>shimron hetmyer</t>
+          <t>shashank singh</t>
         </is>
       </c>
       <c r="B162" t="n">
-        <v>78</v>
+        <v>132</v>
       </c>
       <c r="C162" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>shivam dube</t>
+          <t>sherfane rutherford</t>
         </is>
       </c>
       <c r="B163" t="n">
-        <v>197</v>
+        <v>123</v>
       </c>
       <c r="C163" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>shivang kumar</t>
+          <t>shimron hetmyer</t>
         </is>
       </c>
       <c r="B164" t="n">
-        <v>26</v>
+        <v>78</v>
       </c>
       <c r="C164" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>shreyas iyer</t>
+          <t>shivam dube</t>
         </is>
       </c>
       <c r="B165" t="n">
-        <v>396</v>
+        <v>197</v>
       </c>
       <c r="C165" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>shubham badriprasad dubey</t>
+          <t>shivang kumar</t>
         </is>
       </c>
       <c r="B166" t="n">
-        <v>71</v>
+        <v>26</v>
       </c>
       <c r="C166" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>shubman gill</t>
+          <t>shreyas iyer</t>
         </is>
       </c>
       <c r="B167" t="n">
-        <v>552</v>
+        <v>397</v>
       </c>
       <c r="C167" t="n">
         <v>0</v>
@@ -10497,115 +10497,115 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>spencer johnson</t>
+          <t>shubham badriprasad dubey</t>
         </is>
       </c>
       <c r="B168" t="n">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="C168" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>sunil narine</t>
+          <t>shubman gill</t>
         </is>
       </c>
       <c r="B169" t="n">
-        <v>40</v>
+        <v>552</v>
       </c>
       <c r="C169" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>suryakumar yadav</t>
+          <t>spencer johnson</t>
         </is>
       </c>
       <c r="B170" t="n">
-        <v>195</v>
+        <v>0</v>
       </c>
       <c r="C170" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>suryansh shedge</t>
+          <t>sunil narine</t>
         </is>
       </c>
       <c r="B171" t="n">
-        <v>114</v>
+        <v>40</v>
       </c>
       <c r="C171" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>suyash sharma</t>
+          <t>suryakumar yadav</t>
         </is>
       </c>
       <c r="B172" t="n">
-        <v>0</v>
+        <v>195</v>
       </c>
       <c r="C172" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>t natarajan</t>
+          <t>suryansh shedge</t>
         </is>
       </c>
       <c r="B173" t="n">
-        <v>1</v>
+        <v>149</v>
       </c>
       <c r="C173" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>tilak varma</t>
+          <t>suyash sharma</t>
         </is>
       </c>
       <c r="B174" t="n">
-        <v>336</v>
+        <v>0</v>
       </c>
       <c r="C174" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>tim david</t>
+          <t>t natarajan</t>
         </is>
       </c>
       <c r="B175" t="n">
-        <v>234</v>
+        <v>1</v>
       </c>
       <c r="C175" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>tim seifert</t>
+          <t>tilak varma</t>
         </is>
       </c>
       <c r="B176" t="n">
-        <v>19</v>
+        <v>336</v>
       </c>
       <c r="C176" t="n">
         <v>0</v>
@@ -10614,11 +10614,11 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>travis head</t>
+          <t>tim david</t>
         </is>
       </c>
       <c r="B177" t="n">
-        <v>361</v>
+        <v>262</v>
       </c>
       <c r="C177" t="n">
         <v>0</v>
@@ -10627,24 +10627,24 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>trent boult</t>
+          <t>tim seifert</t>
         </is>
       </c>
       <c r="B178" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="C178" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>tristan stubbs</t>
+          <t>travis head</t>
         </is>
       </c>
       <c r="B179" t="n">
-        <v>271</v>
+        <v>361</v>
       </c>
       <c r="C179" t="n">
         <v>0</v>
@@ -10653,24 +10653,24 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>tushar deshpande</t>
+          <t>trent boult</t>
         </is>
       </c>
       <c r="B180" t="n">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="C180" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>urvil patel</t>
+          <t>tripurana vijay</t>
         </is>
       </c>
       <c r="B181" t="n">
-        <v>116</v>
+        <v>0</v>
       </c>
       <c r="C181" t="n">
         <v>0</v>
@@ -10679,89 +10679,89 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>vaibhav arora</t>
+          <t>tristan stubbs</t>
         </is>
       </c>
       <c r="B182" t="n">
-        <v>1</v>
+        <v>275</v>
       </c>
       <c r="C182" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>vaibhav suryavanshi</t>
+          <t>tushar deshpande</t>
         </is>
       </c>
       <c r="B183" t="n">
-        <v>440</v>
+        <v>26</v>
       </c>
       <c r="C183" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>varun chakravarthy</t>
+          <t>urvil patel</t>
         </is>
       </c>
       <c r="B184" t="n">
-        <v>0</v>
+        <v>116</v>
       </c>
       <c r="C184" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>venkatesh iyer</t>
+          <t>vaibhav arora</t>
         </is>
       </c>
       <c r="B185" t="n">
-        <v>41</v>
+        <v>1</v>
       </c>
       <c r="C185" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>vijaykumar vyshak</t>
+          <t>vaibhav suryavanshi</t>
         </is>
       </c>
       <c r="B186" t="n">
-        <v>2</v>
+        <v>486</v>
       </c>
       <c r="C186" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>vipraj nigam</t>
+          <t>varun chakravarthy</t>
         </is>
       </c>
       <c r="B187" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="C187" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>virat kohli</t>
+          <t>venkatesh iyer</t>
         </is>
       </c>
       <c r="B188" t="n">
-        <v>484</v>
+        <v>114</v>
       </c>
       <c r="C188" t="n">
         <v>0</v>
@@ -10770,105 +10770,144 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>vishnu vinod</t>
+          <t>vijaykumar vyshak</t>
         </is>
       </c>
       <c r="B189" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="C189" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>washington sundar</t>
+          <t>vipraj nigam</t>
         </is>
       </c>
       <c r="B190" t="n">
-        <v>296</v>
+        <v>15</v>
       </c>
       <c r="C190" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>will jacks</t>
+          <t>virat kohli</t>
         </is>
       </c>
       <c r="B191" t="n">
-        <v>92</v>
+        <v>542</v>
       </c>
       <c r="C191" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>xavier bartlett</t>
+          <t>vishnu vinod</t>
         </is>
       </c>
       <c r="B192" t="n">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="C192" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>yash raj punja</t>
+          <t>washington sundar</t>
         </is>
       </c>
       <c r="B193" t="n">
-        <v>0</v>
+        <v>296</v>
       </c>
       <c r="C193" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>yash thakur</t>
+          <t>will jacks</t>
         </is>
       </c>
       <c r="B194" t="n">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="C194" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>yashasvi jaiswal</t>
+          <t>xavier bartlett</t>
         </is>
       </c>
       <c r="B195" t="n">
-        <v>315</v>
+        <v>29</v>
       </c>
       <c r="C195" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
+          <t>yash raj punja</t>
+        </is>
+      </c>
+      <c r="B196" t="n">
+        <v>0</v>
+      </c>
+      <c r="C196" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>yash thakur</t>
+        </is>
+      </c>
+      <c r="B197" t="n">
+        <v>0</v>
+      </c>
+      <c r="C197" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>yashasvi jaiswal</t>
+        </is>
+      </c>
+      <c r="B198" t="n">
+        <v>327</v>
+      </c>
+      <c r="C198" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
           <t>yuzvendra chahal</t>
         </is>
       </c>
-      <c r="B196" t="n">
-        <v>0</v>
-      </c>
-      <c r="C196" t="n">
-        <v>9</v>
+      <c r="B199" t="n">
+        <v>0</v>
+      </c>
+      <c r="C199" t="n">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -10882,7 +10921,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K27"/>
+  <dimension ref="A1:K26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11203,23 +11242,23 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Adam Milne</t>
+          <t>Prithvi Shaw</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>VATSAL11</t>
+          <t>BABA11</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>david miller</t>
+          <t>prasidh krishna</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -11246,7 +11285,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Prithvi Shaw</t>
+          <t>liam livingston</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -11256,13 +11295,13 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>prasidh krishna</t>
+          <t>liam livingstone</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -11289,7 +11328,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>liam livingston</t>
+          <t>rachin ravindra</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -11305,7 +11344,7 @@
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>liam livingstone</t>
+          <t>ravichandran smaran</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -11332,7 +11371,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>rachin ravindra</t>
+          <t>Zeeshan Ansari</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -11342,13 +11381,13 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>ravichandran smaran</t>
+          <t>eshan malinga</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -11375,23 +11414,23 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Zeeshan Ansari</t>
+          <t>Mitchel Owen</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>BABA11</t>
+          <t>DIPESH11</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>eshan malinga</t>
+          <t>mitchell santner</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -11418,23 +11457,23 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Mitchel Owen</t>
+          <t>Jayant Yadav</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>DIPESH11</t>
+          <t>NAKUL11</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>mitchell santner</t>
+          <t>mayank yadav</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -11461,7 +11500,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Jayant Yadav</t>
+          <t>Ajay Mandal</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -11477,7 +11516,7 @@
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>mayank yadav</t>
+          <t>rajat patidar</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -11504,23 +11543,23 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Ajay Mandal</t>
+          <t>Arjun Tendulkar</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>NAKUL11</t>
+          <t>SKY11</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>rajat patidar</t>
+          <t>karun nair</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -11547,7 +11586,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Arjun Tendulkar</t>
+          <t>Kwena Maphaka</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -11563,7 +11602,7 @@
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>karun nair</t>
+          <t>aiden markram</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -11590,23 +11629,23 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Kwena Maphaka</t>
+          <t>Azmatullah Omarzai</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>SKY11</t>
+          <t>HARSH11</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>aiden markram</t>
+          <t>azmatullah</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -11633,23 +11672,23 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Azmatullah Omarzai</t>
+          <t>Tejasvi Singh</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>HARSH11</t>
+          <t>AMEY11</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>azmatullah</t>
+          <t>ravi singh</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -11676,7 +11715,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Tejasvi Singh</t>
+          <t>Sai Kishor</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -11686,13 +11725,13 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>akash singh</t>
+          <t>ishan kishan</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -11719,7 +11758,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Sai Kishor</t>
+          <t>Akash Deep</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -11735,7 +11774,7 @@
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>ishan kishan</t>
+          <t>arshdeep singh</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -11762,23 +11801,23 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Akash Deep</t>
+          <t>Ben Duckett</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>AMEY11</t>
+          <t>PRATIK11</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>arshdeep singh</t>
+          <t>ben dwarshuis</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -11805,7 +11844,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Ben Duckett</t>
+          <t>Rahul Tripathi</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -11821,7 +11860,7 @@
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>ben dwarshuis</t>
+          <t>rahul tewatia</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -11848,7 +11887,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rahul Tripathi</t>
+          <t>Dre Pretorius</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -11864,7 +11903,7 @@
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>rahul tewatia</t>
+          <t>lhuan dre pretorius</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -11891,7 +11930,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Dre Pretorius</t>
+          <t>Matthew Breetzke</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -11907,7 +11946,7 @@
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>lhuan dre pretorius</t>
+          <t>matt henry</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -11934,7 +11973,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Matthew Breetzke</t>
+          <t>Anuj Rawat</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -11950,7 +11989,7 @@
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>matt henry</t>
+          <t>mayank rawat</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -11977,7 +12016,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Anuj Rawat</t>
+          <t>Wanindu Hasaranga</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -11987,13 +12026,13 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>mayank rawat</t>
+          <t>ravichandran smaran</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -12014,49 +12053,6 @@
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Wanindu Hasaranga</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>PRATIK11</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>AR</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>ravichandran smaran</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>no_stats_yet</t>
-        </is>
-      </c>
-      <c r="G27" t="n">
-        <v>0</v>
-      </c>
-      <c r="H27" t="n">
-        <v>0</v>
-      </c>
-      <c r="I27" t="n">
-        <v>0</v>
-      </c>
-      <c r="J27" t="n">
-        <v>0</v>
-      </c>
-      <c r="K27" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12359,19 +12355,19 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>35</v>
+        <v>86</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>35</v>
+        <v>86</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>35</v>
+        <v>86</v>
       </c>
     </row>
   </sheetData>

--- a/IPL_Fantasy_Points.xlsx
+++ b/IPL_Fantasy_Points.xlsx
@@ -604,19 +604,19 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>361</v>
+        <v>367</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>361</v>
+        <v>367</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>361</v>
+        <v>367</v>
       </c>
     </row>
     <row r="5">
@@ -733,19 +733,19 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>99</v>
+        <v>143</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>99</v>
+        <v>143</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>99</v>
+        <v>143</v>
       </c>
     </row>
     <row r="8">
@@ -776,19 +776,19 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>244</v>
+        <v>276</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>244</v>
+        <v>276</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>244</v>
+        <v>276</v>
       </c>
     </row>
     <row r="9">
@@ -905,19 +905,19 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I11" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J11" t="n">
-        <v>140</v>
+        <v>160</v>
       </c>
       <c r="K11" t="n">
-        <v>142</v>
+        <v>165</v>
       </c>
     </row>
     <row r="12">
@@ -1206,19 +1206,19 @@
         </is>
       </c>
       <c r="G18" t="n">
-        <v>420</v>
+        <v>490</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>420</v>
+        <v>490</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>420</v>
+        <v>490</v>
       </c>
     </row>
     <row r="19">
@@ -1854,16 +1854,16 @@
         <v>39</v>
       </c>
       <c r="H33" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I33" t="n">
         <v>0</v>
       </c>
       <c r="J33" t="n">
-        <v>380</v>
+        <v>400</v>
       </c>
       <c r="K33" t="n">
-        <v>380</v>
+        <v>400</v>
       </c>
     </row>
     <row r="34">
@@ -2023,19 +2023,19 @@
         </is>
       </c>
       <c r="G37" t="n">
-        <v>508</v>
+        <v>555</v>
       </c>
       <c r="H37" t="n">
         <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>508</v>
+        <v>555</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>508</v>
+        <v>555</v>
       </c>
     </row>
     <row r="38">
@@ -2109,19 +2109,19 @@
         </is>
       </c>
       <c r="G39" t="n">
-        <v>224</v>
+        <v>235</v>
       </c>
       <c r="H39" t="n">
         <v>7</v>
       </c>
       <c r="I39" t="n">
-        <v>224</v>
+        <v>235</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>224</v>
+        <v>235</v>
       </c>
     </row>
     <row r="40">
@@ -2754,19 +2754,19 @@
         </is>
       </c>
       <c r="G54" t="n">
-        <v>450</v>
+        <v>477</v>
       </c>
       <c r="H54" t="n">
         <v>0</v>
       </c>
       <c r="I54" t="n">
-        <v>450</v>
+        <v>477</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
       </c>
       <c r="K54" t="n">
-        <v>450</v>
+        <v>477</v>
       </c>
     </row>
     <row r="55">
@@ -3098,19 +3098,19 @@
         </is>
       </c>
       <c r="G62" t="n">
-        <v>197</v>
+        <v>223</v>
       </c>
       <c r="H62" t="n">
         <v>1</v>
       </c>
       <c r="I62" t="n">
-        <v>197</v>
+        <v>223</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
       </c>
       <c r="K62" t="n">
-        <v>197</v>
+        <v>223</v>
       </c>
     </row>
     <row r="63">
@@ -3528,19 +3528,19 @@
         </is>
       </c>
       <c r="G72" t="n">
-        <v>306</v>
+        <v>321</v>
       </c>
       <c r="H72" t="n">
         <v>0</v>
       </c>
       <c r="I72" t="n">
-        <v>306</v>
+        <v>321</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
       </c>
       <c r="K72" t="n">
-        <v>306</v>
+        <v>321</v>
       </c>
     </row>
     <row r="73">
@@ -3875,16 +3875,16 @@
         <v>29</v>
       </c>
       <c r="H80" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I80" t="n">
         <v>29</v>
       </c>
       <c r="J80" t="n">
-        <v>100</v>
+        <v>160</v>
       </c>
       <c r="K80" t="n">
-        <v>129</v>
+        <v>189</v>
       </c>
     </row>
     <row r="81">
@@ -4474,19 +4474,19 @@
         </is>
       </c>
       <c r="G94" t="n">
-        <v>116</v>
+        <v>129</v>
       </c>
       <c r="H94" t="n">
         <v>0</v>
       </c>
       <c r="I94" t="n">
-        <v>116</v>
+        <v>129</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
       </c>
       <c r="K94" t="n">
-        <v>116</v>
+        <v>129</v>
       </c>
     </row>
     <row r="95">
@@ -5638,16 +5638,16 @@
         <v>0</v>
       </c>
       <c r="H121" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I121" t="n">
         <v>0</v>
       </c>
       <c r="J121" t="n">
-        <v>100</v>
+        <v>140</v>
       </c>
       <c r="K121" t="n">
-        <v>100</v>
+        <v>140</v>
       </c>
     </row>
     <row r="122">
@@ -6237,19 +6237,19 @@
         </is>
       </c>
       <c r="G135" t="n">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="H135" t="n">
         <v>0</v>
       </c>
       <c r="I135" t="n">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
       </c>
       <c r="K135" t="n">
-        <v>79</v>
+        <v>90</v>
       </c>
     </row>
     <row r="136">
@@ -6409,19 +6409,19 @@
         </is>
       </c>
       <c r="G139" t="n">
-        <v>111</v>
+        <v>121</v>
       </c>
       <c r="H139" t="n">
         <v>0</v>
       </c>
       <c r="I139" t="n">
-        <v>111</v>
+        <v>121</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
       </c>
       <c r="K139" t="n">
-        <v>111</v>
+        <v>121</v>
       </c>
     </row>
     <row r="140">
@@ -7398,19 +7398,19 @@
         </is>
       </c>
       <c r="G162" t="n">
-        <v>481</v>
+        <v>507</v>
       </c>
       <c r="H162" t="n">
         <v>0</v>
       </c>
       <c r="I162" t="n">
-        <v>481</v>
+        <v>507</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
       </c>
       <c r="K162" t="n">
-        <v>481</v>
+        <v>507</v>
       </c>
     </row>
     <row r="163">
@@ -8132,16 +8132,16 @@
         <v>10</v>
       </c>
       <c r="H179" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I179" t="n">
         <v>0</v>
       </c>
       <c r="J179" t="n">
-        <v>240</v>
+        <v>260</v>
       </c>
       <c r="K179" t="n">
-        <v>240</v>
+        <v>260</v>
       </c>
     </row>
   </sheetData>
@@ -8185,7 +8185,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>4121</v>
+        <v>4196</v>
       </c>
     </row>
     <row r="3">
@@ -8198,7 +8198,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>3516</v>
+        <v>3606</v>
       </c>
     </row>
     <row r="4">
@@ -8211,7 +8211,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>3298</v>
+        <v>3351</v>
       </c>
     </row>
     <row r="5">
@@ -8220,11 +8220,11 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>AMEY11</t>
+          <t>NAKUL11</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>3270</v>
+        <v>3283</v>
       </c>
     </row>
     <row r="6">
@@ -8233,7 +8233,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>NAKUL11</t>
+          <t>AMEY11</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -8246,11 +8246,11 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>HARSH11</t>
+          <t>SKY11</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>3084</v>
+        <v>3108</v>
       </c>
     </row>
     <row r="8">
@@ -8259,11 +8259,11 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>SKY11</t>
+          <t>HARSH11</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>3068</v>
+        <v>3105</v>
       </c>
     </row>
     <row r="9">
@@ -8276,7 +8276,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2931</v>
+        <v>3036</v>
       </c>
     </row>
     <row r="10">
@@ -8289,7 +8289,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2633</v>
+        <v>2691</v>
       </c>
     </row>
     <row r="11">
@@ -8302,7 +8302,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2260</v>
+        <v>2306</v>
       </c>
     </row>
   </sheetData>
@@ -8369,7 +8369,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>481</v>
+        <v>507</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
@@ -8447,10 +8447,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11">
@@ -8528,7 +8528,7 @@
         <v>39</v>
       </c>
       <c r="C16" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="17">
@@ -8889,7 +8889,7 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>99</v>
+        <v>143</v>
       </c>
       <c r="C44" t="n">
         <v>0</v>
@@ -8970,7 +8970,7 @@
         <v>2</v>
       </c>
       <c r="C50" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="51">
@@ -9084,7 +9084,7 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>508</v>
+        <v>555</v>
       </c>
       <c r="C59" t="n">
         <v>0</v>
@@ -9110,7 +9110,7 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>420</v>
+        <v>490</v>
       </c>
       <c r="C61" t="n">
         <v>0</v>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>244</v>
+        <v>276</v>
       </c>
       <c r="C74" t="n">
         <v>0</v>
@@ -9698,7 +9698,7 @@
         <v>0</v>
       </c>
       <c r="C106" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="107">
@@ -9812,7 +9812,7 @@
         </is>
       </c>
       <c r="B115" t="n">
-        <v>224</v>
+        <v>235</v>
       </c>
       <c r="C115" t="n">
         <v>7</v>
@@ -9841,7 +9841,7 @@
         <v>10</v>
       </c>
       <c r="C117" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="118">
@@ -9854,7 +9854,7 @@
         <v>29</v>
       </c>
       <c r="C118" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="119">
@@ -9906,7 +9906,7 @@
         <v>3</v>
       </c>
       <c r="C122" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="123">
@@ -9916,7 +9916,7 @@
         </is>
       </c>
       <c r="B123" t="n">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="C123" t="n">
         <v>0</v>
@@ -10124,7 +10124,7 @@
         </is>
       </c>
       <c r="B139" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C139" t="n">
         <v>0</v>
@@ -10254,7 +10254,7 @@
         </is>
       </c>
       <c r="B149" t="n">
-        <v>306</v>
+        <v>321</v>
       </c>
       <c r="C149" t="n">
         <v>0</v>
@@ -10296,7 +10296,7 @@
         <v>0</v>
       </c>
       <c r="C152" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="153">
@@ -10306,7 +10306,7 @@
         </is>
       </c>
       <c r="B153" t="n">
-        <v>111</v>
+        <v>121</v>
       </c>
       <c r="C153" t="n">
         <v>0</v>
@@ -10345,7 +10345,7 @@
         </is>
       </c>
       <c r="B156" t="n">
-        <v>450</v>
+        <v>477</v>
       </c>
       <c r="C156" t="n">
         <v>0</v>
@@ -10462,7 +10462,7 @@
         </is>
       </c>
       <c r="B165" t="n">
-        <v>197</v>
+        <v>223</v>
       </c>
       <c r="C165" t="n">
         <v>1</v>
@@ -10644,7 +10644,7 @@
         </is>
       </c>
       <c r="B179" t="n">
-        <v>361</v>
+        <v>367</v>
       </c>
       <c r="C179" t="n">
         <v>0</v>
@@ -10709,7 +10709,7 @@
         </is>
       </c>
       <c r="B184" t="n">
-        <v>116</v>
+        <v>129</v>
       </c>
       <c r="C184" t="n">
         <v>0</v>

--- a/IPL_Fantasy_Points.xlsx
+++ b/IPL_Fantasy_Points.xlsx
@@ -561,19 +561,19 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>251</v>
+        <v>286</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>251</v>
+        <v>286</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>251</v>
+        <v>286</v>
       </c>
     </row>
     <row r="4">
@@ -1037,16 +1037,16 @@
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>200</v>
+        <v>220</v>
       </c>
       <c r="K14" t="n">
-        <v>200</v>
+        <v>220</v>
       </c>
     </row>
     <row r="15">
@@ -1335,19 +1335,19 @@
         </is>
       </c>
       <c r="G21" t="n">
-        <v>486</v>
+        <v>579</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>486</v>
+        <v>579</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>486</v>
+        <v>579</v>
       </c>
     </row>
     <row r="22">
@@ -2797,19 +2797,19 @@
         </is>
       </c>
       <c r="G55" t="n">
-        <v>134</v>
+        <v>194</v>
       </c>
       <c r="H55" t="n">
         <v>0</v>
       </c>
       <c r="I55" t="n">
-        <v>134</v>
+        <v>194</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
       </c>
       <c r="K55" t="n">
-        <v>134</v>
+        <v>194</v>
       </c>
     </row>
     <row r="56">
@@ -2883,19 +2883,19 @@
         </is>
       </c>
       <c r="G57" t="n">
-        <v>367</v>
+        <v>420</v>
       </c>
       <c r="H57" t="n">
         <v>0</v>
       </c>
       <c r="I57" t="n">
-        <v>367</v>
+        <v>420</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
       </c>
       <c r="K57" t="n">
-        <v>367</v>
+        <v>420</v>
       </c>
     </row>
     <row r="58">
@@ -4302,19 +4302,19 @@
         </is>
       </c>
       <c r="G90" t="n">
-        <v>327</v>
+        <v>370</v>
       </c>
       <c r="H90" t="n">
         <v>0</v>
       </c>
       <c r="I90" t="n">
-        <v>327</v>
+        <v>370</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
       </c>
       <c r="K90" t="n">
-        <v>327</v>
+        <v>370</v>
       </c>
     </row>
     <row r="91">
@@ -5119,19 +5119,19 @@
         </is>
       </c>
       <c r="G109" t="n">
-        <v>467</v>
+        <v>563</v>
       </c>
       <c r="H109" t="n">
         <v>0</v>
       </c>
       <c r="I109" t="n">
-        <v>467</v>
+        <v>563</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
       </c>
       <c r="K109" t="n">
-        <v>467</v>
+        <v>563</v>
       </c>
     </row>
     <row r="110">
@@ -5420,19 +5420,19 @@
         </is>
       </c>
       <c r="G116" t="n">
-        <v>233</v>
+        <v>249</v>
       </c>
       <c r="H116" t="n">
         <v>1</v>
       </c>
       <c r="I116" t="n">
-        <v>233</v>
+        <v>249</v>
       </c>
       <c r="J116" t="n">
         <v>20</v>
       </c>
       <c r="K116" t="n">
-        <v>253</v>
+        <v>269</v>
       </c>
     </row>
     <row r="117">
@@ -6710,19 +6710,19 @@
         </is>
       </c>
       <c r="G146" t="n">
-        <v>216</v>
+        <v>232</v>
       </c>
       <c r="H146" t="n">
         <v>0</v>
       </c>
       <c r="I146" t="n">
-        <v>216</v>
+        <v>232</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
       </c>
       <c r="K146" t="n">
-        <v>216</v>
+        <v>232</v>
       </c>
     </row>
     <row r="147">
@@ -7057,16 +7057,16 @@
         <v>21</v>
       </c>
       <c r="H154" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I154" t="n">
         <v>21</v>
       </c>
       <c r="J154" t="n">
-        <v>340</v>
+        <v>360</v>
       </c>
       <c r="K154" t="n">
-        <v>361</v>
+        <v>381</v>
       </c>
     </row>
     <row r="155">
@@ -8198,7 +8198,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>3606</v>
+        <v>3699</v>
       </c>
     </row>
     <row r="4">
@@ -8211,7 +8211,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>3351</v>
+        <v>3464</v>
       </c>
     </row>
     <row r="5">
@@ -8224,7 +8224,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>3283</v>
+        <v>3326</v>
       </c>
     </row>
     <row r="6">
@@ -8237,7 +8237,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>3270</v>
+        <v>3306</v>
       </c>
     </row>
     <row r="7">
@@ -8250,7 +8250,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>3108</v>
+        <v>3220</v>
       </c>
     </row>
     <row r="8">
@@ -8276,7 +8276,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>3036</v>
+        <v>3091</v>
       </c>
     </row>
     <row r="10">
@@ -8316,7 +8316,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C199"/>
+  <dimension ref="A1:C200"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8437,7 +8437,7 @@
         <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10">
@@ -8902,7 +8902,7 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>367</v>
+        <v>420</v>
       </c>
       <c r="C45" t="n">
         <v>0</v>
@@ -8941,7 +8941,7 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>233</v>
+        <v>249</v>
       </c>
       <c r="C48" t="n">
         <v>1</v>
@@ -9217,7 +9217,7 @@
         <v>21</v>
       </c>
       <c r="C69" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="70">
@@ -9253,7 +9253,7 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>134</v>
+        <v>194</v>
       </c>
       <c r="C72" t="n">
         <v>0</v>
@@ -9396,7 +9396,7 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C83" t="n">
         <v>0</v>
@@ -9617,7 +9617,7 @@
         </is>
       </c>
       <c r="B100" t="n">
-        <v>467</v>
+        <v>563</v>
       </c>
       <c r="C100" t="n">
         <v>0</v>
@@ -9685,7 +9685,7 @@
         <v>0</v>
       </c>
       <c r="C105" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="106">
@@ -9786,7 +9786,7 @@
         </is>
       </c>
       <c r="B113" t="n">
-        <v>216</v>
+        <v>232</v>
       </c>
       <c r="C113" t="n">
         <v>0</v>
@@ -10176,7 +10176,7 @@
         </is>
       </c>
       <c r="B143" t="n">
-        <v>251</v>
+        <v>286</v>
       </c>
       <c r="C143" t="n">
         <v>0</v>
@@ -10575,50 +10575,50 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>suyash sharma</t>
+          <t>sushant mishra</t>
         </is>
       </c>
       <c r="B174" t="n">
         <v>0</v>
       </c>
       <c r="C174" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>t natarajan</t>
+          <t>suyash sharma</t>
         </is>
       </c>
       <c r="B175" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C175" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>tilak varma</t>
+          <t>t natarajan</t>
         </is>
       </c>
       <c r="B176" t="n">
-        <v>336</v>
+        <v>1</v>
       </c>
       <c r="C176" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>tim david</t>
+          <t>tilak varma</t>
         </is>
       </c>
       <c r="B177" t="n">
-        <v>262</v>
+        <v>336</v>
       </c>
       <c r="C177" t="n">
         <v>0</v>
@@ -10627,11 +10627,11 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>tim seifert</t>
+          <t>tim david</t>
         </is>
       </c>
       <c r="B178" t="n">
-        <v>19</v>
+        <v>262</v>
       </c>
       <c r="C178" t="n">
         <v>0</v>
@@ -10640,11 +10640,11 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>travis head</t>
+          <t>tim seifert</t>
         </is>
       </c>
       <c r="B179" t="n">
-        <v>367</v>
+        <v>19</v>
       </c>
       <c r="C179" t="n">
         <v>0</v>
@@ -10653,37 +10653,37 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>trent boult</t>
+          <t>travis head</t>
         </is>
       </c>
       <c r="B180" t="n">
-        <v>8</v>
+        <v>367</v>
       </c>
       <c r="C180" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>tripurana vijay</t>
+          <t>trent boult</t>
         </is>
       </c>
       <c r="B181" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="C181" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>tristan stubbs</t>
+          <t>tripurana vijay</t>
         </is>
       </c>
       <c r="B182" t="n">
-        <v>275</v>
+        <v>0</v>
       </c>
       <c r="C182" t="n">
         <v>0</v>
@@ -10692,128 +10692,128 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>tushar deshpande</t>
+          <t>tristan stubbs</t>
         </is>
       </c>
       <c r="B183" t="n">
-        <v>26</v>
+        <v>275</v>
       </c>
       <c r="C183" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>urvil patel</t>
+          <t>tushar deshpande</t>
         </is>
       </c>
       <c r="B184" t="n">
-        <v>129</v>
+        <v>26</v>
       </c>
       <c r="C184" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>vaibhav arora</t>
+          <t>urvil patel</t>
         </is>
       </c>
       <c r="B185" t="n">
-        <v>1</v>
+        <v>129</v>
       </c>
       <c r="C185" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>vaibhav suryavanshi</t>
+          <t>vaibhav arora</t>
         </is>
       </c>
       <c r="B186" t="n">
-        <v>486</v>
+        <v>1</v>
       </c>
       <c r="C186" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>varun chakravarthy</t>
+          <t>vaibhav suryavanshi</t>
         </is>
       </c>
       <c r="B187" t="n">
-        <v>0</v>
+        <v>579</v>
       </c>
       <c r="C187" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>venkatesh iyer</t>
+          <t>varun chakravarthy</t>
         </is>
       </c>
       <c r="B188" t="n">
-        <v>114</v>
+        <v>0</v>
       </c>
       <c r="C188" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>vijaykumar vyshak</t>
+          <t>venkatesh iyer</t>
         </is>
       </c>
       <c r="B189" t="n">
-        <v>2</v>
+        <v>114</v>
       </c>
       <c r="C189" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>vipraj nigam</t>
+          <t>vijaykumar vyshak</t>
         </is>
       </c>
       <c r="B190" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="C190" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>virat kohli</t>
+          <t>vipraj nigam</t>
         </is>
       </c>
       <c r="B191" t="n">
-        <v>542</v>
+        <v>15</v>
       </c>
       <c r="C191" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>vishnu vinod</t>
+          <t>virat kohli</t>
         </is>
       </c>
       <c r="B192" t="n">
-        <v>15</v>
+        <v>542</v>
       </c>
       <c r="C192" t="n">
         <v>0</v>
@@ -10822,24 +10822,24 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>washington sundar</t>
+          <t>vishnu vinod</t>
         </is>
       </c>
       <c r="B193" t="n">
-        <v>296</v>
+        <v>15</v>
       </c>
       <c r="C193" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>will jacks</t>
+          <t>washington sundar</t>
         </is>
       </c>
       <c r="B194" t="n">
-        <v>92</v>
+        <v>296</v>
       </c>
       <c r="C194" t="n">
         <v>1</v>
@@ -10848,65 +10848,78 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>xavier bartlett</t>
+          <t>will jacks</t>
         </is>
       </c>
       <c r="B195" t="n">
-        <v>29</v>
+        <v>92</v>
       </c>
       <c r="C195" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>yash raj punja</t>
+          <t>xavier bartlett</t>
         </is>
       </c>
       <c r="B196" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="C196" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>yash thakur</t>
+          <t>yash raj punja</t>
         </is>
       </c>
       <c r="B197" t="n">
         <v>0</v>
       </c>
       <c r="C197" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>yashasvi jaiswal</t>
+          <t>yash thakur</t>
         </is>
       </c>
       <c r="B198" t="n">
-        <v>327</v>
+        <v>0</v>
       </c>
       <c r="C198" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
+          <t>yashasvi jaiswal</t>
+        </is>
+      </c>
+      <c r="B199" t="n">
+        <v>370</v>
+      </c>
+      <c r="C199" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
           <t>yuzvendra chahal</t>
         </is>
       </c>
-      <c r="B199" t="n">
-        <v>0</v>
-      </c>
-      <c r="C199" t="n">
+      <c r="B200" t="n">
+        <v>0</v>
+      </c>
+      <c r="C200" t="n">
         <v>10</v>
       </c>
     </row>
@@ -12226,19 +12239,19 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>134</v>
+        <v>194</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>134</v>
+        <v>194</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>134</v>
+        <v>194</v>
       </c>
     </row>
     <row r="3">
@@ -12269,19 +12282,19 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>233</v>
+        <v>249</v>
       </c>
       <c r="H3" t="n">
         <v>1</v>
       </c>
       <c r="I3" t="n">
-        <v>233</v>
+        <v>249</v>
       </c>
       <c r="J3" t="n">
         <v>20</v>
       </c>
       <c r="K3" t="n">
-        <v>253</v>
+        <v>269</v>
       </c>
     </row>
     <row r="4">

--- a/IPL_Fantasy_Points.xlsx
+++ b/IPL_Fantasy_Points.xlsx
@@ -865,16 +865,16 @@
         <v>316</v>
       </c>
       <c r="H10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I10" t="n">
         <v>316</v>
       </c>
       <c r="J10" t="n">
-        <v>100</v>
+        <v>140</v>
       </c>
       <c r="K10" t="n">
-        <v>416</v>
+        <v>456</v>
       </c>
     </row>
     <row r="11">
@@ -3012,19 +3012,19 @@
         </is>
       </c>
       <c r="G60" t="n">
-        <v>430</v>
+        <v>436</v>
       </c>
       <c r="H60" t="n">
         <v>0</v>
       </c>
       <c r="I60" t="n">
-        <v>430</v>
+        <v>436</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
       </c>
       <c r="K60" t="n">
-        <v>430</v>
+        <v>436</v>
       </c>
     </row>
     <row r="61">
@@ -5162,19 +5162,19 @@
         </is>
       </c>
       <c r="G110" t="n">
-        <v>268</v>
+        <v>283</v>
       </c>
       <c r="H110" t="n">
         <v>0</v>
       </c>
       <c r="I110" t="n">
-        <v>268</v>
+        <v>283</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
       </c>
       <c r="K110" t="n">
-        <v>268</v>
+        <v>283</v>
       </c>
     </row>
     <row r="111">
@@ -5334,19 +5334,19 @@
         </is>
       </c>
       <c r="G114" t="n">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="H114" t="n">
         <v>4</v>
       </c>
       <c r="I114" t="n">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="J114" t="n">
         <v>80</v>
       </c>
       <c r="K114" t="n">
-        <v>226</v>
+        <v>233</v>
       </c>
     </row>
     <row r="115">
@@ -6065,19 +6065,19 @@
         </is>
       </c>
       <c r="G131" t="n">
-        <v>336</v>
+        <v>343</v>
       </c>
       <c r="H131" t="n">
         <v>0</v>
       </c>
       <c r="I131" t="n">
-        <v>336</v>
+        <v>343</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
       </c>
       <c r="K131" t="n">
-        <v>336</v>
+        <v>343</v>
       </c>
     </row>
     <row r="132">
@@ -6667,19 +6667,19 @@
         </is>
       </c>
       <c r="G145" t="n">
-        <v>195</v>
+        <v>210</v>
       </c>
       <c r="H145" t="n">
         <v>0</v>
       </c>
       <c r="I145" t="n">
-        <v>195</v>
+        <v>210</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
       </c>
       <c r="K145" t="n">
-        <v>195</v>
+        <v>210</v>
       </c>
     </row>
     <row r="146">
@@ -8211,7 +8211,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>3464</v>
+        <v>3470</v>
       </c>
     </row>
     <row r="5">
@@ -8237,7 +8237,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>3306</v>
+        <v>3321</v>
       </c>
     </row>
     <row r="7">
@@ -8250,7 +8250,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>3220</v>
+        <v>3242</v>
       </c>
     </row>
     <row r="8">
@@ -8259,11 +8259,11 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>HARSH11</t>
+          <t>NIRAV11</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>3105</v>
+        <v>3131</v>
       </c>
     </row>
     <row r="9">
@@ -8272,11 +8272,11 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>NIRAV11</t>
+          <t>HARSH11</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>3091</v>
+        <v>3112</v>
       </c>
     </row>
     <row r="10">
@@ -8775,7 +8775,7 @@
         <v>316</v>
       </c>
       <c r="C35" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="36">
@@ -9032,7 +9032,7 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="C55" t="n">
         <v>4</v>
@@ -10215,7 +10215,7 @@
         </is>
       </c>
       <c r="B146" t="n">
-        <v>268</v>
+        <v>283</v>
       </c>
       <c r="C146" t="n">
         <v>0</v>
@@ -10267,7 +10267,7 @@
         </is>
       </c>
       <c r="B150" t="n">
-        <v>430</v>
+        <v>436</v>
       </c>
       <c r="C150" t="n">
         <v>0</v>
@@ -10374,7 +10374,7 @@
         <v>0</v>
       </c>
       <c r="C158" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="159">
@@ -10553,7 +10553,7 @@
         </is>
       </c>
       <c r="B172" t="n">
-        <v>195</v>
+        <v>210</v>
       </c>
       <c r="C172" t="n">
         <v>0</v>
@@ -10618,7 +10618,7 @@
         </is>
       </c>
       <c r="B177" t="n">
-        <v>336</v>
+        <v>343</v>
       </c>
       <c r="C177" t="n">
         <v>0</v>

--- a/IPL_Fantasy_Points.xlsx
+++ b/IPL_Fantasy_Points.xlsx
@@ -733,19 +733,19 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>143</v>
+        <v>151</v>
       </c>
     </row>
     <row r="8">
@@ -776,19 +776,19 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>276</v>
+        <v>295</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>276</v>
+        <v>295</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>276</v>
+        <v>295</v>
       </c>
     </row>
     <row r="9">
@@ -862,19 +862,19 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="H10" t="n">
         <v>7</v>
       </c>
       <c r="I10" t="n">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="J10" t="n">
         <v>140</v>
       </c>
       <c r="K10" t="n">
-        <v>456</v>
+        <v>460</v>
       </c>
     </row>
     <row r="11">
@@ -948,19 +948,19 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="H12" t="n">
         <v>8</v>
       </c>
       <c r="I12" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="J12" t="n">
         <v>160</v>
       </c>
       <c r="K12" t="n">
-        <v>199</v>
+        <v>203</v>
       </c>
     </row>
     <row r="13">
@@ -994,16 +994,16 @@
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>280</v>
+        <v>340</v>
       </c>
       <c r="K13" t="n">
-        <v>280</v>
+        <v>340</v>
       </c>
     </row>
     <row r="14">
@@ -1249,19 +1249,19 @@
         </is>
       </c>
       <c r="G19" t="n">
-        <v>552</v>
+        <v>616</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>552</v>
+        <v>616</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>552</v>
+        <v>616</v>
       </c>
     </row>
     <row r="20">
@@ -1292,19 +1292,19 @@
         </is>
       </c>
       <c r="G20" t="n">
-        <v>251</v>
+        <v>272</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>251</v>
+        <v>272</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>251</v>
+        <v>272</v>
       </c>
     </row>
     <row r="21">
@@ -1811,16 +1811,16 @@
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I32" t="n">
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>260</v>
+        <v>280</v>
       </c>
       <c r="K32" t="n">
-        <v>260</v>
+        <v>280</v>
       </c>
     </row>
     <row r="33">
@@ -1851,19 +1851,19 @@
         </is>
       </c>
       <c r="G33" t="n">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="H33" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I33" t="n">
         <v>0</v>
       </c>
       <c r="J33" t="n">
-        <v>400</v>
+        <v>420</v>
       </c>
       <c r="K33" t="n">
-        <v>400</v>
+        <v>420</v>
       </c>
     </row>
     <row r="34">
@@ -2625,19 +2625,19 @@
         </is>
       </c>
       <c r="G51" t="n">
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="H51" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="I51" t="n">
         <v>0</v>
       </c>
       <c r="J51" t="n">
-        <v>160</v>
+        <v>220</v>
       </c>
       <c r="K51" t="n">
-        <v>160</v>
+        <v>220</v>
       </c>
     </row>
     <row r="52">
@@ -2668,19 +2668,19 @@
         </is>
       </c>
       <c r="G52" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="H52" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I52" t="n">
         <v>0</v>
       </c>
       <c r="J52" t="n">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="K52" t="n">
-        <v>100</v>
+        <v>120</v>
       </c>
     </row>
     <row r="53">
@@ -3055,19 +3055,19 @@
         </is>
       </c>
       <c r="G61" t="n">
-        <v>286</v>
+        <v>295</v>
       </c>
       <c r="H61" t="n">
         <v>0</v>
       </c>
       <c r="I61" t="n">
-        <v>286</v>
+        <v>295</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
       </c>
       <c r="K61" t="n">
-        <v>286</v>
+        <v>295</v>
       </c>
     </row>
     <row r="62">
@@ -3098,19 +3098,19 @@
         </is>
       </c>
       <c r="G62" t="n">
-        <v>223</v>
+        <v>270</v>
       </c>
       <c r="H62" t="n">
         <v>1</v>
       </c>
       <c r="I62" t="n">
-        <v>223</v>
+        <v>270</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
       </c>
       <c r="K62" t="n">
-        <v>223</v>
+        <v>270</v>
       </c>
     </row>
     <row r="63">
@@ -3141,19 +3141,19 @@
         </is>
       </c>
       <c r="G63" t="n">
-        <v>121</v>
+        <v>161</v>
       </c>
       <c r="H63" t="n">
         <v>0</v>
       </c>
       <c r="I63" t="n">
-        <v>121</v>
+        <v>161</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
       </c>
       <c r="K63" t="n">
-        <v>121</v>
+        <v>161</v>
       </c>
     </row>
     <row r="64">
@@ -3187,16 +3187,16 @@
         <v>35</v>
       </c>
       <c r="H64" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I64" t="n">
         <v>35</v>
       </c>
       <c r="J64" t="n">
-        <v>320</v>
+        <v>380</v>
       </c>
       <c r="K64" t="n">
-        <v>355</v>
+        <v>415</v>
       </c>
     </row>
     <row r="65">
@@ -3528,19 +3528,19 @@
         </is>
       </c>
       <c r="G72" t="n">
-        <v>321</v>
+        <v>337</v>
       </c>
       <c r="H72" t="n">
         <v>0</v>
       </c>
       <c r="I72" t="n">
-        <v>321</v>
+        <v>337</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
       </c>
       <c r="K72" t="n">
-        <v>321</v>
+        <v>337</v>
       </c>
     </row>
     <row r="73">
@@ -3571,19 +3571,19 @@
         </is>
       </c>
       <c r="G73" t="n">
-        <v>554</v>
+        <v>638</v>
       </c>
       <c r="H73" t="n">
         <v>0</v>
       </c>
       <c r="I73" t="n">
-        <v>554</v>
+        <v>638</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
       </c>
       <c r="K73" t="n">
-        <v>554</v>
+        <v>638</v>
       </c>
     </row>
     <row r="74">
@@ -4431,19 +4431,19 @@
         </is>
       </c>
       <c r="G93" t="n">
-        <v>412</v>
+        <v>469</v>
       </c>
       <c r="H93" t="n">
         <v>0</v>
       </c>
       <c r="I93" t="n">
-        <v>412</v>
+        <v>469</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
       </c>
       <c r="K93" t="n">
-        <v>412</v>
+        <v>469</v>
       </c>
     </row>
     <row r="94">
@@ -4689,19 +4689,19 @@
         </is>
       </c>
       <c r="G99" t="n">
-        <v>92</v>
+        <v>106</v>
       </c>
       <c r="H99" t="n">
         <v>1</v>
       </c>
       <c r="I99" t="n">
-        <v>92</v>
+        <v>106</v>
       </c>
       <c r="J99" t="n">
         <v>20</v>
       </c>
       <c r="K99" t="n">
-        <v>112</v>
+        <v>126</v>
       </c>
     </row>
     <row r="100">
@@ -4778,16 +4778,16 @@
         <v>35</v>
       </c>
       <c r="H101" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I101" t="n">
         <v>0</v>
       </c>
       <c r="J101" t="n">
-        <v>420</v>
+        <v>480</v>
       </c>
       <c r="K101" t="n">
-        <v>420</v>
+        <v>480</v>
       </c>
     </row>
     <row r="102">
@@ -5248,19 +5248,19 @@
         </is>
       </c>
       <c r="G112" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="H112" t="n">
         <v>0</v>
       </c>
       <c r="I112" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
       </c>
       <c r="K112" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
     </row>
     <row r="113">
@@ -5334,19 +5334,19 @@
         </is>
       </c>
       <c r="G114" t="n">
-        <v>153</v>
+        <v>172</v>
       </c>
       <c r="H114" t="n">
         <v>4</v>
       </c>
       <c r="I114" t="n">
-        <v>153</v>
+        <v>172</v>
       </c>
       <c r="J114" t="n">
         <v>80</v>
       </c>
       <c r="K114" t="n">
-        <v>233</v>
+        <v>252</v>
       </c>
     </row>
     <row r="115">
@@ -5509,16 +5509,16 @@
         <v>11</v>
       </c>
       <c r="H118" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="I118" t="n">
         <v>0</v>
       </c>
       <c r="J118" t="n">
-        <v>320</v>
+        <v>360</v>
       </c>
       <c r="K118" t="n">
-        <v>320</v>
+        <v>360</v>
       </c>
     </row>
     <row r="119">
@@ -5635,19 +5635,19 @@
         </is>
       </c>
       <c r="G121" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H121" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I121" t="n">
         <v>0</v>
       </c>
       <c r="J121" t="n">
-        <v>140</v>
+        <v>160</v>
       </c>
       <c r="K121" t="n">
-        <v>140</v>
+        <v>160</v>
       </c>
     </row>
     <row r="122">
@@ -6065,19 +6065,19 @@
         </is>
       </c>
       <c r="G131" t="n">
-        <v>343</v>
+        <v>356</v>
       </c>
       <c r="H131" t="n">
         <v>0</v>
       </c>
       <c r="I131" t="n">
-        <v>343</v>
+        <v>356</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
       </c>
       <c r="K131" t="n">
-        <v>343</v>
+        <v>356</v>
       </c>
     </row>
     <row r="132">
@@ -6280,19 +6280,19 @@
         </is>
       </c>
       <c r="G136" t="n">
-        <v>296</v>
+        <v>303</v>
       </c>
       <c r="H136" t="n">
         <v>1</v>
       </c>
       <c r="I136" t="n">
-        <v>296</v>
+        <v>303</v>
       </c>
       <c r="J136" t="n">
         <v>20</v>
       </c>
       <c r="K136" t="n">
-        <v>316</v>
+        <v>323</v>
       </c>
     </row>
     <row r="137">
@@ -6455,16 +6455,16 @@
         <v>7</v>
       </c>
       <c r="H140" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I140" t="n">
         <v>0</v>
       </c>
       <c r="J140" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="K140" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
     </row>
     <row r="141">
@@ -7570,19 +7570,19 @@
         </is>
       </c>
       <c r="G166" t="n">
-        <v>321</v>
+        <v>329</v>
       </c>
       <c r="H166" t="n">
         <v>0</v>
       </c>
       <c r="I166" t="n">
-        <v>321</v>
+        <v>329</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
       </c>
       <c r="K166" t="n">
-        <v>321</v>
+        <v>329</v>
       </c>
     </row>
     <row r="167">
@@ -7831,16 +7831,16 @@
         <v>40</v>
       </c>
       <c r="H172" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I172" t="n">
         <v>40</v>
       </c>
       <c r="J172" t="n">
-        <v>260</v>
+        <v>280</v>
       </c>
       <c r="K172" t="n">
-        <v>300</v>
+        <v>320</v>
       </c>
     </row>
     <row r="173">
@@ -8129,7 +8129,7 @@
         </is>
       </c>
       <c r="G179" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H179" t="n">
         <v>13</v>
@@ -8185,7 +8185,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>4196</v>
+        <v>4296</v>
       </c>
     </row>
     <row r="3">
@@ -8198,7 +8198,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>3699</v>
+        <v>3824</v>
       </c>
     </row>
     <row r="4">
@@ -8211,7 +8211,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>3470</v>
+        <v>3626</v>
       </c>
     </row>
     <row r="5">
@@ -8224,7 +8224,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>3326</v>
+        <v>3457</v>
       </c>
     </row>
     <row r="6">
@@ -8233,11 +8233,11 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>AMEY11</t>
+          <t>SKY11</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>3321</v>
+        <v>3366</v>
       </c>
     </row>
     <row r="7">
@@ -8246,11 +8246,11 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>SKY11</t>
+          <t>AMEY11</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>3242</v>
+        <v>3321</v>
       </c>
     </row>
     <row r="8">
@@ -8263,7 +8263,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>3131</v>
+        <v>3226</v>
       </c>
     </row>
     <row r="9">
@@ -8276,7 +8276,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>3112</v>
+        <v>3152</v>
       </c>
     </row>
     <row r="10">
@@ -8289,7 +8289,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2691</v>
+        <v>2771</v>
       </c>
     </row>
     <row r="11">
@@ -8302,7 +8302,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2306</v>
+        <v>2334</v>
       </c>
     </row>
   </sheetData>
@@ -8316,7 +8316,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C200"/>
+  <dimension ref="A1:C201"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8421,7 +8421,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>251</v>
+        <v>272</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
@@ -8476,7 +8476,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="13">
@@ -8525,10 +8525,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="C16" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="17">
@@ -8538,7 +8538,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="C17" t="n">
         <v>8</v>
@@ -8707,7 +8707,7 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>554</v>
+        <v>638</v>
       </c>
       <c r="C30" t="n">
         <v>0</v>
@@ -8772,7 +8772,7 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="C35" t="n">
         <v>7</v>
@@ -8798,10 +8798,10 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="C37" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="38">
@@ -8863,10 +8863,10 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="C42" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="43">
@@ -8889,7 +8889,7 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="C44" t="n">
         <v>0</v>
@@ -8980,7 +8980,7 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>321</v>
+        <v>329</v>
       </c>
       <c r="C51" t="n">
         <v>0</v>
@@ -9032,7 +9032,7 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>153</v>
+        <v>172</v>
       </c>
       <c r="C55" t="n">
         <v>4</v>
@@ -9178,7 +9178,7 @@
         <v>7</v>
       </c>
       <c r="C66" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="67">
@@ -9227,7 +9227,7 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>412</v>
+        <v>469</v>
       </c>
       <c r="C70" t="n">
         <v>0</v>
@@ -9269,7 +9269,7 @@
         <v>35</v>
       </c>
       <c r="C73" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="74">
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>276</v>
+        <v>295</v>
       </c>
       <c r="C74" t="n">
         <v>0</v>
@@ -9295,7 +9295,7 @@
         <v>11</v>
       </c>
       <c r="C75" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="76">
@@ -9500,7 +9500,7 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="C91" t="n">
         <v>0</v>
@@ -9565,7 +9565,7 @@
         </is>
       </c>
       <c r="B96" t="n">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="C96" t="n">
         <v>0</v>
@@ -9672,7 +9672,7 @@
         <v>0</v>
       </c>
       <c r="C104" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="105">
@@ -9695,10 +9695,10 @@
         </is>
       </c>
       <c r="B106" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C106" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="107">
@@ -9838,7 +9838,7 @@
         </is>
       </c>
       <c r="B117" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C117" t="n">
         <v>13</v>
@@ -10075,7 +10075,7 @@
         <v>35</v>
       </c>
       <c r="C135" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="136">
@@ -10163,7 +10163,7 @@
         </is>
       </c>
       <c r="B142" t="n">
-        <v>286</v>
+        <v>295</v>
       </c>
       <c r="C142" t="n">
         <v>0</v>
@@ -10241,7 +10241,7 @@
         </is>
       </c>
       <c r="B148" t="n">
-        <v>121</v>
+        <v>161</v>
       </c>
       <c r="C148" t="n">
         <v>0</v>
@@ -10254,7 +10254,7 @@
         </is>
       </c>
       <c r="B149" t="n">
-        <v>321</v>
+        <v>337</v>
       </c>
       <c r="C149" t="n">
         <v>0</v>
@@ -10462,7 +10462,7 @@
         </is>
       </c>
       <c r="B165" t="n">
-        <v>223</v>
+        <v>270</v>
       </c>
       <c r="C165" t="n">
         <v>1</v>
@@ -10514,7 +10514,7 @@
         </is>
       </c>
       <c r="B169" t="n">
-        <v>552</v>
+        <v>616</v>
       </c>
       <c r="C169" t="n">
         <v>0</v>
@@ -10530,7 +10530,7 @@
         <v>0</v>
       </c>
       <c r="C170" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="171">
@@ -10543,7 +10543,7 @@
         <v>40</v>
       </c>
       <c r="C171" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="172">
@@ -10614,11 +10614,11 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>tilak varma</t>
+          <t>tejasvi dahiya</t>
         </is>
       </c>
       <c r="B177" t="n">
-        <v>343</v>
+        <v>11</v>
       </c>
       <c r="C177" t="n">
         <v>0</v>
@@ -10627,11 +10627,11 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>tim david</t>
+          <t>tilak varma</t>
         </is>
       </c>
       <c r="B178" t="n">
-        <v>262</v>
+        <v>356</v>
       </c>
       <c r="C178" t="n">
         <v>0</v>
@@ -10640,11 +10640,11 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>tim seifert</t>
+          <t>tim david</t>
         </is>
       </c>
       <c r="B179" t="n">
-        <v>19</v>
+        <v>262</v>
       </c>
       <c r="C179" t="n">
         <v>0</v>
@@ -10653,11 +10653,11 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>travis head</t>
+          <t>tim seifert</t>
         </is>
       </c>
       <c r="B180" t="n">
-        <v>367</v>
+        <v>19</v>
       </c>
       <c r="C180" t="n">
         <v>0</v>
@@ -10666,37 +10666,37 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>trent boult</t>
+          <t>travis head</t>
         </is>
       </c>
       <c r="B181" t="n">
-        <v>8</v>
+        <v>367</v>
       </c>
       <c r="C181" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>tripurana vijay</t>
+          <t>trent boult</t>
         </is>
       </c>
       <c r="B182" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="C182" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>tristan stubbs</t>
+          <t>tripurana vijay</t>
         </is>
       </c>
       <c r="B183" t="n">
-        <v>275</v>
+        <v>0</v>
       </c>
       <c r="C183" t="n">
         <v>0</v>
@@ -10705,128 +10705,128 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>tushar deshpande</t>
+          <t>tristan stubbs</t>
         </is>
       </c>
       <c r="B184" t="n">
-        <v>26</v>
+        <v>275</v>
       </c>
       <c r="C184" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>urvil patel</t>
+          <t>tushar deshpande</t>
         </is>
       </c>
       <c r="B185" t="n">
-        <v>129</v>
+        <v>26</v>
       </c>
       <c r="C185" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>vaibhav arora</t>
+          <t>urvil patel</t>
         </is>
       </c>
       <c r="B186" t="n">
-        <v>1</v>
+        <v>129</v>
       </c>
       <c r="C186" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>vaibhav suryavanshi</t>
+          <t>vaibhav arora</t>
         </is>
       </c>
       <c r="B187" t="n">
-        <v>579</v>
+        <v>1</v>
       </c>
       <c r="C187" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>varun chakravarthy</t>
+          <t>vaibhav suryavanshi</t>
         </is>
       </c>
       <c r="B188" t="n">
-        <v>0</v>
+        <v>579</v>
       </c>
       <c r="C188" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>venkatesh iyer</t>
+          <t>varun chakravarthy</t>
         </is>
       </c>
       <c r="B189" t="n">
-        <v>114</v>
+        <v>0</v>
       </c>
       <c r="C189" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>vijaykumar vyshak</t>
+          <t>venkatesh iyer</t>
         </is>
       </c>
       <c r="B190" t="n">
-        <v>2</v>
+        <v>114</v>
       </c>
       <c r="C190" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>vipraj nigam</t>
+          <t>vijaykumar vyshak</t>
         </is>
       </c>
       <c r="B191" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="C191" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>virat kohli</t>
+          <t>vipraj nigam</t>
         </is>
       </c>
       <c r="B192" t="n">
-        <v>542</v>
+        <v>15</v>
       </c>
       <c r="C192" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>vishnu vinod</t>
+          <t>virat kohli</t>
         </is>
       </c>
       <c r="B193" t="n">
-        <v>15</v>
+        <v>542</v>
       </c>
       <c r="C193" t="n">
         <v>0</v>
@@ -10835,24 +10835,24 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>washington sundar</t>
+          <t>vishnu vinod</t>
         </is>
       </c>
       <c r="B194" t="n">
-        <v>296</v>
+        <v>15</v>
       </c>
       <c r="C194" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>will jacks</t>
+          <t>washington sundar</t>
         </is>
       </c>
       <c r="B195" t="n">
-        <v>92</v>
+        <v>303</v>
       </c>
       <c r="C195" t="n">
         <v>1</v>
@@ -10861,65 +10861,78 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>xavier bartlett</t>
+          <t>will jacks</t>
         </is>
       </c>
       <c r="B196" t="n">
-        <v>29</v>
+        <v>106</v>
       </c>
       <c r="C196" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>yash raj punja</t>
+          <t>xavier bartlett</t>
         </is>
       </c>
       <c r="B197" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="C197" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>yash thakur</t>
+          <t>yash raj punja</t>
         </is>
       </c>
       <c r="B198" t="n">
         <v>0</v>
       </c>
       <c r="C198" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>yashasvi jaiswal</t>
+          <t>yash thakur</t>
         </is>
       </c>
       <c r="B199" t="n">
-        <v>370</v>
+        <v>0</v>
       </c>
       <c r="C199" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
+          <t>yashasvi jaiswal</t>
+        </is>
+      </c>
+      <c r="B200" t="n">
+        <v>370</v>
+      </c>
+      <c r="C200" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
           <t>yuzvendra chahal</t>
         </is>
       </c>
-      <c r="B200" t="n">
-        <v>0</v>
-      </c>
-      <c r="C200" t="n">
+      <c r="B201" t="n">
+        <v>0</v>
+      </c>
+      <c r="C201" t="n">
         <v>10</v>
       </c>
     </row>

--- a/IPL_Fantasy_Points.xlsx
+++ b/IPL_Fantasy_Points.xlsx
@@ -604,19 +604,19 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>367</v>
+        <v>393</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4" t="n">
-        <v>367</v>
+        <v>393</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>367</v>
+        <v>393</v>
       </c>
     </row>
     <row r="5">
@@ -690,19 +690,19 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>337</v>
+        <v>393</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>337</v>
+        <v>393</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>337</v>
+        <v>393</v>
       </c>
     </row>
     <row r="7">
@@ -1206,19 +1206,19 @@
         </is>
       </c>
       <c r="G18" t="n">
-        <v>490</v>
+        <v>569</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>490</v>
+        <v>569</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>490</v>
+        <v>569</v>
       </c>
     </row>
     <row r="19">
@@ -2023,19 +2023,19 @@
         </is>
       </c>
       <c r="G37" t="n">
-        <v>555</v>
+        <v>606</v>
       </c>
       <c r="H37" t="n">
         <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>555</v>
+        <v>606</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>555</v>
+        <v>606</v>
       </c>
     </row>
     <row r="38">
@@ -2109,19 +2109,19 @@
         </is>
       </c>
       <c r="G39" t="n">
-        <v>235</v>
+        <v>264</v>
       </c>
       <c r="H39" t="n">
         <v>7</v>
       </c>
       <c r="I39" t="n">
-        <v>235</v>
+        <v>264</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>235</v>
+        <v>264</v>
       </c>
     </row>
     <row r="40">
@@ -3958,19 +3958,19 @@
         </is>
       </c>
       <c r="G82" t="n">
-        <v>262</v>
+        <v>277</v>
       </c>
       <c r="H82" t="n">
         <v>0</v>
       </c>
       <c r="I82" t="n">
-        <v>262</v>
+        <v>277</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
       </c>
       <c r="K82" t="n">
-        <v>262</v>
+        <v>277</v>
       </c>
     </row>
     <row r="83">
@@ -4219,16 +4219,16 @@
         <v>3</v>
       </c>
       <c r="H88" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I88" t="n">
         <v>0</v>
       </c>
       <c r="J88" t="n">
-        <v>240</v>
+        <v>280</v>
       </c>
       <c r="K88" t="n">
-        <v>240</v>
+        <v>280</v>
       </c>
     </row>
     <row r="89">
@@ -5850,19 +5850,19 @@
         </is>
       </c>
       <c r="G126" t="n">
-        <v>412</v>
+        <v>433</v>
       </c>
       <c r="H126" t="n">
         <v>0</v>
       </c>
       <c r="I126" t="n">
-        <v>412</v>
+        <v>433</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
       </c>
       <c r="K126" t="n">
-        <v>412</v>
+        <v>433</v>
       </c>
     </row>
     <row r="127">
@@ -5936,19 +5936,19 @@
         </is>
       </c>
       <c r="G128" t="n">
-        <v>114</v>
+        <v>158</v>
       </c>
       <c r="H128" t="n">
         <v>0</v>
       </c>
       <c r="I128" t="n">
-        <v>114</v>
+        <v>158</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
       </c>
       <c r="K128" t="n">
-        <v>114</v>
+        <v>158</v>
       </c>
     </row>
     <row r="129">
@@ -6624,19 +6624,19 @@
         </is>
       </c>
       <c r="G144" t="n">
-        <v>542</v>
+        <v>557</v>
       </c>
       <c r="H144" t="n">
         <v>0</v>
       </c>
       <c r="I144" t="n">
-        <v>542</v>
+        <v>557</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
       </c>
       <c r="K144" t="n">
-        <v>542</v>
+        <v>557</v>
       </c>
     </row>
     <row r="145">
@@ -7011,19 +7011,19 @@
         </is>
       </c>
       <c r="G153" t="n">
-        <v>141</v>
+        <v>182</v>
       </c>
       <c r="H153" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I153" t="n">
-        <v>141</v>
+        <v>182</v>
       </c>
       <c r="J153" t="n">
-        <v>200</v>
+        <v>220</v>
       </c>
       <c r="K153" t="n">
-        <v>341</v>
+        <v>402</v>
       </c>
     </row>
     <row r="154">
@@ -7398,19 +7398,19 @@
         </is>
       </c>
       <c r="G162" t="n">
-        <v>507</v>
+        <v>563</v>
       </c>
       <c r="H162" t="n">
         <v>0</v>
       </c>
       <c r="I162" t="n">
-        <v>507</v>
+        <v>563</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
       </c>
       <c r="K162" t="n">
-        <v>507</v>
+        <v>563</v>
       </c>
     </row>
     <row r="163">
@@ -8003,16 +8003,16 @@
         <v>0</v>
       </c>
       <c r="H176" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I176" t="n">
         <v>0</v>
       </c>
       <c r="J176" t="n">
-        <v>160</v>
+        <v>180</v>
       </c>
       <c r="K176" t="n">
-        <v>160</v>
+        <v>180</v>
       </c>
     </row>
     <row r="177">
@@ -8185,7 +8185,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>4296</v>
+        <v>4351</v>
       </c>
     </row>
     <row r="3">
@@ -8198,7 +8198,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>3824</v>
+        <v>3903</v>
       </c>
     </row>
     <row r="4">
@@ -8233,11 +8233,11 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SKY11</t>
+          <t>AMEY11</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>3366</v>
+        <v>3397</v>
       </c>
     </row>
     <row r="7">
@@ -8246,11 +8246,11 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>AMEY11</t>
+          <t>SKY11</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>3321</v>
+        <v>3366</v>
       </c>
     </row>
     <row r="8">
@@ -8263,7 +8263,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>3226</v>
+        <v>3308</v>
       </c>
     </row>
     <row r="9">
@@ -8276,7 +8276,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>3152</v>
+        <v>3217</v>
       </c>
     </row>
     <row r="10">
@@ -8289,7 +8289,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2771</v>
+        <v>2851</v>
       </c>
     </row>
     <row r="11">
@@ -8302,7 +8302,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2334</v>
+        <v>2410</v>
       </c>
     </row>
   </sheetData>
@@ -8369,7 +8369,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>507</v>
+        <v>563</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
@@ -8876,7 +8876,7 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>412</v>
+        <v>433</v>
       </c>
       <c r="C43" t="n">
         <v>0</v>
@@ -8970,7 +8970,7 @@
         <v>2</v>
       </c>
       <c r="C50" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="51">
@@ -9084,7 +9084,7 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>555</v>
+        <v>606</v>
       </c>
       <c r="C59" t="n">
         <v>0</v>
@@ -9110,7 +9110,7 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>490</v>
+        <v>569</v>
       </c>
       <c r="C61" t="n">
         <v>0</v>
@@ -9344,10 +9344,10 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>141</v>
+        <v>182</v>
       </c>
       <c r="C79" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="80">
@@ -9812,7 +9812,7 @@
         </is>
       </c>
       <c r="B115" t="n">
-        <v>235</v>
+        <v>264</v>
       </c>
       <c r="C115" t="n">
         <v>7</v>
@@ -10033,7 +10033,7 @@
         </is>
       </c>
       <c r="B132" t="n">
-        <v>337</v>
+        <v>393</v>
       </c>
       <c r="C132" t="n">
         <v>0</v>
@@ -10088,7 +10088,7 @@
         <v>3</v>
       </c>
       <c r="C136" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="137">
@@ -10296,7 +10296,7 @@
         <v>0</v>
       </c>
       <c r="C152" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="153">
@@ -10595,7 +10595,7 @@
         <v>0</v>
       </c>
       <c r="C175" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="176">
@@ -10644,7 +10644,7 @@
         </is>
       </c>
       <c r="B179" t="n">
-        <v>262</v>
+        <v>277</v>
       </c>
       <c r="C179" t="n">
         <v>0</v>
@@ -10670,10 +10670,10 @@
         </is>
       </c>
       <c r="B181" t="n">
-        <v>367</v>
+        <v>393</v>
       </c>
       <c r="C181" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="182">
@@ -10787,7 +10787,7 @@
         </is>
       </c>
       <c r="B190" t="n">
-        <v>114</v>
+        <v>158</v>
       </c>
       <c r="C190" t="n">
         <v>0</v>
@@ -10826,7 +10826,7 @@
         </is>
       </c>
       <c r="B193" t="n">
-        <v>542</v>
+        <v>557</v>
       </c>
       <c r="C193" t="n">
         <v>0</v>

--- a/IPL_Fantasy_Points.xlsx
+++ b/IPL_Fantasy_Points.xlsx
@@ -561,19 +561,19 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>286</v>
+        <v>312</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>286</v>
+        <v>312</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>286</v>
+        <v>312</v>
       </c>
     </row>
     <row r="4">
@@ -2797,19 +2797,19 @@
         </is>
       </c>
       <c r="G55" t="n">
-        <v>194</v>
+        <v>266</v>
       </c>
       <c r="H55" t="n">
         <v>0</v>
       </c>
       <c r="I55" t="n">
-        <v>194</v>
+        <v>266</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
       </c>
       <c r="K55" t="n">
-        <v>194</v>
+        <v>266</v>
       </c>
     </row>
     <row r="56">
@@ -2926,19 +2926,19 @@
         </is>
       </c>
       <c r="G58" t="n">
-        <v>172</v>
+        <v>215</v>
       </c>
       <c r="H58" t="n">
         <v>0</v>
       </c>
       <c r="I58" t="n">
-        <v>172</v>
+        <v>215</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
       </c>
       <c r="K58" t="n">
-        <v>172</v>
+        <v>215</v>
       </c>
     </row>
     <row r="59">
@@ -3614,19 +3614,19 @@
         </is>
       </c>
       <c r="G74" t="n">
-        <v>441</v>
+        <v>510</v>
       </c>
       <c r="H74" t="n">
         <v>0</v>
       </c>
       <c r="I74" t="n">
-        <v>441</v>
+        <v>510</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
       </c>
       <c r="K74" t="n">
-        <v>441</v>
+        <v>510</v>
       </c>
     </row>
     <row r="75">
@@ -4001,19 +4001,19 @@
         </is>
       </c>
       <c r="G83" t="n">
-        <v>473</v>
+        <v>491</v>
       </c>
       <c r="H83" t="n">
         <v>0</v>
       </c>
       <c r="I83" t="n">
-        <v>473</v>
+        <v>491</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
       </c>
       <c r="K83" t="n">
-        <v>473</v>
+        <v>491</v>
       </c>
     </row>
     <row r="84">
@@ -4388,19 +4388,19 @@
         </is>
       </c>
       <c r="G92" t="n">
-        <v>397</v>
+        <v>498</v>
       </c>
       <c r="H92" t="n">
         <v>0</v>
       </c>
       <c r="I92" t="n">
-        <v>397</v>
+        <v>498</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
       </c>
       <c r="K92" t="n">
-        <v>397</v>
+        <v>498</v>
       </c>
     </row>
     <row r="93">
@@ -5709,31 +5709,31 @@
           <t>BOWL</t>
         </is>
       </c>
-      <c r="D123" t="inlineStr"/>
-      <c r="E123" t="inlineStr">
-        <is>
-          <t>karun nair</t>
-        </is>
-      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>arjun tendulkar</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr"/>
       <c r="F123" t="inlineStr">
         <is>
-          <t>no_stats_yet</t>
+          <t>exact/alias</t>
         </is>
       </c>
       <c r="G123" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H123" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I123" t="n">
         <v>0</v>
       </c>
       <c r="J123" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K123" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="124">
@@ -6111,7 +6111,7 @@
         <v>132</v>
       </c>
       <c r="H132" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I132" t="n">
         <v>132</v>
@@ -6541,16 +6541,16 @@
         <v>31</v>
       </c>
       <c r="H142" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I142" t="n">
         <v>0</v>
       </c>
       <c r="J142" t="n">
-        <v>200</v>
+        <v>240</v>
       </c>
       <c r="K142" t="n">
-        <v>200</v>
+        <v>240</v>
       </c>
     </row>
     <row r="143">
@@ -6710,19 +6710,19 @@
         </is>
       </c>
       <c r="G146" t="n">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="H146" t="n">
         <v>0</v>
       </c>
       <c r="I146" t="n">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
       </c>
       <c r="K146" t="n">
-        <v>232</v>
+        <v>234</v>
       </c>
     </row>
     <row r="147">
@@ -6925,19 +6925,19 @@
         </is>
       </c>
       <c r="G151" t="n">
-        <v>149</v>
+        <v>158</v>
       </c>
       <c r="H151" t="n">
         <v>0</v>
       </c>
       <c r="I151" t="n">
-        <v>149</v>
+        <v>158</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
       </c>
       <c r="K151" t="n">
-        <v>149</v>
+        <v>158</v>
       </c>
     </row>
     <row r="152">
@@ -7143,16 +7143,16 @@
         <v>0</v>
       </c>
       <c r="H156" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I156" t="n">
         <v>0</v>
       </c>
       <c r="J156" t="n">
-        <v>200</v>
+        <v>240</v>
       </c>
       <c r="K156" t="n">
-        <v>200</v>
+        <v>240</v>
       </c>
     </row>
     <row r="157">
@@ -7788,16 +7788,16 @@
         <v>51</v>
       </c>
       <c r="H171" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I171" t="n">
         <v>51</v>
       </c>
       <c r="J171" t="n">
-        <v>140</v>
+        <v>180</v>
       </c>
       <c r="K171" t="n">
-        <v>191</v>
+        <v>231</v>
       </c>
     </row>
     <row r="172">
@@ -8185,7 +8185,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>4351</v>
+        <v>4438</v>
       </c>
     </row>
     <row r="3">
@@ -8211,7 +8211,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>3626</v>
+        <v>3741</v>
       </c>
     </row>
     <row r="5">
@@ -8224,7 +8224,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>3457</v>
+        <v>3558</v>
       </c>
     </row>
     <row r="6">
@@ -8237,7 +8237,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>3397</v>
+        <v>3448</v>
       </c>
     </row>
     <row r="7">
@@ -8250,7 +8250,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>3366</v>
+        <v>3386</v>
       </c>
     </row>
     <row r="8">
@@ -8263,7 +8263,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>3308</v>
+        <v>3334</v>
       </c>
     </row>
     <row r="9">
@@ -8276,7 +8276,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>3217</v>
+        <v>3257</v>
       </c>
     </row>
     <row r="10">
@@ -8302,7 +8302,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2410</v>
+        <v>2450</v>
       </c>
     </row>
   </sheetData>
@@ -8316,7 +8316,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C201"/>
+  <dimension ref="A1:C202"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8343,7 +8343,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>79</v>
+        <v>116</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
@@ -8547,141 +8547,141 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>arshad khan</t>
+          <t>arjun tendulkar</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C18" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>arshdeep singh</t>
+          <t>arshad khan</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C19" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>arshin kulkarni</t>
+          <t>arshdeep singh</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ashok sharma</t>
+          <t>arshin kulkarni</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="C21" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ashutosh sharma</t>
+          <t>ashok sharma</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>153</v>
+        <v>1</v>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ashwani kumar</t>
+          <t>ashutosh sharma</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1</v>
+        <v>153</v>
       </c>
       <c r="C23" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>auqib nabi</t>
+          <t>ashwani kumar</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>avesh khan</t>
+          <t>auqib nabi</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="C25" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>axar patel</t>
+          <t>avesh khan</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>134</v>
+        <v>6</v>
       </c>
       <c r="C26" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>ayush badoni</t>
+          <t>axar patel</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>172</v>
+        <v>134</v>
       </c>
       <c r="C27" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ayush mhatre</t>
+          <t>ayush badoni</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>201</v>
+        <v>215</v>
       </c>
       <c r="C28" t="n">
         <v>0</v>
@@ -8690,206 +8690,206 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>azmatullah</t>
+          <t>ayush mhatre</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>52</v>
+        <v>201</v>
       </c>
       <c r="C29" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>b sai sudharshan</t>
+          <t>azmatullah</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>638</v>
+        <v>52</v>
       </c>
       <c r="C30" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>ben dwarshuis</t>
+          <t>b sai sudharshan</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0</v>
+        <v>638</v>
       </c>
       <c r="C31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>bhuvneshwar kumar</t>
+          <t>ben dwarshuis</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="C32" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>blessing muzarabani</t>
+          <t>bhuvneshwar kumar</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="C33" t="n">
-        <v>4</v>
+        <v>24</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>brijesh sharma</t>
+          <t>blessing muzarabani</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C34" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>cameron green</t>
+          <t>brijesh sharma</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>320</v>
+        <v>2</v>
       </c>
       <c r="C35" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>cooper connolly</t>
+          <t>cameron green</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>473</v>
+        <v>320</v>
       </c>
       <c r="C36" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>corbin bosch</t>
+          <t>cooper connolly</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>48</v>
+        <v>491</v>
       </c>
       <c r="C37" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>danish malewar</t>
+          <t>corbin bosch</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>2</v>
+        <v>48</v>
       </c>
       <c r="C38" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>dasun shanaka</t>
+          <t>danish malewar</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="C39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>david miller</t>
+          <t>dasun shanaka</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>183</v>
+        <v>26</v>
       </c>
       <c r="C40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>david payne</t>
+          <t>david miller</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>6</v>
+        <v>183</v>
       </c>
       <c r="C41" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>deepak chahar</t>
+          <t>david payne</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="C42" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>devdutt padikkal</t>
+          <t>deepak chahar</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>433</v>
+        <v>17</v>
       </c>
       <c r="C43" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>dewald brevis</t>
+          <t>devdutt padikkal</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>151</v>
+        <v>433</v>
       </c>
       <c r="C44" t="n">
         <v>0</v>
@@ -8898,11 +8898,11 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>dhruv chand jurel</t>
+          <t>dewald brevis</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>420</v>
+        <v>151</v>
       </c>
       <c r="C45" t="n">
         <v>0</v>
@@ -8911,37 +8911,37 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>digvesh rathi</t>
+          <t>dhruv chand jurel</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>2</v>
+        <v>420</v>
       </c>
       <c r="C46" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>dilshan madushanka</t>
+          <t>digvesh rathi</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C47" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>donavon ferreira</t>
+          <t>dilshan madushanka</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>249</v>
+        <v>0</v>
       </c>
       <c r="C48" t="n">
         <v>1</v>
@@ -8950,89 +8950,89 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>dushmantha chameera</t>
+          <t>donavon ferreira</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0</v>
+        <v>249</v>
       </c>
       <c r="C49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>eshan malinga</t>
+          <t>dushmantha chameera</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C50" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>finn allen</t>
+          <t>eshan malinga</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>329</v>
+        <v>2</v>
       </c>
       <c r="C51" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>george linde</t>
+          <t>finn allen</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>31</v>
+        <v>329</v>
       </c>
       <c r="C52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>glenn phillips</t>
+          <t>george linde</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>67</v>
+        <v>31</v>
       </c>
       <c r="C53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>gurjapneet singh</t>
+          <t>glenn phillips</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="C54" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>hardik pandya</t>
+          <t>gurjapneet singh</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>172</v>
+        <v>0</v>
       </c>
       <c r="C55" t="n">
         <v>4</v>
@@ -9041,50 +9041,50 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>harpreet brar</t>
+          <t>hardik pandya</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>5</v>
+        <v>172</v>
       </c>
       <c r="C56" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>harsh dubey</t>
+          <t>harpreet brar</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C57" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>harshal patel</t>
+          <t>harsh dubey</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C58" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>heinrich klaasen</t>
+          <t>harshal patel</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>606</v>
+        <v>10</v>
       </c>
       <c r="C59" t="n">
         <v>0</v>
@@ -9093,11 +9093,11 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>himmat singh</t>
+          <t>heinrich klaasen</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>92</v>
+        <v>606</v>
       </c>
       <c r="C60" t="n">
         <v>0</v>
@@ -9106,11 +9106,11 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>ishan kishan</t>
+          <t>himmat singh</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>569</v>
+        <v>92</v>
       </c>
       <c r="C61" t="n">
         <v>0</v>
@@ -9119,11 +9119,11 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>jacob bethell</t>
+          <t>ishan kishan</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>96</v>
+        <v>569</v>
       </c>
       <c r="C62" t="n">
         <v>0</v>
@@ -9132,63 +9132,63 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>jacob duffy</t>
+          <t>jacob bethell</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="C63" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>jamie overton</t>
+          <t>jacob duffy</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>136</v>
+        <v>0</v>
       </c>
       <c r="C64" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>jason holder</t>
+          <t>jamie overton</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>58</v>
+        <v>136</v>
       </c>
       <c r="C65" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>jasprit bumrah</t>
+          <t>jason holder</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>7</v>
+        <v>58</v>
       </c>
       <c r="C66" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>jaydev unadkat</t>
+          <t>jasprit bumrah</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C67" t="n">
         <v>4</v>
@@ -9197,219 +9197,219 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>jitesh sharma</t>
+          <t>jaydev unadkat</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>90</v>
+        <v>4</v>
       </c>
       <c r="C68" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>jofra archer</t>
+          <t>jitesh sharma</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>21</v>
+        <v>90</v>
       </c>
       <c r="C69" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>jos buttler</t>
+          <t>jofra archer</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>469</v>
+        <v>21</v>
       </c>
       <c r="C70" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>josh hazlewood</t>
+          <t>jos buttler</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0</v>
+        <v>469</v>
       </c>
       <c r="C71" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>josh inglis</t>
+          <t>josh hazlewood</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>194</v>
+        <v>0</v>
       </c>
       <c r="C72" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>kagiso rabada</t>
+          <t>josh inglis</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>35</v>
+        <v>266</v>
       </c>
       <c r="C73" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>kartik sharma</t>
+          <t>kagiso rabada</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>295</v>
+        <v>35</v>
       </c>
       <c r="C74" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>kartik tyagi</t>
+          <t>kartik sharma</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>11</v>
+        <v>295</v>
       </c>
       <c r="C75" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>karun nair</t>
+          <t>kartik tyagi</t>
         </is>
       </c>
       <c r="B76" t="n">
+        <v>11</v>
+      </c>
+      <c r="C76" t="n">
         <v>18</v>
-      </c>
-      <c r="C76" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>khaleel ahmed</t>
+          <t>karun nair</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="C77" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>krish bhagat</t>
+          <t>khaleel ahmed</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="C78" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>krunal pandya</t>
+          <t>krish bhagat</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>182</v>
+        <v>10</v>
       </c>
       <c r="C79" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>kuldeep yadav</t>
+          <t>krunal pandya</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>9</v>
+        <v>182</v>
       </c>
       <c r="C80" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>kumar kushagra</t>
+          <t>kuldeep yadav</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="C81" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>kyle jamieson</t>
+          <t>kumar kushagra</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="C82" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>lhuan dre pretorius</t>
+          <t>kyle jamieson</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="C83" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>liam livingstone</t>
+          <t>lhuan dre pretorius</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="C84" t="n">
         <v>0</v>
@@ -9418,167 +9418,167 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>lockie ferguson</t>
+          <t>liam livingstone</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="C85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>lokesh rahul</t>
+          <t>lockie ferguson</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>533</v>
+        <v>0</v>
       </c>
       <c r="C86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>lungi ngidi</t>
+          <t>lokesh rahul</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>4</v>
+        <v>533</v>
       </c>
       <c r="C87" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>madhav tiwari</t>
+          <t>lungi ngidi</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="C88" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>manav suthar</t>
+          <t>madhav tiwari</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="C89" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>manimaran siddharth</t>
+          <t>manav suthar</t>
         </is>
       </c>
       <c r="B90" t="n">
         <v>0</v>
       </c>
       <c r="C90" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>manish pandey</t>
+          <t>manimaran siddharth</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="C91" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>marco jansen</t>
+          <t>manish pandey</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="C92" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>marcus stoinis</t>
+          <t>marco jansen</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>216</v>
+        <v>51</v>
       </c>
       <c r="C93" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>matheesha pathirana</t>
+          <t>marcus stoinis</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>0</v>
+        <v>216</v>
       </c>
       <c r="C94" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>matt henry</t>
+          <t>matheesha pathirana</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C95" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>matt short</t>
+          <t>matt henry</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>60</v>
+        <v>7</v>
       </c>
       <c r="C96" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>mayank markande</t>
+          <t>matt short</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="C97" t="n">
         <v>0</v>
@@ -9587,7 +9587,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>mayank rawat</t>
+          <t>mayank markande</t>
         </is>
       </c>
       <c r="B98" t="n">
@@ -9600,11 +9600,11 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>mayank yadav</t>
+          <t>mayank rawat</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C99" t="n">
         <v>0</v>
@@ -9613,11 +9613,11 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>mitchell marsh</t>
+          <t>mayank yadav</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>563</v>
+        <v>5</v>
       </c>
       <c r="C100" t="n">
         <v>0</v>
@@ -9626,115 +9626,115 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>mitchell santner</t>
+          <t>mitchell marsh</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>26</v>
+        <v>563</v>
       </c>
       <c r="C101" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>mitchell starc</t>
+          <t>mitchell santner</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="C102" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>mohammed shami</t>
+          <t>mitchell starc</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="C103" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>mohammed siraj</t>
+          <t>mohammed shami</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="C104" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>mohsin khan</t>
+          <t>mohammed siraj</t>
         </is>
       </c>
       <c r="B105" t="n">
         <v>0</v>
       </c>
       <c r="C105" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>mukesh choudhary</t>
+          <t>mohsin khan</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C106" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>mukesh kumar</t>
+          <t>mukesh choudhary</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C107" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>mukul choudhary</t>
+          <t>mukesh kumar</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>169</v>
+        <v>0</v>
       </c>
       <c r="C108" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>naman dhir</t>
+          <t>mukul choudhary</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>312</v>
+        <v>170</v>
       </c>
       <c r="C109" t="n">
         <v>0</v>
@@ -9743,37 +9743,37 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>nandre burger</t>
+          <t>naman dhir</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>3</v>
+        <v>312</v>
       </c>
       <c r="C110" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>navdeep saini</t>
+          <t>nandre burger</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C111" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>nehal wadhera</t>
+          <t>navdeep saini</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="C112" t="n">
         <v>0</v>
@@ -9782,11 +9782,11 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>nicholas pooran</t>
+          <t>nehal wadhera</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>232</v>
+        <v>65</v>
       </c>
       <c r="C113" t="n">
         <v>0</v>
@@ -9795,11 +9795,11 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>nishant sindhu</t>
+          <t>nicholas pooran</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>38</v>
+        <v>234</v>
       </c>
       <c r="C114" t="n">
         <v>0</v>
@@ -9808,76 +9808,76 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>nitish kumar reddy</t>
+          <t>nishant sindhu</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>264</v>
+        <v>38</v>
       </c>
       <c r="C115" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>nitish rana</t>
+          <t>nitish kumar reddy</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>225</v>
+        <v>264</v>
       </c>
       <c r="C116" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>noor ahmad</t>
+          <t>nitish rana</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>11</v>
+        <v>225</v>
       </c>
       <c r="C117" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>pat cummins</t>
+          <t>noor ahmad</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="C118" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>pathum nissanka</t>
+          <t>pat cummins</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>278</v>
+        <v>29</v>
       </c>
       <c r="C119" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>philip salt</t>
+          <t>pathum nissanka</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>202</v>
+        <v>278</v>
       </c>
       <c r="C120" t="n">
         <v>0</v>
@@ -9886,11 +9886,11 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>prabhsimran singh</t>
+          <t>philip salt</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>441</v>
+        <v>202</v>
       </c>
       <c r="C121" t="n">
         <v>0</v>
@@ -9899,76 +9899,76 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>praful hinge</t>
+          <t>prabhsimran singh</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>3</v>
+        <v>510</v>
       </c>
       <c r="C122" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>prashant veer</t>
+          <t>praful hinge</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>90</v>
+        <v>3</v>
       </c>
       <c r="C123" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>prasidh krishna</t>
+          <t>prashant veer</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="C124" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>prince yadav</t>
+          <t>prasidh krishna</t>
         </is>
       </c>
       <c r="B125" t="n">
         <v>0</v>
       </c>
       <c r="C125" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>priyansh arya</t>
+          <t>prince yadav</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>364</v>
+        <v>0</v>
       </c>
       <c r="C126" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>quinton de kock</t>
+          <t>priyansh arya</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>132</v>
+        <v>364</v>
       </c>
       <c r="C127" t="n">
         <v>0</v>
@@ -9977,37 +9977,37 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>raghu sharma</t>
+          <t>quinton de kock</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>0</v>
+        <v>132</v>
       </c>
       <c r="C128" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>rahul chahar</t>
+          <t>raghu sharma</t>
         </is>
       </c>
       <c r="B129" t="n">
         <v>0</v>
       </c>
       <c r="C129" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>rahul tewatia</t>
+          <t>rahul chahar</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>98</v>
+        <v>0</v>
       </c>
       <c r="C130" t="n">
         <v>0</v>
@@ -10016,50 +10016,50 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>raj angad bawa</t>
+          <t>rahul tewatia</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>16</v>
+        <v>98</v>
       </c>
       <c r="C131" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>rajat patidar</t>
+          <t>raj angad bawa</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>393</v>
+        <v>16</v>
       </c>
       <c r="C132" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>ramakrishna ghosh</t>
+          <t>rajat patidar</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>0</v>
+        <v>393</v>
       </c>
       <c r="C133" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>ramandeep singh</t>
+          <t>ramakrishna ghosh</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="C134" t="n">
         <v>1</v>
@@ -10068,63 +10068,63 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>rashid khan</t>
+          <t>ramandeep singh</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>35</v>
+        <v>82</v>
       </c>
       <c r="C135" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>rasikh salam</t>
+          <t>rashid khan</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>3</v>
+        <v>35</v>
       </c>
       <c r="C136" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>ravi bishnoi</t>
+          <t>rasikh salam</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C137" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>ravi singh</t>
+          <t>ravi bishnoi</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C138" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>ravichandran smaran</t>
+          <t>ravi singh</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="C139" t="n">
         <v>0</v>
@@ -10133,50 +10133,50 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>ravindra jadeja</t>
+          <t>ravichandran smaran</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>190</v>
+        <v>18</v>
       </c>
       <c r="C140" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>ravisrinivasan sai kishore</t>
+          <t>ravindra jadeja</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>0</v>
+        <v>190</v>
       </c>
       <c r="C141" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>rinku singh</t>
+          <t>ravisrinivasan sai kishore</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>295</v>
+        <v>0</v>
       </c>
       <c r="C142" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>rishabh pant</t>
+          <t>rinku singh</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>286</v>
+        <v>295</v>
       </c>
       <c r="C143" t="n">
         <v>0</v>
@@ -10185,37 +10185,37 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>riyan parag</t>
+          <t>rishabh pant</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>258</v>
+        <v>312</v>
       </c>
       <c r="C144" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>robin minz</t>
+          <t>riyan parag</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>6</v>
+        <v>258</v>
       </c>
       <c r="C145" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>rohit sharma</t>
+          <t>robin minz</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>283</v>
+        <v>6</v>
       </c>
       <c r="C146" t="n">
         <v>0</v>
@@ -10224,37 +10224,37 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>romario shepherd</t>
+          <t>rohit sharma</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>83</v>
+        <v>283</v>
       </c>
       <c r="C147" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>rovman powell</t>
+          <t>romario shepherd</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>161</v>
+        <v>83</v>
       </c>
       <c r="C148" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>ruturaj gaikwad</t>
+          <t>rovman powell</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>337</v>
+        <v>161</v>
       </c>
       <c r="C149" t="n">
         <v>0</v>
@@ -10263,11 +10263,11 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>ryan rickelton</t>
+          <t>ruturaj gaikwad</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>436</v>
+        <v>337</v>
       </c>
       <c r="C150" t="n">
         <v>0</v>
@@ -10276,11 +10276,11 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>sahil parakh</t>
+          <t>ryan rickelton</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>22</v>
+        <v>436</v>
       </c>
       <c r="C151" t="n">
         <v>0</v>
@@ -10289,37 +10289,37 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>sakib hussain</t>
+          <t>sahil parakh</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="C152" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>salil arora</t>
+          <t>sakib hussain</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>121</v>
+        <v>0</v>
       </c>
       <c r="C153" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>sameer rizvi</t>
+          <t>salil arora</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>252</v>
+        <v>121</v>
       </c>
       <c r="C154" t="n">
         <v>0</v>
@@ -10328,37 +10328,37 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>sandeep sharma</t>
+          <t>sameer rizvi</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>0</v>
+        <v>252</v>
       </c>
       <c r="C155" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>sanju samson</t>
+          <t>sandeep sharma</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>477</v>
+        <v>0</v>
       </c>
       <c r="C156" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>sarfaraz khan</t>
+          <t>sanju samson</t>
         </is>
       </c>
       <c r="B157" t="n">
-        <v>161</v>
+        <v>477</v>
       </c>
       <c r="C157" t="n">
         <v>0</v>
@@ -10367,89 +10367,89 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>saurabh dubey</t>
+          <t>sarfaraz khan</t>
         </is>
       </c>
       <c r="B158" t="n">
-        <v>0</v>
+        <v>161</v>
       </c>
       <c r="C158" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>shahbaz ahmed</t>
+          <t>saurabh dubey</t>
         </is>
       </c>
       <c r="B159" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="C159" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>shahrukh khan</t>
+          <t>shahbaz ahmed</t>
         </is>
       </c>
       <c r="B160" t="n">
-        <v>43</v>
+        <v>58</v>
       </c>
       <c r="C160" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>shardul thakur</t>
+          <t>shahrukh khan</t>
         </is>
       </c>
       <c r="B161" t="n">
-        <v>14</v>
+        <v>43</v>
       </c>
       <c r="C161" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>shashank singh</t>
+          <t>shardul thakur</t>
         </is>
       </c>
       <c r="B162" t="n">
-        <v>132</v>
+        <v>14</v>
       </c>
       <c r="C162" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>sherfane rutherford</t>
+          <t>shashank singh</t>
         </is>
       </c>
       <c r="B163" t="n">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="C163" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>shimron hetmyer</t>
+          <t>sherfane rutherford</t>
         </is>
       </c>
       <c r="B164" t="n">
-        <v>78</v>
+        <v>123</v>
       </c>
       <c r="C164" t="n">
         <v>0</v>
@@ -10458,50 +10458,50 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>shivam dube</t>
+          <t>shimron hetmyer</t>
         </is>
       </c>
       <c r="B165" t="n">
-        <v>270</v>
+        <v>78</v>
       </c>
       <c r="C165" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>shivang kumar</t>
+          <t>shivam dube</t>
         </is>
       </c>
       <c r="B166" t="n">
-        <v>26</v>
+        <v>270</v>
       </c>
       <c r="C166" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>shreyas iyer</t>
+          <t>shivang kumar</t>
         </is>
       </c>
       <c r="B167" t="n">
-        <v>397</v>
+        <v>26</v>
       </c>
       <c r="C167" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>shubham badriprasad dubey</t>
+          <t>shreyas iyer</t>
         </is>
       </c>
       <c r="B168" t="n">
-        <v>76</v>
+        <v>498</v>
       </c>
       <c r="C168" t="n">
         <v>0</v>
@@ -10510,11 +10510,11 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>shubman gill</t>
+          <t>shubham badriprasad dubey</t>
         </is>
       </c>
       <c r="B169" t="n">
-        <v>616</v>
+        <v>76</v>
       </c>
       <c r="C169" t="n">
         <v>0</v>
@@ -10523,50 +10523,50 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>spencer johnson</t>
+          <t>shubman gill</t>
         </is>
       </c>
       <c r="B170" t="n">
-        <v>0</v>
+        <v>616</v>
       </c>
       <c r="C170" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>sunil narine</t>
+          <t>spencer johnson</t>
         </is>
       </c>
       <c r="B171" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C171" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>suryakumar yadav</t>
+          <t>sunil narine</t>
         </is>
       </c>
       <c r="B172" t="n">
-        <v>210</v>
+        <v>40</v>
       </c>
       <c r="C172" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>suryansh shedge</t>
+          <t>suryakumar yadav</t>
         </is>
       </c>
       <c r="B173" t="n">
-        <v>149</v>
+        <v>210</v>
       </c>
       <c r="C173" t="n">
         <v>0</v>
@@ -10575,11 +10575,11 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>sushant mishra</t>
+          <t>suryansh shedge</t>
         </is>
       </c>
       <c r="B174" t="n">
-        <v>0</v>
+        <v>158</v>
       </c>
       <c r="C174" t="n">
         <v>0</v>
@@ -10588,50 +10588,50 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>suyash sharma</t>
+          <t>sushant mishra</t>
         </is>
       </c>
       <c r="B175" t="n">
         <v>0</v>
       </c>
       <c r="C175" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>t natarajan</t>
+          <t>suyash sharma</t>
         </is>
       </c>
       <c r="B176" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C176" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>tejasvi dahiya</t>
+          <t>t natarajan</t>
         </is>
       </c>
       <c r="B177" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="C177" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>tilak varma</t>
+          <t>tejasvi dahiya</t>
         </is>
       </c>
       <c r="B178" t="n">
-        <v>356</v>
+        <v>11</v>
       </c>
       <c r="C178" t="n">
         <v>0</v>
@@ -10640,11 +10640,11 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>tim david</t>
+          <t>tilak varma</t>
         </is>
       </c>
       <c r="B179" t="n">
-        <v>277</v>
+        <v>356</v>
       </c>
       <c r="C179" t="n">
         <v>0</v>
@@ -10653,11 +10653,11 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>tim seifert</t>
+          <t>tim david</t>
         </is>
       </c>
       <c r="B180" t="n">
-        <v>19</v>
+        <v>277</v>
       </c>
       <c r="C180" t="n">
         <v>0</v>
@@ -10666,50 +10666,50 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>travis head</t>
+          <t>tim seifert</t>
         </is>
       </c>
       <c r="B181" t="n">
-        <v>393</v>
+        <v>19</v>
       </c>
       <c r="C181" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>trent boult</t>
+          <t>travis head</t>
         </is>
       </c>
       <c r="B182" t="n">
-        <v>8</v>
+        <v>393</v>
       </c>
       <c r="C182" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>tripurana vijay</t>
+          <t>trent boult</t>
         </is>
       </c>
       <c r="B183" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="C183" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>tristan stubbs</t>
+          <t>tripurana vijay</t>
         </is>
       </c>
       <c r="B184" t="n">
-        <v>275</v>
+        <v>0</v>
       </c>
       <c r="C184" t="n">
         <v>0</v>
@@ -10718,128 +10718,128 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>tushar deshpande</t>
+          <t>tristan stubbs</t>
         </is>
       </c>
       <c r="B185" t="n">
-        <v>26</v>
+        <v>275</v>
       </c>
       <c r="C185" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>urvil patel</t>
+          <t>tushar deshpande</t>
         </is>
       </c>
       <c r="B186" t="n">
-        <v>129</v>
+        <v>26</v>
       </c>
       <c r="C186" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>vaibhav arora</t>
+          <t>urvil patel</t>
         </is>
       </c>
       <c r="B187" t="n">
-        <v>1</v>
+        <v>129</v>
       </c>
       <c r="C187" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>vaibhav suryavanshi</t>
+          <t>vaibhav arora</t>
         </is>
       </c>
       <c r="B188" t="n">
-        <v>579</v>
+        <v>1</v>
       </c>
       <c r="C188" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>varun chakravarthy</t>
+          <t>vaibhav suryavanshi</t>
         </is>
       </c>
       <c r="B189" t="n">
-        <v>0</v>
+        <v>579</v>
       </c>
       <c r="C189" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>venkatesh iyer</t>
+          <t>varun chakravarthy</t>
         </is>
       </c>
       <c r="B190" t="n">
-        <v>158</v>
+        <v>0</v>
       </c>
       <c r="C190" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>vijaykumar vyshak</t>
+          <t>venkatesh iyer</t>
         </is>
       </c>
       <c r="B191" t="n">
-        <v>2</v>
+        <v>158</v>
       </c>
       <c r="C191" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>vipraj nigam</t>
+          <t>vijaykumar vyshak</t>
         </is>
       </c>
       <c r="B192" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="C192" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>virat kohli</t>
+          <t>vipraj nigam</t>
         </is>
       </c>
       <c r="B193" t="n">
-        <v>557</v>
+        <v>15</v>
       </c>
       <c r="C193" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>vishnu vinod</t>
+          <t>virat kohli</t>
         </is>
       </c>
       <c r="B194" t="n">
-        <v>15</v>
+        <v>557</v>
       </c>
       <c r="C194" t="n">
         <v>0</v>
@@ -10848,24 +10848,24 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>washington sundar</t>
+          <t>vishnu vinod</t>
         </is>
       </c>
       <c r="B195" t="n">
-        <v>303</v>
+        <v>15</v>
       </c>
       <c r="C195" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>will jacks</t>
+          <t>washington sundar</t>
         </is>
       </c>
       <c r="B196" t="n">
-        <v>106</v>
+        <v>303</v>
       </c>
       <c r="C196" t="n">
         <v>1</v>
@@ -10874,66 +10874,79 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>xavier bartlett</t>
+          <t>will jacks</t>
         </is>
       </c>
       <c r="B197" t="n">
-        <v>29</v>
+        <v>106</v>
       </c>
       <c r="C197" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>yash raj punja</t>
+          <t>xavier bartlett</t>
         </is>
       </c>
       <c r="B198" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="C198" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>yash thakur</t>
+          <t>yash raj punja</t>
         </is>
       </c>
       <c r="B199" t="n">
         <v>0</v>
       </c>
       <c r="C199" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>yashasvi jaiswal</t>
+          <t>yash thakur</t>
         </is>
       </c>
       <c r="B200" t="n">
-        <v>370</v>
+        <v>0</v>
       </c>
       <c r="C200" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
+          <t>yashasvi jaiswal</t>
+        </is>
+      </c>
+      <c r="B201" t="n">
+        <v>370</v>
+      </c>
+      <c r="C201" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
           <t>yuzvendra chahal</t>
         </is>
       </c>
-      <c r="B201" t="n">
-        <v>0</v>
-      </c>
-      <c r="C201" t="n">
-        <v>10</v>
+      <c r="B202" t="n">
+        <v>0</v>
+      </c>
+      <c r="C202" t="n">
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -10947,7 +10960,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K26"/>
+  <dimension ref="A1:K25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11569,7 +11582,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Arjun Tendulkar</t>
+          <t>Kwena Maphaka</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -11585,7 +11598,7 @@
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>karun nair</t>
+          <t>aiden markram</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -11612,23 +11625,23 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Kwena Maphaka</t>
+          <t>Azmatullah Omarzai</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>SKY11</t>
+          <t>HARSH11</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>aiden markram</t>
+          <t>azmatullah</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -11655,23 +11668,23 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Azmatullah Omarzai</t>
+          <t>Tejasvi Singh</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>HARSH11</t>
+          <t>AMEY11</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>azmatullah</t>
+          <t>ravi singh</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -11698,7 +11711,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Tejasvi Singh</t>
+          <t>Sai Kishor</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -11708,13 +11721,13 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>BOWL</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>ravi singh</t>
+          <t>ishan kishan</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -11741,7 +11754,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Sai Kishor</t>
+          <t>Akash Deep</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -11757,7 +11770,7 @@
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>ishan kishan</t>
+          <t>arshdeep singh</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -11784,23 +11797,23 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Akash Deep</t>
+          <t>Ben Duckett</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>AMEY11</t>
+          <t>PRATIK11</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>BOWL</t>
+          <t>BAT</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>arshdeep singh</t>
+          <t>ben dwarshuis</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -11827,7 +11840,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Ben Duckett</t>
+          <t>Rahul Tripathi</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -11843,7 +11856,7 @@
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>ben dwarshuis</t>
+          <t>rahul tewatia</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -11870,7 +11883,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Rahul Tripathi</t>
+          <t>Dre Pretorius</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -11886,7 +11899,7 @@
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>rahul tewatia</t>
+          <t>lhuan dre pretorius</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -11913,7 +11926,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Dre Pretorius</t>
+          <t>Matthew Breetzke</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -11929,7 +11942,7 @@
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>lhuan dre pretorius</t>
+          <t>matt henry</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -11956,7 +11969,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Matthew Breetzke</t>
+          <t>Anuj Rawat</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -11972,7 +11985,7 @@
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>matt henry</t>
+          <t>mayank rawat</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -11999,7 +12012,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Anuj Rawat</t>
+          <t>Wanindu Hasaranga</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -12009,13 +12022,13 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>mayank rawat</t>
+          <t>ravichandran smaran</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -12036,49 +12049,6 @@
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Wanindu Hasaranga</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>PRATIK11</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>AR</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>ravichandran smaran</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>no_stats_yet</t>
-        </is>
-      </c>
-      <c r="G26" t="n">
-        <v>0</v>
-      </c>
-      <c r="H26" t="n">
-        <v>0</v>
-      </c>
-      <c r="I26" t="n">
-        <v>0</v>
-      </c>
-      <c r="J26" t="n">
-        <v>0</v>
-      </c>
-      <c r="K26" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12252,19 +12222,19 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>194</v>
+        <v>266</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>194</v>
+        <v>266</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>194</v>
+        <v>266</v>
       </c>
     </row>
     <row r="3">

--- a/IPL_Fantasy_Points.xlsx
+++ b/IPL_Fantasy_Points.xlsx
@@ -819,19 +819,19 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>312</v>
+        <v>318</v>
       </c>
     </row>
     <row r="10">
@@ -862,19 +862,19 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="H10" t="n">
         <v>7</v>
       </c>
       <c r="I10" t="n">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="J10" t="n">
         <v>140</v>
       </c>
       <c r="K10" t="n">
-        <v>460</v>
+        <v>462</v>
       </c>
     </row>
     <row r="11">
@@ -948,19 +948,19 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="H12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I12" t="n">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="J12" t="n">
-        <v>160</v>
+        <v>180</v>
       </c>
       <c r="K12" t="n">
-        <v>203</v>
+        <v>232</v>
       </c>
     </row>
     <row r="13">
@@ -1292,19 +1292,19 @@
         </is>
       </c>
       <c r="G20" t="n">
-        <v>272</v>
+        <v>335</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>272</v>
+        <v>335</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>272</v>
+        <v>335</v>
       </c>
     </row>
     <row r="21">
@@ -1335,19 +1335,19 @@
         </is>
       </c>
       <c r="G21" t="n">
-        <v>579</v>
+        <v>583</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>579</v>
+        <v>583</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>579</v>
+        <v>583</v>
       </c>
     </row>
     <row r="22">
@@ -1808,19 +1808,19 @@
         </is>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H32" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I32" t="n">
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>280</v>
+        <v>300</v>
       </c>
       <c r="K32" t="n">
-        <v>280</v>
+        <v>300</v>
       </c>
     </row>
     <row r="33">
@@ -2281,19 +2281,19 @@
         </is>
       </c>
       <c r="G43" t="n">
-        <v>190</v>
+        <v>209</v>
       </c>
       <c r="H43" t="n">
         <v>8</v>
       </c>
       <c r="I43" t="n">
-        <v>190</v>
+        <v>209</v>
       </c>
       <c r="J43" t="n">
         <v>160</v>
       </c>
       <c r="K43" t="n">
-        <v>350</v>
+        <v>369</v>
       </c>
     </row>
     <row r="44">
@@ -2324,19 +2324,19 @@
         </is>
       </c>
       <c r="G44" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="H44" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I44" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="J44" t="n">
-        <v>200</v>
+        <v>240</v>
       </c>
       <c r="K44" t="n">
-        <v>214</v>
+        <v>264</v>
       </c>
     </row>
     <row r="45">
@@ -2625,19 +2625,19 @@
         </is>
       </c>
       <c r="G51" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="H51" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I51" t="n">
         <v>0</v>
       </c>
       <c r="J51" t="n">
-        <v>220</v>
+        <v>240</v>
       </c>
       <c r="K51" t="n">
-        <v>220</v>
+        <v>240</v>
       </c>
     </row>
     <row r="52">
@@ -2668,19 +2668,19 @@
         </is>
       </c>
       <c r="G52" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="H52" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I52" t="n">
         <v>0</v>
       </c>
       <c r="J52" t="n">
-        <v>120</v>
+        <v>160</v>
       </c>
       <c r="K52" t="n">
-        <v>120</v>
+        <v>160</v>
       </c>
     </row>
     <row r="53">
@@ -2840,19 +2840,19 @@
         </is>
       </c>
       <c r="G56" t="n">
-        <v>183</v>
+        <v>211</v>
       </c>
       <c r="H56" t="n">
         <v>0</v>
       </c>
       <c r="I56" t="n">
-        <v>183</v>
+        <v>211</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
       </c>
       <c r="K56" t="n">
-        <v>183</v>
+        <v>211</v>
       </c>
     </row>
     <row r="57">
@@ -2883,19 +2883,19 @@
         </is>
       </c>
       <c r="G57" t="n">
-        <v>420</v>
+        <v>458</v>
       </c>
       <c r="H57" t="n">
         <v>0</v>
       </c>
       <c r="I57" t="n">
-        <v>420</v>
+        <v>458</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
       </c>
       <c r="K57" t="n">
-        <v>420</v>
+        <v>458</v>
       </c>
     </row>
     <row r="58">
@@ -3012,19 +3012,19 @@
         </is>
       </c>
       <c r="G60" t="n">
-        <v>436</v>
+        <v>448</v>
       </c>
       <c r="H60" t="n">
         <v>0</v>
       </c>
       <c r="I60" t="n">
-        <v>436</v>
+        <v>448</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
       </c>
       <c r="K60" t="n">
-        <v>436</v>
+        <v>448</v>
       </c>
     </row>
     <row r="61">
@@ -3141,19 +3141,19 @@
         </is>
       </c>
       <c r="G63" t="n">
-        <v>161</v>
+        <v>190</v>
       </c>
       <c r="H63" t="n">
         <v>0</v>
       </c>
       <c r="I63" t="n">
-        <v>161</v>
+        <v>190</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
       </c>
       <c r="K63" t="n">
-        <v>161</v>
+        <v>190</v>
       </c>
     </row>
     <row r="64">
@@ -3356,19 +3356,19 @@
         </is>
       </c>
       <c r="G68" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H68" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I68" t="n">
         <v>0</v>
       </c>
       <c r="J68" t="n">
-        <v>200</v>
+        <v>220</v>
       </c>
       <c r="K68" t="n">
-        <v>200</v>
+        <v>220</v>
       </c>
     </row>
     <row r="69">
@@ -3445,16 +3445,16 @@
         <v>0</v>
       </c>
       <c r="H70" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I70" t="n">
         <v>0</v>
       </c>
       <c r="J70" t="n">
-        <v>180</v>
+        <v>220</v>
       </c>
       <c r="K70" t="n">
-        <v>180</v>
+        <v>220</v>
       </c>
     </row>
     <row r="71">
@@ -4302,19 +4302,19 @@
         </is>
       </c>
       <c r="G90" t="n">
-        <v>370</v>
+        <v>397</v>
       </c>
       <c r="H90" t="n">
         <v>0</v>
       </c>
       <c r="I90" t="n">
-        <v>370</v>
+        <v>397</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
       </c>
       <c r="K90" t="n">
-        <v>370</v>
+        <v>397</v>
       </c>
     </row>
     <row r="91">
@@ -4345,19 +4345,19 @@
         </is>
       </c>
       <c r="G91" t="n">
-        <v>533</v>
+        <v>593</v>
       </c>
       <c r="H91" t="n">
         <v>0</v>
       </c>
       <c r="I91" t="n">
-        <v>533</v>
+        <v>593</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
       </c>
       <c r="K91" t="n">
-        <v>533</v>
+        <v>593</v>
       </c>
     </row>
     <row r="92">
@@ -4689,19 +4689,19 @@
         </is>
       </c>
       <c r="G99" t="n">
-        <v>106</v>
+        <v>139</v>
       </c>
       <c r="H99" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I99" t="n">
-        <v>106</v>
+        <v>139</v>
       </c>
       <c r="J99" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="K99" t="n">
-        <v>126</v>
+        <v>179</v>
       </c>
     </row>
     <row r="100">
@@ -4732,19 +4732,19 @@
         </is>
       </c>
       <c r="G100" t="n">
-        <v>258</v>
+        <v>272</v>
       </c>
       <c r="H100" t="n">
         <v>2</v>
       </c>
       <c r="I100" t="n">
-        <v>258</v>
+        <v>272</v>
       </c>
       <c r="J100" t="n">
         <v>40</v>
       </c>
       <c r="K100" t="n">
-        <v>298</v>
+        <v>312</v>
       </c>
     </row>
     <row r="101">
@@ -5033,19 +5033,19 @@
         </is>
       </c>
       <c r="G107" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="H107" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I107" t="n">
         <v>0</v>
       </c>
       <c r="J107" t="n">
-        <v>180</v>
+        <v>220</v>
       </c>
       <c r="K107" t="n">
-        <v>180</v>
+        <v>220</v>
       </c>
     </row>
     <row r="108">
@@ -5248,19 +5248,19 @@
         </is>
       </c>
       <c r="G112" t="n">
-        <v>45</v>
+        <v>70</v>
       </c>
       <c r="H112" t="n">
         <v>0</v>
       </c>
       <c r="I112" t="n">
-        <v>45</v>
+        <v>70</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
       </c>
       <c r="K112" t="n">
-        <v>45</v>
+        <v>70</v>
       </c>
     </row>
     <row r="113">
@@ -5334,19 +5334,19 @@
         </is>
       </c>
       <c r="G114" t="n">
-        <v>172</v>
+        <v>206</v>
       </c>
       <c r="H114" t="n">
         <v>4</v>
       </c>
       <c r="I114" t="n">
-        <v>172</v>
+        <v>206</v>
       </c>
       <c r="J114" t="n">
         <v>80</v>
       </c>
       <c r="K114" t="n">
-        <v>252</v>
+        <v>286</v>
       </c>
     </row>
     <row r="115">
@@ -5420,19 +5420,19 @@
         </is>
       </c>
       <c r="G116" t="n">
-        <v>249</v>
+        <v>267</v>
       </c>
       <c r="H116" t="n">
         <v>1</v>
       </c>
       <c r="I116" t="n">
-        <v>249</v>
+        <v>267</v>
       </c>
       <c r="J116" t="n">
         <v>20</v>
       </c>
       <c r="K116" t="n">
-        <v>269</v>
+        <v>287</v>
       </c>
     </row>
     <row r="117">
@@ -5552,16 +5552,16 @@
         <v>4</v>
       </c>
       <c r="H119" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="I119" t="n">
         <v>0</v>
       </c>
       <c r="J119" t="n">
-        <v>200</v>
+        <v>260</v>
       </c>
       <c r="K119" t="n">
-        <v>200</v>
+        <v>260</v>
       </c>
     </row>
     <row r="120">
@@ -6022,19 +6022,19 @@
         </is>
       </c>
       <c r="G130" t="n">
-        <v>153</v>
+        <v>171</v>
       </c>
       <c r="H130" t="n">
         <v>0</v>
       </c>
       <c r="I130" t="n">
-        <v>153</v>
+        <v>171</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
       </c>
       <c r="K130" t="n">
-        <v>153</v>
+        <v>171</v>
       </c>
     </row>
     <row r="131">
@@ -6065,19 +6065,19 @@
         </is>
       </c>
       <c r="G131" t="n">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="H131" t="n">
         <v>0</v>
       </c>
       <c r="I131" t="n">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
       </c>
       <c r="K131" t="n">
-        <v>356</v>
+        <v>359</v>
       </c>
     </row>
     <row r="132">
@@ -6323,19 +6323,19 @@
         </is>
       </c>
       <c r="G137" t="n">
-        <v>134</v>
+        <v>173</v>
       </c>
       <c r="H137" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I137" t="n">
-        <v>134</v>
+        <v>173</v>
       </c>
       <c r="J137" t="n">
-        <v>200</v>
+        <v>220</v>
       </c>
       <c r="K137" t="n">
-        <v>334</v>
+        <v>393</v>
       </c>
     </row>
     <row r="138">
@@ -6667,19 +6667,19 @@
         </is>
       </c>
       <c r="G145" t="n">
-        <v>210</v>
+        <v>270</v>
       </c>
       <c r="H145" t="n">
         <v>0</v>
       </c>
       <c r="I145" t="n">
-        <v>210</v>
+        <v>270</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
       </c>
       <c r="K145" t="n">
-        <v>210</v>
+        <v>270</v>
       </c>
     </row>
     <row r="146">
@@ -7054,19 +7054,19 @@
         </is>
       </c>
       <c r="G154" t="n">
+        <v>53</v>
+      </c>
+      <c r="H154" t="n">
         <v>21</v>
       </c>
-      <c r="H154" t="n">
-        <v>18</v>
-      </c>
       <c r="I154" t="n">
-        <v>21</v>
+        <v>53</v>
       </c>
       <c r="J154" t="n">
-        <v>360</v>
+        <v>420</v>
       </c>
       <c r="K154" t="n">
-        <v>381</v>
+        <v>473</v>
       </c>
     </row>
     <row r="155">
@@ -7484,19 +7484,19 @@
         </is>
       </c>
       <c r="G164" t="n">
-        <v>86</v>
+        <v>108</v>
       </c>
       <c r="H164" t="n">
         <v>0</v>
       </c>
       <c r="I164" t="n">
-        <v>86</v>
+        <v>108</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
       </c>
       <c r="K164" t="n">
-        <v>86</v>
+        <v>108</v>
       </c>
     </row>
     <row r="165">
@@ -7570,19 +7570,19 @@
         </is>
       </c>
       <c r="G166" t="n">
-        <v>329</v>
+        <v>349</v>
       </c>
       <c r="H166" t="n">
         <v>0</v>
       </c>
       <c r="I166" t="n">
-        <v>329</v>
+        <v>349</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
       </c>
       <c r="K166" t="n">
-        <v>329</v>
+        <v>349</v>
       </c>
     </row>
     <row r="167">
@@ -7831,16 +7831,16 @@
         <v>40</v>
       </c>
       <c r="H172" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I172" t="n">
         <v>40</v>
       </c>
       <c r="J172" t="n">
-        <v>280</v>
+        <v>300</v>
       </c>
       <c r="K172" t="n">
-        <v>320</v>
+        <v>340</v>
       </c>
     </row>
     <row r="173">
@@ -8089,16 +8089,16 @@
         <v>9</v>
       </c>
       <c r="H178" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="I178" t="n">
         <v>0</v>
       </c>
       <c r="J178" t="n">
-        <v>140</v>
+        <v>200</v>
       </c>
       <c r="K178" t="n">
-        <v>140</v>
+        <v>200</v>
       </c>
     </row>
     <row r="179">
@@ -8198,7 +8198,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>3903</v>
+        <v>3990</v>
       </c>
     </row>
     <row r="4">
@@ -8211,7 +8211,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>3741</v>
+        <v>3908</v>
       </c>
     </row>
     <row r="5">
@@ -8224,7 +8224,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>3558</v>
+        <v>3752</v>
       </c>
     </row>
     <row r="6">
@@ -8237,7 +8237,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>3448</v>
+        <v>3600</v>
       </c>
     </row>
     <row r="7">
@@ -8250,7 +8250,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>3386</v>
+        <v>3523</v>
       </c>
     </row>
     <row r="8">
@@ -8263,7 +8263,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>3334</v>
+        <v>3371</v>
       </c>
     </row>
     <row r="9">
@@ -8276,7 +8276,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>3257</v>
+        <v>3337</v>
       </c>
     </row>
     <row r="10">
@@ -8289,7 +8289,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2851</v>
+        <v>2980</v>
       </c>
     </row>
     <row r="11">
@@ -8302,7 +8302,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2450</v>
+        <v>2572</v>
       </c>
     </row>
   </sheetData>
@@ -8382,7 +8382,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>86</v>
+        <v>108</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
@@ -8421,7 +8421,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>272</v>
+        <v>335</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
@@ -8473,10 +8473,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="13">
@@ -8538,10 +8538,10 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="C17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18">
@@ -8616,7 +8616,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>153</v>
+        <v>171</v>
       </c>
       <c r="C23" t="n">
         <v>0</v>
@@ -8668,10 +8668,10 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>134</v>
+        <v>173</v>
       </c>
       <c r="C27" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="28">
@@ -8775,7 +8775,7 @@
         <v>2</v>
       </c>
       <c r="C35" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="36">
@@ -8785,7 +8785,7 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="C36" t="n">
         <v>7</v>
@@ -8811,10 +8811,10 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C38" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="39">
@@ -8837,7 +8837,7 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>26</v>
+        <v>55</v>
       </c>
       <c r="C40" t="n">
         <v>1</v>
@@ -8850,7 +8850,7 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>183</v>
+        <v>211</v>
       </c>
       <c r="C41" t="n">
         <v>0</v>
@@ -8876,10 +8876,10 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="C43" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="44">
@@ -8915,7 +8915,7 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>420</v>
+        <v>458</v>
       </c>
       <c r="C46" t="n">
         <v>0</v>
@@ -8954,7 +8954,7 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>249</v>
+        <v>267</v>
       </c>
       <c r="C49" t="n">
         <v>1</v>
@@ -8993,7 +8993,7 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>329</v>
+        <v>349</v>
       </c>
       <c r="C52" t="n">
         <v>0</v>
@@ -9045,7 +9045,7 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>172</v>
+        <v>206</v>
       </c>
       <c r="C56" t="n">
         <v>4</v>
@@ -9227,10 +9227,10 @@
         </is>
       </c>
       <c r="B70" t="n">
+        <v>53</v>
+      </c>
+      <c r="C70" t="n">
         <v>21</v>
-      </c>
-      <c r="C70" t="n">
-        <v>18</v>
       </c>
     </row>
     <row r="71">
@@ -9373,7 +9373,7 @@
         <v>9</v>
       </c>
       <c r="C81" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="82">
@@ -9448,7 +9448,7 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>533</v>
+        <v>593</v>
       </c>
       <c r="C87" t="n">
         <v>0</v>
@@ -9464,7 +9464,7 @@
         <v>4</v>
       </c>
       <c r="C88" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="89">
@@ -9513,7 +9513,7 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>45</v>
+        <v>70</v>
       </c>
       <c r="C92" t="n">
         <v>0</v>
@@ -9659,7 +9659,7 @@
         <v>0</v>
       </c>
       <c r="C103" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="104">
@@ -9747,7 +9747,7 @@
         </is>
       </c>
       <c r="B110" t="n">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="C110" t="n">
         <v>0</v>
@@ -9760,10 +9760,10 @@
         </is>
       </c>
       <c r="B111" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="C111" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="112">
@@ -10150,7 +10150,7 @@
         </is>
       </c>
       <c r="B141" t="n">
-        <v>190</v>
+        <v>209</v>
       </c>
       <c r="C141" t="n">
         <v>8</v>
@@ -10202,7 +10202,7 @@
         </is>
       </c>
       <c r="B145" t="n">
-        <v>258</v>
+        <v>272</v>
       </c>
       <c r="C145" t="n">
         <v>2</v>
@@ -10254,7 +10254,7 @@
         </is>
       </c>
       <c r="B149" t="n">
-        <v>161</v>
+        <v>190</v>
       </c>
       <c r="C149" t="n">
         <v>0</v>
@@ -10280,7 +10280,7 @@
         </is>
       </c>
       <c r="B151" t="n">
-        <v>436</v>
+        <v>448</v>
       </c>
       <c r="C151" t="n">
         <v>0</v>
@@ -10293,7 +10293,7 @@
         </is>
       </c>
       <c r="B152" t="n">
-        <v>22</v>
+        <v>46</v>
       </c>
       <c r="C152" t="n">
         <v>0</v>
@@ -10384,10 +10384,10 @@
         </is>
       </c>
       <c r="B159" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C159" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="160">
@@ -10423,10 +10423,10 @@
         </is>
       </c>
       <c r="B162" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="C162" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="163">
@@ -10514,7 +10514,7 @@
         </is>
       </c>
       <c r="B169" t="n">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="C169" t="n">
         <v>0</v>
@@ -10556,7 +10556,7 @@
         <v>40</v>
       </c>
       <c r="C172" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="173">
@@ -10566,7 +10566,7 @@
         </is>
       </c>
       <c r="B173" t="n">
-        <v>210</v>
+        <v>270</v>
       </c>
       <c r="C173" t="n">
         <v>0</v>
@@ -10631,7 +10631,7 @@
         </is>
       </c>
       <c r="B178" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C178" t="n">
         <v>0</v>
@@ -10644,7 +10644,7 @@
         </is>
       </c>
       <c r="B179" t="n">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="C179" t="n">
         <v>0</v>
@@ -10774,7 +10774,7 @@
         </is>
       </c>
       <c r="B189" t="n">
-        <v>579</v>
+        <v>583</v>
       </c>
       <c r="C189" t="n">
         <v>0</v>
@@ -10787,10 +10787,10 @@
         </is>
       </c>
       <c r="B190" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C190" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="191">
@@ -10878,10 +10878,10 @@
         </is>
       </c>
       <c r="B197" t="n">
-        <v>106</v>
+        <v>139</v>
       </c>
       <c r="C197" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="198">
@@ -10907,7 +10907,7 @@
         <v>0</v>
       </c>
       <c r="C199" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="200">
@@ -10930,7 +10930,7 @@
         </is>
       </c>
       <c r="B201" t="n">
-        <v>370</v>
+        <v>397</v>
       </c>
       <c r="C201" t="n">
         <v>0</v>
@@ -12265,19 +12265,19 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>249</v>
+        <v>267</v>
       </c>
       <c r="H3" t="n">
         <v>1</v>
       </c>
       <c r="I3" t="n">
-        <v>249</v>
+        <v>267</v>
       </c>
       <c r="J3" t="n">
         <v>20</v>
       </c>
       <c r="K3" t="n">
-        <v>269</v>
+        <v>287</v>
       </c>
     </row>
     <row r="4">
@@ -12351,19 +12351,19 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>86</v>
+        <v>108</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>86</v>
+        <v>108</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>86</v>
+        <v>108</v>
       </c>
     </row>
   </sheetData>

--- a/IPL_Fantasy_Points.xlsx
+++ b/IPL_Fantasy_Points.xlsx
@@ -647,19 +647,19 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>90</v>
+        <v>105</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>90</v>
+        <v>105</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>90</v>
+        <v>105</v>
       </c>
     </row>
     <row r="6">
@@ -690,19 +690,19 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>393</v>
+        <v>486</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>393</v>
+        <v>486</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>393</v>
+        <v>486</v>
       </c>
     </row>
     <row r="7">
@@ -991,7 +991,7 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H13" t="n">
         <v>17</v>
@@ -1249,19 +1249,19 @@
         </is>
       </c>
       <c r="G19" t="n">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>616</v>
+        <v>618</v>
       </c>
     </row>
     <row r="20">
@@ -1550,19 +1550,19 @@
         </is>
       </c>
       <c r="G26" t="n">
-        <v>98</v>
+        <v>166</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>98</v>
+        <v>166</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>98</v>
+        <v>166</v>
       </c>
     </row>
     <row r="27">
@@ -1596,16 +1596,16 @@
         <v>58</v>
       </c>
       <c r="H27" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I27" t="n">
         <v>58</v>
       </c>
       <c r="J27" t="n">
-        <v>260</v>
+        <v>300</v>
       </c>
       <c r="K27" t="n">
-        <v>318</v>
+        <v>358</v>
       </c>
     </row>
     <row r="28">
@@ -2410,19 +2410,19 @@
         </is>
       </c>
       <c r="G46" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H46" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I46" t="n">
         <v>0</v>
       </c>
       <c r="J46" t="n">
-        <v>280</v>
+        <v>300</v>
       </c>
       <c r="K46" t="n">
-        <v>280</v>
+        <v>300</v>
       </c>
     </row>
     <row r="47">
@@ -2499,16 +2499,16 @@
         <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I48" t="n">
         <v>0</v>
       </c>
       <c r="J48" t="n">
-        <v>120</v>
+        <v>180</v>
       </c>
       <c r="K48" t="n">
-        <v>120</v>
+        <v>180</v>
       </c>
     </row>
     <row r="49">
@@ -3184,19 +3184,19 @@
         </is>
       </c>
       <c r="G64" t="n">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="H64" t="n">
         <v>19</v>
       </c>
       <c r="I64" t="n">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="J64" t="n">
         <v>380</v>
       </c>
       <c r="K64" t="n">
-        <v>415</v>
+        <v>423</v>
       </c>
     </row>
     <row r="65">
@@ -3571,19 +3571,19 @@
         </is>
       </c>
       <c r="G73" t="n">
-        <v>638</v>
+        <v>652</v>
       </c>
       <c r="H73" t="n">
         <v>0</v>
       </c>
       <c r="I73" t="n">
-        <v>638</v>
+        <v>652</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
       </c>
       <c r="K73" t="n">
-        <v>638</v>
+        <v>652</v>
       </c>
     </row>
     <row r="74">
@@ -3958,19 +3958,19 @@
         </is>
       </c>
       <c r="G82" t="n">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="H82" t="n">
         <v>0</v>
       </c>
       <c r="I82" t="n">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
       </c>
       <c r="K82" t="n">
-        <v>277</v>
+        <v>281</v>
       </c>
     </row>
     <row r="83">
@@ -4219,16 +4219,16 @@
         <v>3</v>
       </c>
       <c r="H88" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I88" t="n">
         <v>0</v>
       </c>
       <c r="J88" t="n">
-        <v>280</v>
+        <v>320</v>
       </c>
       <c r="K88" t="n">
-        <v>280</v>
+        <v>320</v>
       </c>
     </row>
     <row r="89">
@@ -4431,19 +4431,19 @@
         </is>
       </c>
       <c r="G93" t="n">
-        <v>469</v>
+        <v>498</v>
       </c>
       <c r="H93" t="n">
         <v>0</v>
       </c>
       <c r="I93" t="n">
-        <v>469</v>
+        <v>498</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
       </c>
       <c r="K93" t="n">
-        <v>469</v>
+        <v>498</v>
       </c>
     </row>
     <row r="94">
@@ -4560,19 +4560,19 @@
         </is>
       </c>
       <c r="G96" t="n">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="H96" t="n">
         <v>0</v>
       </c>
       <c r="I96" t="n">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
       </c>
       <c r="K96" t="n">
-        <v>38</v>
+        <v>43</v>
       </c>
     </row>
     <row r="97">
@@ -4775,19 +4775,19 @@
         </is>
       </c>
       <c r="G101" t="n">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="H101" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="I101" t="n">
         <v>0</v>
       </c>
       <c r="J101" t="n">
-        <v>480</v>
+        <v>520</v>
       </c>
       <c r="K101" t="n">
-        <v>480</v>
+        <v>520</v>
       </c>
     </row>
     <row r="102">
@@ -4821,16 +4821,16 @@
         <v>0</v>
       </c>
       <c r="H102" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I102" t="n">
         <v>0</v>
       </c>
       <c r="J102" t="n">
-        <v>240</v>
+        <v>260</v>
       </c>
       <c r="K102" t="n">
-        <v>240</v>
+        <v>260</v>
       </c>
     </row>
     <row r="103">
@@ -5850,19 +5850,19 @@
         </is>
       </c>
       <c r="G126" t="n">
-        <v>433</v>
+        <v>463</v>
       </c>
       <c r="H126" t="n">
         <v>0</v>
       </c>
       <c r="I126" t="n">
-        <v>433</v>
+        <v>463</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
       </c>
       <c r="K126" t="n">
-        <v>433</v>
+        <v>463</v>
       </c>
     </row>
     <row r="127">
@@ -5936,19 +5936,19 @@
         </is>
       </c>
       <c r="G128" t="n">
-        <v>158</v>
+        <v>177</v>
       </c>
       <c r="H128" t="n">
         <v>0</v>
       </c>
       <c r="I128" t="n">
-        <v>158</v>
+        <v>177</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
       </c>
       <c r="K128" t="n">
-        <v>158</v>
+        <v>177</v>
       </c>
     </row>
     <row r="129">
@@ -6280,19 +6280,19 @@
         </is>
       </c>
       <c r="G136" t="n">
-        <v>303</v>
+        <v>311</v>
       </c>
       <c r="H136" t="n">
         <v>1</v>
       </c>
       <c r="I136" t="n">
-        <v>303</v>
+        <v>311</v>
       </c>
       <c r="J136" t="n">
         <v>20</v>
       </c>
       <c r="K136" t="n">
-        <v>323</v>
+        <v>331</v>
       </c>
     </row>
     <row r="137">
@@ -6624,19 +6624,19 @@
         </is>
       </c>
       <c r="G144" t="n">
-        <v>557</v>
+        <v>600</v>
       </c>
       <c r="H144" t="n">
         <v>0</v>
       </c>
       <c r="I144" t="n">
-        <v>557</v>
+        <v>600</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
       </c>
       <c r="K144" t="n">
-        <v>557</v>
+        <v>600</v>
       </c>
     </row>
     <row r="145">
@@ -7011,19 +7011,19 @@
         </is>
       </c>
       <c r="G153" t="n">
-        <v>182</v>
+        <v>225</v>
       </c>
       <c r="H153" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="I153" t="n">
-        <v>182</v>
+        <v>225</v>
       </c>
       <c r="J153" t="n">
-        <v>220</v>
+        <v>260</v>
       </c>
       <c r="K153" t="n">
-        <v>402</v>
+        <v>485</v>
       </c>
     </row>
     <row r="154">
@@ -7186,16 +7186,16 @@
         <v>34</v>
       </c>
       <c r="H157" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="I157" t="n">
         <v>0</v>
       </c>
       <c r="J157" t="n">
-        <v>480</v>
+        <v>520</v>
       </c>
       <c r="K157" t="n">
-        <v>480</v>
+        <v>520</v>
       </c>
     </row>
     <row r="158">
@@ -8185,7 +8185,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>4438</v>
+        <v>4496</v>
       </c>
     </row>
     <row r="3">
@@ -8198,7 +8198,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>3990</v>
+        <v>4100</v>
       </c>
     </row>
     <row r="4">
@@ -8211,7 +8211,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>3908</v>
+        <v>3916</v>
       </c>
     </row>
     <row r="5">
@@ -8224,7 +8224,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>3752</v>
+        <v>3846</v>
       </c>
     </row>
     <row r="6">
@@ -8237,7 +8237,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>3600</v>
+        <v>3766</v>
       </c>
     </row>
     <row r="7">
@@ -8263,7 +8263,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>3371</v>
+        <v>3479</v>
       </c>
     </row>
     <row r="9">
@@ -8276,7 +8276,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>3337</v>
+        <v>3394</v>
       </c>
     </row>
     <row r="10">
@@ -8289,7 +8289,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2980</v>
+        <v>3060</v>
       </c>
     </row>
     <row r="11">
@@ -8316,7 +8316,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C202"/>
+  <dimension ref="A1:C203"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8720,7 +8720,7 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>638</v>
+        <v>652</v>
       </c>
       <c r="C31" t="n">
         <v>0</v>
@@ -8749,7 +8749,7 @@
         <v>34</v>
       </c>
       <c r="C33" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="34">
@@ -8889,7 +8889,7 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>433</v>
+        <v>463</v>
       </c>
       <c r="C44" t="n">
         <v>0</v>
@@ -9152,7 +9152,7 @@
         <v>0</v>
       </c>
       <c r="C64" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="65">
@@ -9178,7 +9178,7 @@
         <v>58</v>
       </c>
       <c r="C66" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="67">
@@ -9214,7 +9214,7 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>90</v>
+        <v>105</v>
       </c>
       <c r="C69" t="n">
         <v>0</v>
@@ -9240,7 +9240,7 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>469</v>
+        <v>498</v>
       </c>
       <c r="C71" t="n">
         <v>0</v>
@@ -9256,7 +9256,7 @@
         <v>0</v>
       </c>
       <c r="C72" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="73">
@@ -9279,10 +9279,10 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="C74" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="75">
@@ -9357,10 +9357,10 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>182</v>
+        <v>225</v>
       </c>
       <c r="C80" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="81">
@@ -9379,11 +9379,11 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>kumar kushagra</t>
+          <t>kulwant khejroliya</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="C82" t="n">
         <v>0</v>
@@ -9392,37 +9392,37 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>kyle jamieson</t>
+          <t>kumar kushagra</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="C83" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>lhuan dre pretorius</t>
+          <t>kyle jamieson</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="C84" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>liam livingstone</t>
+          <t>lhuan dre pretorius</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="C85" t="n">
         <v>0</v>
@@ -9431,167 +9431,167 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>lockie ferguson</t>
+          <t>liam livingstone</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="C86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>lokesh rahul</t>
+          <t>lockie ferguson</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>593</v>
+        <v>0</v>
       </c>
       <c r="C87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>lungi ngidi</t>
+          <t>lokesh rahul</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>4</v>
+        <v>593</v>
       </c>
       <c r="C88" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>madhav tiwari</t>
+          <t>lungi ngidi</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="C89" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>manav suthar</t>
+          <t>madhav tiwari</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="C90" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>manimaran siddharth</t>
+          <t>manav suthar</t>
         </is>
       </c>
       <c r="B91" t="n">
         <v>0</v>
       </c>
       <c r="C91" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>manish pandey</t>
+          <t>manimaran siddharth</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="C92" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>marco jansen</t>
+          <t>manish pandey</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>51</v>
+        <v>70</v>
       </c>
       <c r="C93" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>marcus stoinis</t>
+          <t>marco jansen</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>216</v>
+        <v>51</v>
       </c>
       <c r="C94" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>matheesha pathirana</t>
+          <t>marcus stoinis</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>0</v>
+        <v>216</v>
       </c>
       <c r="C95" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>matt henry</t>
+          <t>matheesha pathirana</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C96" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>matt short</t>
+          <t>matt henry</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>60</v>
+        <v>7</v>
       </c>
       <c r="C97" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>mayank markande</t>
+          <t>matt short</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="C98" t="n">
         <v>0</v>
@@ -9600,7 +9600,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>mayank rawat</t>
+          <t>mayank markande</t>
         </is>
       </c>
       <c r="B99" t="n">
@@ -9613,11 +9613,11 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>mayank yadav</t>
+          <t>mayank rawat</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C100" t="n">
         <v>0</v>
@@ -9626,11 +9626,11 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>mitchell marsh</t>
+          <t>mayank yadav</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>563</v>
+        <v>5</v>
       </c>
       <c r="C101" t="n">
         <v>0</v>
@@ -9639,115 +9639,115 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>mitchell santner</t>
+          <t>mitchell marsh</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>26</v>
+        <v>563</v>
       </c>
       <c r="C102" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>mitchell starc</t>
+          <t>mitchell santner</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="C103" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>mohammed shami</t>
+          <t>mitchell starc</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="C104" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>mohammed siraj</t>
+          <t>mohammed shami</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="C105" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>mohsin khan</t>
+          <t>mohammed siraj</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C106" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>mukesh choudhary</t>
+          <t>mohsin khan</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C107" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>mukesh kumar</t>
+          <t>mukesh choudhary</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C108" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>mukul choudhary</t>
+          <t>mukesh kumar</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>170</v>
+        <v>0</v>
       </c>
       <c r="C109" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>naman dhir</t>
+          <t>mukul choudhary</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>318</v>
+        <v>170</v>
       </c>
       <c r="C110" t="n">
         <v>0</v>
@@ -9756,37 +9756,37 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>nandre burger</t>
+          <t>naman dhir</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>13</v>
+        <v>318</v>
       </c>
       <c r="C111" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>navdeep saini</t>
+          <t>nandre burger</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="C112" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>nehal wadhera</t>
+          <t>navdeep saini</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="C113" t="n">
         <v>0</v>
@@ -9795,11 +9795,11 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>nicholas pooran</t>
+          <t>nehal wadhera</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>234</v>
+        <v>65</v>
       </c>
       <c r="C114" t="n">
         <v>0</v>
@@ -9808,11 +9808,11 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>nishant sindhu</t>
+          <t>nicholas pooran</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>38</v>
+        <v>234</v>
       </c>
       <c r="C115" t="n">
         <v>0</v>
@@ -9821,76 +9821,76 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>nitish kumar reddy</t>
+          <t>nishant sindhu</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>264</v>
+        <v>43</v>
       </c>
       <c r="C116" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>nitish rana</t>
+          <t>nitish kumar reddy</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>225</v>
+        <v>264</v>
       </c>
       <c r="C117" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>noor ahmad</t>
+          <t>nitish rana</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>11</v>
+        <v>225</v>
       </c>
       <c r="C118" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>pat cummins</t>
+          <t>noor ahmad</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="C119" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>pathum nissanka</t>
+          <t>pat cummins</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>278</v>
+        <v>29</v>
       </c>
       <c r="C120" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>philip salt</t>
+          <t>pathum nissanka</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>202</v>
+        <v>278</v>
       </c>
       <c r="C121" t="n">
         <v>0</v>
@@ -9899,11 +9899,11 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>prabhsimran singh</t>
+          <t>philip salt</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>510</v>
+        <v>202</v>
       </c>
       <c r="C122" t="n">
         <v>0</v>
@@ -9912,76 +9912,76 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>praful hinge</t>
+          <t>prabhsimran singh</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>3</v>
+        <v>510</v>
       </c>
       <c r="C123" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>prashant veer</t>
+          <t>praful hinge</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>90</v>
+        <v>3</v>
       </c>
       <c r="C124" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>prasidh krishna</t>
+          <t>prashant veer</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="C125" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>prince yadav</t>
+          <t>prasidh krishna</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C126" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>priyansh arya</t>
+          <t>prince yadav</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>364</v>
+        <v>0</v>
       </c>
       <c r="C127" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>quinton de kock</t>
+          <t>priyansh arya</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>132</v>
+        <v>364</v>
       </c>
       <c r="C128" t="n">
         <v>0</v>
@@ -9990,37 +9990,37 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>raghu sharma</t>
+          <t>quinton de kock</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>0</v>
+        <v>132</v>
       </c>
       <c r="C129" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>rahul chahar</t>
+          <t>raghu sharma</t>
         </is>
       </c>
       <c r="B130" t="n">
         <v>0</v>
       </c>
       <c r="C130" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>rahul tewatia</t>
+          <t>rahul chahar</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>98</v>
+        <v>0</v>
       </c>
       <c r="C131" t="n">
         <v>0</v>
@@ -10029,50 +10029,50 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>raj angad bawa</t>
+          <t>rahul tewatia</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>16</v>
+        <v>166</v>
       </c>
       <c r="C132" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>rajat patidar</t>
+          <t>raj angad bawa</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>393</v>
+        <v>16</v>
       </c>
       <c r="C133" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>ramakrishna ghosh</t>
+          <t>rajat patidar</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>0</v>
+        <v>486</v>
       </c>
       <c r="C134" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>ramandeep singh</t>
+          <t>ramakrishna ghosh</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="C135" t="n">
         <v>1</v>
@@ -10081,63 +10081,63 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>rashid khan</t>
+          <t>ramandeep singh</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>35</v>
+        <v>82</v>
       </c>
       <c r="C136" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>rasikh salam</t>
+          <t>rashid khan</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>3</v>
+        <v>43</v>
       </c>
       <c r="C137" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>ravi bishnoi</t>
+          <t>rasikh salam</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C138" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>ravi singh</t>
+          <t>ravi bishnoi</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C139" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>ravichandran smaran</t>
+          <t>ravi singh</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="C140" t="n">
         <v>0</v>
@@ -10146,50 +10146,50 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>ravindra jadeja</t>
+          <t>ravichandran smaran</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>209</v>
+        <v>18</v>
       </c>
       <c r="C141" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>ravisrinivasan sai kishore</t>
+          <t>ravindra jadeja</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>0</v>
+        <v>209</v>
       </c>
       <c r="C142" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>rinku singh</t>
+          <t>ravisrinivasan sai kishore</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>295</v>
+        <v>0</v>
       </c>
       <c r="C143" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>rishabh pant</t>
+          <t>rinku singh</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>312</v>
+        <v>295</v>
       </c>
       <c r="C144" t="n">
         <v>0</v>
@@ -10198,37 +10198,37 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>riyan parag</t>
+          <t>rishabh pant</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>272</v>
+        <v>312</v>
       </c>
       <c r="C145" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>robin minz</t>
+          <t>riyan parag</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>6</v>
+        <v>272</v>
       </c>
       <c r="C146" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>rohit sharma</t>
+          <t>robin minz</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>283</v>
+        <v>6</v>
       </c>
       <c r="C147" t="n">
         <v>0</v>
@@ -10237,37 +10237,37 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>romario shepherd</t>
+          <t>rohit sharma</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>83</v>
+        <v>283</v>
       </c>
       <c r="C148" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>rovman powell</t>
+          <t>romario shepherd</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>190</v>
+        <v>83</v>
       </c>
       <c r="C149" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>ruturaj gaikwad</t>
+          <t>rovman powell</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>337</v>
+        <v>190</v>
       </c>
       <c r="C150" t="n">
         <v>0</v>
@@ -10276,11 +10276,11 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>ryan rickelton</t>
+          <t>ruturaj gaikwad</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>448</v>
+        <v>337</v>
       </c>
       <c r="C151" t="n">
         <v>0</v>
@@ -10289,11 +10289,11 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>sahil parakh</t>
+          <t>ryan rickelton</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>46</v>
+        <v>448</v>
       </c>
       <c r="C152" t="n">
         <v>0</v>
@@ -10302,37 +10302,37 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>sakib hussain</t>
+          <t>sahil parakh</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="C153" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>salil arora</t>
+          <t>sakib hussain</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>121</v>
+        <v>0</v>
       </c>
       <c r="C154" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>sameer rizvi</t>
+          <t>salil arora</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>252</v>
+        <v>121</v>
       </c>
       <c r="C155" t="n">
         <v>0</v>
@@ -10341,37 +10341,37 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>sandeep sharma</t>
+          <t>sameer rizvi</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>0</v>
+        <v>252</v>
       </c>
       <c r="C156" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>sanju samson</t>
+          <t>sandeep sharma</t>
         </is>
       </c>
       <c r="B157" t="n">
-        <v>477</v>
+        <v>0</v>
       </c>
       <c r="C157" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>sarfaraz khan</t>
+          <t>sanju samson</t>
         </is>
       </c>
       <c r="B158" t="n">
-        <v>161</v>
+        <v>477</v>
       </c>
       <c r="C158" t="n">
         <v>0</v>
@@ -10380,24 +10380,24 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>saurabh dubey</t>
+          <t>sarfaraz khan</t>
         </is>
       </c>
       <c r="B159" t="n">
-        <v>4</v>
+        <v>161</v>
       </c>
       <c r="C159" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>shahbaz ahmed</t>
+          <t>saurabh dubey</t>
         </is>
       </c>
       <c r="B160" t="n">
-        <v>58</v>
+        <v>4</v>
       </c>
       <c r="C160" t="n">
         <v>5</v>
@@ -10406,63 +10406,63 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>shahrukh khan</t>
+          <t>shahbaz ahmed</t>
         </is>
       </c>
       <c r="B161" t="n">
-        <v>43</v>
+        <v>58</v>
       </c>
       <c r="C161" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>shardul thakur</t>
+          <t>shahrukh khan</t>
         </is>
       </c>
       <c r="B162" t="n">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="C162" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>shashank singh</t>
+          <t>shardul thakur</t>
         </is>
       </c>
       <c r="B163" t="n">
-        <v>132</v>
+        <v>24</v>
       </c>
       <c r="C163" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>sherfane rutherford</t>
+          <t>shashank singh</t>
         </is>
       </c>
       <c r="B164" t="n">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="C164" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>shimron hetmyer</t>
+          <t>sherfane rutherford</t>
         </is>
       </c>
       <c r="B165" t="n">
-        <v>78</v>
+        <v>123</v>
       </c>
       <c r="C165" t="n">
         <v>0</v>
@@ -10471,50 +10471,50 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>shivam dube</t>
+          <t>shimron hetmyer</t>
         </is>
       </c>
       <c r="B166" t="n">
-        <v>270</v>
+        <v>78</v>
       </c>
       <c r="C166" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>shivang kumar</t>
+          <t>shivam dube</t>
         </is>
       </c>
       <c r="B167" t="n">
-        <v>26</v>
+        <v>270</v>
       </c>
       <c r="C167" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>shreyas iyer</t>
+          <t>shivang kumar</t>
         </is>
       </c>
       <c r="B168" t="n">
-        <v>498</v>
+        <v>26</v>
       </c>
       <c r="C168" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>shubham badriprasad dubey</t>
+          <t>shreyas iyer</t>
         </is>
       </c>
       <c r="B169" t="n">
-        <v>81</v>
+        <v>498</v>
       </c>
       <c r="C169" t="n">
         <v>0</v>
@@ -10523,11 +10523,11 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>shubman gill</t>
+          <t>shubham badriprasad dubey</t>
         </is>
       </c>
       <c r="B170" t="n">
-        <v>616</v>
+        <v>81</v>
       </c>
       <c r="C170" t="n">
         <v>0</v>
@@ -10536,50 +10536,50 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>spencer johnson</t>
+          <t>shubman gill</t>
         </is>
       </c>
       <c r="B171" t="n">
-        <v>0</v>
+        <v>618</v>
       </c>
       <c r="C171" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>sunil narine</t>
+          <t>spencer johnson</t>
         </is>
       </c>
       <c r="B172" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C172" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>suryakumar yadav</t>
+          <t>sunil narine</t>
         </is>
       </c>
       <c r="B173" t="n">
-        <v>270</v>
+        <v>40</v>
       </c>
       <c r="C173" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>suryansh shedge</t>
+          <t>suryakumar yadav</t>
         </is>
       </c>
       <c r="B174" t="n">
-        <v>158</v>
+        <v>270</v>
       </c>
       <c r="C174" t="n">
         <v>0</v>
@@ -10588,11 +10588,11 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>sushant mishra</t>
+          <t>suryansh shedge</t>
         </is>
       </c>
       <c r="B175" t="n">
-        <v>0</v>
+        <v>158</v>
       </c>
       <c r="C175" t="n">
         <v>0</v>
@@ -10601,50 +10601,50 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>suyash sharma</t>
+          <t>sushant mishra</t>
         </is>
       </c>
       <c r="B176" t="n">
         <v>0</v>
       </c>
       <c r="C176" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>t natarajan</t>
+          <t>suyash sharma</t>
         </is>
       </c>
       <c r="B177" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C177" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>tejasvi dahiya</t>
+          <t>t natarajan</t>
         </is>
       </c>
       <c r="B178" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="C178" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>tilak varma</t>
+          <t>tejasvi dahiya</t>
         </is>
       </c>
       <c r="B179" t="n">
-        <v>359</v>
+        <v>12</v>
       </c>
       <c r="C179" t="n">
         <v>0</v>
@@ -10653,11 +10653,11 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>tim david</t>
+          <t>tilak varma</t>
         </is>
       </c>
       <c r="B180" t="n">
-        <v>277</v>
+        <v>359</v>
       </c>
       <c r="C180" t="n">
         <v>0</v>
@@ -10666,11 +10666,11 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>tim seifert</t>
+          <t>tim david</t>
         </is>
       </c>
       <c r="B181" t="n">
-        <v>19</v>
+        <v>281</v>
       </c>
       <c r="C181" t="n">
         <v>0</v>
@@ -10679,50 +10679,50 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>travis head</t>
+          <t>tim seifert</t>
         </is>
       </c>
       <c r="B182" t="n">
-        <v>393</v>
+        <v>19</v>
       </c>
       <c r="C182" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>trent boult</t>
+          <t>travis head</t>
         </is>
       </c>
       <c r="B183" t="n">
-        <v>8</v>
+        <v>393</v>
       </c>
       <c r="C183" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>tripurana vijay</t>
+          <t>trent boult</t>
         </is>
       </c>
       <c r="B184" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="C184" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>tristan stubbs</t>
+          <t>tripurana vijay</t>
         </is>
       </c>
       <c r="B185" t="n">
-        <v>275</v>
+        <v>0</v>
       </c>
       <c r="C185" t="n">
         <v>0</v>
@@ -10731,128 +10731,128 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>tushar deshpande</t>
+          <t>tristan stubbs</t>
         </is>
       </c>
       <c r="B186" t="n">
-        <v>26</v>
+        <v>275</v>
       </c>
       <c r="C186" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>urvil patel</t>
+          <t>tushar deshpande</t>
         </is>
       </c>
       <c r="B187" t="n">
-        <v>129</v>
+        <v>26</v>
       </c>
       <c r="C187" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>vaibhav arora</t>
+          <t>urvil patel</t>
         </is>
       </c>
       <c r="B188" t="n">
-        <v>1</v>
+        <v>129</v>
       </c>
       <c r="C188" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>vaibhav suryavanshi</t>
+          <t>vaibhav arora</t>
         </is>
       </c>
       <c r="B189" t="n">
-        <v>583</v>
+        <v>1</v>
       </c>
       <c r="C189" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>varun chakravarthy</t>
+          <t>vaibhav suryavanshi</t>
         </is>
       </c>
       <c r="B190" t="n">
-        <v>5</v>
+        <v>583</v>
       </c>
       <c r="C190" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>venkatesh iyer</t>
+          <t>varun chakravarthy</t>
         </is>
       </c>
       <c r="B191" t="n">
-        <v>158</v>
+        <v>5</v>
       </c>
       <c r="C191" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>vijaykumar vyshak</t>
+          <t>venkatesh iyer</t>
         </is>
       </c>
       <c r="B192" t="n">
-        <v>2</v>
+        <v>177</v>
       </c>
       <c r="C192" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>vipraj nigam</t>
+          <t>vijaykumar vyshak</t>
         </is>
       </c>
       <c r="B193" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="C193" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>virat kohli</t>
+          <t>vipraj nigam</t>
         </is>
       </c>
       <c r="B194" t="n">
-        <v>557</v>
+        <v>15</v>
       </c>
       <c r="C194" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>vishnu vinod</t>
+          <t>virat kohli</t>
         </is>
       </c>
       <c r="B195" t="n">
-        <v>15</v>
+        <v>600</v>
       </c>
       <c r="C195" t="n">
         <v>0</v>
@@ -10861,91 +10861,104 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>washington sundar</t>
+          <t>vishnu vinod</t>
         </is>
       </c>
       <c r="B196" t="n">
-        <v>303</v>
+        <v>15</v>
       </c>
       <c r="C196" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>will jacks</t>
+          <t>washington sundar</t>
         </is>
       </c>
       <c r="B197" t="n">
-        <v>139</v>
+        <v>311</v>
       </c>
       <c r="C197" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>xavier bartlett</t>
+          <t>will jacks</t>
         </is>
       </c>
       <c r="B198" t="n">
-        <v>29</v>
+        <v>139</v>
       </c>
       <c r="C198" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>yash raj punja</t>
+          <t>xavier bartlett</t>
         </is>
       </c>
       <c r="B199" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="C199" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>yash thakur</t>
+          <t>yash raj punja</t>
         </is>
       </c>
       <c r="B200" t="n">
         <v>0</v>
       </c>
       <c r="C200" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>yashasvi jaiswal</t>
+          <t>yash thakur</t>
         </is>
       </c>
       <c r="B201" t="n">
-        <v>397</v>
+        <v>0</v>
       </c>
       <c r="C201" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
+          <t>yashasvi jaiswal</t>
+        </is>
+      </c>
+      <c r="B202" t="n">
+        <v>397</v>
+      </c>
+      <c r="C202" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
           <t>yuzvendra chahal</t>
         </is>
       </c>
-      <c r="B202" t="n">
-        <v>0</v>
-      </c>
-      <c r="C202" t="n">
+      <c r="B203" t="n">
+        <v>0</v>
+      </c>
+      <c r="C203" t="n">
         <v>12</v>
       </c>
     </row>

--- a/IPL_Fantasy_Points.xlsx
+++ b/IPL_Fantasy_Points.xlsx
@@ -604,19 +604,19 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>393</v>
+        <v>410</v>
       </c>
       <c r="H4" t="n">
         <v>1</v>
       </c>
       <c r="I4" t="n">
-        <v>393</v>
+        <v>410</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>393</v>
+        <v>410</v>
       </c>
     </row>
     <row r="5">
@@ -1206,19 +1206,19 @@
         </is>
       </c>
       <c r="G18" t="n">
-        <v>569</v>
+        <v>602</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>569</v>
+        <v>602</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>569</v>
+        <v>602</v>
       </c>
     </row>
     <row r="19">
@@ -1335,19 +1335,19 @@
         </is>
       </c>
       <c r="G21" t="n">
-        <v>583</v>
+        <v>680</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>583</v>
+        <v>680</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>583</v>
+        <v>680</v>
       </c>
     </row>
     <row r="22">
@@ -2023,19 +2023,19 @@
         </is>
       </c>
       <c r="G37" t="n">
-        <v>606</v>
+        <v>624</v>
       </c>
       <c r="H37" t="n">
         <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>606</v>
+        <v>624</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>606</v>
+        <v>624</v>
       </c>
     </row>
     <row r="38">
@@ -2109,19 +2109,19 @@
         </is>
       </c>
       <c r="G39" t="n">
-        <v>264</v>
+        <v>302</v>
       </c>
       <c r="H39" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I39" t="n">
-        <v>264</v>
+        <v>302</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>264</v>
+        <v>302</v>
       </c>
     </row>
     <row r="40">
@@ -2281,19 +2281,19 @@
         </is>
       </c>
       <c r="G43" t="n">
-        <v>209</v>
+        <v>221</v>
       </c>
       <c r="H43" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I43" t="n">
-        <v>209</v>
+        <v>221</v>
       </c>
       <c r="J43" t="n">
-        <v>160</v>
+        <v>200</v>
       </c>
       <c r="K43" t="n">
-        <v>369</v>
+        <v>421</v>
       </c>
     </row>
     <row r="44">
@@ -2883,19 +2883,19 @@
         </is>
       </c>
       <c r="G57" t="n">
-        <v>458</v>
+        <v>508</v>
       </c>
       <c r="H57" t="n">
         <v>0</v>
       </c>
       <c r="I57" t="n">
-        <v>458</v>
+        <v>508</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
       </c>
       <c r="K57" t="n">
-        <v>458</v>
+        <v>508</v>
       </c>
     </row>
     <row r="58">
@@ -3872,19 +3872,19 @@
         </is>
       </c>
       <c r="G80" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H80" t="n">
         <v>8</v>
       </c>
       <c r="I80" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J80" t="n">
         <v>160</v>
       </c>
       <c r="K80" t="n">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="81">
@@ -4302,19 +4302,19 @@
         </is>
       </c>
       <c r="G90" t="n">
-        <v>397</v>
+        <v>426</v>
       </c>
       <c r="H90" t="n">
         <v>0</v>
       </c>
       <c r="I90" t="n">
-        <v>397</v>
+        <v>426</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
       </c>
       <c r="K90" t="n">
-        <v>397</v>
+        <v>426</v>
       </c>
     </row>
     <row r="91">
@@ -4732,19 +4732,19 @@
         </is>
       </c>
       <c r="G100" t="n">
-        <v>272</v>
+        <v>298</v>
       </c>
       <c r="H100" t="n">
         <v>2</v>
       </c>
       <c r="I100" t="n">
-        <v>272</v>
+        <v>298</v>
       </c>
       <c r="J100" t="n">
         <v>40</v>
       </c>
       <c r="K100" t="n">
-        <v>312</v>
+        <v>338</v>
       </c>
     </row>
     <row r="101">
@@ -5033,19 +5033,19 @@
         </is>
       </c>
       <c r="G107" t="n">
+        <v>14</v>
+      </c>
+      <c r="H107" t="n">
         <v>13</v>
       </c>
-      <c r="H107" t="n">
-        <v>11</v>
-      </c>
       <c r="I107" t="n">
         <v>0</v>
       </c>
       <c r="J107" t="n">
-        <v>220</v>
+        <v>260</v>
       </c>
       <c r="K107" t="n">
-        <v>220</v>
+        <v>260</v>
       </c>
     </row>
     <row r="108">
@@ -5420,19 +5420,19 @@
         </is>
       </c>
       <c r="G116" t="n">
-        <v>267</v>
+        <v>279</v>
       </c>
       <c r="H116" t="n">
         <v>1</v>
       </c>
       <c r="I116" t="n">
-        <v>267</v>
+        <v>279</v>
       </c>
       <c r="J116" t="n">
         <v>20</v>
       </c>
       <c r="K116" t="n">
-        <v>287</v>
+        <v>299</v>
       </c>
     </row>
     <row r="117">
@@ -6409,19 +6409,19 @@
         </is>
       </c>
       <c r="G139" t="n">
-        <v>121</v>
+        <v>156</v>
       </c>
       <c r="H139" t="n">
         <v>0</v>
       </c>
       <c r="I139" t="n">
-        <v>121</v>
+        <v>156</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
       </c>
       <c r="K139" t="n">
-        <v>121</v>
+        <v>156</v>
       </c>
     </row>
     <row r="140">
@@ -7054,19 +7054,19 @@
         </is>
       </c>
       <c r="G154" t="n">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="H154" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I154" t="n">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="J154" t="n">
-        <v>420</v>
+        <v>480</v>
       </c>
       <c r="K154" t="n">
-        <v>473</v>
+        <v>537</v>
       </c>
     </row>
     <row r="155">
@@ -8185,7 +8185,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>4496</v>
+        <v>4497</v>
       </c>
     </row>
     <row r="3">
@@ -8198,7 +8198,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>4100</v>
+        <v>4230</v>
       </c>
     </row>
     <row r="4">
@@ -8211,7 +8211,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>3916</v>
+        <v>3966</v>
       </c>
     </row>
     <row r="5">
@@ -8224,7 +8224,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>3846</v>
+        <v>3941</v>
       </c>
     </row>
     <row r="6">
@@ -8237,7 +8237,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>3766</v>
+        <v>3830</v>
       </c>
     </row>
     <row r="7">
@@ -8250,7 +8250,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>3523</v>
+        <v>3535</v>
       </c>
     </row>
     <row r="8">
@@ -8263,7 +8263,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>3479</v>
+        <v>3496</v>
       </c>
     </row>
     <row r="9">
@@ -8276,7 +8276,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>3394</v>
+        <v>3429</v>
       </c>
     </row>
     <row r="10">
@@ -8289,7 +8289,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>3060</v>
+        <v>3168</v>
       </c>
     </row>
     <row r="11">
@@ -8837,7 +8837,7 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="C40" t="n">
         <v>1</v>
@@ -8915,7 +8915,7 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>458</v>
+        <v>508</v>
       </c>
       <c r="C46" t="n">
         <v>0</v>
@@ -8954,7 +8954,7 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>267</v>
+        <v>279</v>
       </c>
       <c r="C49" t="n">
         <v>1</v>
@@ -8980,10 +8980,10 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C51" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="52">
@@ -9097,7 +9097,7 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>606</v>
+        <v>624</v>
       </c>
       <c r="C60" t="n">
         <v>0</v>
@@ -9123,7 +9123,7 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>569</v>
+        <v>602</v>
       </c>
       <c r="C62" t="n">
         <v>0</v>
@@ -9227,10 +9227,10 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="C70" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="71">
@@ -9773,10 +9773,10 @@
         </is>
       </c>
       <c r="B112" t="n">
+        <v>14</v>
+      </c>
+      <c r="C112" t="n">
         <v>13</v>
-      </c>
-      <c r="C112" t="n">
-        <v>11</v>
       </c>
     </row>
     <row r="113">
@@ -9838,10 +9838,10 @@
         </is>
       </c>
       <c r="B117" t="n">
-        <v>264</v>
+        <v>302</v>
       </c>
       <c r="C117" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="118">
@@ -9877,7 +9877,7 @@
         </is>
       </c>
       <c r="B120" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C120" t="n">
         <v>8</v>
@@ -9932,7 +9932,7 @@
         <v>3</v>
       </c>
       <c r="C124" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="125">
@@ -10150,7 +10150,7 @@
         </is>
       </c>
       <c r="B141" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C141" t="n">
         <v>0</v>
@@ -10163,10 +10163,10 @@
         </is>
       </c>
       <c r="B142" t="n">
-        <v>209</v>
+        <v>221</v>
       </c>
       <c r="C142" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="143">
@@ -10215,7 +10215,7 @@
         </is>
       </c>
       <c r="B146" t="n">
-        <v>272</v>
+        <v>298</v>
       </c>
       <c r="C146" t="n">
         <v>2</v>
@@ -10319,7 +10319,7 @@
         </is>
       </c>
       <c r="B154" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C154" t="n">
         <v>15</v>
@@ -10332,7 +10332,7 @@
         </is>
       </c>
       <c r="B155" t="n">
-        <v>121</v>
+        <v>156</v>
       </c>
       <c r="C155" t="n">
         <v>0</v>
@@ -10501,10 +10501,10 @@
         </is>
       </c>
       <c r="B168" t="n">
-        <v>26</v>
+        <v>53</v>
       </c>
       <c r="C168" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="169">
@@ -10605,10 +10605,10 @@
         </is>
       </c>
       <c r="B176" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C176" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="177">
@@ -10696,7 +10696,7 @@
         </is>
       </c>
       <c r="B183" t="n">
-        <v>393</v>
+        <v>410</v>
       </c>
       <c r="C183" t="n">
         <v>1</v>
@@ -10787,7 +10787,7 @@
         </is>
       </c>
       <c r="B190" t="n">
-        <v>583</v>
+        <v>680</v>
       </c>
       <c r="C190" t="n">
         <v>0</v>
@@ -10920,7 +10920,7 @@
         <v>0</v>
       </c>
       <c r="C200" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="201">
@@ -10943,7 +10943,7 @@
         </is>
       </c>
       <c r="B202" t="n">
-        <v>397</v>
+        <v>426</v>
       </c>
       <c r="C202" t="n">
         <v>0</v>
@@ -12278,19 +12278,19 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>267</v>
+        <v>279</v>
       </c>
       <c r="H3" t="n">
         <v>1</v>
       </c>
       <c r="I3" t="n">
-        <v>267</v>
+        <v>279</v>
       </c>
       <c r="J3" t="n">
         <v>20</v>
       </c>
       <c r="K3" t="n">
-        <v>287</v>
+        <v>299</v>
       </c>
     </row>
     <row r="4">

--- a/IPL_Fantasy_Points.xlsx
+++ b/IPL_Fantasy_Points.xlsx
@@ -994,16 +994,16 @@
         <v>5</v>
       </c>
       <c r="H13" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>340</v>
+        <v>360</v>
       </c>
       <c r="K13" t="n">
-        <v>340</v>
+        <v>360</v>
       </c>
     </row>
     <row r="14">
@@ -1249,19 +1249,19 @@
         </is>
       </c>
       <c r="G19" t="n">
-        <v>618</v>
+        <v>722</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>618</v>
+        <v>722</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>618</v>
+        <v>722</v>
       </c>
     </row>
     <row r="20">
@@ -1335,19 +1335,19 @@
         </is>
       </c>
       <c r="G21" t="n">
-        <v>680</v>
+        <v>776</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>680</v>
+        <v>776</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>680</v>
+        <v>776</v>
       </c>
     </row>
     <row r="22">
@@ -1550,19 +1550,19 @@
         </is>
       </c>
       <c r="G26" t="n">
-        <v>166</v>
+        <v>183</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>166</v>
+        <v>183</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>166</v>
+        <v>183</v>
       </c>
     </row>
     <row r="27">
@@ -1596,16 +1596,16 @@
         <v>58</v>
       </c>
       <c r="H27" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="I27" t="n">
         <v>58</v>
       </c>
       <c r="J27" t="n">
-        <v>300</v>
+        <v>340</v>
       </c>
       <c r="K27" t="n">
-        <v>358</v>
+        <v>398</v>
       </c>
     </row>
     <row r="28">
@@ -2281,19 +2281,19 @@
         </is>
       </c>
       <c r="G43" t="n">
-        <v>221</v>
+        <v>266</v>
       </c>
       <c r="H43" t="n">
         <v>10</v>
       </c>
       <c r="I43" t="n">
-        <v>221</v>
+        <v>266</v>
       </c>
       <c r="J43" t="n">
         <v>200</v>
       </c>
       <c r="K43" t="n">
-        <v>421</v>
+        <v>466</v>
       </c>
     </row>
     <row r="44">
@@ -2413,16 +2413,16 @@
         <v>6</v>
       </c>
       <c r="H46" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I46" t="n">
         <v>0</v>
       </c>
       <c r="J46" t="n">
-        <v>300</v>
+        <v>320</v>
       </c>
       <c r="K46" t="n">
-        <v>300</v>
+        <v>320</v>
       </c>
     </row>
     <row r="47">
@@ -2883,19 +2883,19 @@
         </is>
       </c>
       <c r="G57" t="n">
-        <v>508</v>
+        <v>515</v>
       </c>
       <c r="H57" t="n">
         <v>0</v>
       </c>
       <c r="I57" t="n">
-        <v>508</v>
+        <v>515</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
       </c>
       <c r="K57" t="n">
-        <v>508</v>
+        <v>515</v>
       </c>
     </row>
     <row r="58">
@@ -3571,19 +3571,19 @@
         </is>
       </c>
       <c r="G73" t="n">
-        <v>652</v>
+        <v>710</v>
       </c>
       <c r="H73" t="n">
         <v>0</v>
       </c>
       <c r="I73" t="n">
-        <v>652</v>
+        <v>710</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
       </c>
       <c r="K73" t="n">
-        <v>652</v>
+        <v>710</v>
       </c>
     </row>
     <row r="74">
@@ -4302,19 +4302,19 @@
         </is>
       </c>
       <c r="G90" t="n">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="H90" t="n">
         <v>0</v>
       </c>
       <c r="I90" t="n">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
       </c>
       <c r="K90" t="n">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="91">
@@ -4431,19 +4431,19 @@
         </is>
       </c>
       <c r="G93" t="n">
-        <v>498</v>
+        <v>507</v>
       </c>
       <c r="H93" t="n">
         <v>0</v>
       </c>
       <c r="I93" t="n">
-        <v>498</v>
+        <v>507</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
       </c>
       <c r="K93" t="n">
-        <v>498</v>
+        <v>507</v>
       </c>
     </row>
     <row r="94">
@@ -4732,19 +4732,19 @@
         </is>
       </c>
       <c r="G100" t="n">
-        <v>298</v>
+        <v>309</v>
       </c>
       <c r="H100" t="n">
         <v>2</v>
       </c>
       <c r="I100" t="n">
-        <v>298</v>
+        <v>309</v>
       </c>
       <c r="J100" t="n">
         <v>40</v>
       </c>
       <c r="K100" t="n">
-        <v>338</v>
+        <v>349</v>
       </c>
     </row>
     <row r="101">
@@ -4778,16 +4778,16 @@
         <v>44</v>
       </c>
       <c r="H101" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I101" t="n">
         <v>0</v>
       </c>
       <c r="J101" t="n">
-        <v>520</v>
+        <v>560</v>
       </c>
       <c r="K101" t="n">
-        <v>520</v>
+        <v>560</v>
       </c>
     </row>
     <row r="102">
@@ -5036,16 +5036,16 @@
         <v>14</v>
       </c>
       <c r="H107" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I107" t="n">
         <v>0</v>
       </c>
       <c r="J107" t="n">
-        <v>260</v>
+        <v>280</v>
       </c>
       <c r="K107" t="n">
-        <v>260</v>
+        <v>280</v>
       </c>
     </row>
     <row r="108">
@@ -5420,19 +5420,19 @@
         </is>
       </c>
       <c r="G116" t="n">
-        <v>279</v>
+        <v>317</v>
       </c>
       <c r="H116" t="n">
         <v>1</v>
       </c>
       <c r="I116" t="n">
-        <v>279</v>
+        <v>317</v>
       </c>
       <c r="J116" t="n">
         <v>20</v>
       </c>
       <c r="K116" t="n">
-        <v>299</v>
+        <v>337</v>
       </c>
     </row>
     <row r="117">
@@ -6280,19 +6280,19 @@
         </is>
       </c>
       <c r="G136" t="n">
-        <v>311</v>
+        <v>327</v>
       </c>
       <c r="H136" t="n">
         <v>1</v>
       </c>
       <c r="I136" t="n">
-        <v>311</v>
+        <v>327</v>
       </c>
       <c r="J136" t="n">
         <v>20</v>
       </c>
       <c r="K136" t="n">
-        <v>331</v>
+        <v>347</v>
       </c>
     </row>
     <row r="137">
@@ -7054,19 +7054,19 @@
         </is>
       </c>
       <c r="G154" t="n">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="H154" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I154" t="n">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="J154" t="n">
-        <v>480</v>
+        <v>500</v>
       </c>
       <c r="K154" t="n">
-        <v>537</v>
+        <v>564</v>
       </c>
     </row>
     <row r="155">
@@ -8185,7 +8185,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>4497</v>
+        <v>4555</v>
       </c>
     </row>
     <row r="3">
@@ -8198,7 +8198,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>4230</v>
+        <v>4487</v>
       </c>
     </row>
     <row r="4">
@@ -8207,11 +8207,11 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>BABA11</t>
+          <t>NAKUL11</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>3966</v>
+        <v>4022</v>
       </c>
     </row>
     <row r="5">
@@ -8220,11 +8220,11 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>NAKUL11</t>
+          <t>BABA11</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>3941</v>
+        <v>3973</v>
       </c>
     </row>
     <row r="6">
@@ -8237,7 +8237,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>3830</v>
+        <v>3857</v>
       </c>
     </row>
     <row r="7">
@@ -8250,7 +8250,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>3535</v>
+        <v>3573</v>
       </c>
     </row>
     <row r="8">
@@ -8263,7 +8263,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>3496</v>
+        <v>3516</v>
       </c>
     </row>
     <row r="9">
@@ -8276,7 +8276,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>3429</v>
+        <v>3445</v>
       </c>
     </row>
     <row r="10">
@@ -8289,7 +8289,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>3168</v>
+        <v>3233</v>
       </c>
     </row>
     <row r="11">
@@ -8720,7 +8720,7 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>652</v>
+        <v>710</v>
       </c>
       <c r="C31" t="n">
         <v>0</v>
@@ -8775,7 +8775,7 @@
         <v>2</v>
       </c>
       <c r="C35" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="36">
@@ -8837,7 +8837,7 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="C40" t="n">
         <v>1</v>
@@ -8915,7 +8915,7 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>508</v>
+        <v>515</v>
       </c>
       <c r="C46" t="n">
         <v>0</v>
@@ -8954,7 +8954,7 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>279</v>
+        <v>317</v>
       </c>
       <c r="C49" t="n">
         <v>1</v>
@@ -9178,7 +9178,7 @@
         <v>58</v>
       </c>
       <c r="C66" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="67">
@@ -9227,10 +9227,10 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="C70" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="71">
@@ -9240,7 +9240,7 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>498</v>
+        <v>507</v>
       </c>
       <c r="C71" t="n">
         <v>0</v>
@@ -9282,7 +9282,7 @@
         <v>44</v>
       </c>
       <c r="C74" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="75">
@@ -9698,7 +9698,7 @@
         <v>5</v>
       </c>
       <c r="C106" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="107">
@@ -9776,7 +9776,7 @@
         <v>14</v>
       </c>
       <c r="C112" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="113">
@@ -9958,7 +9958,7 @@
         <v>6</v>
       </c>
       <c r="C126" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="127">
@@ -10033,7 +10033,7 @@
         </is>
       </c>
       <c r="B132" t="n">
-        <v>166</v>
+        <v>183</v>
       </c>
       <c r="C132" t="n">
         <v>0</v>
@@ -10163,7 +10163,7 @@
         </is>
       </c>
       <c r="B142" t="n">
-        <v>221</v>
+        <v>266</v>
       </c>
       <c r="C142" t="n">
         <v>10</v>
@@ -10215,7 +10215,7 @@
         </is>
       </c>
       <c r="B146" t="n">
-        <v>298</v>
+        <v>309</v>
       </c>
       <c r="C146" t="n">
         <v>2</v>
@@ -10540,7 +10540,7 @@
         </is>
       </c>
       <c r="B171" t="n">
-        <v>618</v>
+        <v>722</v>
       </c>
       <c r="C171" t="n">
         <v>0</v>
@@ -10787,7 +10787,7 @@
         </is>
       </c>
       <c r="B190" t="n">
-        <v>680</v>
+        <v>776</v>
       </c>
       <c r="C190" t="n">
         <v>0</v>
@@ -10878,7 +10878,7 @@
         </is>
       </c>
       <c r="B197" t="n">
-        <v>311</v>
+        <v>327</v>
       </c>
       <c r="C197" t="n">
         <v>1</v>
@@ -10943,7 +10943,7 @@
         </is>
       </c>
       <c r="B202" t="n">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C202" t="n">
         <v>0</v>
@@ -12278,19 +12278,19 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>279</v>
+        <v>317</v>
       </c>
       <c r="H3" t="n">
         <v>1</v>
       </c>
       <c r="I3" t="n">
-        <v>279</v>
+        <v>317</v>
       </c>
       <c r="J3" t="n">
         <v>20</v>
       </c>
       <c r="K3" t="n">
-        <v>299</v>
+        <v>337</v>
       </c>
     </row>
     <row r="4">

--- a/IPL_Fantasy_Points.xlsx
+++ b/IPL_Fantasy_Points.xlsx
@@ -647,19 +647,19 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>105</v>
+        <v>116</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>105</v>
+        <v>116</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>105</v>
+        <v>116</v>
       </c>
     </row>
     <row r="6">
@@ -690,19 +690,19 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>486</v>
+        <v>501</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>486</v>
+        <v>501</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>486</v>
+        <v>501</v>
       </c>
     </row>
     <row r="7">
@@ -994,16 +994,16 @@
         <v>5</v>
       </c>
       <c r="H13" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>360</v>
+        <v>380</v>
       </c>
       <c r="K13" t="n">
-        <v>360</v>
+        <v>380</v>
       </c>
     </row>
     <row r="14">
@@ -1249,19 +1249,19 @@
         </is>
       </c>
       <c r="G19" t="n">
-        <v>722</v>
+        <v>732</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>722</v>
+        <v>732</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>722</v>
+        <v>732</v>
       </c>
     </row>
     <row r="20">
@@ -1550,19 +1550,19 @@
         </is>
       </c>
       <c r="G26" t="n">
-        <v>183</v>
+        <v>190</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>183</v>
+        <v>190</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>183</v>
+        <v>190</v>
       </c>
     </row>
     <row r="27">
@@ -1593,19 +1593,19 @@
         </is>
       </c>
       <c r="G27" t="n">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="H27" t="n">
         <v>17</v>
       </c>
       <c r="I27" t="n">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="J27" t="n">
         <v>340</v>
       </c>
       <c r="K27" t="n">
-        <v>398</v>
+        <v>405</v>
       </c>
     </row>
     <row r="28">
@@ -3184,19 +3184,19 @@
         </is>
       </c>
       <c r="G64" t="n">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="H64" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I64" t="n">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="J64" t="n">
-        <v>380</v>
+        <v>420</v>
       </c>
       <c r="K64" t="n">
-        <v>423</v>
+        <v>470</v>
       </c>
     </row>
     <row r="65">
@@ -3571,19 +3571,19 @@
         </is>
       </c>
       <c r="G73" t="n">
-        <v>710</v>
+        <v>722</v>
       </c>
       <c r="H73" t="n">
         <v>0</v>
       </c>
       <c r="I73" t="n">
-        <v>710</v>
+        <v>722</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
       </c>
       <c r="K73" t="n">
-        <v>710</v>
+        <v>722</v>
       </c>
     </row>
     <row r="74">
@@ -3958,19 +3958,19 @@
         </is>
       </c>
       <c r="G82" t="n">
-        <v>281</v>
+        <v>305</v>
       </c>
       <c r="H82" t="n">
         <v>0</v>
       </c>
       <c r="I82" t="n">
-        <v>281</v>
+        <v>305</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
       </c>
       <c r="K82" t="n">
-        <v>281</v>
+        <v>305</v>
       </c>
     </row>
     <row r="83">
@@ -4219,16 +4219,16 @@
         <v>3</v>
       </c>
       <c r="H88" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I88" t="n">
         <v>0</v>
       </c>
       <c r="J88" t="n">
-        <v>320</v>
+        <v>380</v>
       </c>
       <c r="K88" t="n">
-        <v>320</v>
+        <v>380</v>
       </c>
     </row>
     <row r="89">
@@ -4431,19 +4431,19 @@
         </is>
       </c>
       <c r="G93" t="n">
-        <v>507</v>
+        <v>526</v>
       </c>
       <c r="H93" t="n">
         <v>0</v>
       </c>
       <c r="I93" t="n">
-        <v>507</v>
+        <v>526</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
       </c>
       <c r="K93" t="n">
-        <v>507</v>
+        <v>526</v>
       </c>
     </row>
     <row r="94">
@@ -4560,19 +4560,19 @@
         </is>
       </c>
       <c r="G96" t="n">
-        <v>43</v>
+        <v>63</v>
       </c>
       <c r="H96" t="n">
         <v>0</v>
       </c>
       <c r="I96" t="n">
-        <v>43</v>
+        <v>63</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
       </c>
       <c r="K96" t="n">
-        <v>43</v>
+        <v>63</v>
       </c>
     </row>
     <row r="97">
@@ -4775,19 +4775,19 @@
         </is>
       </c>
       <c r="G101" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="H101" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I101" t="n">
         <v>0</v>
       </c>
       <c r="J101" t="n">
-        <v>560</v>
+        <v>580</v>
       </c>
       <c r="K101" t="n">
-        <v>560</v>
+        <v>580</v>
       </c>
     </row>
     <row r="102">
@@ -4821,16 +4821,16 @@
         <v>0</v>
       </c>
       <c r="H102" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I102" t="n">
         <v>0</v>
       </c>
       <c r="J102" t="n">
-        <v>260</v>
+        <v>300</v>
       </c>
       <c r="K102" t="n">
-        <v>260</v>
+        <v>300</v>
       </c>
     </row>
     <row r="103">
@@ -5850,19 +5850,19 @@
         </is>
       </c>
       <c r="G126" t="n">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="H126" t="n">
         <v>0</v>
       </c>
       <c r="I126" t="n">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
       </c>
       <c r="K126" t="n">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="127">
@@ -5936,19 +5936,19 @@
         </is>
       </c>
       <c r="G128" t="n">
-        <v>177</v>
+        <v>209</v>
       </c>
       <c r="H128" t="n">
         <v>0</v>
       </c>
       <c r="I128" t="n">
-        <v>177</v>
+        <v>209</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
       </c>
       <c r="K128" t="n">
-        <v>177</v>
+        <v>209</v>
       </c>
     </row>
     <row r="129">
@@ -6280,19 +6280,19 @@
         </is>
       </c>
       <c r="G136" t="n">
-        <v>327</v>
+        <v>377</v>
       </c>
       <c r="H136" t="n">
         <v>1</v>
       </c>
       <c r="I136" t="n">
-        <v>327</v>
+        <v>377</v>
       </c>
       <c r="J136" t="n">
         <v>20</v>
       </c>
       <c r="K136" t="n">
-        <v>347</v>
+        <v>397</v>
       </c>
     </row>
     <row r="137">
@@ -6624,19 +6624,19 @@
         </is>
       </c>
       <c r="G144" t="n">
-        <v>600</v>
+        <v>675</v>
       </c>
       <c r="H144" t="n">
         <v>0</v>
       </c>
       <c r="I144" t="n">
-        <v>600</v>
+        <v>675</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
       </c>
       <c r="K144" t="n">
-        <v>600</v>
+        <v>675</v>
       </c>
     </row>
     <row r="145">
@@ -7011,19 +7011,19 @@
         </is>
       </c>
       <c r="G153" t="n">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="H153" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I153" t="n">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="J153" t="n">
-        <v>260</v>
+        <v>280</v>
       </c>
       <c r="K153" t="n">
-        <v>485</v>
+        <v>506</v>
       </c>
     </row>
     <row r="154">
@@ -7186,16 +7186,16 @@
         <v>34</v>
       </c>
       <c r="H157" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I157" t="n">
         <v>0</v>
       </c>
       <c r="J157" t="n">
-        <v>520</v>
+        <v>560</v>
       </c>
       <c r="K157" t="n">
-        <v>520</v>
+        <v>560</v>
       </c>
     </row>
     <row r="158">
@@ -8185,7 +8185,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>4555</v>
+        <v>4651</v>
       </c>
     </row>
     <row r="3">
@@ -8198,7 +8198,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>4487</v>
+        <v>4511</v>
       </c>
     </row>
     <row r="4">
@@ -8211,7 +8211,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>4022</v>
+        <v>4121</v>
       </c>
     </row>
     <row r="5">
@@ -8224,7 +8224,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>3973</v>
+        <v>4020</v>
       </c>
     </row>
     <row r="6">
@@ -8237,7 +8237,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>3857</v>
+        <v>3993</v>
       </c>
     </row>
     <row r="7">
@@ -8263,7 +8263,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>3516</v>
+        <v>3562</v>
       </c>
     </row>
     <row r="9">
@@ -8276,7 +8276,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>3445</v>
+        <v>3528</v>
       </c>
     </row>
     <row r="10">
@@ -8564,10 +8564,10 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="C19" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20">
@@ -8720,7 +8720,7 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>710</v>
+        <v>722</v>
       </c>
       <c r="C31" t="n">
         <v>0</v>
@@ -8749,7 +8749,7 @@
         <v>34</v>
       </c>
       <c r="C33" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="34">
@@ -8889,7 +8889,7 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="C44" t="n">
         <v>0</v>
@@ -9175,7 +9175,7 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="C66" t="n">
         <v>17</v>
@@ -9214,7 +9214,7 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>105</v>
+        <v>116</v>
       </c>
       <c r="C69" t="n">
         <v>0</v>
@@ -9240,7 +9240,7 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>507</v>
+        <v>526</v>
       </c>
       <c r="C71" t="n">
         <v>0</v>
@@ -9256,7 +9256,7 @@
         <v>0</v>
       </c>
       <c r="C72" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="73">
@@ -9279,10 +9279,10 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="C74" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="75">
@@ -9357,10 +9357,10 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C80" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="81">
@@ -9698,7 +9698,7 @@
         <v>5</v>
       </c>
       <c r="C106" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="107">
@@ -9825,7 +9825,7 @@
         </is>
       </c>
       <c r="B116" t="n">
-        <v>43</v>
+        <v>63</v>
       </c>
       <c r="C116" t="n">
         <v>0</v>
@@ -10033,7 +10033,7 @@
         </is>
       </c>
       <c r="B132" t="n">
-        <v>183</v>
+        <v>190</v>
       </c>
       <c r="C132" t="n">
         <v>0</v>
@@ -10059,7 +10059,7 @@
         </is>
       </c>
       <c r="B134" t="n">
-        <v>486</v>
+        <v>501</v>
       </c>
       <c r="C134" t="n">
         <v>0</v>
@@ -10098,10 +10098,10 @@
         </is>
       </c>
       <c r="B137" t="n">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="C137" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="138">
@@ -10114,7 +10114,7 @@
         <v>3</v>
       </c>
       <c r="C138" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="139">
@@ -10540,7 +10540,7 @@
         </is>
       </c>
       <c r="B171" t="n">
-        <v>722</v>
+        <v>732</v>
       </c>
       <c r="C171" t="n">
         <v>0</v>
@@ -10670,7 +10670,7 @@
         </is>
       </c>
       <c r="B181" t="n">
-        <v>281</v>
+        <v>305</v>
       </c>
       <c r="C181" t="n">
         <v>0</v>
@@ -10813,7 +10813,7 @@
         </is>
       </c>
       <c r="B192" t="n">
-        <v>177</v>
+        <v>209</v>
       </c>
       <c r="C192" t="n">
         <v>0</v>
@@ -10852,7 +10852,7 @@
         </is>
       </c>
       <c r="B195" t="n">
-        <v>600</v>
+        <v>675</v>
       </c>
       <c r="C195" t="n">
         <v>0</v>
@@ -10878,7 +10878,7 @@
         </is>
       </c>
       <c r="B197" t="n">
-        <v>327</v>
+        <v>377</v>
       </c>
       <c r="C197" t="n">
         <v>1</v>
